--- a/docs/Atelier-Rusalka-Sitemap.xlsx
+++ b/docs/Atelier-Rusalka-Sitemap.xlsx
@@ -620,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -630,14 +630,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Atelier Rusalka — Sitemap Tracker</t>
+          <t>Atelier Rusalka Sitemap Tracker</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-05-14 13:45</t>
+          <t>Generated 2026-05-14 14:13</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>122</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8">
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>48</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10">
@@ -711,89 +711,125 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>By section (Done / Total)</t>
+          <t>By section (Done out of Total)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Marketing flow</t>
+          <t>Homepage</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>28 / 39</t>
+          <t>10 / 11</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>Customer area</t>
+          <t>Consultation quiz</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>2 / 6</t>
+          <t>1 / 36</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Reference pages</t>
+          <t>After the quiz</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>3 / 10</t>
+          <t>6 / 12</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Admin tools</t>
+          <t>Cart and checkout</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>11 / 14</t>
+          <t>13 / 16</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>Integrations</t>
+          <t>Customer account</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>12 / 24</t>
+          <t>2 / 6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>Design system</t>
+          <t>Reference pages</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>15 / 16</t>
+          <t>1 / 4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>Cross-cutting concerns</t>
+          <t>Admin tools</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>10 / 13</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Outside services we connect to</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>11 / 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>15 / 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Other things to do</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>1 / 13</t>
         </is>
@@ -810,7 +846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I151"/>
+  <dimension ref="A1:I213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -874,14 +910,14 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>MARKETING FLOW</t>
+          <t>HOMEPAGE</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>Marketing flow</t>
+          <t>Homepage</t>
         </is>
       </c>
       <c r="B3" s="14" t="inlineStr">
@@ -896,7 +932,7 @@
       </c>
       <c r="D3" s="15" t="inlineStr">
         <is>
-          <t>Hero · featured · subscription · footer</t>
+          <t>The landing page (hero video, featured section, subscription cards, footer)</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr"/>
@@ -908,7 +944,7 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Marketing flow</t>
+          <t>Homepage</t>
         </is>
       </c>
       <c r="B4" s="16" t="inlineStr">
@@ -923,7 +959,7 @@
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>Promo bar (Exclusive welcome offer)</t>
+          <t>Top promo bar with welcome offer</t>
         </is>
       </c>
       <c r="E4" s="17" t="inlineStr">
@@ -943,7 +979,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>Marketing flow</t>
+          <t>Homepage</t>
         </is>
       </c>
       <c r="B5" s="16" t="inlineStr">
@@ -958,7 +994,7 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>Nav with kyrill / Atelier Rusalka wordmark + logo</t>
+          <t>Site nav with logo and wordmark</t>
         </is>
       </c>
       <c r="E5" s="17" t="inlineStr">
@@ -978,7 +1014,7 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>Marketing flow</t>
+          <t>Homepage</t>
         </is>
       </c>
       <c r="B6" s="16" t="inlineStr">
@@ -993,7 +1029,7 @@
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>Hero — single video (carousel removed)</t>
+          <t>Hero with single looping video</t>
         </is>
       </c>
       <c r="E6" s="17" t="inlineStr">
@@ -1013,7 +1049,7 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>Marketing flow</t>
+          <t>Homepage</t>
         </is>
       </c>
       <c r="B7" s="16" t="inlineStr">
@@ -1028,7 +1064,7 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>Hero — asymmetric CTA, narrower radius, fluid width</t>
+          <t>Hero CTA button placed bottom right</t>
         </is>
       </c>
       <c r="E7" s="17" t="inlineStr">
@@ -1048,7 +1084,7 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
         <is>
-          <t>Marketing flow</t>
+          <t>Homepage</t>
         </is>
       </c>
       <c r="B8" s="16" t="inlineStr">
@@ -1063,7 +1099,7 @@
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>Featured section — halo badge + trust anchors</t>
+          <t>Featured section with halo badge and trust line</t>
         </is>
       </c>
       <c r="E8" s="17" t="inlineStr">
@@ -1083,7 +1119,7 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>Marketing flow</t>
+          <t>Homepage</t>
         </is>
       </c>
       <c r="B9" s="16" t="inlineStr">
@@ -1098,7 +1134,7 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>Featured CTA — 'Compose your formula'</t>
+          <t>Compose your formula button copy</t>
         </is>
       </c>
       <c r="E9" s="17" t="inlineStr">
@@ -1118,7 +1154,7 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>Marketing flow</t>
+          <t>Homepage</t>
         </is>
       </c>
       <c r="B10" s="16" t="inlineStr">
@@ -1133,7 +1169,7 @@
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>Subscription section — 3-card grid</t>
+          <t>Subscription section with three cards</t>
         </is>
       </c>
       <c r="E10" s="17" t="inlineStr">
@@ -1153,7 +1189,7 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>Marketing flow</t>
+          <t>Homepage</t>
         </is>
       </c>
       <c r="B11" s="16" t="inlineStr">
@@ -1168,7 +1204,7 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>Footer — fluid layout</t>
+          <t>Footer that scales with the page</t>
         </is>
       </c>
       <c r="E11" s="17" t="inlineStr">
@@ -1188,7 +1224,7 @@
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>Marketing flow</t>
+          <t>Homepage</t>
         </is>
       </c>
       <c r="B12" s="16" t="inlineStr">
@@ -1203,7 +1239,7 @@
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>Mobile hamburger menu</t>
+          <t>Mobile menu (hamburger)</t>
         </is>
       </c>
       <c r="E12" s="17" t="inlineStr">
@@ -1223,7 +1259,7 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>Marketing flow</t>
+          <t>Homepage</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
@@ -1238,7 +1274,7 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>Fluid scaling on 1920+ monitors</t>
+          <t>Layout scales to large external monitors</t>
         </is>
       </c>
       <c r="E13" s="17" t="inlineStr">
@@ -1258,7 +1294,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>Marketing flow</t>
+          <t>Homepage</t>
         </is>
       </c>
       <c r="B14" s="16" t="inlineStr">
@@ -1273,7 +1309,7 @@
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>Imagination-gap photo on featured section</t>
+          <t>Real product photo for featured section</t>
         </is>
       </c>
       <c r="E14" s="18" t="inlineStr">
@@ -1289,86 +1325,54 @@
       <c r="G14" s="16" t="inlineStr"/>
       <c r="H14" s="16" t="inlineStr">
         <is>
-          <t>Needs real product photo asset</t>
+          <t>Waiting on photography assets</t>
         </is>
       </c>
       <c r="I14" s="16" t="inlineStr"/>
     </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>Marketing flow</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>Consultation Quiz</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>CONSULTATION QUIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>Consultation quiz</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>Quiz overview</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>/quiz</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
-        <is>
-          <t>Multi-step form (~31 questions)</t>
-        </is>
-      </c>
-      <c r="E15" s="15" t="inlineStr"/>
-      <c r="F15" s="15" t="inlineStr"/>
-      <c r="G15" s="15" t="inlineStr"/>
-      <c r="H15" s="15" t="inlineStr"/>
-      <c r="I15" s="15" t="inlineStr"/>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>Marketing flow</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>Consultation Quiz</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>/quiz</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>31-question flow</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>P0 critical</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr"/>
-      <c r="H16" s="16" t="inlineStr">
-        <is>
-          <t>Existed before recent rebrand</t>
-        </is>
-      </c>
-      <c r="I16" s="16" t="inlineStr"/>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>The quiz is a single page that walks the customer through 31 questions one at a time. Each question below shares the same URL but is tracked separately so we can polish each step.</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr"/>
+      <c r="F16" s="15" t="inlineStr"/>
+      <c r="G16" s="15" t="inlineStr"/>
+      <c r="H16" s="15" t="inlineStr"/>
+      <c r="I16" s="15" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>Marketing flow</t>
+          <t>Consultation quiz</t>
         </is>
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>Consultation Quiz</t>
+          <t>Quiz overview</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
@@ -1378,36 +1382,32 @@
       </c>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>Mobile responsive per question step</t>
-        </is>
-      </c>
-      <c r="E17" s="19" t="inlineStr">
-        <is>
-          <t>Todo</t>
+          <t>Quiz framework working end to end</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>P1 high</t>
+          <t>P0 critical</t>
         </is>
       </c>
       <c r="G17" s="16" t="inlineStr"/>
-      <c r="H17" s="16" t="inlineStr">
-        <is>
-          <t>Needs audit at 375px</t>
-        </is>
-      </c>
+      <c r="H17" s="16" t="inlineStr"/>
       <c r="I17" s="16" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>Marketing flow</t>
+          <t>Consultation quiz</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>Consultation Quiz</t>
+          <t>Quiz overview</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>Typography pass per question (readability, not mono)</t>
+          <t>Each question reachable by a step number in the URL</t>
         </is>
       </c>
       <c r="E18" s="19" t="inlineStr">
@@ -1427,22 +1427,26 @@
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
-          <t>P1 high</t>
+          <t>P2 medium</t>
         </is>
       </c>
       <c r="G18" s="16" t="inlineStr"/>
-      <c r="H18" s="16" t="inlineStr"/>
+      <c r="H18" s="16" t="inlineStr">
+        <is>
+          <t>Currently you have to walk the form. Future improvement.</t>
+        </is>
+      </c>
       <c r="I18" s="16" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>Marketing flow</t>
+          <t>Consultation quiz</t>
         </is>
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>Consultation Quiz</t>
+          <t>Quiz overview</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
@@ -1452,7 +1456,7 @@
       </c>
       <c r="D19" s="16" t="inlineStr">
         <is>
-          <t>Deep-link to specific step (?step=N)</t>
+          <t>Save partial answers if customer drops off</t>
         </is>
       </c>
       <c r="E19" s="19" t="inlineStr">
@@ -1472,12 +1476,12 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>Marketing flow</t>
+          <t>Consultation quiz</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>Consultation Quiz</t>
+          <t>Quiz overview</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
@@ -1487,7 +1491,7 @@
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>Fragrance picker — visual swatch + tooltip (per UX video)</t>
+          <t>Polish quiz typography across all questions</t>
         </is>
       </c>
       <c r="E20" s="19" t="inlineStr">
@@ -1497,22 +1501,26 @@
       </c>
       <c r="F20" s="16" t="inlineStr">
         <is>
-          <t>P2 medium</t>
+          <t>P1 high</t>
         </is>
       </c>
       <c r="G20" s="16" t="inlineStr"/>
-      <c r="H20" s="16" t="inlineStr"/>
+      <c r="H20" s="16" t="inlineStr">
+        <is>
+          <t>Headings and body text feel too small or mono on some steps</t>
+        </is>
+      </c>
       <c r="I20" s="16" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>Marketing flow</t>
+          <t>Consultation quiz</t>
         </is>
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>Consultation Quiz</t>
+          <t>Quiz overview</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
@@ -1522,7 +1530,7 @@
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>Conversion optimisation pass per step</t>
+          <t>Mobile usability check on every question</t>
         </is>
       </c>
       <c r="E21" s="19" t="inlineStr">
@@ -1542,22 +1550,22 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>Marketing flow</t>
+          <t>Consultation quiz</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>Results</t>
+          <t>Step 1 of 31</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>/results</t>
+          <t>/quiz</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>Recommended formula + regimen</t>
+          <t>About You: How old are you?</t>
         </is>
       </c>
       <c r="E22" s="15" t="inlineStr"/>
@@ -1569,27 +1577,27 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>Marketing flow</t>
+          <t>Consultation quiz</t>
         </is>
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>Results</t>
+          <t>Step 1 of 31</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>/results</t>
+          <t>/quiz</t>
         </is>
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>Trust-anchor strip under header</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Design and copy polish for this step</t>
+        </is>
+      </c>
+      <c r="E23" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
         </is>
       </c>
       <c r="F23" s="16" t="inlineStr">
@@ -1601,65 +1609,57 @@
       <c r="H23" s="16" t="inlineStr"/>
       <c r="I23" s="16" t="inlineStr"/>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
-        <is>
-          <t>Marketing flow</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>Results</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>/results</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>Ingredient progressive disclosure (click to expand)</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>P1 high</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr"/>
-      <c r="H24" s="16" t="inlineStr"/>
-      <c r="I24" s="16" t="inlineStr"/>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>Consultation quiz</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>Step 2 of 31</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>/quiz</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>About You: What is your biological sex?</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr"/>
+      <c r="F24" s="15" t="inlineStr"/>
+      <c r="G24" s="15" t="inlineStr"/>
+      <c r="H24" s="15" t="inlineStr"/>
+      <c r="I24" s="15" t="inlineStr"/>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>Marketing flow</t>
+          <t>Consultation quiz</t>
         </is>
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>Results</t>
+          <t>Step 2 of 31</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>/results</t>
+          <t>/quiz</t>
         </is>
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>3D botanical scene</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Design and copy polish for this step</t>
+        </is>
+      </c>
+      <c r="E25" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
         </is>
       </c>
       <c r="F25" s="16" t="inlineStr">
@@ -1668,67 +1668,55 @@
         </is>
       </c>
       <c r="G25" s="16" t="inlineStr"/>
-      <c r="H25" s="16" t="inlineStr">
-        <is>
-          <t>ProductScene component, dynamic-imported</t>
-        </is>
-      </c>
+      <c r="H25" s="16" t="inlineStr"/>
       <c r="I25" s="16" t="inlineStr"/>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="16" t="inlineStr">
-        <is>
-          <t>Marketing flow</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>Results</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>/results</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>Side-by-side plan selector</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>P1 high</t>
-        </is>
-      </c>
-      <c r="G26" s="16" t="inlineStr"/>
-      <c r="H26" s="16" t="inlineStr"/>
-      <c r="I26" s="16" t="inlineStr"/>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>Consultation quiz</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>Step 3 of 31</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>/quiz</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>About You: Where do you live?</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr"/>
+      <c r="F26" s="15" t="inlineStr"/>
+      <c r="G26" s="15" t="inlineStr"/>
+      <c r="H26" s="15" t="inlineStr"/>
+      <c r="I26" s="15" t="inlineStr"/>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>Marketing flow</t>
+          <t>Consultation quiz</t>
         </is>
       </c>
       <c r="B27" s="16" t="inlineStr">
         <is>
-          <t>Results</t>
+          <t>Step 3 of 31</t>
         </is>
       </c>
       <c r="C27" s="16" t="inlineStr">
         <is>
-          <t>/results</t>
+          <t>/quiz</t>
         </is>
       </c>
       <c r="D27" s="16" t="inlineStr">
         <is>
-          <t>Mobile responsive</t>
+          <t>Design and copy polish for this step</t>
         </is>
       </c>
       <c r="E27" s="19" t="inlineStr">
@@ -1738,278 +1726,250 @@
       </c>
       <c r="F27" s="16" t="inlineStr">
         <is>
-          <t>P1 high</t>
+          <t>P2 medium</t>
         </is>
       </c>
       <c r="G27" s="16" t="inlineStr"/>
-      <c r="H27" s="16" t="inlineStr">
-        <is>
-          <t>Needs audit on 375px and 414px</t>
-        </is>
-      </c>
+      <c r="H27" s="16" t="inlineStr"/>
       <c r="I27" s="16" t="inlineStr"/>
     </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
-        <is>
-          <t>Marketing flow</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>Results</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>/results</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>Error / empty state design</t>
-        </is>
-      </c>
-      <c r="E28" s="19" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F28" s="16" t="inlineStr">
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>Consultation quiz</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>Step 4 of 31</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>/quiz</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>About You: How would you describe your environment?</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr"/>
+      <c r="F28" s="15" t="inlineStr"/>
+      <c r="G28" s="15" t="inlineStr"/>
+      <c r="H28" s="15" t="inlineStr"/>
+      <c r="I28" s="15" t="inlineStr"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>Consultation quiz</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>Step 4 of 31</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>/quiz</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="inlineStr">
+        <is>
+          <t>Design and copy polish for this step</t>
+        </is>
+      </c>
+      <c r="E29" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F29" s="16" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G28" s="16" t="inlineStr"/>
-      <c r="H28" s="16" t="inlineStr"/>
-      <c r="I28" s="16" t="inlineStr"/>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="14" t="inlineStr">
-        <is>
-          <t>Marketing flow</t>
-        </is>
-      </c>
-      <c r="B29" s="14" t="inlineStr">
-        <is>
-          <t>Cart</t>
-        </is>
-      </c>
-      <c r="C29" s="15" t="inlineStr">
-        <is>
-          <t>/cart</t>
-        </is>
-      </c>
-      <c r="D29" s="15" t="inlineStr">
-        <is>
-          <t>Plan selection · trust strip</t>
-        </is>
-      </c>
-      <c r="E29" s="15" t="inlineStr"/>
-      <c r="F29" s="15" t="inlineStr"/>
-      <c r="G29" s="15" t="inlineStr"/>
-      <c r="H29" s="15" t="inlineStr"/>
-      <c r="I29" s="15" t="inlineStr"/>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="16" t="inlineStr">
-        <is>
-          <t>Marketing flow</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>Cart</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>/cart</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>3-card subscription plan grid</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F30" s="16" t="inlineStr">
-        <is>
-          <t>P0 critical</t>
-        </is>
-      </c>
-      <c r="G30" s="16" t="inlineStr"/>
-      <c r="H30" s="16" t="inlineStr"/>
-      <c r="I30" s="16" t="inlineStr"/>
+      <c r="G29" s="16" t="inlineStr"/>
+      <c r="H29" s="16" t="inlineStr"/>
+      <c r="I29" s="16" t="inlineStr"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>Consultation quiz</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>Step 5 of 31</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>/quiz</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>About You: How much water do you drink daily?</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr"/>
+      <c r="F30" s="15" t="inlineStr"/>
+      <c r="G30" s="15" t="inlineStr"/>
+      <c r="H30" s="15" t="inlineStr"/>
+      <c r="I30" s="15" t="inlineStr"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="16" t="inlineStr">
         <is>
-          <t>Marketing flow</t>
+          <t>Consultation quiz</t>
         </is>
       </c>
       <c r="B31" s="16" t="inlineStr">
         <is>
-          <t>Cart</t>
+          <t>Step 5 of 31</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
         <is>
-          <t>/cart</t>
+          <t>/quiz</t>
         </is>
       </c>
       <c r="D31" s="16" t="inlineStr">
         <is>
-          <t>Bi-monthly default + 'Most Popular' tag</t>
-        </is>
-      </c>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Design and copy polish for this step</t>
+        </is>
+      </c>
+      <c r="E31" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
         </is>
       </c>
       <c r="F31" s="16" t="inlineStr">
         <is>
-          <t>P0 critical</t>
+          <t>P2 medium</t>
         </is>
       </c>
       <c r="G31" s="16" t="inlineStr"/>
       <c r="H31" s="16" t="inlineStr"/>
       <c r="I31" s="16" t="inlineStr"/>
     </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="16" t="inlineStr">
-        <is>
-          <t>Marketing flow</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>Cart</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>/cart</t>
-        </is>
-      </c>
-      <c r="D32" s="16" t="inlineStr">
-        <is>
-          <t>Reassurance copy inside each card</t>
-        </is>
-      </c>
-      <c r="E32" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F32" s="16" t="inlineStr">
-        <is>
-          <t>P1 high</t>
-        </is>
-      </c>
-      <c r="G32" s="16" t="inlineStr"/>
-      <c r="H32" s="16" t="inlineStr"/>
-      <c r="I32" s="16" t="inlineStr"/>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>Consultation quiz</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>Step 6 of 31</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>/quiz</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>About You: How many hours of sleep do you typically get?</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr"/>
+      <c r="F32" s="15" t="inlineStr"/>
+      <c r="G32" s="15" t="inlineStr"/>
+      <c r="H32" s="15" t="inlineStr"/>
+      <c r="I32" s="15" t="inlineStr"/>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="16" t="inlineStr">
         <is>
-          <t>Marketing flow</t>
+          <t>Consultation quiz</t>
         </is>
       </c>
       <c r="B33" s="16" t="inlineStr">
         <is>
-          <t>Cart</t>
+          <t>Step 6 of 31</t>
         </is>
       </c>
       <c r="C33" s="16" t="inlineStr">
         <is>
-          <t>/cart</t>
+          <t>/quiz</t>
         </is>
       </c>
       <c r="D33" s="16" t="inlineStr">
         <is>
-          <t>Trust strip under primary CTA</t>
-        </is>
-      </c>
-      <c r="E33" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Design and copy polish for this step</t>
+        </is>
+      </c>
+      <c r="E33" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
         </is>
       </c>
       <c r="F33" s="16" t="inlineStr">
         <is>
-          <t>P1 high</t>
+          <t>P2 medium</t>
         </is>
       </c>
       <c r="G33" s="16" t="inlineStr"/>
       <c r="H33" s="16" t="inlineStr"/>
       <c r="I33" s="16" t="inlineStr"/>
     </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="16" t="inlineStr">
-        <is>
-          <t>Marketing flow</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="inlineStr">
-        <is>
-          <t>Cart</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>/cart</t>
-        </is>
-      </c>
-      <c r="D34" s="16" t="inlineStr">
-        <is>
-          <t>Card surfaces follow palette tokens</t>
-        </is>
-      </c>
-      <c r="E34" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F34" s="16" t="inlineStr">
-        <is>
-          <t>P2 medium</t>
-        </is>
-      </c>
-      <c r="G34" s="16" t="inlineStr"/>
-      <c r="H34" s="16" t="inlineStr"/>
-      <c r="I34" s="16" t="inlineStr"/>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>Consultation quiz</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>Step 7 of 31</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>/quiz</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>About You: How would you rate your daily stress level?</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr"/>
+      <c r="F34" s="15" t="inlineStr"/>
+      <c r="G34" s="15" t="inlineStr"/>
+      <c r="H34" s="15" t="inlineStr"/>
+      <c r="I34" s="15" t="inlineStr"/>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="16" t="inlineStr">
         <is>
-          <t>Marketing flow</t>
+          <t>Consultation quiz</t>
         </is>
       </c>
       <c r="B35" s="16" t="inlineStr">
         <is>
-          <t>Cart</t>
+          <t>Step 7 of 31</t>
         </is>
       </c>
       <c r="C35" s="16" t="inlineStr">
         <is>
-          <t>/cart</t>
+          <t>/quiz</t>
         </is>
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
-          <t>Empty-cart state — 'Begin the consultation'</t>
-        </is>
-      </c>
-      <c r="E35" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Design and copy polish for this step</t>
+        </is>
+      </c>
+      <c r="E35" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
         </is>
       </c>
       <c r="F35" s="16" t="inlineStr">
@@ -2021,201 +1981,181 @@
       <c r="H35" s="16" t="inlineStr"/>
       <c r="I35" s="16" t="inlineStr"/>
     </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="16" t="inlineStr">
-        <is>
-          <t>Marketing flow</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="inlineStr">
-        <is>
-          <t>Cart</t>
-        </is>
-      </c>
-      <c r="C36" s="16" t="inlineStr">
-        <is>
-          <t>/cart</t>
-        </is>
-      </c>
-      <c r="D36" s="16" t="inlineStr">
-        <is>
-          <t>Mobile responsive (3-col → 1-col at 720px)</t>
-        </is>
-      </c>
-      <c r="E36" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F36" s="16" t="inlineStr">
-        <is>
-          <t>P1 high</t>
-        </is>
-      </c>
-      <c r="G36" s="16" t="inlineStr"/>
-      <c r="H36" s="16" t="inlineStr"/>
-      <c r="I36" s="16" t="inlineStr"/>
-    </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="14" t="inlineStr">
-        <is>
-          <t>Marketing flow</t>
-        </is>
-      </c>
-      <c r="B37" s="14" t="inlineStr">
-        <is>
-          <t>Checkout</t>
-        </is>
-      </c>
-      <c r="C37" s="15" t="inlineStr">
-        <is>
-          <t>/checkout</t>
-        </is>
-      </c>
-      <c r="D37" s="15" t="inlineStr">
-        <is>
-          <t>Stripe redirect</t>
-        </is>
-      </c>
-      <c r="E37" s="15" t="inlineStr"/>
-      <c r="F37" s="15" t="inlineStr"/>
-      <c r="G37" s="15" t="inlineStr"/>
-      <c r="H37" s="15" t="inlineStr"/>
-      <c r="I37" s="15" t="inlineStr"/>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="16" t="inlineStr">
-        <is>
-          <t>Marketing flow</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="inlineStr">
-        <is>
-          <t>Checkout</t>
-        </is>
-      </c>
-      <c r="C38" s="16" t="inlineStr">
-        <is>
-          <t>/checkout</t>
-        </is>
-      </c>
-      <c r="D38" s="16" t="inlineStr">
-        <is>
-          <t>Stripe checkout session creation</t>
-        </is>
-      </c>
-      <c r="E38" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F38" s="16" t="inlineStr">
-        <is>
-          <t>P0 critical</t>
-        </is>
-      </c>
-      <c r="G38" s="16" t="inlineStr"/>
-      <c r="H38" s="16" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-      <c r="I38" s="16" t="inlineStr"/>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>Consultation quiz</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>Step 8 of 31</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>/quiz</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
+        <is>
+          <t>About You: How would you describe your diet?</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="inlineStr"/>
+      <c r="F36" s="15" t="inlineStr"/>
+      <c r="G36" s="15" t="inlineStr"/>
+      <c r="H36" s="15" t="inlineStr"/>
+      <c r="I36" s="15" t="inlineStr"/>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>Consultation quiz</t>
+        </is>
+      </c>
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t>Step 8 of 31</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="inlineStr">
+        <is>
+          <t>/quiz</t>
+        </is>
+      </c>
+      <c r="D37" s="16" t="inlineStr">
+        <is>
+          <t>Design and copy polish for this step</t>
+        </is>
+      </c>
+      <c r="E37" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F37" s="16" t="inlineStr">
+        <is>
+          <t>P2 medium</t>
+        </is>
+      </c>
+      <c r="G37" s="16" t="inlineStr"/>
+      <c r="H37" s="16" t="inlineStr"/>
+      <c r="I37" s="16" t="inlineStr"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>Consultation quiz</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>Step 9 of 31</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>/quiz</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="inlineStr">
+        <is>
+          <t>About You: How much daily sun exposure do you get?</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr"/>
+      <c r="F38" s="15" t="inlineStr"/>
+      <c r="G38" s="15" t="inlineStr"/>
+      <c r="H38" s="15" t="inlineStr"/>
+      <c r="I38" s="15" t="inlineStr"/>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="16" t="inlineStr">
         <is>
-          <t>Marketing flow</t>
+          <t>Consultation quiz</t>
         </is>
       </c>
       <c r="B39" s="16" t="inlineStr">
         <is>
-          <t>Checkout</t>
+          <t>Step 9 of 31</t>
         </is>
       </c>
       <c r="C39" s="16" t="inlineStr">
         <is>
-          <t>/checkout</t>
+          <t>/quiz</t>
         </is>
       </c>
       <c r="D39" s="16" t="inlineStr">
         <is>
-          <t>Trust strip under Pay button</t>
-        </is>
-      </c>
-      <c r="E39" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Design and copy polish for this step</t>
+        </is>
+      </c>
+      <c r="E39" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
         </is>
       </c>
       <c r="F39" s="16" t="inlineStr">
         <is>
-          <t>P1 high</t>
+          <t>P2 medium</t>
         </is>
       </c>
       <c r="G39" s="16" t="inlineStr"/>
       <c r="H39" s="16" t="inlineStr"/>
       <c r="I39" s="16" t="inlineStr"/>
     </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="16" t="inlineStr">
-        <is>
-          <t>Marketing flow</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="inlineStr">
-        <is>
-          <t>Checkout</t>
-        </is>
-      </c>
-      <c r="C40" s="16" t="inlineStr">
-        <is>
-          <t>/checkout</t>
-        </is>
-      </c>
-      <c r="D40" s="16" t="inlineStr">
-        <is>
-          <t>CTAs follow palette tokens</t>
-        </is>
-      </c>
-      <c r="E40" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F40" s="16" t="inlineStr">
-        <is>
-          <t>P2 medium</t>
-        </is>
-      </c>
-      <c r="G40" s="16" t="inlineStr"/>
-      <c r="H40" s="16" t="inlineStr"/>
-      <c r="I40" s="16" t="inlineStr"/>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>Consultation quiz</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>Step 10 of 31</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="inlineStr">
+        <is>
+          <t>/quiz</t>
+        </is>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>About You: Are you currently pregnant or breastfeeding?</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr"/>
+      <c r="F40" s="15" t="inlineStr"/>
+      <c r="G40" s="15" t="inlineStr"/>
+      <c r="H40" s="15" t="inlineStr"/>
+      <c r="I40" s="15" t="inlineStr"/>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>Marketing flow</t>
+          <t>Consultation quiz</t>
         </is>
       </c>
       <c r="B41" s="16" t="inlineStr">
         <is>
-          <t>Checkout</t>
+          <t>Step 10 of 31</t>
         </is>
       </c>
       <c r="C41" s="16" t="inlineStr">
         <is>
-          <t>/checkout</t>
+          <t>/quiz</t>
         </is>
       </c>
       <c r="D41" s="16" t="inlineStr">
         <is>
-          <t>Subscription recurring note copy</t>
-        </is>
-      </c>
-      <c r="E41" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Design and copy polish for this step</t>
+        </is>
+      </c>
+      <c r="E41" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
         </is>
       </c>
       <c r="F41" s="16" t="inlineStr">
@@ -2227,192 +2167,176 @@
       <c r="H41" s="16" t="inlineStr"/>
       <c r="I41" s="16" t="inlineStr"/>
     </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="16" t="inlineStr">
-        <is>
-          <t>Marketing flow</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="inlineStr">
-        <is>
-          <t>Checkout</t>
-        </is>
-      </c>
-      <c r="C42" s="16" t="inlineStr">
-        <is>
-          <t>/checkout</t>
-        </is>
-      </c>
-      <c r="D42" s="16" t="inlineStr">
-        <is>
-          <t>Error state styling</t>
-        </is>
-      </c>
-      <c r="E42" s="19" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F42" s="16" t="inlineStr">
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>Consultation quiz</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>Step 11 of 31</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="inlineStr">
+        <is>
+          <t>/quiz</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t>Your Skin: How would you describe your skin type?</t>
+        </is>
+      </c>
+      <c r="E42" s="15" t="inlineStr"/>
+      <c r="F42" s="15" t="inlineStr"/>
+      <c r="G42" s="15" t="inlineStr"/>
+      <c r="H42" s="15" t="inlineStr"/>
+      <c r="I42" s="15" t="inlineStr"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>Consultation quiz</t>
+        </is>
+      </c>
+      <c r="B43" s="16" t="inlineStr">
+        <is>
+          <t>Step 11 of 31</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="inlineStr">
+        <is>
+          <t>/quiz</t>
+        </is>
+      </c>
+      <c r="D43" s="16" t="inlineStr">
+        <is>
+          <t>Design and copy polish for this step</t>
+        </is>
+      </c>
+      <c r="E43" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F43" s="16" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G42" s="16" t="inlineStr"/>
-      <c r="H42" s="16" t="inlineStr"/>
-      <c r="I42" s="16" t="inlineStr"/>
-    </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="14" t="inlineStr">
-        <is>
-          <t>Marketing flow</t>
-        </is>
-      </c>
-      <c r="B43" s="14" t="inlineStr">
-        <is>
-          <t>Confirmation</t>
-        </is>
-      </c>
-      <c r="C43" s="15" t="inlineStr">
-        <is>
-          <t>/confirmation?session_id=…</t>
-        </is>
-      </c>
-      <c r="D43" s="15" t="inlineStr">
-        <is>
-          <t>Post-payment screen — verifies Stripe session</t>
-        </is>
-      </c>
-      <c r="E43" s="15" t="inlineStr"/>
-      <c r="F43" s="15" t="inlineStr"/>
-      <c r="G43" s="15" t="inlineStr"/>
-      <c r="H43" s="15" t="inlineStr"/>
-      <c r="I43" s="15" t="inlineStr"/>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="16" t="inlineStr">
-        <is>
-          <t>Marketing flow</t>
-        </is>
-      </c>
-      <c r="B44" s="16" t="inlineStr">
-        <is>
-          <t>Confirmation</t>
-        </is>
-      </c>
-      <c r="C44" s="16" t="inlineStr">
-        <is>
-          <t>/confirmation?session_id=…</t>
-        </is>
-      </c>
-      <c r="D44" s="16" t="inlineStr">
-        <is>
-          <t>Stripe session verification (server-side)</t>
-        </is>
-      </c>
-      <c r="E44" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F44" s="16" t="inlineStr">
-        <is>
-          <t>P0 critical</t>
-        </is>
-      </c>
-      <c r="G44" s="16" t="inlineStr"/>
-      <c r="H44" s="16" t="inlineStr"/>
-      <c r="I44" s="16" t="inlineStr"/>
+      <c r="G43" s="16" t="inlineStr"/>
+      <c r="H43" s="16" t="inlineStr"/>
+      <c r="I43" s="16" t="inlineStr"/>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>Consultation quiz</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>Step 12 of 31</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="inlineStr">
+        <is>
+          <t>/quiz</t>
+        </is>
+      </c>
+      <c r="D44" s="15" t="inlineStr">
+        <is>
+          <t>Your Skin: What are your biggest skin concerns right now?</t>
+        </is>
+      </c>
+      <c r="E44" s="15" t="inlineStr"/>
+      <c r="F44" s="15" t="inlineStr"/>
+      <c r="G44" s="15" t="inlineStr"/>
+      <c r="H44" s="15" t="inlineStr"/>
+      <c r="I44" s="15" t="inlineStr"/>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="16" t="inlineStr">
         <is>
-          <t>Marketing flow</t>
+          <t>Consultation quiz</t>
         </is>
       </c>
       <c r="B45" s="16" t="inlineStr">
         <is>
-          <t>Confirmation</t>
+          <t>Step 12 of 31</t>
         </is>
       </c>
       <c r="C45" s="16" t="inlineStr">
         <is>
-          <t>/confirmation?session_id=…</t>
+          <t>/quiz</t>
         </is>
       </c>
       <c r="D45" s="16" t="inlineStr">
         <is>
-          <t>Webhook auto-fulfill on payment success</t>
-        </is>
-      </c>
-      <c r="E45" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Design and copy polish for this step</t>
+        </is>
+      </c>
+      <c r="E45" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
         </is>
       </c>
       <c r="F45" s="16" t="inlineStr">
         <is>
-          <t>P0 critical</t>
+          <t>P2 medium</t>
         </is>
       </c>
       <c r="G45" s="16" t="inlineStr"/>
       <c r="H45" s="16" t="inlineStr"/>
       <c r="I45" s="16" t="inlineStr"/>
     </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="16" t="inlineStr">
-        <is>
-          <t>Marketing flow</t>
-        </is>
-      </c>
-      <c r="B46" s="16" t="inlineStr">
-        <is>
-          <t>Confirmation</t>
-        </is>
-      </c>
-      <c r="C46" s="16" t="inlineStr">
-        <is>
-          <t>/confirmation?session_id=…</t>
-        </is>
-      </c>
-      <c r="D46" s="16" t="inlineStr">
-        <is>
-          <t>Order details + next-steps copy</t>
-        </is>
-      </c>
-      <c r="E46" s="19" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F46" s="16" t="inlineStr">
-        <is>
-          <t>P1 high</t>
-        </is>
-      </c>
-      <c r="G46" s="16" t="inlineStr"/>
-      <c r="H46" s="16" t="inlineStr"/>
-      <c r="I46" s="16" t="inlineStr"/>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t>Consultation quiz</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>Step 13 of 31</t>
+        </is>
+      </c>
+      <c r="C46" s="15" t="inlineStr">
+        <is>
+          <t>/quiz</t>
+        </is>
+      </c>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>Your Skin: How sensitive is your skin to the sun?</t>
+        </is>
+      </c>
+      <c r="E46" s="15" t="inlineStr"/>
+      <c r="F46" s="15" t="inlineStr"/>
+      <c r="G46" s="15" t="inlineStr"/>
+      <c r="H46" s="15" t="inlineStr"/>
+      <c r="I46" s="15" t="inlineStr"/>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>Marketing flow</t>
+          <t>Consultation quiz</t>
         </is>
       </c>
       <c r="B47" s="16" t="inlineStr">
         <is>
-          <t>Confirmation</t>
+          <t>Step 13 of 31</t>
         </is>
       </c>
       <c r="C47" s="16" t="inlineStr">
         <is>
-          <t>/confirmation?session_id=…</t>
+          <t>/quiz</t>
         </is>
       </c>
       <c r="D47" s="16" t="inlineStr">
         <is>
-          <t>Tracking link surfaced (once Direx integration lands)</t>
+          <t>Design and copy polish for this step</t>
         </is>
       </c>
       <c r="E47" s="19" t="inlineStr">
@@ -2422,179 +2346,183 @@
       </c>
       <c r="F47" s="16" t="inlineStr">
         <is>
-          <t>P1 high</t>
+          <t>P2 medium</t>
         </is>
       </c>
       <c r="G47" s="16" t="inlineStr"/>
       <c r="H47" s="16" t="inlineStr"/>
       <c r="I47" s="16" t="inlineStr"/>
     </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="13" t="inlineStr">
-        <is>
-          <t>CUSTOMER AREA</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="14" t="inlineStr">
-        <is>
-          <t>Customer area</t>
-        </is>
-      </c>
-      <c r="B49" s="14" t="inlineStr">
-        <is>
-          <t>Account</t>
-        </is>
-      </c>
-      <c r="C49" s="15" t="inlineStr">
-        <is>
-          <t>/account</t>
-        </is>
-      </c>
-      <c r="D49" s="15" t="inlineStr">
-        <is>
-          <t>Dashboard · orders · settings</t>
-        </is>
-      </c>
-      <c r="E49" s="15" t="inlineStr"/>
-      <c r="F49" s="15" t="inlineStr"/>
-      <c r="G49" s="15" t="inlineStr"/>
-      <c r="H49" s="15" t="inlineStr"/>
-      <c r="I49" s="15" t="inlineStr"/>
-    </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="16" t="inlineStr">
-        <is>
-          <t>Customer area</t>
-        </is>
-      </c>
-      <c r="B50" s="16" t="inlineStr">
-        <is>
-          <t>Account</t>
-        </is>
-      </c>
-      <c r="C50" s="16" t="inlineStr">
-        <is>
-          <t>/account</t>
-        </is>
-      </c>
-      <c r="D50" s="16" t="inlineStr">
-        <is>
-          <t>Auth + sign-in flow</t>
-        </is>
-      </c>
-      <c r="E50" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F50" s="16" t="inlineStr">
-        <is>
-          <t>P0 critical</t>
-        </is>
-      </c>
-      <c r="G50" s="16" t="inlineStr"/>
-      <c r="H50" s="16" t="inlineStr">
-        <is>
-          <t>Supabase auth, existing</t>
-        </is>
-      </c>
-      <c r="I50" s="16" t="inlineStr"/>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>Consultation quiz</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>Step 14 of 31</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
+          <t>/quiz</t>
+        </is>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>Your Skin: How does your skin feel after cleansing with just water?</t>
+        </is>
+      </c>
+      <c r="E48" s="15" t="inlineStr"/>
+      <c r="F48" s="15" t="inlineStr"/>
+      <c r="G48" s="15" t="inlineStr"/>
+      <c r="H48" s="15" t="inlineStr"/>
+      <c r="I48" s="15" t="inlineStr"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>Consultation quiz</t>
+        </is>
+      </c>
+      <c r="B49" s="16" t="inlineStr">
+        <is>
+          <t>Step 14 of 31</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="inlineStr">
+        <is>
+          <t>/quiz</t>
+        </is>
+      </c>
+      <c r="D49" s="16" t="inlineStr">
+        <is>
+          <t>Design and copy polish for this step</t>
+        </is>
+      </c>
+      <c r="E49" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F49" s="16" t="inlineStr">
+        <is>
+          <t>P2 medium</t>
+        </is>
+      </c>
+      <c r="G49" s="16" t="inlineStr"/>
+      <c r="H49" s="16" t="inlineStr"/>
+      <c r="I49" s="16" t="inlineStr"/>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="14" t="inlineStr">
+        <is>
+          <t>Consultation quiz</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>Step 15 of 31</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="inlineStr">
+        <is>
+          <t>/quiz</t>
+        </is>
+      </c>
+      <c r="D50" s="15" t="inlineStr">
+        <is>
+          <t>Your Skin: How often do you experience breakouts?</t>
+        </is>
+      </c>
+      <c r="E50" s="15" t="inlineStr"/>
+      <c r="F50" s="15" t="inlineStr"/>
+      <c r="G50" s="15" t="inlineStr"/>
+      <c r="H50" s="15" t="inlineStr"/>
+      <c r="I50" s="15" t="inlineStr"/>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>Customer area</t>
+          <t>Consultation quiz</t>
         </is>
       </c>
       <c r="B51" s="16" t="inlineStr">
         <is>
-          <t>Account</t>
+          <t>Step 15 of 31</t>
         </is>
       </c>
       <c r="C51" s="16" t="inlineStr">
         <is>
-          <t>/account</t>
+          <t>/quiz</t>
         </is>
       </c>
       <c r="D51" s="16" t="inlineStr">
         <is>
-          <t>Dashboard layout</t>
-        </is>
-      </c>
-      <c r="E51" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Design and copy polish for this step</t>
+        </is>
+      </c>
+      <c r="E51" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
         </is>
       </c>
       <c r="F51" s="16" t="inlineStr">
         <is>
-          <t>P1 high</t>
+          <t>P2 medium</t>
         </is>
       </c>
       <c r="G51" s="16" t="inlineStr"/>
-      <c r="H51" s="16" t="inlineStr">
-        <is>
-          <t>Editorial styling</t>
-        </is>
-      </c>
+      <c r="H51" s="16" t="inlineStr"/>
       <c r="I51" s="16" t="inlineStr"/>
     </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="16" t="inlineStr">
-        <is>
-          <t>Customer area</t>
-        </is>
-      </c>
-      <c r="B52" s="16" t="inlineStr">
-        <is>
-          <t>Account</t>
-        </is>
-      </c>
-      <c r="C52" s="16" t="inlineStr">
-        <is>
-          <t>/account</t>
-        </is>
-      </c>
-      <c r="D52" s="16" t="inlineStr">
-        <is>
-          <t>Order history view</t>
-        </is>
-      </c>
-      <c r="E52" s="19" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F52" s="16" t="inlineStr">
-        <is>
-          <t>P1 high</t>
-        </is>
-      </c>
-      <c r="G52" s="16" t="inlineStr"/>
-      <c r="H52" s="16" t="inlineStr"/>
-      <c r="I52" s="16" t="inlineStr"/>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="14" t="inlineStr">
+        <is>
+          <t>Consultation quiz</t>
+        </is>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>Step 16 of 31</t>
+        </is>
+      </c>
+      <c r="C52" s="15" t="inlineStr">
+        <is>
+          <t>/quiz</t>
+        </is>
+      </c>
+      <c r="D52" s="15" t="inlineStr">
+        <is>
+          <t>Your Skin: Do you experience any of the following?</t>
+        </is>
+      </c>
+      <c r="E52" s="15" t="inlineStr"/>
+      <c r="F52" s="15" t="inlineStr"/>
+      <c r="G52" s="15" t="inlineStr"/>
+      <c r="H52" s="15" t="inlineStr"/>
+      <c r="I52" s="15" t="inlineStr"/>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>Customer area</t>
+          <t>Consultation quiz</t>
         </is>
       </c>
       <c r="B53" s="16" t="inlineStr">
         <is>
-          <t>Account</t>
+          <t>Step 16 of 31</t>
         </is>
       </c>
       <c r="C53" s="16" t="inlineStr">
         <is>
-          <t>/account</t>
+          <t>/quiz</t>
         </is>
       </c>
       <c r="D53" s="16" t="inlineStr">
         <is>
-          <t>Active subscription management</t>
+          <t>Design and copy polish for this step</t>
         </is>
       </c>
       <c r="E53" s="19" t="inlineStr">
@@ -2604,67 +2532,59 @@
       </c>
       <c r="F53" s="16" t="inlineStr">
         <is>
-          <t>P0 critical</t>
+          <t>P2 medium</t>
         </is>
       </c>
       <c r="G53" s="16" t="inlineStr"/>
       <c r="H53" s="16" t="inlineStr"/>
       <c r="I53" s="16" t="inlineStr"/>
     </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="16" t="inlineStr">
-        <is>
-          <t>Customer area</t>
-        </is>
-      </c>
-      <c r="B54" s="16" t="inlineStr">
-        <is>
-          <t>Account</t>
-        </is>
-      </c>
-      <c r="C54" s="16" t="inlineStr">
-        <is>
-          <t>/account</t>
-        </is>
-      </c>
-      <c r="D54" s="16" t="inlineStr">
-        <is>
-          <t>Quiz answer retake from account</t>
-        </is>
-      </c>
-      <c r="E54" s="19" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F54" s="16" t="inlineStr">
-        <is>
-          <t>P2 medium</t>
-        </is>
-      </c>
-      <c r="G54" s="16" t="inlineStr"/>
-      <c r="H54" s="16" t="inlineStr"/>
-      <c r="I54" s="16" t="inlineStr"/>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="14" t="inlineStr">
+        <is>
+          <t>Consultation quiz</t>
+        </is>
+      </c>
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>Step 17 of 31</t>
+        </is>
+      </c>
+      <c r="C54" s="15" t="inlineStr">
+        <is>
+          <t>/quiz</t>
+        </is>
+      </c>
+      <c r="D54" s="15" t="inlineStr">
+        <is>
+          <t>Your Skin: How visible are your pores?</t>
+        </is>
+      </c>
+      <c r="E54" s="15" t="inlineStr"/>
+      <c r="F54" s="15" t="inlineStr"/>
+      <c r="G54" s="15" t="inlineStr"/>
+      <c r="H54" s="15" t="inlineStr"/>
+      <c r="I54" s="15" t="inlineStr"/>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>Customer area</t>
+          <t>Consultation quiz</t>
         </is>
       </c>
       <c r="B55" s="16" t="inlineStr">
         <is>
-          <t>Account</t>
+          <t>Step 17 of 31</t>
         </is>
       </c>
       <c r="C55" s="16" t="inlineStr">
         <is>
-          <t>/account</t>
+          <t>/quiz</t>
         </is>
       </c>
       <c r="D55" s="16" t="inlineStr">
         <is>
-          <t>Profile / shipping address editor</t>
+          <t>Design and copy polish for this step</t>
         </is>
       </c>
       <c r="E55" s="19" t="inlineStr">
@@ -2674,101 +2594,121 @@
       </c>
       <c r="F55" s="16" t="inlineStr">
         <is>
-          <t>P1 high</t>
+          <t>P2 medium</t>
         </is>
       </c>
       <c r="G55" s="16" t="inlineStr"/>
       <c r="H55" s="16" t="inlineStr"/>
       <c r="I55" s="16" t="inlineStr"/>
     </row>
-    <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="13" t="inlineStr">
-        <is>
-          <t>REFERENCE PAGES</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="14" t="inlineStr">
-        <is>
-          <t>Reference pages</t>
-        </is>
-      </c>
-      <c r="B57" s="14" t="inlineStr">
-        <is>
-          <t>Ingredients</t>
-        </is>
-      </c>
-      <c r="C57" s="15" t="inlineStr">
-        <is>
-          <t>/ingredients</t>
-        </is>
-      </c>
-      <c r="D57" s="15" t="inlineStr">
-        <is>
-          <t>Botanical glossary</t>
-        </is>
-      </c>
-      <c r="E57" s="15" t="inlineStr"/>
-      <c r="F57" s="15" t="inlineStr"/>
-      <c r="G57" s="15" t="inlineStr"/>
-      <c r="H57" s="15" t="inlineStr"/>
-      <c r="I57" s="15" t="inlineStr"/>
-    </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="16" t="inlineStr">
-        <is>
-          <t>Reference pages</t>
-        </is>
-      </c>
-      <c r="B58" s="16" t="inlineStr">
-        <is>
-          <t>Ingredients</t>
-        </is>
-      </c>
-      <c r="C58" s="16" t="inlineStr">
-        <is>
-          <t>/ingredients</t>
-        </is>
-      </c>
-      <c r="D58" s="16" t="inlineStr">
-        <is>
-          <t>Ingredient list pulled from Supabase</t>
-        </is>
-      </c>
-      <c r="E58" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F58" s="16" t="inlineStr">
-        <is>
-          <t>P1 high</t>
-        </is>
-      </c>
-      <c r="G58" s="16" t="inlineStr"/>
-      <c r="H58" s="16" t="inlineStr"/>
-      <c r="I58" s="16" t="inlineStr"/>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="14" t="inlineStr">
+        <is>
+          <t>Consultation quiz</t>
+        </is>
+      </c>
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>Step 18 of 31</t>
+        </is>
+      </c>
+      <c r="C56" s="15" t="inlineStr">
+        <is>
+          <t>/quiz</t>
+        </is>
+      </c>
+      <c r="D56" s="15" t="inlineStr">
+        <is>
+          <t>Your Skin: How would you describe your skin tone?</t>
+        </is>
+      </c>
+      <c r="E56" s="15" t="inlineStr"/>
+      <c r="F56" s="15" t="inlineStr"/>
+      <c r="G56" s="15" t="inlineStr"/>
+      <c r="H56" s="15" t="inlineStr"/>
+      <c r="I56" s="15" t="inlineStr"/>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="16" t="inlineStr">
+        <is>
+          <t>Consultation quiz</t>
+        </is>
+      </c>
+      <c r="B57" s="16" t="inlineStr">
+        <is>
+          <t>Step 18 of 31</t>
+        </is>
+      </c>
+      <c r="C57" s="16" t="inlineStr">
+        <is>
+          <t>/quiz</t>
+        </is>
+      </c>
+      <c r="D57" s="16" t="inlineStr">
+        <is>
+          <t>Design and copy polish for this step</t>
+        </is>
+      </c>
+      <c r="E57" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F57" s="16" t="inlineStr">
+        <is>
+          <t>P2 medium</t>
+        </is>
+      </c>
+      <c r="G57" s="16" t="inlineStr"/>
+      <c r="H57" s="16" t="inlineStr"/>
+      <c r="I57" s="16" t="inlineStr"/>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="14" t="inlineStr">
+        <is>
+          <t>Consultation quiz</t>
+        </is>
+      </c>
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t>Step 19 of 31</t>
+        </is>
+      </c>
+      <c r="C58" s="15" t="inlineStr">
+        <is>
+          <t>/quiz</t>
+        </is>
+      </c>
+      <c r="D58" s="15" t="inlineStr">
+        <is>
+          <t>Your Skin: Rate the following about your skin right now.</t>
+        </is>
+      </c>
+      <c r="E58" s="15" t="inlineStr"/>
+      <c r="F58" s="15" t="inlineStr"/>
+      <c r="G58" s="15" t="inlineStr"/>
+      <c r="H58" s="15" t="inlineStr"/>
+      <c r="I58" s="15" t="inlineStr"/>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>Reference pages</t>
+          <t>Consultation quiz</t>
         </is>
       </c>
       <c r="B59" s="16" t="inlineStr">
         <is>
-          <t>Ingredients</t>
+          <t>Step 19 of 31</t>
         </is>
       </c>
       <c r="C59" s="16" t="inlineStr">
         <is>
-          <t>/ingredients</t>
+          <t>/quiz</t>
         </is>
       </c>
       <c r="D59" s="16" t="inlineStr">
         <is>
-          <t>Filter by function / botanical type</t>
+          <t>Design and copy polish for this step</t>
         </is>
       </c>
       <c r="E59" s="19" t="inlineStr">
@@ -2785,60 +2725,52 @@
       <c r="H59" s="16" t="inlineStr"/>
       <c r="I59" s="16" t="inlineStr"/>
     </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="16" t="inlineStr">
-        <is>
-          <t>Reference pages</t>
-        </is>
-      </c>
-      <c r="B60" s="16" t="inlineStr">
-        <is>
-          <t>Ingredients</t>
-        </is>
-      </c>
-      <c r="C60" s="16" t="inlineStr">
-        <is>
-          <t>/ingredients</t>
-        </is>
-      </c>
-      <c r="D60" s="16" t="inlineStr">
-        <is>
-          <t>Per-ingredient detail page (origin, function, scientific name)</t>
-        </is>
-      </c>
-      <c r="E60" s="19" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F60" s="16" t="inlineStr">
-        <is>
-          <t>P2 medium</t>
-        </is>
-      </c>
-      <c r="G60" s="16" t="inlineStr"/>
-      <c r="H60" s="16" t="inlineStr"/>
-      <c r="I60" s="16" t="inlineStr"/>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="14" t="inlineStr">
+        <is>
+          <t>Consultation quiz</t>
+        </is>
+      </c>
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t>Step 20 of 31</t>
+        </is>
+      </c>
+      <c r="C60" s="15" t="inlineStr">
+        <is>
+          <t>/quiz</t>
+        </is>
+      </c>
+      <c r="D60" s="15" t="inlineStr">
+        <is>
+          <t>Your Skin: Have you ever had an allergic reaction to a skincare product?</t>
+        </is>
+      </c>
+      <c r="E60" s="15" t="inlineStr"/>
+      <c r="F60" s="15" t="inlineStr"/>
+      <c r="G60" s="15" t="inlineStr"/>
+      <c r="H60" s="15" t="inlineStr"/>
+      <c r="I60" s="15" t="inlineStr"/>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>Reference pages</t>
+          <t>Consultation quiz</t>
         </is>
       </c>
       <c r="B61" s="16" t="inlineStr">
         <is>
-          <t>Ingredients</t>
+          <t>Step 20 of 31</t>
         </is>
       </c>
       <c r="C61" s="16" t="inlineStr">
         <is>
-          <t>/ingredients</t>
+          <t>/quiz</t>
         </is>
       </c>
       <c r="D61" s="16" t="inlineStr">
         <is>
-          <t>Editorial typography pass</t>
+          <t>Design and copy polish for this step</t>
         </is>
       </c>
       <c r="E61" s="19" t="inlineStr">
@@ -2848,7 +2780,7 @@
       </c>
       <c r="F61" s="16" t="inlineStr">
         <is>
-          <t>P1 high</t>
+          <t>P2 medium</t>
         </is>
       </c>
       <c r="G61" s="16" t="inlineStr"/>
@@ -2858,22 +2790,22 @@
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>Reference pages</t>
+          <t>Consultation quiz</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>Skin Analysis</t>
+          <t>Step 21 of 31</t>
         </is>
       </c>
       <c r="C62" s="15" t="inlineStr">
         <is>
-          <t>/analysis</t>
+          <t>/quiz</t>
         </is>
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t>Skin profile breakdown</t>
+          <t>Routine and Preferences: How many steps is your current skincare routine?</t>
         </is>
       </c>
       <c r="E62" s="15" t="inlineStr"/>
@@ -2885,92 +2817,84 @@
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>Reference pages</t>
+          <t>Consultation quiz</t>
         </is>
       </c>
       <c r="B63" s="16" t="inlineStr">
         <is>
-          <t>Skin Analysis</t>
+          <t>Step 21 of 31</t>
         </is>
       </c>
       <c r="C63" s="16" t="inlineStr">
         <is>
-          <t>/analysis</t>
+          <t>/quiz</t>
         </is>
       </c>
       <c r="D63" s="16" t="inlineStr">
         <is>
-          <t>Profile data render</t>
-        </is>
-      </c>
-      <c r="E63" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Design and copy polish for this step</t>
+        </is>
+      </c>
+      <c r="E63" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
         </is>
       </c>
       <c r="F63" s="16" t="inlineStr">
         <is>
-          <t>P1 high</t>
+          <t>P2 medium</t>
         </is>
       </c>
       <c r="G63" s="16" t="inlineStr"/>
       <c r="H63" s="16" t="inlineStr"/>
       <c r="I63" s="16" t="inlineStr"/>
     </row>
-    <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="16" t="inlineStr">
-        <is>
-          <t>Reference pages</t>
-        </is>
-      </c>
-      <c r="B64" s="16" t="inlineStr">
-        <is>
-          <t>Skin Analysis</t>
-        </is>
-      </c>
-      <c r="C64" s="16" t="inlineStr">
-        <is>
-          <t>/analysis</t>
-        </is>
-      </c>
-      <c r="D64" s="16" t="inlineStr">
-        <is>
-          <t>Visual breakdown of concerns + priorities</t>
-        </is>
-      </c>
-      <c r="E64" s="19" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F64" s="16" t="inlineStr">
-        <is>
-          <t>P1 high</t>
-        </is>
-      </c>
-      <c r="G64" s="16" t="inlineStr"/>
-      <c r="H64" s="16" t="inlineStr"/>
-      <c r="I64" s="16" t="inlineStr"/>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="14" t="inlineStr">
+        <is>
+          <t>Consultation quiz</t>
+        </is>
+      </c>
+      <c r="B64" s="14" t="inlineStr">
+        <is>
+          <t>Step 22 of 31</t>
+        </is>
+      </c>
+      <c r="C64" s="15" t="inlineStr">
+        <is>
+          <t>/quiz</t>
+        </is>
+      </c>
+      <c r="D64" s="15" t="inlineStr">
+        <is>
+          <t>Routine and Preferences: What texture do you prefer in a moisturiser?</t>
+        </is>
+      </c>
+      <c r="E64" s="15" t="inlineStr"/>
+      <c r="F64" s="15" t="inlineStr"/>
+      <c r="G64" s="15" t="inlineStr"/>
+      <c r="H64" s="15" t="inlineStr"/>
+      <c r="I64" s="15" t="inlineStr"/>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>Reference pages</t>
+          <t>Consultation quiz</t>
         </is>
       </c>
       <c r="B65" s="16" t="inlineStr">
         <is>
-          <t>Skin Analysis</t>
+          <t>Step 22 of 31</t>
         </is>
       </c>
       <c r="C65" s="16" t="inlineStr">
         <is>
-          <t>/analysis</t>
+          <t>/quiz</t>
         </is>
       </c>
       <c r="D65" s="16" t="inlineStr">
         <is>
-          <t>Compare against last quiz result (trend)</t>
+          <t>Design and copy polish for this step</t>
         </is>
       </c>
       <c r="E65" s="19" t="inlineStr">
@@ -2980,7 +2904,7 @@
       </c>
       <c r="F65" s="16" t="inlineStr">
         <is>
-          <t>P3 low</t>
+          <t>P2 medium</t>
         </is>
       </c>
       <c r="G65" s="16" t="inlineStr"/>
@@ -2990,22 +2914,22 @@
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>Reference pages</t>
+          <t>Consultation quiz</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>Detailed Report</t>
+          <t>Step 23 of 31</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>/report</t>
+          <t>/quiz</t>
         </is>
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>Long-form regimen explanation</t>
+          <t>Routine and Preferences: What type of cleanser do you prefer?</t>
         </is>
       </c>
       <c r="E66" s="15" t="inlineStr"/>
@@ -3017,92 +2941,84 @@
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>Reference pages</t>
+          <t>Consultation quiz</t>
         </is>
       </c>
       <c r="B67" s="16" t="inlineStr">
         <is>
-          <t>Detailed Report</t>
+          <t>Step 23 of 31</t>
         </is>
       </c>
       <c r="C67" s="16" t="inlineStr">
         <is>
-          <t>/report</t>
+          <t>/quiz</t>
         </is>
       </c>
       <c r="D67" s="16" t="inlineStr">
         <is>
-          <t>Regimen rationale per product</t>
-        </is>
-      </c>
-      <c r="E67" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Design and copy polish for this step</t>
+        </is>
+      </c>
+      <c r="E67" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
         </is>
       </c>
       <c r="F67" s="16" t="inlineStr">
         <is>
-          <t>P1 high</t>
+          <t>P2 medium</t>
         </is>
       </c>
       <c r="G67" s="16" t="inlineStr"/>
       <c r="H67" s="16" t="inlineStr"/>
       <c r="I67" s="16" t="inlineStr"/>
     </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="16" t="inlineStr">
-        <is>
-          <t>Reference pages</t>
-        </is>
-      </c>
-      <c r="B68" s="16" t="inlineStr">
-        <is>
-          <t>Detailed Report</t>
-        </is>
-      </c>
-      <c r="C68" s="16" t="inlineStr">
-        <is>
-          <t>/report</t>
-        </is>
-      </c>
-      <c r="D68" s="16" t="inlineStr">
-        <is>
-          <t>Print-friendly stylesheet</t>
-        </is>
-      </c>
-      <c r="E68" s="19" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F68" s="16" t="inlineStr">
-        <is>
-          <t>P2 medium</t>
-        </is>
-      </c>
-      <c r="G68" s="16" t="inlineStr"/>
-      <c r="H68" s="16" t="inlineStr"/>
-      <c r="I68" s="16" t="inlineStr"/>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="14" t="inlineStr">
+        <is>
+          <t>Consultation quiz</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="inlineStr">
+        <is>
+          <t>Step 24 of 31</t>
+        </is>
+      </c>
+      <c r="C68" s="15" t="inlineStr">
+        <is>
+          <t>/quiz</t>
+        </is>
+      </c>
+      <c r="D68" s="15" t="inlineStr">
+        <is>
+          <t>Routine and Preferences: Rank these skincare priorities from most to least important.</t>
+        </is>
+      </c>
+      <c r="E68" s="15" t="inlineStr"/>
+      <c r="F68" s="15" t="inlineStr"/>
+      <c r="G68" s="15" t="inlineStr"/>
+      <c r="H68" s="15" t="inlineStr"/>
+      <c r="I68" s="15" t="inlineStr"/>
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="16" t="inlineStr">
         <is>
-          <t>Reference pages</t>
+          <t>Consultation quiz</t>
         </is>
       </c>
       <c r="B69" s="16" t="inlineStr">
         <is>
-          <t>Detailed Report</t>
+          <t>Step 24 of 31</t>
         </is>
       </c>
       <c r="C69" s="16" t="inlineStr">
         <is>
-          <t>/report</t>
+          <t>/quiz</t>
         </is>
       </c>
       <c r="D69" s="16" t="inlineStr">
         <is>
-          <t>PDF export option</t>
+          <t>Design and copy polish for this step</t>
         </is>
       </c>
       <c r="E69" s="19" t="inlineStr">
@@ -3112,311 +3028,307 @@
       </c>
       <c r="F69" s="16" t="inlineStr">
         <is>
-          <t>P3 low</t>
+          <t>P2 medium</t>
         </is>
       </c>
       <c r="G69" s="16" t="inlineStr"/>
       <c r="H69" s="16" t="inlineStr"/>
       <c r="I69" s="16" t="inlineStr"/>
     </row>
-    <row r="70" ht="22" customHeight="1">
-      <c r="A70" s="13" t="inlineStr">
-        <is>
-          <t>ADMIN TOOLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="14" t="inlineStr">
-        <is>
-          <t>Admin tools</t>
-        </is>
-      </c>
-      <c r="B71" s="14" t="inlineStr">
-        <is>
-          <t>Fulfillment Studio</t>
-        </is>
-      </c>
-      <c r="C71" s="15" t="inlineStr">
-        <is>
-          <t>fulfillment-studio/ (separate Vite app)</t>
-        </is>
-      </c>
-      <c r="D71" s="15" t="inlineStr">
-        <is>
-          <t>Order list · GTIN assignment · label print · INCI XML export</t>
-        </is>
-      </c>
-      <c r="E71" s="15" t="inlineStr"/>
-      <c r="F71" s="15" t="inlineStr"/>
-      <c r="G71" s="15" t="inlineStr"/>
-      <c r="H71" s="15" t="inlineStr"/>
-      <c r="I71" s="15" t="inlineStr"/>
-    </row>
-    <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="16" t="inlineStr">
-        <is>
-          <t>Admin tools</t>
-        </is>
-      </c>
-      <c r="B72" s="16" t="inlineStr">
-        <is>
-          <t>Fulfillment Studio</t>
-        </is>
-      </c>
-      <c r="C72" s="16" t="inlineStr">
-        <is>
-          <t>fulfillment-studio/ (separate Vite app)</t>
-        </is>
-      </c>
-      <c r="D72" s="16" t="inlineStr">
-        <is>
-          <t>Admin auth gate (user_roles table)</t>
-        </is>
-      </c>
-      <c r="E72" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F72" s="16" t="inlineStr">
-        <is>
-          <t>P0 critical</t>
-        </is>
-      </c>
-      <c r="G72" s="16" t="inlineStr"/>
-      <c r="H72" s="16" t="inlineStr"/>
-      <c r="I72" s="16" t="inlineStr"/>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="14" t="inlineStr">
+        <is>
+          <t>Consultation quiz</t>
+        </is>
+      </c>
+      <c r="B70" s="14" t="inlineStr">
+        <is>
+          <t>Step 25 of 31</t>
+        </is>
+      </c>
+      <c r="C70" s="15" t="inlineStr">
+        <is>
+          <t>/quiz</t>
+        </is>
+      </c>
+      <c r="D70" s="15" t="inlineStr">
+        <is>
+          <t>Routine and Preferences: Which ingredient philosophies matter to you?</t>
+        </is>
+      </c>
+      <c r="E70" s="15" t="inlineStr"/>
+      <c r="F70" s="15" t="inlineStr"/>
+      <c r="G70" s="15" t="inlineStr"/>
+      <c r="H70" s="15" t="inlineStr"/>
+      <c r="I70" s="15" t="inlineStr"/>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="16" t="inlineStr">
+        <is>
+          <t>Consultation quiz</t>
+        </is>
+      </c>
+      <c r="B71" s="16" t="inlineStr">
+        <is>
+          <t>Step 25 of 31</t>
+        </is>
+      </c>
+      <c r="C71" s="16" t="inlineStr">
+        <is>
+          <t>/quiz</t>
+        </is>
+      </c>
+      <c r="D71" s="16" t="inlineStr">
+        <is>
+          <t>Design and copy polish for this step</t>
+        </is>
+      </c>
+      <c r="E71" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F71" s="16" t="inlineStr">
+        <is>
+          <t>P2 medium</t>
+        </is>
+      </c>
+      <c r="G71" s="16" t="inlineStr"/>
+      <c r="H71" s="16" t="inlineStr"/>
+      <c r="I71" s="16" t="inlineStr"/>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="14" t="inlineStr">
+        <is>
+          <t>Consultation quiz</t>
+        </is>
+      </c>
+      <c r="B72" s="14" t="inlineStr">
+        <is>
+          <t>Step 26 of 31</t>
+        </is>
+      </c>
+      <c r="C72" s="15" t="inlineStr">
+        <is>
+          <t>/quiz</t>
+        </is>
+      </c>
+      <c r="D72" s="15" t="inlineStr">
+        <is>
+          <t>Routine and Preferences: How adventurous are you with skincare ingredients?</t>
+        </is>
+      </c>
+      <c r="E72" s="15" t="inlineStr"/>
+      <c r="F72" s="15" t="inlineStr"/>
+      <c r="G72" s="15" t="inlineStr"/>
+      <c r="H72" s="15" t="inlineStr"/>
+      <c r="I72" s="15" t="inlineStr"/>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="A73" s="16" t="inlineStr">
         <is>
-          <t>Admin tools</t>
+          <t>Consultation quiz</t>
         </is>
       </c>
       <c r="B73" s="16" t="inlineStr">
         <is>
-          <t>Fulfillment Studio</t>
+          <t>Step 26 of 31</t>
         </is>
       </c>
       <c r="C73" s="16" t="inlineStr">
         <is>
-          <t>fulfillment-studio/ (separate Vite app)</t>
+          <t>/quiz</t>
         </is>
       </c>
       <c r="D73" s="16" t="inlineStr">
         <is>
-          <t>Order list with status filter</t>
-        </is>
-      </c>
-      <c r="E73" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Design and copy polish for this step</t>
+        </is>
+      </c>
+      <c r="E73" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
         </is>
       </c>
       <c r="F73" s="16" t="inlineStr">
         <is>
-          <t>P0 critical</t>
+          <t>P2 medium</t>
         </is>
       </c>
       <c r="G73" s="16" t="inlineStr"/>
       <c r="H73" s="16" t="inlineStr"/>
       <c r="I73" s="16" t="inlineStr"/>
     </row>
-    <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="16" t="inlineStr">
-        <is>
-          <t>Admin tools</t>
-        </is>
-      </c>
-      <c r="B74" s="16" t="inlineStr">
-        <is>
-          <t>Fulfillment Studio</t>
-        </is>
-      </c>
-      <c r="C74" s="16" t="inlineStr">
-        <is>
-          <t>fulfillment-studio/ (separate Vite app)</t>
-        </is>
-      </c>
-      <c r="D74" s="16" t="inlineStr">
-        <is>
-          <t>Fulfill order — assigns GTINs from pool</t>
-        </is>
-      </c>
-      <c r="E74" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F74" s="16" t="inlineStr">
-        <is>
-          <t>P0 critical</t>
-        </is>
-      </c>
-      <c r="G74" s="16" t="inlineStr"/>
-      <c r="H74" s="16" t="inlineStr"/>
-      <c r="I74" s="16" t="inlineStr"/>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="14" t="inlineStr">
+        <is>
+          <t>Consultation quiz</t>
+        </is>
+      </c>
+      <c r="B74" s="14" t="inlineStr">
+        <is>
+          <t>Step 27 of 31</t>
+        </is>
+      </c>
+      <c r="C74" s="15" t="inlineStr">
+        <is>
+          <t>/quiz</t>
+        </is>
+      </c>
+      <c r="D74" s="15" t="inlineStr">
+        <is>
+          <t>Routine and Preferences: Have you used retinol or retinoids before?</t>
+        </is>
+      </c>
+      <c r="E74" s="15" t="inlineStr"/>
+      <c r="F74" s="15" t="inlineStr"/>
+      <c r="G74" s="15" t="inlineStr"/>
+      <c r="H74" s="15" t="inlineStr"/>
+      <c r="I74" s="15" t="inlineStr"/>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="16" t="inlineStr">
         <is>
-          <t>Admin tools</t>
+          <t>Consultation quiz</t>
         </is>
       </c>
       <c r="B75" s="16" t="inlineStr">
         <is>
-          <t>Fulfillment Studio</t>
+          <t>Step 27 of 31</t>
         </is>
       </c>
       <c r="C75" s="16" t="inlineStr">
         <is>
-          <t>fulfillment-studio/ (separate Vite app)</t>
+          <t>/quiz</t>
         </is>
       </c>
       <c r="D75" s="16" t="inlineStr">
         <is>
-          <t>Print label per card + bulk print</t>
-        </is>
-      </c>
-      <c r="E75" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Design and copy polish for this step</t>
+        </is>
+      </c>
+      <c r="E75" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
         </is>
       </c>
       <c r="F75" s="16" t="inlineStr">
         <is>
-          <t>P0 critical</t>
+          <t>P2 medium</t>
         </is>
       </c>
       <c r="G75" s="16" t="inlineStr"/>
       <c r="H75" s="16" t="inlineStr"/>
       <c r="I75" s="16" t="inlineStr"/>
     </row>
-    <row r="76" ht="18" customHeight="1">
-      <c r="A76" s="16" t="inlineStr">
-        <is>
-          <t>Admin tools</t>
-        </is>
-      </c>
-      <c r="B76" s="16" t="inlineStr">
-        <is>
-          <t>Fulfillment Studio</t>
-        </is>
-      </c>
-      <c r="C76" s="16" t="inlineStr">
-        <is>
-          <t>fulfillment-studio/ (separate Vite app)</t>
-        </is>
-      </c>
-      <c r="D76" s="16" t="inlineStr">
-        <is>
-          <t>GS1 EAN-13 100% target barcode rendering</t>
-        </is>
-      </c>
-      <c r="E76" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F76" s="16" t="inlineStr">
-        <is>
-          <t>P1 high</t>
-        </is>
-      </c>
-      <c r="G76" s="16" t="inlineStr"/>
-      <c r="H76" s="16" t="inlineStr"/>
-      <c r="I76" s="16" t="inlineStr"/>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="14" t="inlineStr">
+        <is>
+          <t>Consultation quiz</t>
+        </is>
+      </c>
+      <c r="B76" s="14" t="inlineStr">
+        <is>
+          <t>Step 28 of 31</t>
+        </is>
+      </c>
+      <c r="C76" s="15" t="inlineStr">
+        <is>
+          <t>/quiz</t>
+        </is>
+      </c>
+      <c r="D76" s="15" t="inlineStr">
+        <is>
+          <t>Routine and Preferences: How much time do you spend on your skincare routine?</t>
+        </is>
+      </c>
+      <c r="E76" s="15" t="inlineStr"/>
+      <c r="F76" s="15" t="inlineStr"/>
+      <c r="G76" s="15" t="inlineStr"/>
+      <c r="H76" s="15" t="inlineStr"/>
+      <c r="I76" s="15" t="inlineStr"/>
     </row>
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="16" t="inlineStr">
         <is>
-          <t>Admin tools</t>
+          <t>Consultation quiz</t>
         </is>
       </c>
       <c r="B77" s="16" t="inlineStr">
         <is>
-          <t>Fulfillment Studio</t>
+          <t>Step 28 of 31</t>
         </is>
       </c>
       <c r="C77" s="16" t="inlineStr">
         <is>
-          <t>fulfillment-studio/ (separate Vite app)</t>
+          <t>/quiz</t>
         </is>
       </c>
       <c r="D77" s="16" t="inlineStr">
         <is>
-          <t>INCI Beauty XML download per product</t>
-        </is>
-      </c>
-      <c r="E77" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Design and copy polish for this step</t>
+        </is>
+      </c>
+      <c r="E77" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
         </is>
       </c>
       <c r="F77" s="16" t="inlineStr">
         <is>
-          <t>P1 high</t>
+          <t>P2 medium</t>
         </is>
       </c>
       <c r="G77" s="16" t="inlineStr"/>
       <c r="H77" s="16" t="inlineStr"/>
       <c r="I77" s="16" t="inlineStr"/>
     </row>
-    <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="16" t="inlineStr">
-        <is>
-          <t>Admin tools</t>
-        </is>
-      </c>
-      <c r="B78" s="16" t="inlineStr">
-        <is>
-          <t>Fulfillment Studio</t>
-        </is>
-      </c>
-      <c r="C78" s="16" t="inlineStr">
-        <is>
-          <t>fulfillment-studio/ (separate Vite app)</t>
-        </is>
-      </c>
-      <c r="D78" s="16" t="inlineStr">
-        <is>
-          <t>Order cancel + test-delete actions</t>
-        </is>
-      </c>
-      <c r="E78" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F78" s="16" t="inlineStr">
-        <is>
-          <t>P2 medium</t>
-        </is>
-      </c>
-      <c r="G78" s="16" t="inlineStr"/>
-      <c r="H78" s="16" t="inlineStr"/>
-      <c r="I78" s="16" t="inlineStr"/>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="14" t="inlineStr">
+        <is>
+          <t>Consultation quiz</t>
+        </is>
+      </c>
+      <c r="B78" s="14" t="inlineStr">
+        <is>
+          <t>Step 29 of 31</t>
+        </is>
+      </c>
+      <c r="C78" s="15" t="inlineStr">
+        <is>
+          <t>/quiz</t>
+        </is>
+      </c>
+      <c r="D78" s="15" t="inlineStr">
+        <is>
+          <t>Routine and Preferences: Is there anything you would like to avoid in your products?</t>
+        </is>
+      </c>
+      <c r="E78" s="15" t="inlineStr"/>
+      <c r="F78" s="15" t="inlineStr"/>
+      <c r="G78" s="15" t="inlineStr"/>
+      <c r="H78" s="15" t="inlineStr"/>
+      <c r="I78" s="15" t="inlineStr"/>
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="A79" s="16" t="inlineStr">
         <is>
-          <t>Admin tools</t>
+          <t>Consultation quiz</t>
         </is>
       </c>
       <c r="B79" s="16" t="inlineStr">
         <is>
-          <t>Fulfillment Studio</t>
+          <t>Step 29 of 31</t>
         </is>
       </c>
       <c r="C79" s="16" t="inlineStr">
         <is>
-          <t>fulfillment-studio/ (separate Vite app)</t>
+          <t>/quiz</t>
         </is>
       </c>
       <c r="D79" s="16" t="inlineStr">
         <is>
-          <t>Direx 'Create shipment' button per order</t>
+          <t>Design and copy polish for this step</t>
         </is>
       </c>
       <c r="E79" s="19" t="inlineStr">
@@ -3426,67 +3338,59 @@
       </c>
       <c r="F79" s="16" t="inlineStr">
         <is>
-          <t>P0 critical</t>
+          <t>P2 medium</t>
         </is>
       </c>
       <c r="G79" s="16" t="inlineStr"/>
       <c r="H79" s="16" t="inlineStr"/>
       <c r="I79" s="16" t="inlineStr"/>
     </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="16" t="inlineStr">
-        <is>
-          <t>Admin tools</t>
-        </is>
-      </c>
-      <c r="B80" s="16" t="inlineStr">
-        <is>
-          <t>Fulfillment Studio</t>
-        </is>
-      </c>
-      <c r="C80" s="16" t="inlineStr">
-        <is>
-          <t>fulfillment-studio/ (separate Vite app)</t>
-        </is>
-      </c>
-      <c r="D80" s="16" t="inlineStr">
-        <is>
-          <t>Direx 'Close manifest + schedule pickup' batch action</t>
-        </is>
-      </c>
-      <c r="E80" s="19" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F80" s="16" t="inlineStr">
-        <is>
-          <t>P0 critical</t>
-        </is>
-      </c>
-      <c r="G80" s="16" t="inlineStr"/>
-      <c r="H80" s="16" t="inlineStr"/>
-      <c r="I80" s="16" t="inlineStr"/>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="14" t="inlineStr">
+        <is>
+          <t>Consultation quiz</t>
+        </is>
+      </c>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>Step 30 of 31</t>
+        </is>
+      </c>
+      <c r="C80" s="15" t="inlineStr">
+        <is>
+          <t>/quiz</t>
+        </is>
+      </c>
+      <c r="D80" s="15" t="inlineStr">
+        <is>
+          <t>Routine and Preferences: Do you have any known skin allergies?</t>
+        </is>
+      </c>
+      <c r="E80" s="15" t="inlineStr"/>
+      <c r="F80" s="15" t="inlineStr"/>
+      <c r="G80" s="15" t="inlineStr"/>
+      <c r="H80" s="15" t="inlineStr"/>
+      <c r="I80" s="15" t="inlineStr"/>
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="A81" s="16" t="inlineStr">
         <is>
-          <t>Admin tools</t>
+          <t>Consultation quiz</t>
         </is>
       </c>
       <c r="B81" s="16" t="inlineStr">
         <is>
-          <t>Fulfillment Studio</t>
+          <t>Step 30 of 31</t>
         </is>
       </c>
       <c r="C81" s="16" t="inlineStr">
         <is>
-          <t>fulfillment-studio/ (separate Vite app)</t>
+          <t>/quiz</t>
         </is>
       </c>
       <c r="D81" s="16" t="inlineStr">
         <is>
-          <t>Auto-deploy to Vercel (currently manual)</t>
+          <t>Design and copy polish for this step</t>
         </is>
       </c>
       <c r="E81" s="19" t="inlineStr">
@@ -3506,22 +3410,22 @@
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>Admin tools</t>
+          <t>Consultation quiz</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>Barcode Studio</t>
+          <t>Step 31 of 31</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>barcode-studio/ (separate Vite app)</t>
+          <t>/quiz</t>
         </is>
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
-          <t>GTIN issuance + Excel import</t>
+          <t>Routine and Preferences: Would you like fragrance in your products?</t>
         </is>
       </c>
       <c r="E82" s="15" t="inlineStr"/>
@@ -3533,127 +3437,91 @@
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="16" t="inlineStr">
         <is>
-          <t>Admin tools</t>
+          <t>Consultation quiz</t>
         </is>
       </c>
       <c r="B83" s="16" t="inlineStr">
         <is>
-          <t>Barcode Studio</t>
+          <t>Step 31 of 31</t>
         </is>
       </c>
       <c r="C83" s="16" t="inlineStr">
         <is>
-          <t>barcode-studio/ (separate Vite app)</t>
+          <t>/quiz</t>
         </is>
       </c>
       <c r="D83" s="16" t="inlineStr">
         <is>
-          <t>GTIN issuer management</t>
-        </is>
-      </c>
-      <c r="E83" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Design and copy polish for this step</t>
+        </is>
+      </c>
+      <c r="E83" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
         </is>
       </c>
       <c r="F83" s="16" t="inlineStr">
         <is>
-          <t>P0 critical</t>
+          <t>P2 medium</t>
         </is>
       </c>
       <c r="G83" s="16" t="inlineStr"/>
       <c r="H83" s="16" t="inlineStr"/>
       <c r="I83" s="16" t="inlineStr"/>
     </row>
-    <row r="84" ht="18" customHeight="1">
-      <c r="A84" s="16" t="inlineStr">
-        <is>
-          <t>Admin tools</t>
-        </is>
-      </c>
-      <c r="B84" s="16" t="inlineStr">
-        <is>
-          <t>Barcode Studio</t>
-        </is>
-      </c>
-      <c r="C84" s="16" t="inlineStr">
-        <is>
-          <t>barcode-studio/ (separate Vite app)</t>
-        </is>
-      </c>
-      <c r="D84" s="16" t="inlineStr">
-        <is>
-          <t>Prefix-based GTIN generation (deprecated)</t>
-        </is>
-      </c>
-      <c r="E84" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F84" s="16" t="inlineStr">
-        <is>
-          <t>P2 medium</t>
-        </is>
-      </c>
-      <c r="G84" s="16" t="inlineStr"/>
-      <c r="H84" s="16" t="inlineStr"/>
-      <c r="I84" s="16" t="inlineStr"/>
-    </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="A85" s="16" t="inlineStr">
-        <is>
-          <t>Admin tools</t>
-        </is>
-      </c>
-      <c r="B85" s="16" t="inlineStr">
-        <is>
-          <t>Barcode Studio</t>
-        </is>
-      </c>
-      <c r="C85" s="16" t="inlineStr">
-        <is>
-          <t>barcode-studio/ (separate Vite app)</t>
-        </is>
-      </c>
-      <c r="D85" s="16" t="inlineStr">
-        <is>
-          <t>Excel import for GTIN pool</t>
-        </is>
-      </c>
-      <c r="E85" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F85" s="16" t="inlineStr">
-        <is>
-          <t>P0 critical</t>
-        </is>
-      </c>
-      <c r="G85" s="16" t="inlineStr"/>
-      <c r="H85" s="16" t="inlineStr"/>
-      <c r="I85" s="16" t="inlineStr"/>
+    <row r="84" ht="22" customHeight="1">
+      <c r="A84" s="13" t="inlineStr">
+        <is>
+          <t>AFTER THE QUIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="14" t="inlineStr">
+        <is>
+          <t>After the quiz</t>
+        </is>
+      </c>
+      <c r="B85" s="14" t="inlineStr">
+        <is>
+          <t>Results</t>
+        </is>
+      </c>
+      <c r="C85" s="15" t="inlineStr">
+        <is>
+          <t>/results</t>
+        </is>
+      </c>
+      <c r="D85" s="15" t="inlineStr">
+        <is>
+          <t>The page that shows the customer their personalised products and the regimen we recommend</t>
+        </is>
+      </c>
+      <c r="E85" s="15" t="inlineStr"/>
+      <c r="F85" s="15" t="inlineStr"/>
+      <c r="G85" s="15" t="inlineStr"/>
+      <c r="H85" s="15" t="inlineStr"/>
+      <c r="I85" s="15" t="inlineStr"/>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="A86" s="16" t="inlineStr">
         <is>
-          <t>Admin tools</t>
+          <t>After the quiz</t>
         </is>
       </c>
       <c r="B86" s="16" t="inlineStr">
         <is>
-          <t>Barcode Studio</t>
+          <t>Results</t>
         </is>
       </c>
       <c r="C86" s="16" t="inlineStr">
         <is>
-          <t>barcode-studio/ (separate Vite app)</t>
+          <t>/results</t>
         </is>
       </c>
       <c r="D86" s="16" t="inlineStr">
         <is>
-          <t>Live preview at GS1 spec scale</t>
+          <t>Trust line near the top</t>
         </is>
       </c>
       <c r="E86" s="17" t="inlineStr">
@@ -3663,66 +3531,102 @@
       </c>
       <c r="F86" s="16" t="inlineStr">
         <is>
-          <t>P1 high</t>
+          <t>P2 medium</t>
         </is>
       </c>
       <c r="G86" s="16" t="inlineStr"/>
       <c r="H86" s="16" t="inlineStr"/>
       <c r="I86" s="16" t="inlineStr"/>
     </row>
-    <row r="87" ht="22" customHeight="1">
-      <c r="A87" s="13" t="inlineStr">
-        <is>
-          <t>INTEGRATIONS</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="14" t="inlineStr">
-        <is>
-          <t>Integrations</t>
-        </is>
-      </c>
-      <c r="B88" s="14" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="C88" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D88" s="15" t="inlineStr">
-        <is>
-          <t>Payment + subscription billing</t>
-        </is>
-      </c>
-      <c r="E88" s="15" t="inlineStr"/>
-      <c r="F88" s="15" t="inlineStr"/>
-      <c r="G88" s="15" t="inlineStr"/>
-      <c r="H88" s="15" t="inlineStr"/>
-      <c r="I88" s="15" t="inlineStr"/>
+    <row r="87" ht="18" customHeight="1">
+      <c r="A87" s="16" t="inlineStr">
+        <is>
+          <t>After the quiz</t>
+        </is>
+      </c>
+      <c r="B87" s="16" t="inlineStr">
+        <is>
+          <t>Results</t>
+        </is>
+      </c>
+      <c r="C87" s="16" t="inlineStr">
+        <is>
+          <t>/results</t>
+        </is>
+      </c>
+      <c r="D87" s="16" t="inlineStr">
+        <is>
+          <t>Ingredient cards expand when clicked to show details</t>
+        </is>
+      </c>
+      <c r="E87" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F87" s="16" t="inlineStr">
+        <is>
+          <t>P1 high</t>
+        </is>
+      </c>
+      <c r="G87" s="16" t="inlineStr"/>
+      <c r="H87" s="16" t="inlineStr"/>
+      <c r="I87" s="16" t="inlineStr"/>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="A88" s="16" t="inlineStr">
+        <is>
+          <t>After the quiz</t>
+        </is>
+      </c>
+      <c r="B88" s="16" t="inlineStr">
+        <is>
+          <t>Results</t>
+        </is>
+      </c>
+      <c r="C88" s="16" t="inlineStr">
+        <is>
+          <t>/results</t>
+        </is>
+      </c>
+      <c r="D88" s="16" t="inlineStr">
+        <is>
+          <t>3D botanical scene shows alongside the recommendation</t>
+        </is>
+      </c>
+      <c r="E88" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F88" s="16" t="inlineStr">
+        <is>
+          <t>P2 medium</t>
+        </is>
+      </c>
+      <c r="G88" s="16" t="inlineStr"/>
+      <c r="H88" s="16" t="inlineStr"/>
+      <c r="I88" s="16" t="inlineStr"/>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="A89" s="16" t="inlineStr">
         <is>
-          <t>Integrations</t>
+          <t>After the quiz</t>
         </is>
       </c>
       <c r="B89" s="16" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Results</t>
         </is>
       </c>
       <c r="C89" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/results</t>
         </is>
       </c>
       <c r="D89" s="16" t="inlineStr">
         <is>
-          <t>Checkout session creation API route</t>
+          <t>Subscription plan picker is side by side</t>
         </is>
       </c>
       <c r="E89" s="17" t="inlineStr">
@@ -3732,7 +3636,7 @@
       </c>
       <c r="F89" s="16" t="inlineStr">
         <is>
-          <t>P0 critical</t>
+          <t>P1 high</t>
         </is>
       </c>
       <c r="G89" s="16" t="inlineStr"/>
@@ -3742,32 +3646,32 @@
     <row r="90" ht="18" customHeight="1">
       <c r="A90" s="16" t="inlineStr">
         <is>
-          <t>Integrations</t>
+          <t>After the quiz</t>
         </is>
       </c>
       <c r="B90" s="16" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Results</t>
         </is>
       </c>
       <c r="C90" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/results</t>
         </is>
       </c>
       <c r="D90" s="16" t="inlineStr">
         <is>
-          <t>Webhook handler — auto-fulfill on success</t>
-        </is>
-      </c>
-      <c r="E90" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Mobile usability check</t>
+        </is>
+      </c>
+      <c r="E90" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
         </is>
       </c>
       <c r="F90" s="16" t="inlineStr">
         <is>
-          <t>P0 critical</t>
+          <t>P1 high</t>
         </is>
       </c>
       <c r="G90" s="16" t="inlineStr"/>
@@ -3777,101 +3681,89 @@
     <row r="91" ht="18" customHeight="1">
       <c r="A91" s="16" t="inlineStr">
         <is>
-          <t>Integrations</t>
+          <t>After the quiz</t>
         </is>
       </c>
       <c r="B91" s="16" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Results</t>
         </is>
       </c>
       <c r="C91" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/results</t>
         </is>
       </c>
       <c r="D91" s="16" t="inlineStr">
         <is>
-          <t>Webhook 500 fixes (subtotal NOT NULL, service-role admin)</t>
-        </is>
-      </c>
-      <c r="E91" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Empty state and error state designs</t>
+        </is>
+      </c>
+      <c r="E91" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
         </is>
       </c>
       <c r="F91" s="16" t="inlineStr">
         <is>
-          <t>P0 critical</t>
+          <t>P2 medium</t>
         </is>
       </c>
       <c r="G91" s="16" t="inlineStr"/>
       <c r="H91" s="16" t="inlineStr"/>
       <c r="I91" s="16" t="inlineStr"/>
     </row>
-    <row r="92" ht="18" customHeight="1">
-      <c r="A92" s="16" t="inlineStr">
-        <is>
-          <t>Integrations</t>
-        </is>
-      </c>
-      <c r="B92" s="16" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="C92" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D92" s="16" t="inlineStr">
-        <is>
-          <t>Subscription billing cycle handling</t>
-        </is>
-      </c>
-      <c r="E92" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F92" s="16" t="inlineStr">
-        <is>
-          <t>P0 critical</t>
-        </is>
-      </c>
-      <c r="G92" s="16" t="inlineStr"/>
-      <c r="H92" s="16" t="inlineStr">
-        <is>
-          <t>Bi-monthly + annual plans</t>
-        </is>
-      </c>
-      <c r="I92" s="16" t="inlineStr"/>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="14" t="inlineStr">
+        <is>
+          <t>After the quiz</t>
+        </is>
+      </c>
+      <c r="B92" s="14" t="inlineStr">
+        <is>
+          <t>Skin Analysis</t>
+        </is>
+      </c>
+      <c r="C92" s="15" t="inlineStr">
+        <is>
+          <t>/analysis</t>
+        </is>
+      </c>
+      <c r="D92" s="15" t="inlineStr">
+        <is>
+          <t>A breakdown of the customer's skin profile from their quiz answers</t>
+        </is>
+      </c>
+      <c r="E92" s="15" t="inlineStr"/>
+      <c r="F92" s="15" t="inlineStr"/>
+      <c r="G92" s="15" t="inlineStr"/>
+      <c r="H92" s="15" t="inlineStr"/>
+      <c r="I92" s="15" t="inlineStr"/>
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="A93" s="16" t="inlineStr">
         <is>
-          <t>Integrations</t>
+          <t>After the quiz</t>
         </is>
       </c>
       <c r="B93" s="16" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Skin Analysis</t>
         </is>
       </c>
       <c r="C93" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/analysis</t>
         </is>
       </c>
       <c r="D93" s="16" t="inlineStr">
         <is>
-          <t>Failed payment retry policy</t>
-        </is>
-      </c>
-      <c r="E93" s="19" t="inlineStr">
-        <is>
-          <t>Todo</t>
+          <t>Show the profile information clearly</t>
+        </is>
+      </c>
+      <c r="E93" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="F93" s="16" t="inlineStr">
@@ -3883,122 +3775,122 @@
       <c r="H93" s="16" t="inlineStr"/>
       <c r="I93" s="16" t="inlineStr"/>
     </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="14" t="inlineStr">
-        <is>
-          <t>Integrations</t>
-        </is>
-      </c>
-      <c r="B94" s="14" t="inlineStr">
-        <is>
-          <t>Supabase</t>
-        </is>
-      </c>
-      <c r="C94" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D94" s="15" t="inlineStr">
-        <is>
-          <t>Database + auth + storage</t>
-        </is>
-      </c>
-      <c r="E94" s="15" t="inlineStr"/>
-      <c r="F94" s="15" t="inlineStr"/>
-      <c r="G94" s="15" t="inlineStr"/>
-      <c r="H94" s="15" t="inlineStr"/>
-      <c r="I94" s="15" t="inlineStr"/>
+    <row r="94" ht="18" customHeight="1">
+      <c r="A94" s="16" t="inlineStr">
+        <is>
+          <t>After the quiz</t>
+        </is>
+      </c>
+      <c r="B94" s="16" t="inlineStr">
+        <is>
+          <t>Skin Analysis</t>
+        </is>
+      </c>
+      <c r="C94" s="16" t="inlineStr">
+        <is>
+          <t>/analysis</t>
+        </is>
+      </c>
+      <c r="D94" s="16" t="inlineStr">
+        <is>
+          <t>Visual breakdown of concerns and priorities</t>
+        </is>
+      </c>
+      <c r="E94" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F94" s="16" t="inlineStr">
+        <is>
+          <t>P1 high</t>
+        </is>
+      </c>
+      <c r="G94" s="16" t="inlineStr"/>
+      <c r="H94" s="16" t="inlineStr"/>
+      <c r="I94" s="16" t="inlineStr"/>
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="A95" s="16" t="inlineStr">
         <is>
-          <t>Integrations</t>
+          <t>After the quiz</t>
         </is>
       </c>
       <c r="B95" s="16" t="inlineStr">
         <is>
-          <t>Supabase</t>
+          <t>Skin Analysis</t>
         </is>
       </c>
       <c r="C95" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/analysis</t>
         </is>
       </c>
       <c r="D95" s="16" t="inlineStr">
         <is>
-          <t>products + ingredients tables</t>
-        </is>
-      </c>
-      <c r="E95" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Compare with their previous quiz if they retake it</t>
+        </is>
+      </c>
+      <c r="E95" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
         </is>
       </c>
       <c r="F95" s="16" t="inlineStr">
         <is>
-          <t>P0 critical</t>
+          <t>P3 low</t>
         </is>
       </c>
       <c r="G95" s="16" t="inlineStr"/>
       <c r="H95" s="16" t="inlineStr"/>
       <c r="I95" s="16" t="inlineStr"/>
     </row>
-    <row r="96" ht="18" customHeight="1">
-      <c r="A96" s="16" t="inlineStr">
-        <is>
-          <t>Integrations</t>
-        </is>
-      </c>
-      <c r="B96" s="16" t="inlineStr">
-        <is>
-          <t>Supabase</t>
-        </is>
-      </c>
-      <c r="C96" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D96" s="16" t="inlineStr">
-        <is>
-          <t>customer_orders + quiz_results tables</t>
-        </is>
-      </c>
-      <c r="E96" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F96" s="16" t="inlineStr">
-        <is>
-          <t>P0 critical</t>
-        </is>
-      </c>
-      <c r="G96" s="16" t="inlineStr"/>
-      <c r="H96" s="16" t="inlineStr"/>
-      <c r="I96" s="16" t="inlineStr"/>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="14" t="inlineStr">
+        <is>
+          <t>After the quiz</t>
+        </is>
+      </c>
+      <c r="B96" s="14" t="inlineStr">
+        <is>
+          <t>Detailed Report</t>
+        </is>
+      </c>
+      <c r="C96" s="15" t="inlineStr">
+        <is>
+          <t>/report</t>
+        </is>
+      </c>
+      <c r="D96" s="15" t="inlineStr">
+        <is>
+          <t>A longer page that explains the customer's regimen in depth</t>
+        </is>
+      </c>
+      <c r="E96" s="15" t="inlineStr"/>
+      <c r="F96" s="15" t="inlineStr"/>
+      <c r="G96" s="15" t="inlineStr"/>
+      <c r="H96" s="15" t="inlineStr"/>
+      <c r="I96" s="15" t="inlineStr"/>
     </row>
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="16" t="inlineStr">
         <is>
-          <t>Integrations</t>
+          <t>After the quiz</t>
         </is>
       </c>
       <c r="B97" s="16" t="inlineStr">
         <is>
-          <t>Supabase</t>
+          <t>Detailed Report</t>
         </is>
       </c>
       <c r="C97" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/report</t>
         </is>
       </c>
       <c r="D97" s="16" t="inlineStr">
         <is>
-          <t>gtin_pool + gtin_product_records tables</t>
+          <t>Explain the rationale behind each product</t>
         </is>
       </c>
       <c r="E97" s="17" t="inlineStr">
@@ -4008,7 +3900,7 @@
       </c>
       <c r="F97" s="16" t="inlineStr">
         <is>
-          <t>P0 critical</t>
+          <t>P1 high</t>
         </is>
       </c>
       <c r="G97" s="16" t="inlineStr"/>
@@ -4018,32 +3910,32 @@
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="16" t="inlineStr">
         <is>
-          <t>Integrations</t>
+          <t>After the quiz</t>
         </is>
       </c>
       <c r="B98" s="16" t="inlineStr">
         <is>
-          <t>Supabase</t>
+          <t>Detailed Report</t>
         </is>
       </c>
       <c r="C98" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/report</t>
         </is>
       </c>
       <c r="D98" s="16" t="inlineStr">
         <is>
-          <t>user_roles table for admin gating</t>
-        </is>
-      </c>
-      <c r="E98" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Make it look right when printed</t>
+        </is>
+      </c>
+      <c r="E98" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
         </is>
       </c>
       <c r="F98" s="16" t="inlineStr">
         <is>
-          <t>P0 critical</t>
+          <t>P2 medium</t>
         </is>
       </c>
       <c r="G98" s="16" t="inlineStr"/>
@@ -4053,96 +3945,64 @@
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="16" t="inlineStr">
         <is>
-          <t>Integrations</t>
+          <t>After the quiz</t>
         </is>
       </c>
       <c r="B99" s="16" t="inlineStr">
         <is>
-          <t>Supabase</t>
+          <t>Detailed Report</t>
         </is>
       </c>
       <c r="C99" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/report</t>
         </is>
       </c>
       <c r="D99" s="16" t="inlineStr">
         <is>
-          <t>Storage bucket 'products' (public)</t>
-        </is>
-      </c>
-      <c r="E99" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Add a download as PDF option</t>
+        </is>
+      </c>
+      <c r="E99" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
         </is>
       </c>
       <c r="F99" s="16" t="inlineStr">
         <is>
-          <t>P1 high</t>
+          <t>P3 low</t>
         </is>
       </c>
       <c r="G99" s="16" t="inlineStr"/>
-      <c r="H99" s="16" t="inlineStr">
-        <is>
-          <t>Holds placeholder rose bulgare jpg</t>
-        </is>
-      </c>
+      <c r="H99" s="16" t="inlineStr"/>
       <c r="I99" s="16" t="inlineStr"/>
     </row>
-    <row r="100" ht="18" customHeight="1">
-      <c r="A100" s="16" t="inlineStr">
-        <is>
-          <t>Integrations</t>
-        </is>
-      </c>
-      <c r="B100" s="16" t="inlineStr">
-        <is>
-          <t>Supabase</t>
-        </is>
-      </c>
-      <c r="C100" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D100" s="16" t="inlineStr">
-        <is>
-          <t>Per-product photo upload pipeline (1 jpg per GTIN)</t>
-        </is>
-      </c>
-      <c r="E100" s="19" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F100" s="16" t="inlineStr">
-        <is>
-          <t>P1 high</t>
-        </is>
-      </c>
-      <c r="G100" s="16" t="inlineStr"/>
-      <c r="H100" s="16" t="inlineStr"/>
-      <c r="I100" s="16" t="inlineStr"/>
+    <row r="100" ht="22" customHeight="1">
+      <c r="A100" s="13" t="inlineStr">
+        <is>
+          <t>CART AND CHECKOUT</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="20" customHeight="1">
       <c r="A101" s="14" t="inlineStr">
         <is>
-          <t>Integrations</t>
+          <t>Cart and checkout</t>
         </is>
       </c>
       <c r="B101" s="14" t="inlineStr">
         <is>
-          <t>INCI Beauty XML</t>
+          <t>Cart</t>
         </is>
       </c>
       <c r="C101" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/cart</t>
         </is>
       </c>
       <c r="D101" s="15" t="inlineStr">
         <is>
-          <t>Per-product XML export for inci.com import</t>
+          <t>The customer's bag and where they pick their subscription plan</t>
         </is>
       </c>
       <c r="E101" s="15" t="inlineStr"/>
@@ -4154,22 +4014,22 @@
     <row r="102" ht="18" customHeight="1">
       <c r="A102" s="16" t="inlineStr">
         <is>
-          <t>Integrations</t>
+          <t>Cart and checkout</t>
         </is>
       </c>
       <c r="B102" s="16" t="inlineStr">
         <is>
-          <t>INCI Beauty XML</t>
+          <t>Cart</t>
         </is>
       </c>
       <c r="C102" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/cart</t>
         </is>
       </c>
       <c r="D102" s="16" t="inlineStr">
         <is>
-          <t>XML generator (schema-compliant)</t>
+          <t>Three subscription plan cards side by side</t>
         </is>
       </c>
       <c r="E102" s="17" t="inlineStr">
@@ -4179,7 +4039,7 @@
       </c>
       <c r="F102" s="16" t="inlineStr">
         <is>
-          <t>P1 high</t>
+          <t>P0 critical</t>
         </is>
       </c>
       <c r="G102" s="16" t="inlineStr"/>
@@ -4189,22 +4049,22 @@
     <row r="103" ht="18" customHeight="1">
       <c r="A103" s="16" t="inlineStr">
         <is>
-          <t>Integrations</t>
+          <t>Cart and checkout</t>
         </is>
       </c>
       <c r="B103" s="16" t="inlineStr">
         <is>
-          <t>INCI Beauty XML</t>
+          <t>Cart</t>
         </is>
       </c>
       <c r="C103" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/cart</t>
         </is>
       </c>
       <c r="D103" s="16" t="inlineStr">
         <is>
-          <t>Download button in fulfillment studio</t>
+          <t>Bi-monthly plan selected by default with 'Most Popular' tag</t>
         </is>
       </c>
       <c r="E103" s="17" t="inlineStr">
@@ -4214,7 +4074,7 @@
       </c>
       <c r="F103" s="16" t="inlineStr">
         <is>
-          <t>P1 high</t>
+          <t>P0 critical</t>
         </is>
       </c>
       <c r="G103" s="16" t="inlineStr"/>
@@ -4224,22 +4084,22 @@
     <row r="104" ht="18" customHeight="1">
       <c r="A104" s="16" t="inlineStr">
         <is>
-          <t>Integrations</t>
+          <t>Cart and checkout</t>
         </is>
       </c>
       <c r="B104" s="16" t="inlineStr">
         <is>
-          <t>INCI Beauty XML</t>
+          <t>Cart</t>
         </is>
       </c>
       <c r="C104" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/cart</t>
         </is>
       </c>
       <c r="D104" s="16" t="inlineStr">
         <is>
-          <t>Placeholder image hosted on Supabase Storage</t>
+          <t>Reassurance copy inside each plan card</t>
         </is>
       </c>
       <c r="E104" s="17" t="inlineStr">
@@ -4259,27 +4119,27 @@
     <row r="105" ht="18" customHeight="1">
       <c r="A105" s="16" t="inlineStr">
         <is>
-          <t>Integrations</t>
+          <t>Cart and checkout</t>
         </is>
       </c>
       <c r="B105" s="16" t="inlineStr">
         <is>
-          <t>INCI Beauty XML</t>
+          <t>Cart</t>
         </is>
       </c>
       <c r="C105" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/cart</t>
         </is>
       </c>
       <c r="D105" s="16" t="inlineStr">
         <is>
-          <t>Per-product image URL derivation by GTIN</t>
-        </is>
-      </c>
-      <c r="E105" s="19" t="inlineStr">
-        <is>
-          <t>Todo</t>
+          <t>Trust strip under the checkout button</t>
+        </is>
+      </c>
+      <c r="E105" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="F105" s="16" t="inlineStr">
@@ -4294,159 +4154,159 @@
     <row r="106" ht="18" customHeight="1">
       <c r="A106" s="16" t="inlineStr">
         <is>
-          <t>Integrations</t>
+          <t>Cart and checkout</t>
         </is>
       </c>
       <c r="B106" s="16" t="inlineStr">
         <is>
-          <t>INCI Beauty XML</t>
+          <t>Cart</t>
         </is>
       </c>
       <c r="C106" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/cart</t>
         </is>
       </c>
       <c r="D106" s="16" t="inlineStr">
         <is>
-          <t>End-to-end import test on INCI Beauty platform</t>
-        </is>
-      </c>
-      <c r="E106" s="19" t="inlineStr">
-        <is>
-          <t>Todo</t>
+          <t>Card colours follow the palette</t>
+        </is>
+      </c>
+      <c r="E106" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="F106" s="16" t="inlineStr">
         <is>
-          <t>P0 critical</t>
+          <t>P2 medium</t>
         </is>
       </c>
       <c r="G106" s="16" t="inlineStr"/>
       <c r="H106" s="16" t="inlineStr"/>
       <c r="I106" s="16" t="inlineStr"/>
     </row>
-    <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="14" t="inlineStr">
-        <is>
-          <t>Integrations</t>
-        </is>
-      </c>
-      <c r="B107" s="14" t="inlineStr">
-        <is>
-          <t>Direx Courier</t>
-        </is>
-      </c>
-      <c r="C107" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D107" s="15" t="inlineStr">
-        <is>
-          <t>Bulgarian parcel-delivery API integration</t>
-        </is>
-      </c>
-      <c r="E107" s="15" t="inlineStr"/>
-      <c r="F107" s="15" t="inlineStr"/>
-      <c r="G107" s="15" t="inlineStr"/>
-      <c r="H107" s="15" t="inlineStr"/>
-      <c r="I107" s="15" t="inlineStr"/>
+    <row r="107" ht="18" customHeight="1">
+      <c r="A107" s="16" t="inlineStr">
+        <is>
+          <t>Cart and checkout</t>
+        </is>
+      </c>
+      <c r="B107" s="16" t="inlineStr">
+        <is>
+          <t>Cart</t>
+        </is>
+      </c>
+      <c r="C107" s="16" t="inlineStr">
+        <is>
+          <t>/cart</t>
+        </is>
+      </c>
+      <c r="D107" s="16" t="inlineStr">
+        <is>
+          <t>Empty cart screen invites them to start the quiz</t>
+        </is>
+      </c>
+      <c r="E107" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F107" s="16" t="inlineStr">
+        <is>
+          <t>P2 medium</t>
+        </is>
+      </c>
+      <c r="G107" s="16" t="inlineStr"/>
+      <c r="H107" s="16" t="inlineStr"/>
+      <c r="I107" s="16" t="inlineStr"/>
     </row>
     <row r="108" ht="18" customHeight="1">
       <c r="A108" s="16" t="inlineStr">
         <is>
-          <t>Integrations</t>
+          <t>Cart and checkout</t>
         </is>
       </c>
       <c r="B108" s="16" t="inlineStr">
         <is>
-          <t>Direx Courier</t>
+          <t>Cart</t>
         </is>
       </c>
       <c r="C108" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/cart</t>
         </is>
       </c>
       <c r="D108" s="16" t="inlineStr">
         <is>
-          <t>Phase 0 — Token plumbing + env vars + sender registration</t>
-        </is>
-      </c>
-      <c r="E108" s="19" t="inlineStr">
-        <is>
-          <t>Todo</t>
+          <t>Stacks to one column on mobile</t>
+        </is>
+      </c>
+      <c r="E108" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="F108" s="16" t="inlineStr">
         <is>
-          <t>P0 critical</t>
+          <t>P1 high</t>
         </is>
       </c>
       <c r="G108" s="16" t="inlineStr"/>
       <c r="H108" s="16" t="inlineStr"/>
       <c r="I108" s="16" t="inlineStr"/>
     </row>
-    <row r="109" ht="18" customHeight="1">
-      <c r="A109" s="16" t="inlineStr">
-        <is>
-          <t>Integrations</t>
-        </is>
-      </c>
-      <c r="B109" s="16" t="inlineStr">
-        <is>
-          <t>Direx Courier</t>
-        </is>
-      </c>
-      <c r="C109" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D109" s="16" t="inlineStr">
-        <is>
-          <t>Phase 1 — Shipment create button + label fetch</t>
-        </is>
-      </c>
-      <c r="E109" s="19" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F109" s="16" t="inlineStr">
-        <is>
-          <t>P0 critical</t>
-        </is>
-      </c>
-      <c r="G109" s="16" t="inlineStr"/>
-      <c r="H109" s="16" t="inlineStr"/>
-      <c r="I109" s="16" t="inlineStr"/>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="14" t="inlineStr">
+        <is>
+          <t>Cart and checkout</t>
+        </is>
+      </c>
+      <c r="B109" s="14" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C109" s="15" t="inlineStr">
+        <is>
+          <t>/checkout</t>
+        </is>
+      </c>
+      <c r="D109" s="15" t="inlineStr">
+        <is>
+          <t>The handoff to Stripe where the customer enters card details</t>
+        </is>
+      </c>
+      <c r="E109" s="15" t="inlineStr"/>
+      <c r="F109" s="15" t="inlineStr"/>
+      <c r="G109" s="15" t="inlineStr"/>
+      <c r="H109" s="15" t="inlineStr"/>
+      <c r="I109" s="15" t="inlineStr"/>
     </row>
     <row r="110" ht="18" customHeight="1">
       <c r="A110" s="16" t="inlineStr">
         <is>
-          <t>Integrations</t>
+          <t>Cart and checkout</t>
         </is>
       </c>
       <c r="B110" s="16" t="inlineStr">
         <is>
-          <t>Direx Courier</t>
+          <t>Checkout</t>
         </is>
       </c>
       <c r="C110" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/checkout</t>
         </is>
       </c>
       <c r="D110" s="16" t="inlineStr">
         <is>
-          <t>Phase 2 — Manifest close-out + pickup scheduling</t>
-        </is>
-      </c>
-      <c r="E110" s="19" t="inlineStr">
-        <is>
-          <t>Todo</t>
+          <t>Hand off to Stripe for payment</t>
+        </is>
+      </c>
+      <c r="E110" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="F110" s="16" t="inlineStr">
@@ -4461,27 +4321,27 @@
     <row r="111" ht="18" customHeight="1">
       <c r="A111" s="16" t="inlineStr">
         <is>
-          <t>Integrations</t>
+          <t>Cart and checkout</t>
         </is>
       </c>
       <c r="B111" s="16" t="inlineStr">
         <is>
-          <t>Direx Courier</t>
+          <t>Checkout</t>
         </is>
       </c>
       <c r="C111" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/checkout</t>
         </is>
       </c>
       <c r="D111" s="16" t="inlineStr">
         <is>
-          <t>Phase 3 — Tracking polling cron (6h cadence)</t>
-        </is>
-      </c>
-      <c r="E111" s="19" t="inlineStr">
-        <is>
-          <t>Todo</t>
+          <t>Trust strip under the pay button</t>
+        </is>
+      </c>
+      <c r="E111" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="F111" s="16" t="inlineStr">
@@ -4496,32 +4356,32 @@
     <row r="112" ht="18" customHeight="1">
       <c r="A112" s="16" t="inlineStr">
         <is>
-          <t>Integrations</t>
+          <t>Cart and checkout</t>
         </is>
       </c>
       <c r="B112" s="16" t="inlineStr">
         <is>
-          <t>Direx Courier</t>
+          <t>Checkout</t>
         </is>
       </c>
       <c r="C112" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/checkout</t>
         </is>
       </c>
       <c r="D112" s="16" t="inlineStr">
         <is>
-          <t>Phase 4 — Customer-facing tracking timeline in /account</t>
-        </is>
-      </c>
-      <c r="E112" s="19" t="inlineStr">
-        <is>
-          <t>Todo</t>
+          <t>Buttons follow the palette</t>
+        </is>
+      </c>
+      <c r="E112" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="F112" s="16" t="inlineStr">
         <is>
-          <t>P1 high</t>
+          <t>P2 medium</t>
         </is>
       </c>
       <c r="G112" s="16" t="inlineStr"/>
@@ -4531,27 +4391,27 @@
     <row r="113" ht="18" customHeight="1">
       <c r="A113" s="16" t="inlineStr">
         <is>
-          <t>Integrations</t>
+          <t>Cart and checkout</t>
         </is>
       </c>
       <c r="B113" s="16" t="inlineStr">
         <is>
-          <t>Direx Courier</t>
+          <t>Checkout</t>
         </is>
       </c>
       <c r="C113" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/checkout</t>
         </is>
       </c>
       <c r="D113" s="16" t="inlineStr">
         <is>
-          <t>Phase 5 — 'Shipped' email + tracking link</t>
-        </is>
-      </c>
-      <c r="E113" s="19" t="inlineStr">
-        <is>
-          <t>Todo</t>
+          <t>Recurring charge note for subscription plans</t>
+        </is>
+      </c>
+      <c r="E113" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="F113" s="16" t="inlineStr">
@@ -4566,22 +4426,22 @@
     <row r="114" ht="18" customHeight="1">
       <c r="A114" s="16" t="inlineStr">
         <is>
-          <t>Integrations</t>
+          <t>Cart and checkout</t>
         </is>
       </c>
       <c r="B114" s="16" t="inlineStr">
         <is>
-          <t>Direx Courier</t>
+          <t>Checkout</t>
         </is>
       </c>
       <c r="C114" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/checkout</t>
         </is>
       </c>
       <c r="D114" s="16" t="inlineStr">
         <is>
-          <t>Confirm Kyrill warehouse sender ID at my.direx.bg</t>
+          <t>Error message styling when payment fails</t>
         </is>
       </c>
       <c r="E114" s="19" t="inlineStr">
@@ -4591,110 +4451,134 @@
       </c>
       <c r="F114" s="16" t="inlineStr">
         <is>
+          <t>P2 medium</t>
+        </is>
+      </c>
+      <c r="G114" s="16" t="inlineStr"/>
+      <c r="H114" s="16" t="inlineStr"/>
+      <c r="I114" s="16" t="inlineStr"/>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="14" t="inlineStr">
+        <is>
+          <t>Cart and checkout</t>
+        </is>
+      </c>
+      <c r="B115" s="14" t="inlineStr">
+        <is>
+          <t>Confirmation</t>
+        </is>
+      </c>
+      <c r="C115" s="15" t="inlineStr">
+        <is>
+          <t>/confirmation</t>
+        </is>
+      </c>
+      <c r="D115" s="15" t="inlineStr">
+        <is>
+          <t>The thank you page after a successful payment</t>
+        </is>
+      </c>
+      <c r="E115" s="15" t="inlineStr"/>
+      <c r="F115" s="15" t="inlineStr"/>
+      <c r="G115" s="15" t="inlineStr"/>
+      <c r="H115" s="15" t="inlineStr"/>
+      <c r="I115" s="15" t="inlineStr"/>
+    </row>
+    <row r="116" ht="18" customHeight="1">
+      <c r="A116" s="16" t="inlineStr">
+        <is>
+          <t>Cart and checkout</t>
+        </is>
+      </c>
+      <c r="B116" s="16" t="inlineStr">
+        <is>
+          <t>Confirmation</t>
+        </is>
+      </c>
+      <c r="C116" s="16" t="inlineStr">
+        <is>
+          <t>/confirmation</t>
+        </is>
+      </c>
+      <c r="D116" s="16" t="inlineStr">
+        <is>
+          <t>Verify the Stripe session and confirm the order</t>
+        </is>
+      </c>
+      <c r="E116" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F116" s="16" t="inlineStr">
+        <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G114" s="16" t="inlineStr"/>
-      <c r="H114" s="16" t="inlineStr">
-        <is>
-          <t>Operational prerequisite</t>
-        </is>
-      </c>
-      <c r="I114" s="16" t="inlineStr"/>
-    </row>
-    <row r="115" ht="18" customHeight="1">
-      <c r="A115" s="16" t="inlineStr">
-        <is>
-          <t>Integrations</t>
-        </is>
-      </c>
-      <c r="B115" s="16" t="inlineStr">
-        <is>
-          <t>Direx Courier</t>
-        </is>
-      </c>
-      <c r="C115" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D115" s="16" t="inlineStr">
-        <is>
-          <t>Decide BG-only vs international shipping scope</t>
-        </is>
-      </c>
-      <c r="E115" s="19" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F115" s="16" t="inlineStr">
-        <is>
-          <t>P1 high</t>
-        </is>
-      </c>
-      <c r="G115" s="16" t="inlineStr"/>
-      <c r="H115" s="16" t="inlineStr"/>
-      <c r="I115" s="16" t="inlineStr"/>
-    </row>
-    <row r="116" ht="22" customHeight="1">
-      <c r="A116" s="13" t="inlineStr">
-        <is>
-          <t>DESIGN SYSTEM</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="14" t="inlineStr">
-        <is>
-          <t>Design system</t>
-        </is>
-      </c>
-      <c r="B117" s="14" t="inlineStr">
-        <is>
-          <t>Design Lab (?lab=1)</t>
-        </is>
-      </c>
-      <c r="C117" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D117" s="15" t="inlineStr">
-        <is>
-          <t>Floating dev tool for live A/B-ing typography, palette, card corners</t>
-        </is>
-      </c>
-      <c r="E117" s="15" t="inlineStr"/>
-      <c r="F117" s="15" t="inlineStr"/>
-      <c r="G117" s="15" t="inlineStr"/>
-      <c r="H117" s="15" t="inlineStr"/>
-      <c r="I117" s="15" t="inlineStr"/>
+      <c r="G116" s="16" t="inlineStr"/>
+      <c r="H116" s="16" t="inlineStr"/>
+      <c r="I116" s="16" t="inlineStr"/>
+    </row>
+    <row r="117" ht="18" customHeight="1">
+      <c r="A117" s="16" t="inlineStr">
+        <is>
+          <t>Cart and checkout</t>
+        </is>
+      </c>
+      <c r="B117" s="16" t="inlineStr">
+        <is>
+          <t>Confirmation</t>
+        </is>
+      </c>
+      <c r="C117" s="16" t="inlineStr">
+        <is>
+          <t>/confirmation</t>
+        </is>
+      </c>
+      <c r="D117" s="16" t="inlineStr">
+        <is>
+          <t>Auto-create the order in our system after payment</t>
+        </is>
+      </c>
+      <c r="E117" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F117" s="16" t="inlineStr">
+        <is>
+          <t>P0 critical</t>
+        </is>
+      </c>
+      <c r="G117" s="16" t="inlineStr"/>
+      <c r="H117" s="16" t="inlineStr"/>
+      <c r="I117" s="16" t="inlineStr"/>
     </row>
     <row r="118" ht="18" customHeight="1">
       <c r="A118" s="16" t="inlineStr">
         <is>
-          <t>Design system</t>
+          <t>Cart and checkout</t>
         </is>
       </c>
       <c r="B118" s="16" t="inlineStr">
         <is>
-          <t>Design Lab (?lab=1)</t>
+          <t>Confirmation</t>
         </is>
       </c>
       <c r="C118" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/confirmation</t>
         </is>
       </c>
       <c r="D118" s="16" t="inlineStr">
         <is>
-          <t>5 typography slots (display, ed-display, body, ed-body, mono)</t>
-        </is>
-      </c>
-      <c r="E118" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Show order details and next steps</t>
+        </is>
+      </c>
+      <c r="E118" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
         </is>
       </c>
       <c r="F118" s="16" t="inlineStr">
@@ -4709,27 +4593,27 @@
     <row r="119" ht="18" customHeight="1">
       <c r="A119" s="16" t="inlineStr">
         <is>
-          <t>Design system</t>
+          <t>Cart and checkout</t>
         </is>
       </c>
       <c r="B119" s="16" t="inlineStr">
         <is>
-          <t>Design Lab (?lab=1)</t>
+          <t>Confirmation</t>
         </is>
       </c>
       <c r="C119" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/confirmation</t>
         </is>
       </c>
       <c r="D119" s="16" t="inlineStr">
         <is>
-          <t>~70-font catalog with Google Fonts dynamic loading</t>
-        </is>
-      </c>
-      <c r="E119" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Show tracking link once the courier integration is live</t>
+        </is>
+      </c>
+      <c r="E119" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
         </is>
       </c>
       <c r="F119" s="16" t="inlineStr">
@@ -4741,95 +4625,59 @@
       <c r="H119" s="16" t="inlineStr"/>
       <c r="I119" s="16" t="inlineStr"/>
     </row>
-    <row r="120" ht="18" customHeight="1">
-      <c r="A120" s="16" t="inlineStr">
-        <is>
-          <t>Design system</t>
-        </is>
-      </c>
-      <c r="B120" s="16" t="inlineStr">
-        <is>
-          <t>Design Lab (?lab=1)</t>
-        </is>
-      </c>
-      <c r="C120" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D120" s="16" t="inlineStr">
-        <is>
-          <t>Picker mode — click any text to identify slot</t>
-        </is>
-      </c>
-      <c r="E120" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F120" s="16" t="inlineStr">
-        <is>
-          <t>P1 high</t>
-        </is>
-      </c>
-      <c r="G120" s="16" t="inlineStr"/>
-      <c r="H120" s="16" t="inlineStr"/>
-      <c r="I120" s="16" t="inlineStr"/>
-    </row>
-    <row r="121" ht="18" customHeight="1">
-      <c r="A121" s="16" t="inlineStr">
-        <is>
-          <t>Design system</t>
-        </is>
-      </c>
-      <c r="B121" s="16" t="inlineStr">
-        <is>
-          <t>Design Lab (?lab=1)</t>
-        </is>
-      </c>
-      <c r="C121" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D121" s="16" t="inlineStr">
-        <is>
-          <t>Per-element override panel (B / I / U / colour)</t>
-        </is>
-      </c>
-      <c r="E121" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F121" s="16" t="inlineStr">
-        <is>
-          <t>P1 high</t>
-        </is>
-      </c>
-      <c r="G121" s="16" t="inlineStr"/>
-      <c r="H121" s="16" t="inlineStr"/>
-      <c r="I121" s="16" t="inlineStr"/>
+    <row r="120" ht="22" customHeight="1">
+      <c r="A120" s="13" t="inlineStr">
+        <is>
+          <t>CUSTOMER ACCOUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="14" t="inlineStr">
+        <is>
+          <t>Customer account</t>
+        </is>
+      </c>
+      <c r="B121" s="14" t="inlineStr">
+        <is>
+          <t>Account dashboard</t>
+        </is>
+      </c>
+      <c r="C121" s="15" t="inlineStr">
+        <is>
+          <t>/account</t>
+        </is>
+      </c>
+      <c r="D121" s="15" t="inlineStr">
+        <is>
+          <t>Where the customer manages their orders, subscription, and profile</t>
+        </is>
+      </c>
+      <c r="E121" s="15" t="inlineStr"/>
+      <c r="F121" s="15" t="inlineStr"/>
+      <c r="G121" s="15" t="inlineStr"/>
+      <c r="H121" s="15" t="inlineStr"/>
+      <c r="I121" s="15" t="inlineStr"/>
     </row>
     <row r="122" ht="18" customHeight="1">
       <c r="A122" s="16" t="inlineStr">
         <is>
-          <t>Design system</t>
+          <t>Customer account</t>
         </is>
       </c>
       <c r="B122" s="16" t="inlineStr">
         <is>
-          <t>Design Lab (?lab=1)</t>
+          <t>Account dashboard</t>
         </is>
       </c>
       <c r="C122" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/account</t>
         </is>
       </c>
       <c r="D122" s="16" t="inlineStr">
         <is>
-          <t>6 curated presets + custom save/load</t>
+          <t>Sign in works end to end</t>
         </is>
       </c>
       <c r="E122" s="17" t="inlineStr">
@@ -4839,7 +4687,7 @@
       </c>
       <c r="F122" s="16" t="inlineStr">
         <is>
-          <t>P1 high</t>
+          <t>P0 critical</t>
         </is>
       </c>
       <c r="G122" s="16" t="inlineStr"/>
@@ -4849,22 +4697,22 @@
     <row r="123" ht="18" customHeight="1">
       <c r="A123" s="16" t="inlineStr">
         <is>
-          <t>Design system</t>
+          <t>Customer account</t>
         </is>
       </c>
       <c r="B123" s="16" t="inlineStr">
         <is>
-          <t>Design Lab (?lab=1)</t>
+          <t>Account dashboard</t>
         </is>
       </c>
       <c r="C123" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/account</t>
         </is>
       </c>
       <c r="D123" s="16" t="inlineStr">
         <is>
-          <t>6 brand-inspired presets (Aesop, Le Labo, Glossier, etc.)</t>
+          <t>Dashboard layout looks right</t>
         </is>
       </c>
       <c r="E123" s="17" t="inlineStr">
@@ -4874,7 +4722,7 @@
       </c>
       <c r="F123" s="16" t="inlineStr">
         <is>
-          <t>P2 medium</t>
+          <t>P1 high</t>
         </is>
       </c>
       <c r="G123" s="16" t="inlineStr"/>
@@ -4884,27 +4732,27 @@
     <row r="124" ht="18" customHeight="1">
       <c r="A124" s="16" t="inlineStr">
         <is>
-          <t>Design system</t>
+          <t>Customer account</t>
         </is>
       </c>
       <c r="B124" s="16" t="inlineStr">
         <is>
-          <t>Design Lab (?lab=1)</t>
+          <t>Account dashboard</t>
         </is>
       </c>
       <c r="C124" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/account</t>
         </is>
       </c>
       <c r="D124" s="16" t="inlineStr">
         <is>
-          <t>7 curated palettes + custom hex editor</t>
-        </is>
-      </c>
-      <c r="E124" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Past orders view</t>
+        </is>
+      </c>
+      <c r="E124" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
         </is>
       </c>
       <c r="F124" s="16" t="inlineStr">
@@ -4919,32 +4767,32 @@
     <row r="125" ht="18" customHeight="1">
       <c r="A125" s="16" t="inlineStr">
         <is>
-          <t>Design system</t>
+          <t>Customer account</t>
         </is>
       </c>
       <c r="B125" s="16" t="inlineStr">
         <is>
-          <t>Design Lab (?lab=1)</t>
+          <t>Account dashboard</t>
         </is>
       </c>
       <c r="C125" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/account</t>
         </is>
       </c>
       <c r="D125" s="16" t="inlineStr">
         <is>
-          <t>Card radius selector (5 presets)</t>
-        </is>
-      </c>
-      <c r="E125" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Subscription management (pause, cancel, change plan)</t>
+        </is>
+      </c>
+      <c r="E125" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
         </is>
       </c>
       <c r="F125" s="16" t="inlineStr">
         <is>
-          <t>P2 medium</t>
+          <t>P0 critical</t>
         </is>
       </c>
       <c r="G125" s="16" t="inlineStr"/>
@@ -4954,32 +4802,32 @@
     <row r="126" ht="18" customHeight="1">
       <c r="A126" s="16" t="inlineStr">
         <is>
-          <t>Design system</t>
+          <t>Customer account</t>
         </is>
       </c>
       <c r="B126" s="16" t="inlineStr">
         <is>
-          <t>Design Lab (?lab=1)</t>
+          <t>Account dashboard</t>
         </is>
       </c>
       <c r="C126" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/account</t>
         </is>
       </c>
       <c r="D126" s="16" t="inlineStr">
         <is>
-          <t>Modular palette tokens (Card surface, CTA bg/fg, line)</t>
-        </is>
-      </c>
-      <c r="E126" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Retake the quiz from inside the account</t>
+        </is>
+      </c>
+      <c r="E126" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
         </is>
       </c>
       <c r="F126" s="16" t="inlineStr">
         <is>
-          <t>P1 high</t>
+          <t>P2 medium</t>
         </is>
       </c>
       <c r="G126" s="16" t="inlineStr"/>
@@ -4989,96 +4837,64 @@
     <row r="127" ht="18" customHeight="1">
       <c r="A127" s="16" t="inlineStr">
         <is>
-          <t>Design system</t>
+          <t>Customer account</t>
         </is>
       </c>
       <c r="B127" s="16" t="inlineStr">
         <is>
-          <t>Design Lab (?lab=1)</t>
+          <t>Account dashboard</t>
         </is>
       </c>
       <c r="C127" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/account</t>
         </is>
       </c>
       <c r="D127" s="16" t="inlineStr">
         <is>
-          <t>Collapsible sections + Expand all toggle</t>
-        </is>
-      </c>
-      <c r="E127" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Edit profile and shipping address</t>
+        </is>
+      </c>
+      <c r="E127" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
         </is>
       </c>
       <c r="F127" s="16" t="inlineStr">
         <is>
-          <t>P2 medium</t>
+          <t>P1 high</t>
         </is>
       </c>
       <c r="G127" s="16" t="inlineStr"/>
       <c r="H127" s="16" t="inlineStr"/>
       <c r="I127" s="16" t="inlineStr"/>
     </row>
-    <row r="128" ht="18" customHeight="1">
-      <c r="A128" s="16" t="inlineStr">
-        <is>
-          <t>Design system</t>
-        </is>
-      </c>
-      <c r="B128" s="16" t="inlineStr">
-        <is>
-          <t>Design Lab (?lab=1)</t>
-        </is>
-      </c>
-      <c r="C128" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D128" s="16" t="inlineStr">
-        <is>
-          <t>Sitemap Map tab (deprecated — moved to Excel)</t>
-        </is>
-      </c>
-      <c r="E128" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F128" s="16" t="inlineStr">
-        <is>
-          <t>P3 low</t>
-        </is>
-      </c>
-      <c r="G128" s="16" t="inlineStr"/>
-      <c r="H128" s="16" t="inlineStr">
-        <is>
-          <t>Could remove the tab now that Excel tracker exists</t>
-        </is>
-      </c>
-      <c r="I128" s="16" t="inlineStr"/>
+    <row r="128" ht="22" customHeight="1">
+      <c r="A128" s="13" t="inlineStr">
+        <is>
+          <t>REFERENCE PAGES</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="20" customHeight="1">
       <c r="A129" s="14" t="inlineStr">
         <is>
-          <t>Design system</t>
+          <t>Reference pages</t>
         </is>
       </c>
       <c r="B129" s="14" t="inlineStr">
         <is>
-          <t>Design tokens</t>
+          <t>Ingredients</t>
         </is>
       </c>
       <c r="C129" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/ingredients</t>
         </is>
       </c>
       <c r="D129" s="15" t="inlineStr">
         <is>
-          <t>Site-wide CSS variables in editorial.css + atelier-2026.css</t>
+          <t>A glossary of all the botanicals we use</t>
         </is>
       </c>
       <c r="E129" s="15" t="inlineStr"/>
@@ -5090,22 +4906,22 @@
     <row r="130" ht="18" customHeight="1">
       <c r="A130" s="16" t="inlineStr">
         <is>
-          <t>Design system</t>
+          <t>Reference pages</t>
         </is>
       </c>
       <c r="B130" s="16" t="inlineStr">
         <is>
-          <t>Design tokens</t>
+          <t>Ingredients</t>
         </is>
       </c>
       <c r="C130" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/ingredients</t>
         </is>
       </c>
       <c r="D130" s="16" t="inlineStr">
         <is>
-          <t>Type tokens at :root (--serif, --sans, --mono, --ed-display, --ed-body)</t>
+          <t>Show every ingredient from the database</t>
         </is>
       </c>
       <c r="E130" s="17" t="inlineStr">
@@ -5125,32 +4941,32 @@
     <row r="131" ht="18" customHeight="1">
       <c r="A131" s="16" t="inlineStr">
         <is>
-          <t>Design system</t>
+          <t>Reference pages</t>
         </is>
       </c>
       <c r="B131" s="16" t="inlineStr">
         <is>
-          <t>Design tokens</t>
+          <t>Ingredients</t>
         </is>
       </c>
       <c r="C131" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/ingredients</t>
         </is>
       </c>
       <c r="D131" s="16" t="inlineStr">
         <is>
-          <t>Palette tokens (bg, surface-card, ink, cta-bg, cta-fg, line, moss/rose/amber)</t>
-        </is>
-      </c>
-      <c r="E131" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Filter by function or type</t>
+        </is>
+      </c>
+      <c r="E131" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
         </is>
       </c>
       <c r="F131" s="16" t="inlineStr">
         <is>
-          <t>P1 high</t>
+          <t>P2 medium</t>
         </is>
       </c>
       <c r="G131" s="16" t="inlineStr"/>
@@ -5160,27 +4976,27 @@
     <row r="132" ht="18" customHeight="1">
       <c r="A132" s="16" t="inlineStr">
         <is>
-          <t>Design system</t>
+          <t>Reference pages</t>
         </is>
       </c>
       <c r="B132" s="16" t="inlineStr">
         <is>
-          <t>Design tokens</t>
+          <t>Ingredients</t>
         </is>
       </c>
       <c r="C132" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/ingredients</t>
         </is>
       </c>
       <c r="D132" s="16" t="inlineStr">
         <is>
-          <t>Card-radius token (--card-radius)</t>
-        </is>
-      </c>
-      <c r="E132" s="17" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>Detail page per ingredient (origin, function, scientific name)</t>
+        </is>
+      </c>
+      <c r="E132" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
         </is>
       </c>
       <c r="F132" s="16" t="inlineStr">
@@ -5195,139 +5011,131 @@
     <row r="133" ht="18" customHeight="1">
       <c r="A133" s="16" t="inlineStr">
         <is>
-          <t>Design system</t>
+          <t>Reference pages</t>
         </is>
       </c>
       <c r="B133" s="16" t="inlineStr">
         <is>
-          <t>Design tokens</t>
+          <t>Ingredients</t>
         </is>
       </c>
       <c r="C133" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>/ingredients</t>
         </is>
       </c>
       <c r="D133" s="16" t="inlineStr">
         <is>
-          <t>Refactor all literal font-family declarations to vars</t>
-        </is>
-      </c>
-      <c r="E133" s="17" t="inlineStr">
+          <t>Type and layout polish</t>
+        </is>
+      </c>
+      <c r="E133" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F133" s="16" t="inlineStr">
+        <is>
+          <t>P1 high</t>
+        </is>
+      </c>
+      <c r="G133" s="16" t="inlineStr"/>
+      <c r="H133" s="16" t="inlineStr"/>
+      <c r="I133" s="16" t="inlineStr"/>
+    </row>
+    <row r="134" ht="22" customHeight="1">
+      <c r="A134" s="13" t="inlineStr">
+        <is>
+          <t>ADMIN TOOLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="14" t="inlineStr">
+        <is>
+          <t>Admin tools</t>
+        </is>
+      </c>
+      <c r="B135" s="14" t="inlineStr">
+        <is>
+          <t>Fulfillment Studio</t>
+        </is>
+      </c>
+      <c r="C135" s="15" t="inlineStr">
+        <is>
+          <t>fulfillment-studio (separate dashboard)</t>
+        </is>
+      </c>
+      <c r="D135" s="15" t="inlineStr">
+        <is>
+          <t>The operations dashboard for picking, packing, printing labels, and exporting product data</t>
+        </is>
+      </c>
+      <c r="E135" s="15" t="inlineStr"/>
+      <c r="F135" s="15" t="inlineStr"/>
+      <c r="G135" s="15" t="inlineStr"/>
+      <c r="H135" s="15" t="inlineStr"/>
+      <c r="I135" s="15" t="inlineStr"/>
+    </row>
+    <row r="136" ht="18" customHeight="1">
+      <c r="A136" s="16" t="inlineStr">
+        <is>
+          <t>Admin tools</t>
+        </is>
+      </c>
+      <c r="B136" s="16" t="inlineStr">
+        <is>
+          <t>Fulfillment Studio</t>
+        </is>
+      </c>
+      <c r="C136" s="16" t="inlineStr">
+        <is>
+          <t>fulfillment-studio (separate dashboard)</t>
+        </is>
+      </c>
+      <c r="D136" s="16" t="inlineStr">
+        <is>
+          <t>Only admins can sign in</t>
+        </is>
+      </c>
+      <c r="E136" s="17" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F133" s="16" t="inlineStr">
-        <is>
-          <t>P1 high</t>
-        </is>
-      </c>
-      <c r="G133" s="16" t="inlineStr"/>
-      <c r="H133" s="16" t="inlineStr">
-        <is>
-          <t>~390 declarations across 14 CSS files</t>
-        </is>
-      </c>
-      <c r="I133" s="16" t="inlineStr"/>
-    </row>
-    <row r="134" ht="18" customHeight="1">
-      <c r="A134" s="16" t="inlineStr">
-        <is>
-          <t>Design system</t>
-        </is>
-      </c>
-      <c r="B134" s="16" t="inlineStr">
-        <is>
-          <t>Design tokens</t>
-        </is>
-      </c>
-      <c r="C134" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D134" s="16" t="inlineStr">
-        <is>
-          <t>Refactor inner-page (editorial.css) cards to use --surface-card</t>
-        </is>
-      </c>
-      <c r="E134" s="19" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F134" s="16" t="inlineStr">
-        <is>
-          <t>P2 medium</t>
-        </is>
-      </c>
-      <c r="G134" s="16" t="inlineStr"/>
-      <c r="H134" s="16" t="inlineStr">
-        <is>
-          <t>Quiz / account pages still on --bg-cream</t>
-        </is>
-      </c>
-      <c r="I134" s="16" t="inlineStr"/>
-    </row>
-    <row r="135" ht="22" customHeight="1">
-      <c r="A135" s="13" t="inlineStr">
-        <is>
-          <t>CROSS-CUTTING CONCERNS</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="20" customHeight="1">
-      <c r="A136" s="14" t="inlineStr">
-        <is>
-          <t>Cross-cutting concerns</t>
-        </is>
-      </c>
-      <c r="B136" s="14" t="inlineStr">
-        <is>
-          <t>Brand</t>
-        </is>
-      </c>
-      <c r="C136" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D136" s="15" t="inlineStr">
-        <is>
-          <t>Wordmark, logo, voice</t>
-        </is>
-      </c>
-      <c r="E136" s="15" t="inlineStr"/>
-      <c r="F136" s="15" t="inlineStr"/>
-      <c r="G136" s="15" t="inlineStr"/>
-      <c r="H136" s="15" t="inlineStr"/>
-      <c r="I136" s="15" t="inlineStr"/>
+      <c r="F136" s="16" t="inlineStr">
+        <is>
+          <t>P0 critical</t>
+        </is>
+      </c>
+      <c r="G136" s="16" t="inlineStr"/>
+      <c r="H136" s="16" t="inlineStr"/>
+      <c r="I136" s="16" t="inlineStr"/>
     </row>
     <row r="137" ht="18" customHeight="1">
       <c r="A137" s="16" t="inlineStr">
         <is>
-          <t>Cross-cutting concerns</t>
+          <t>Admin tools</t>
         </is>
       </c>
       <c r="B137" s="16" t="inlineStr">
         <is>
-          <t>Brand</t>
+          <t>Fulfillment Studio</t>
         </is>
       </c>
       <c r="C137" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>fulfillment-studio (separate dashboard)</t>
         </is>
       </c>
       <c r="D137" s="16" t="inlineStr">
         <is>
-          <t>Final logo design (currently using rusalka illustration as PNG)</t>
-        </is>
-      </c>
-      <c r="E137" s="20" t="inlineStr">
-        <is>
-          <t>In progress</t>
+          <t>List of pending and fulfilled orders with filters</t>
+        </is>
+      </c>
+      <c r="E137" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="F137" s="16" t="inlineStr">
@@ -5336,42 +5144,38 @@
         </is>
       </c>
       <c r="G137" s="16" t="inlineStr"/>
-      <c r="H137" s="16" t="inlineStr">
-        <is>
-          <t>Real designer brief outstanding</t>
-        </is>
-      </c>
+      <c r="H137" s="16" t="inlineStr"/>
       <c r="I137" s="16" t="inlineStr"/>
     </row>
     <row r="138" ht="18" customHeight="1">
       <c r="A138" s="16" t="inlineStr">
         <is>
-          <t>Cross-cutting concerns</t>
+          <t>Admin tools</t>
         </is>
       </c>
       <c r="B138" s="16" t="inlineStr">
         <is>
-          <t>Brand</t>
+          <t>Fulfillment Studio</t>
         </is>
       </c>
       <c r="C138" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>fulfillment-studio (separate dashboard)</t>
         </is>
       </c>
       <c r="D138" s="16" t="inlineStr">
         <is>
-          <t>Favicon update from rusalka mark</t>
-        </is>
-      </c>
-      <c r="E138" s="19" t="inlineStr">
-        <is>
-          <t>Todo</t>
+          <t>Assign barcodes when an order is fulfilled</t>
+        </is>
+      </c>
+      <c r="E138" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="F138" s="16" t="inlineStr">
         <is>
-          <t>P2 medium</t>
+          <t>P0 critical</t>
         </is>
       </c>
       <c r="G138" s="16" t="inlineStr"/>
@@ -5381,32 +5185,32 @@
     <row r="139" ht="18" customHeight="1">
       <c r="A139" s="16" t="inlineStr">
         <is>
-          <t>Cross-cutting concerns</t>
+          <t>Admin tools</t>
         </is>
       </c>
       <c r="B139" s="16" t="inlineStr">
         <is>
-          <t>Brand</t>
+          <t>Fulfillment Studio</t>
         </is>
       </c>
       <c r="C139" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>fulfillment-studio (separate dashboard)</t>
         </is>
       </c>
       <c r="D139" s="16" t="inlineStr">
         <is>
-          <t>Open Graph / social card image</t>
-        </is>
-      </c>
-      <c r="E139" s="19" t="inlineStr">
-        <is>
-          <t>Todo</t>
+          <t>Print one or all labels at once</t>
+        </is>
+      </c>
+      <c r="E139" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="F139" s="16" t="inlineStr">
         <is>
-          <t>P2 medium</t>
+          <t>P0 critical</t>
         </is>
       </c>
       <c r="G139" s="16" t="inlineStr"/>
@@ -5416,94 +5220,102 @@
     <row r="140" ht="18" customHeight="1">
       <c r="A140" s="16" t="inlineStr">
         <is>
-          <t>Cross-cutting concerns</t>
+          <t>Admin tools</t>
         </is>
       </c>
       <c r="B140" s="16" t="inlineStr">
         <is>
-          <t>Brand</t>
+          <t>Fulfillment Studio</t>
         </is>
       </c>
       <c r="C140" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>fulfillment-studio (separate dashboard)</t>
         </is>
       </c>
       <c r="D140" s="16" t="inlineStr">
         <is>
-          <t>Brand voice guidelines doc</t>
-        </is>
-      </c>
-      <c r="E140" s="19" t="inlineStr">
-        <is>
-          <t>Todo</t>
+          <t>Barcodes printed at GS1 standard size</t>
+        </is>
+      </c>
+      <c r="E140" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="F140" s="16" t="inlineStr">
         <is>
-          <t>P2 medium</t>
+          <t>P1 high</t>
         </is>
       </c>
       <c r="G140" s="16" t="inlineStr"/>
       <c r="H140" s="16" t="inlineStr"/>
       <c r="I140" s="16" t="inlineStr"/>
     </row>
-    <row r="141" ht="20" customHeight="1">
-      <c r="A141" s="14" t="inlineStr">
-        <is>
-          <t>Cross-cutting concerns</t>
-        </is>
-      </c>
-      <c r="B141" s="14" t="inlineStr">
-        <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="C141" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D141" s="15" t="inlineStr">
-        <is>
-          <t>ARIA, contrast, keyboard nav</t>
-        </is>
-      </c>
-      <c r="E141" s="15" t="inlineStr"/>
-      <c r="F141" s="15" t="inlineStr"/>
-      <c r="G141" s="15" t="inlineStr"/>
-      <c r="H141" s="15" t="inlineStr"/>
-      <c r="I141" s="15" t="inlineStr"/>
+    <row r="141" ht="18" customHeight="1">
+      <c r="A141" s="16" t="inlineStr">
+        <is>
+          <t>Admin tools</t>
+        </is>
+      </c>
+      <c r="B141" s="16" t="inlineStr">
+        <is>
+          <t>Fulfillment Studio</t>
+        </is>
+      </c>
+      <c r="C141" s="16" t="inlineStr">
+        <is>
+          <t>fulfillment-studio (separate dashboard)</t>
+        </is>
+      </c>
+      <c r="D141" s="16" t="inlineStr">
+        <is>
+          <t>Download an XML file per product for INCI Beauty</t>
+        </is>
+      </c>
+      <c r="E141" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F141" s="16" t="inlineStr">
+        <is>
+          <t>P1 high</t>
+        </is>
+      </c>
+      <c r="G141" s="16" t="inlineStr"/>
+      <c r="H141" s="16" t="inlineStr"/>
+      <c r="I141" s="16" t="inlineStr"/>
     </row>
     <row r="142" ht="18" customHeight="1">
       <c r="A142" s="16" t="inlineStr">
         <is>
-          <t>Cross-cutting concerns</t>
+          <t>Admin tools</t>
         </is>
       </c>
       <c r="B142" s="16" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Fulfillment Studio</t>
         </is>
       </c>
       <c r="C142" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>fulfillment-studio (separate dashboard)</t>
         </is>
       </c>
       <c r="D142" s="16" t="inlineStr">
         <is>
-          <t>Audit colour contrast across curated palettes (WCAG AA)</t>
-        </is>
-      </c>
-      <c r="E142" s="19" t="inlineStr">
-        <is>
-          <t>Todo</t>
+          <t>Cancel an order or delete a test order</t>
+        </is>
+      </c>
+      <c r="E142" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="F142" s="16" t="inlineStr">
         <is>
-          <t>P1 high</t>
+          <t>P2 medium</t>
         </is>
       </c>
       <c r="G142" s="16" t="inlineStr"/>
@@ -5513,22 +5325,22 @@
     <row r="143" ht="18" customHeight="1">
       <c r="A143" s="16" t="inlineStr">
         <is>
-          <t>Cross-cutting concerns</t>
+          <t>Admin tools</t>
         </is>
       </c>
       <c r="B143" s="16" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Fulfillment Studio</t>
         </is>
       </c>
       <c r="C143" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>fulfillment-studio (separate dashboard)</t>
         </is>
       </c>
       <c r="D143" s="16" t="inlineStr">
         <is>
-          <t>Keyboard navigation through quiz</t>
+          <t>Create a shipment with the Direx courier</t>
         </is>
       </c>
       <c r="E143" s="19" t="inlineStr">
@@ -5538,7 +5350,7 @@
       </c>
       <c r="F143" s="16" t="inlineStr">
         <is>
-          <t>P1 high</t>
+          <t>P0 critical</t>
         </is>
       </c>
       <c r="G143" s="16" t="inlineStr"/>
@@ -5548,22 +5360,22 @@
     <row r="144" ht="18" customHeight="1">
       <c r="A144" s="16" t="inlineStr">
         <is>
-          <t>Cross-cutting concerns</t>
+          <t>Admin tools</t>
         </is>
       </c>
       <c r="B144" s="16" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Fulfillment Studio</t>
         </is>
       </c>
       <c r="C144" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>fulfillment-studio (separate dashboard)</t>
         </is>
       </c>
       <c r="D144" s="16" t="inlineStr">
         <is>
-          <t>Screen reader pass on results page (3D scene needs alt content)</t>
+          <t>Close the daily manifest and schedule a pickup</t>
         </is>
       </c>
       <c r="E144" s="19" t="inlineStr">
@@ -5573,7 +5385,7 @@
       </c>
       <c r="F144" s="16" t="inlineStr">
         <is>
-          <t>P1 high</t>
+          <t>P0 critical</t>
         </is>
       </c>
       <c r="G144" s="16" t="inlineStr"/>
@@ -5583,22 +5395,22 @@
     <row r="145" ht="18" customHeight="1">
       <c r="A145" s="16" t="inlineStr">
         <is>
-          <t>Cross-cutting concerns</t>
+          <t>Admin tools</t>
         </is>
       </c>
       <c r="B145" s="16" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Fulfillment Studio</t>
         </is>
       </c>
       <c r="C145" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>fulfillment-studio (separate dashboard)</t>
         </is>
       </c>
       <c r="D145" s="16" t="inlineStr">
         <is>
-          <t>Focus rings on all interactive elements</t>
+          <t>Auto deploy this dashboard when we push (currently manual)</t>
         </is>
       </c>
       <c r="E145" s="19" t="inlineStr">
@@ -5608,7 +5420,7 @@
       </c>
       <c r="F145" s="16" t="inlineStr">
         <is>
-          <t>P1 high</t>
+          <t>P2 medium</t>
         </is>
       </c>
       <c r="G145" s="16" t="inlineStr"/>
@@ -5618,22 +5430,22 @@
     <row r="146" ht="20" customHeight="1">
       <c r="A146" s="14" t="inlineStr">
         <is>
-          <t>Cross-cutting concerns</t>
+          <t>Admin tools</t>
         </is>
       </c>
       <c r="B146" s="14" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Barcode Studio</t>
         </is>
       </c>
       <c r="C146" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>barcode-studio (separate dashboard)</t>
         </is>
       </c>
       <c r="D146" s="15" t="inlineStr">
         <is>
-          <t>Bundle size, load speed, image optimisation</t>
+          <t>Where we manage our pool of product barcodes</t>
         </is>
       </c>
       <c r="E146" s="15" t="inlineStr"/>
@@ -5645,22 +5457,22 @@
     <row r="147" ht="18" customHeight="1">
       <c r="A147" s="16" t="inlineStr">
         <is>
-          <t>Cross-cutting concerns</t>
+          <t>Admin tools</t>
         </is>
       </c>
       <c r="B147" s="16" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Barcode Studio</t>
         </is>
       </c>
       <c r="C147" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>barcode-studio (separate dashboard)</t>
         </is>
       </c>
       <c r="D147" s="16" t="inlineStr">
         <is>
-          <t>Hero video preload strategy</t>
+          <t>Manage which company prefix we issue from</t>
         </is>
       </c>
       <c r="E147" s="17" t="inlineStr">
@@ -5670,7 +5482,7 @@
       </c>
       <c r="F147" s="16" t="inlineStr">
         <is>
-          <t>P1 high</t>
+          <t>P0 critical</t>
         </is>
       </c>
       <c r="G147" s="16" t="inlineStr"/>
@@ -5680,32 +5492,32 @@
     <row r="148" ht="18" customHeight="1">
       <c r="A148" s="16" t="inlineStr">
         <is>
-          <t>Cross-cutting concerns</t>
+          <t>Admin tools</t>
         </is>
       </c>
       <c r="B148" s="16" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Barcode Studio</t>
         </is>
       </c>
       <c r="C148" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>barcode-studio (separate dashboard)</t>
         </is>
       </c>
       <c r="D148" s="16" t="inlineStr">
         <is>
-          <t>Migrate hero video to optimised codec (av1 / hevc)</t>
-        </is>
-      </c>
-      <c r="E148" s="19" t="inlineStr">
-        <is>
-          <t>Todo</t>
+          <t>Bulk import barcodes from an Excel file</t>
+        </is>
+      </c>
+      <c r="E148" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="F148" s="16" t="inlineStr">
         <is>
-          <t>P2 medium</t>
+          <t>P0 critical</t>
         </is>
       </c>
       <c r="G148" s="16" t="inlineStr"/>
@@ -5715,27 +5527,27 @@
     <row r="149" ht="18" customHeight="1">
       <c r="A149" s="16" t="inlineStr">
         <is>
-          <t>Cross-cutting concerns</t>
+          <t>Admin tools</t>
         </is>
       </c>
       <c r="B149" s="16" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Barcode Studio</t>
         </is>
       </c>
       <c r="C149" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>barcode-studio (separate dashboard)</t>
         </is>
       </c>
       <c r="D149" s="16" t="inlineStr">
         <is>
-          <t>Next.js Image component for product photos</t>
-        </is>
-      </c>
-      <c r="E149" s="19" t="inlineStr">
-        <is>
-          <t>Todo</t>
+          <t>Live preview at the actual print size</t>
+        </is>
+      </c>
+      <c r="E149" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="F149" s="16" t="inlineStr">
@@ -5747,87 +5559,2108 @@
       <c r="H149" s="16" t="inlineStr"/>
       <c r="I149" s="16" t="inlineStr"/>
     </row>
-    <row r="150" ht="18" customHeight="1">
-      <c r="A150" s="16" t="inlineStr">
-        <is>
-          <t>Cross-cutting concerns</t>
-        </is>
-      </c>
-      <c r="B150" s="16" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C150" s="16" t="inlineStr">
+    <row r="150" ht="22" customHeight="1">
+      <c r="A150" s="13" t="inlineStr">
+        <is>
+          <t>OUTSIDE SERVICES WE CONNECT TO</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="20" customHeight="1">
+      <c r="A151" s="14" t="inlineStr">
+        <is>
+          <t>Outside services we connect to</t>
+        </is>
+      </c>
+      <c r="B151" s="14" t="inlineStr">
+        <is>
+          <t>Stripe (payments)</t>
+        </is>
+      </c>
+      <c r="C151" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D150" s="16" t="inlineStr">
-        <is>
-          <t>Font subset / preload optimisation</t>
-        </is>
-      </c>
-      <c r="E150" s="19" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F150" s="16" t="inlineStr">
+      <c r="D151" s="15" t="inlineStr">
+        <is>
+          <t>How we charge customers and run subscriptions</t>
+        </is>
+      </c>
+      <c r="E151" s="15" t="inlineStr"/>
+      <c r="F151" s="15" t="inlineStr"/>
+      <c r="G151" s="15" t="inlineStr"/>
+      <c r="H151" s="15" t="inlineStr"/>
+      <c r="I151" s="15" t="inlineStr"/>
+    </row>
+    <row r="152" ht="18" customHeight="1">
+      <c r="A152" s="16" t="inlineStr">
+        <is>
+          <t>Outside services we connect to</t>
+        </is>
+      </c>
+      <c r="B152" s="16" t="inlineStr">
+        <is>
+          <t>Stripe (payments)</t>
+        </is>
+      </c>
+      <c r="C152" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D152" s="16" t="inlineStr">
+        <is>
+          <t>Send the customer to Stripe to pay</t>
+        </is>
+      </c>
+      <c r="E152" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F152" s="16" t="inlineStr">
+        <is>
+          <t>P0 critical</t>
+        </is>
+      </c>
+      <c r="G152" s="16" t="inlineStr"/>
+      <c r="H152" s="16" t="inlineStr"/>
+      <c r="I152" s="16" t="inlineStr"/>
+    </row>
+    <row r="153" ht="18" customHeight="1">
+      <c r="A153" s="16" t="inlineStr">
+        <is>
+          <t>Outside services we connect to</t>
+        </is>
+      </c>
+      <c r="B153" s="16" t="inlineStr">
+        <is>
+          <t>Stripe (payments)</t>
+        </is>
+      </c>
+      <c r="C153" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D153" s="16" t="inlineStr">
+        <is>
+          <t>Automatically create the order when Stripe confirms payment</t>
+        </is>
+      </c>
+      <c r="E153" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F153" s="16" t="inlineStr">
+        <is>
+          <t>P0 critical</t>
+        </is>
+      </c>
+      <c r="G153" s="16" t="inlineStr"/>
+      <c r="H153" s="16" t="inlineStr"/>
+      <c r="I153" s="16" t="inlineStr"/>
+    </row>
+    <row r="154" ht="18" customHeight="1">
+      <c r="A154" s="16" t="inlineStr">
+        <is>
+          <t>Outside services we connect to</t>
+        </is>
+      </c>
+      <c r="B154" s="16" t="inlineStr">
+        <is>
+          <t>Stripe (payments)</t>
+        </is>
+      </c>
+      <c r="C154" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D154" s="16" t="inlineStr">
+        <is>
+          <t>Subscription billing (bi-monthly and annual)</t>
+        </is>
+      </c>
+      <c r="E154" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F154" s="16" t="inlineStr">
+        <is>
+          <t>P0 critical</t>
+        </is>
+      </c>
+      <c r="G154" s="16" t="inlineStr"/>
+      <c r="H154" s="16" t="inlineStr"/>
+      <c r="I154" s="16" t="inlineStr"/>
+    </row>
+    <row r="155" ht="18" customHeight="1">
+      <c r="A155" s="16" t="inlineStr">
+        <is>
+          <t>Outside services we connect to</t>
+        </is>
+      </c>
+      <c r="B155" s="16" t="inlineStr">
+        <is>
+          <t>Stripe (payments)</t>
+        </is>
+      </c>
+      <c r="C155" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D155" s="16" t="inlineStr">
+        <is>
+          <t>Plan for what happens when a recurring charge fails</t>
+        </is>
+      </c>
+      <c r="E155" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F155" s="16" t="inlineStr">
+        <is>
+          <t>P1 high</t>
+        </is>
+      </c>
+      <c r="G155" s="16" t="inlineStr"/>
+      <c r="H155" s="16" t="inlineStr"/>
+      <c r="I155" s="16" t="inlineStr"/>
+    </row>
+    <row r="156" ht="20" customHeight="1">
+      <c r="A156" s="14" t="inlineStr">
+        <is>
+          <t>Outside services we connect to</t>
+        </is>
+      </c>
+      <c r="B156" s="14" t="inlineStr">
+        <is>
+          <t>Supabase (database and storage)</t>
+        </is>
+      </c>
+      <c r="C156" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D156" s="15" t="inlineStr">
+        <is>
+          <t>Where customer data, products, and images live</t>
+        </is>
+      </c>
+      <c r="E156" s="15" t="inlineStr"/>
+      <c r="F156" s="15" t="inlineStr"/>
+      <c r="G156" s="15" t="inlineStr"/>
+      <c r="H156" s="15" t="inlineStr"/>
+      <c r="I156" s="15" t="inlineStr"/>
+    </row>
+    <row r="157" ht="18" customHeight="1">
+      <c r="A157" s="16" t="inlineStr">
+        <is>
+          <t>Outside services we connect to</t>
+        </is>
+      </c>
+      <c r="B157" s="16" t="inlineStr">
+        <is>
+          <t>Supabase (database and storage)</t>
+        </is>
+      </c>
+      <c r="C157" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D157" s="16" t="inlineStr">
+        <is>
+          <t>Products and ingredients data set up</t>
+        </is>
+      </c>
+      <c r="E157" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F157" s="16" t="inlineStr">
+        <is>
+          <t>P0 critical</t>
+        </is>
+      </c>
+      <c r="G157" s="16" t="inlineStr"/>
+      <c r="H157" s="16" t="inlineStr"/>
+      <c r="I157" s="16" t="inlineStr"/>
+    </row>
+    <row r="158" ht="18" customHeight="1">
+      <c r="A158" s="16" t="inlineStr">
+        <is>
+          <t>Outside services we connect to</t>
+        </is>
+      </c>
+      <c r="B158" s="16" t="inlineStr">
+        <is>
+          <t>Supabase (database and storage)</t>
+        </is>
+      </c>
+      <c r="C158" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D158" s="16" t="inlineStr">
+        <is>
+          <t>Customer orders and quiz results data set up</t>
+        </is>
+      </c>
+      <c r="E158" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F158" s="16" t="inlineStr">
+        <is>
+          <t>P0 critical</t>
+        </is>
+      </c>
+      <c r="G158" s="16" t="inlineStr"/>
+      <c r="H158" s="16" t="inlineStr"/>
+      <c r="I158" s="16" t="inlineStr"/>
+    </row>
+    <row r="159" ht="18" customHeight="1">
+      <c r="A159" s="16" t="inlineStr">
+        <is>
+          <t>Outside services we connect to</t>
+        </is>
+      </c>
+      <c r="B159" s="16" t="inlineStr">
+        <is>
+          <t>Supabase (database and storage)</t>
+        </is>
+      </c>
+      <c r="C159" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D159" s="16" t="inlineStr">
+        <is>
+          <t>Barcode pool and product records data set up</t>
+        </is>
+      </c>
+      <c r="E159" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F159" s="16" t="inlineStr">
+        <is>
+          <t>P0 critical</t>
+        </is>
+      </c>
+      <c r="G159" s="16" t="inlineStr"/>
+      <c r="H159" s="16" t="inlineStr"/>
+      <c r="I159" s="16" t="inlineStr"/>
+    </row>
+    <row r="160" ht="18" customHeight="1">
+      <c r="A160" s="16" t="inlineStr">
+        <is>
+          <t>Outside services we connect to</t>
+        </is>
+      </c>
+      <c r="B160" s="16" t="inlineStr">
+        <is>
+          <t>Supabase (database and storage)</t>
+        </is>
+      </c>
+      <c r="C160" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D160" s="16" t="inlineStr">
+        <is>
+          <t>Admin role check so only the right people can use the dashboard</t>
+        </is>
+      </c>
+      <c r="E160" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F160" s="16" t="inlineStr">
+        <is>
+          <t>P0 critical</t>
+        </is>
+      </c>
+      <c r="G160" s="16" t="inlineStr"/>
+      <c r="H160" s="16" t="inlineStr"/>
+      <c r="I160" s="16" t="inlineStr"/>
+    </row>
+    <row r="161" ht="18" customHeight="1">
+      <c r="A161" s="16" t="inlineStr">
+        <is>
+          <t>Outside services we connect to</t>
+        </is>
+      </c>
+      <c r="B161" s="16" t="inlineStr">
+        <is>
+          <t>Supabase (database and storage)</t>
+        </is>
+      </c>
+      <c r="C161" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D161" s="16" t="inlineStr">
+        <is>
+          <t>Public product image storage (the bucket called products)</t>
+        </is>
+      </c>
+      <c r="E161" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F161" s="16" t="inlineStr">
+        <is>
+          <t>P1 high</t>
+        </is>
+      </c>
+      <c r="G161" s="16" t="inlineStr"/>
+      <c r="H161" s="16" t="inlineStr"/>
+      <c r="I161" s="16" t="inlineStr"/>
+    </row>
+    <row r="162" ht="18" customHeight="1">
+      <c r="A162" s="16" t="inlineStr">
+        <is>
+          <t>Outside services we connect to</t>
+        </is>
+      </c>
+      <c r="B162" s="16" t="inlineStr">
+        <is>
+          <t>Supabase (database and storage)</t>
+        </is>
+      </c>
+      <c r="C162" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D162" s="16" t="inlineStr">
+        <is>
+          <t>Upload one real product photo per barcode</t>
+        </is>
+      </c>
+      <c r="E162" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F162" s="16" t="inlineStr">
+        <is>
+          <t>P1 high</t>
+        </is>
+      </c>
+      <c r="G162" s="16" t="inlineStr"/>
+      <c r="H162" s="16" t="inlineStr"/>
+      <c r="I162" s="16" t="inlineStr"/>
+    </row>
+    <row r="163" ht="20" customHeight="1">
+      <c r="A163" s="14" t="inlineStr">
+        <is>
+          <t>Outside services we connect to</t>
+        </is>
+      </c>
+      <c r="B163" s="14" t="inlineStr">
+        <is>
+          <t>INCI Beauty (product import)</t>
+        </is>
+      </c>
+      <c r="C163" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D163" s="15" t="inlineStr">
+        <is>
+          <t>External cosmetic ingredient database where our products get listed</t>
+        </is>
+      </c>
+      <c r="E163" s="15" t="inlineStr"/>
+      <c r="F163" s="15" t="inlineStr"/>
+      <c r="G163" s="15" t="inlineStr"/>
+      <c r="H163" s="15" t="inlineStr"/>
+      <c r="I163" s="15" t="inlineStr"/>
+    </row>
+    <row r="164" ht="18" customHeight="1">
+      <c r="A164" s="16" t="inlineStr">
+        <is>
+          <t>Outside services we connect to</t>
+        </is>
+      </c>
+      <c r="B164" s="16" t="inlineStr">
+        <is>
+          <t>INCI Beauty (product import)</t>
+        </is>
+      </c>
+      <c r="C164" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D164" s="16" t="inlineStr">
+        <is>
+          <t>Generate the XML file from each product</t>
+        </is>
+      </c>
+      <c r="E164" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F164" s="16" t="inlineStr">
+        <is>
+          <t>P1 high</t>
+        </is>
+      </c>
+      <c r="G164" s="16" t="inlineStr"/>
+      <c r="H164" s="16" t="inlineStr"/>
+      <c r="I164" s="16" t="inlineStr"/>
+    </row>
+    <row r="165" ht="18" customHeight="1">
+      <c r="A165" s="16" t="inlineStr">
+        <is>
+          <t>Outside services we connect to</t>
+        </is>
+      </c>
+      <c r="B165" s="16" t="inlineStr">
+        <is>
+          <t>INCI Beauty (product import)</t>
+        </is>
+      </c>
+      <c r="C165" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D165" s="16" t="inlineStr">
+        <is>
+          <t>Download button inside the fulfillment dashboard</t>
+        </is>
+      </c>
+      <c r="E165" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F165" s="16" t="inlineStr">
+        <is>
+          <t>P1 high</t>
+        </is>
+      </c>
+      <c r="G165" s="16" t="inlineStr"/>
+      <c r="H165" s="16" t="inlineStr"/>
+      <c r="I165" s="16" t="inlineStr"/>
+    </row>
+    <row r="166" ht="18" customHeight="1">
+      <c r="A166" s="16" t="inlineStr">
+        <is>
+          <t>Outside services we connect to</t>
+        </is>
+      </c>
+      <c r="B166" s="16" t="inlineStr">
+        <is>
+          <t>INCI Beauty (product import)</t>
+        </is>
+      </c>
+      <c r="C166" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D166" s="16" t="inlineStr">
+        <is>
+          <t>Placeholder image hosted publicly</t>
+        </is>
+      </c>
+      <c r="E166" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F166" s="16" t="inlineStr">
+        <is>
+          <t>P1 high</t>
+        </is>
+      </c>
+      <c r="G166" s="16" t="inlineStr"/>
+      <c r="H166" s="16" t="inlineStr"/>
+      <c r="I166" s="16" t="inlineStr"/>
+    </row>
+    <row r="167" ht="18" customHeight="1">
+      <c r="A167" s="16" t="inlineStr">
+        <is>
+          <t>Outside services we connect to</t>
+        </is>
+      </c>
+      <c r="B167" s="16" t="inlineStr">
+        <is>
+          <t>INCI Beauty (product import)</t>
+        </is>
+      </c>
+      <c r="C167" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D167" s="16" t="inlineStr">
+        <is>
+          <t>Use a different image per product</t>
+        </is>
+      </c>
+      <c r="E167" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F167" s="16" t="inlineStr">
+        <is>
+          <t>P1 high</t>
+        </is>
+      </c>
+      <c r="G167" s="16" t="inlineStr"/>
+      <c r="H167" s="16" t="inlineStr"/>
+      <c r="I167" s="16" t="inlineStr"/>
+    </row>
+    <row r="168" ht="18" customHeight="1">
+      <c r="A168" s="16" t="inlineStr">
+        <is>
+          <t>Outside services we connect to</t>
+        </is>
+      </c>
+      <c r="B168" s="16" t="inlineStr">
+        <is>
+          <t>INCI Beauty (product import)</t>
+        </is>
+      </c>
+      <c r="C168" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D168" s="16" t="inlineStr">
+        <is>
+          <t>Try a real import on INCI Beauty and confirm it works</t>
+        </is>
+      </c>
+      <c r="E168" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F168" s="16" t="inlineStr">
+        <is>
+          <t>P0 critical</t>
+        </is>
+      </c>
+      <c r="G168" s="16" t="inlineStr"/>
+      <c r="H168" s="16" t="inlineStr"/>
+      <c r="I168" s="16" t="inlineStr"/>
+    </row>
+    <row r="169" ht="20" customHeight="1">
+      <c r="A169" s="14" t="inlineStr">
+        <is>
+          <t>Outside services we connect to</t>
+        </is>
+      </c>
+      <c r="B169" s="14" t="inlineStr">
+        <is>
+          <t>Direx Courier (Bulgarian shipping)</t>
+        </is>
+      </c>
+      <c r="C169" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D169" s="15" t="inlineStr">
+        <is>
+          <t>The courier that picks up parcels from our warehouse and delivers them</t>
+        </is>
+      </c>
+      <c r="E169" s="15" t="inlineStr"/>
+      <c r="F169" s="15" t="inlineStr"/>
+      <c r="G169" s="15" t="inlineStr"/>
+      <c r="H169" s="15" t="inlineStr"/>
+      <c r="I169" s="15" t="inlineStr"/>
+    </row>
+    <row r="170" ht="18" customHeight="1">
+      <c r="A170" s="16" t="inlineStr">
+        <is>
+          <t>Outside services we connect to</t>
+        </is>
+      </c>
+      <c r="B170" s="16" t="inlineStr">
+        <is>
+          <t>Direx Courier (Bulgarian shipping)</t>
+        </is>
+      </c>
+      <c r="C170" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D170" s="16" t="inlineStr">
+        <is>
+          <t>Get our login working with their system</t>
+        </is>
+      </c>
+      <c r="E170" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F170" s="16" t="inlineStr">
+        <is>
+          <t>P0 critical</t>
+        </is>
+      </c>
+      <c r="G170" s="16" t="inlineStr"/>
+      <c r="H170" s="16" t="inlineStr"/>
+      <c r="I170" s="16" t="inlineStr"/>
+    </row>
+    <row r="171" ht="18" customHeight="1">
+      <c r="A171" s="16" t="inlineStr">
+        <is>
+          <t>Outside services we connect to</t>
+        </is>
+      </c>
+      <c r="B171" s="16" t="inlineStr">
+        <is>
+          <t>Direx Courier (Bulgarian shipping)</t>
+        </is>
+      </c>
+      <c r="C171" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D171" s="16" t="inlineStr">
+        <is>
+          <t>Register the warehouse as a sender on their portal</t>
+        </is>
+      </c>
+      <c r="E171" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F171" s="16" t="inlineStr">
+        <is>
+          <t>P0 critical</t>
+        </is>
+      </c>
+      <c r="G171" s="16" t="inlineStr"/>
+      <c r="H171" s="16" t="inlineStr">
+        <is>
+          <t>Operational, not technical</t>
+        </is>
+      </c>
+      <c r="I171" s="16" t="inlineStr"/>
+    </row>
+    <row r="172" ht="18" customHeight="1">
+      <c r="A172" s="16" t="inlineStr">
+        <is>
+          <t>Outside services we connect to</t>
+        </is>
+      </c>
+      <c r="B172" s="16" t="inlineStr">
+        <is>
+          <t>Direx Courier (Bulgarian shipping)</t>
+        </is>
+      </c>
+      <c r="C172" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D172" s="16" t="inlineStr">
+        <is>
+          <t>Confirm whether we ship Bulgaria only, or international too</t>
+        </is>
+      </c>
+      <c r="E172" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F172" s="16" t="inlineStr">
+        <is>
+          <t>P1 high</t>
+        </is>
+      </c>
+      <c r="G172" s="16" t="inlineStr"/>
+      <c r="H172" s="16" t="inlineStr"/>
+      <c r="I172" s="16" t="inlineStr"/>
+    </row>
+    <row r="173" ht="18" customHeight="1">
+      <c r="A173" s="16" t="inlineStr">
+        <is>
+          <t>Outside services we connect to</t>
+        </is>
+      </c>
+      <c r="B173" s="16" t="inlineStr">
+        <is>
+          <t>Direx Courier (Bulgarian shipping)</t>
+        </is>
+      </c>
+      <c r="C173" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D173" s="16" t="inlineStr">
+        <is>
+          <t>Add a Create Shipment button per order with label download</t>
+        </is>
+      </c>
+      <c r="E173" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F173" s="16" t="inlineStr">
+        <is>
+          <t>P0 critical</t>
+        </is>
+      </c>
+      <c r="G173" s="16" t="inlineStr"/>
+      <c r="H173" s="16" t="inlineStr"/>
+      <c r="I173" s="16" t="inlineStr"/>
+    </row>
+    <row r="174" ht="18" customHeight="1">
+      <c r="A174" s="16" t="inlineStr">
+        <is>
+          <t>Outside services we connect to</t>
+        </is>
+      </c>
+      <c r="B174" s="16" t="inlineStr">
+        <is>
+          <t>Direx Courier (Bulgarian shipping)</t>
+        </is>
+      </c>
+      <c r="C174" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D174" s="16" t="inlineStr">
+        <is>
+          <t>Close manifest and schedule pickup actions</t>
+        </is>
+      </c>
+      <c r="E174" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F174" s="16" t="inlineStr">
+        <is>
+          <t>P0 critical</t>
+        </is>
+      </c>
+      <c r="G174" s="16" t="inlineStr"/>
+      <c r="H174" s="16" t="inlineStr"/>
+      <c r="I174" s="16" t="inlineStr"/>
+    </row>
+    <row r="175" ht="18" customHeight="1">
+      <c r="A175" s="16" t="inlineStr">
+        <is>
+          <t>Outside services we connect to</t>
+        </is>
+      </c>
+      <c r="B175" s="16" t="inlineStr">
+        <is>
+          <t>Direx Courier (Bulgarian shipping)</t>
+        </is>
+      </c>
+      <c r="C175" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D175" s="16" t="inlineStr">
+        <is>
+          <t>Automatic tracking updates every 6 hours</t>
+        </is>
+      </c>
+      <c r="E175" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F175" s="16" t="inlineStr">
+        <is>
+          <t>P1 high</t>
+        </is>
+      </c>
+      <c r="G175" s="16" t="inlineStr"/>
+      <c r="H175" s="16" t="inlineStr"/>
+      <c r="I175" s="16" t="inlineStr"/>
+    </row>
+    <row r="176" ht="18" customHeight="1">
+      <c r="A176" s="16" t="inlineStr">
+        <is>
+          <t>Outside services we connect to</t>
+        </is>
+      </c>
+      <c r="B176" s="16" t="inlineStr">
+        <is>
+          <t>Direx Courier (Bulgarian shipping)</t>
+        </is>
+      </c>
+      <c r="C176" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D176" s="16" t="inlineStr">
+        <is>
+          <t>Customer can see tracking from their account</t>
+        </is>
+      </c>
+      <c r="E176" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F176" s="16" t="inlineStr">
+        <is>
+          <t>P1 high</t>
+        </is>
+      </c>
+      <c r="G176" s="16" t="inlineStr"/>
+      <c r="H176" s="16" t="inlineStr"/>
+      <c r="I176" s="16" t="inlineStr"/>
+    </row>
+    <row r="177" ht="18" customHeight="1">
+      <c r="A177" s="16" t="inlineStr">
+        <is>
+          <t>Outside services we connect to</t>
+        </is>
+      </c>
+      <c r="B177" s="16" t="inlineStr">
+        <is>
+          <t>Direx Courier (Bulgarian shipping)</t>
+        </is>
+      </c>
+      <c r="C177" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D177" s="16" t="inlineStr">
+        <is>
+          <t>Shipped email with tracking link</t>
+        </is>
+      </c>
+      <c r="E177" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F177" s="16" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G150" s="16" t="inlineStr"/>
-      <c r="H150" s="16" t="inlineStr"/>
-      <c r="I150" s="16" t="inlineStr"/>
-    </row>
-    <row r="151" ht="18" customHeight="1">
-      <c r="A151" s="16" t="inlineStr">
-        <is>
-          <t>Cross-cutting concerns</t>
-        </is>
-      </c>
-      <c r="B151" s="16" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C151" s="16" t="inlineStr">
+      <c r="G177" s="16" t="inlineStr"/>
+      <c r="H177" s="16" t="inlineStr"/>
+      <c r="I177" s="16" t="inlineStr"/>
+    </row>
+    <row r="178" ht="22" customHeight="1">
+      <c r="A178" s="13" t="inlineStr">
+        <is>
+          <t>DESIGN SYSTEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="20" customHeight="1">
+      <c r="A179" s="14" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="B179" s="14" t="inlineStr">
+        <is>
+          <t>Design Lab (open with ?lab=1)</t>
+        </is>
+      </c>
+      <c r="C179" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D151" s="16" t="inlineStr">
-        <is>
-          <t>Lighthouse audit + remediation</t>
-        </is>
-      </c>
-      <c r="E151" s="19" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F151" s="16" t="inlineStr">
+      <c r="D179" s="15" t="inlineStr">
+        <is>
+          <t>The floating dev panel for trying different fonts, palettes, and card styles live on the page</t>
+        </is>
+      </c>
+      <c r="E179" s="15" t="inlineStr"/>
+      <c r="F179" s="15" t="inlineStr"/>
+      <c r="G179" s="15" t="inlineStr"/>
+      <c r="H179" s="15" t="inlineStr"/>
+      <c r="I179" s="15" t="inlineStr"/>
+    </row>
+    <row r="180" ht="18" customHeight="1">
+      <c r="A180" s="16" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="B180" s="16" t="inlineStr">
+        <is>
+          <t>Design Lab (open with ?lab=1)</t>
+        </is>
+      </c>
+      <c r="C180" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D180" s="16" t="inlineStr">
+        <is>
+          <t>Five font slots (headlines, inner pages, body, inner body, captions and buttons)</t>
+        </is>
+      </c>
+      <c r="E180" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F180" s="16" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G151" s="16" t="inlineStr"/>
-      <c r="H151" s="16" t="inlineStr"/>
-      <c r="I151" s="16" t="inlineStr"/>
+      <c r="G180" s="16" t="inlineStr"/>
+      <c r="H180" s="16" t="inlineStr"/>
+      <c r="I180" s="16" t="inlineStr"/>
+    </row>
+    <row r="181" ht="18" customHeight="1">
+      <c r="A181" s="16" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="B181" s="16" t="inlineStr">
+        <is>
+          <t>Design Lab (open with ?lab=1)</t>
+        </is>
+      </c>
+      <c r="C181" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D181" s="16" t="inlineStr">
+        <is>
+          <t>Roughly 70 fonts to choose from</t>
+        </is>
+      </c>
+      <c r="E181" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F181" s="16" t="inlineStr">
+        <is>
+          <t>P1 high</t>
+        </is>
+      </c>
+      <c r="G181" s="16" t="inlineStr"/>
+      <c r="H181" s="16" t="inlineStr"/>
+      <c r="I181" s="16" t="inlineStr"/>
+    </row>
+    <row r="182" ht="18" customHeight="1">
+      <c r="A182" s="16" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="B182" s="16" t="inlineStr">
+        <is>
+          <t>Design Lab (open with ?lab=1)</t>
+        </is>
+      </c>
+      <c r="C182" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D182" s="16" t="inlineStr">
+        <is>
+          <t>Picker mode: click any text to see what controls it</t>
+        </is>
+      </c>
+      <c r="E182" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F182" s="16" t="inlineStr">
+        <is>
+          <t>P1 high</t>
+        </is>
+      </c>
+      <c r="G182" s="16" t="inlineStr"/>
+      <c r="H182" s="16" t="inlineStr"/>
+      <c r="I182" s="16" t="inlineStr"/>
+    </row>
+    <row r="183" ht="18" customHeight="1">
+      <c r="A183" s="16" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="B183" s="16" t="inlineStr">
+        <is>
+          <t>Design Lab (open with ?lab=1)</t>
+        </is>
+      </c>
+      <c r="C183" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D183" s="16" t="inlineStr">
+        <is>
+          <t>Per element override panel with bold, italic, underline, colour</t>
+        </is>
+      </c>
+      <c r="E183" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F183" s="16" t="inlineStr">
+        <is>
+          <t>P1 high</t>
+        </is>
+      </c>
+      <c r="G183" s="16" t="inlineStr"/>
+      <c r="H183" s="16" t="inlineStr"/>
+      <c r="I183" s="16" t="inlineStr"/>
+    </row>
+    <row r="184" ht="18" customHeight="1">
+      <c r="A184" s="16" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="B184" s="16" t="inlineStr">
+        <is>
+          <t>Design Lab (open with ?lab=1)</t>
+        </is>
+      </c>
+      <c r="C184" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D184" s="16" t="inlineStr">
+        <is>
+          <t>Six built-in design directions plus your own saved ones</t>
+        </is>
+      </c>
+      <c r="E184" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F184" s="16" t="inlineStr">
+        <is>
+          <t>P1 high</t>
+        </is>
+      </c>
+      <c r="G184" s="16" t="inlineStr"/>
+      <c r="H184" s="16" t="inlineStr"/>
+      <c r="I184" s="16" t="inlineStr"/>
+    </row>
+    <row r="185" ht="18" customHeight="1">
+      <c r="A185" s="16" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="B185" s="16" t="inlineStr">
+        <is>
+          <t>Design Lab (open with ?lab=1)</t>
+        </is>
+      </c>
+      <c r="C185" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D185" s="16" t="inlineStr">
+        <is>
+          <t>Six brand inspired directions (Aesop, Le Labo, Glossier, etc.)</t>
+        </is>
+      </c>
+      <c r="E185" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F185" s="16" t="inlineStr">
+        <is>
+          <t>P2 medium</t>
+        </is>
+      </c>
+      <c r="G185" s="16" t="inlineStr"/>
+      <c r="H185" s="16" t="inlineStr"/>
+      <c r="I185" s="16" t="inlineStr"/>
+    </row>
+    <row r="186" ht="18" customHeight="1">
+      <c r="A186" s="16" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="B186" s="16" t="inlineStr">
+        <is>
+          <t>Design Lab (open with ?lab=1)</t>
+        </is>
+      </c>
+      <c r="C186" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D186" s="16" t="inlineStr">
+        <is>
+          <t>Seven built-in palettes plus your own hex picker</t>
+        </is>
+      </c>
+      <c r="E186" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F186" s="16" t="inlineStr">
+        <is>
+          <t>P1 high</t>
+        </is>
+      </c>
+      <c r="G186" s="16" t="inlineStr"/>
+      <c r="H186" s="16" t="inlineStr"/>
+      <c r="I186" s="16" t="inlineStr"/>
+    </row>
+    <row r="187" ht="18" customHeight="1">
+      <c r="A187" s="16" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="B187" s="16" t="inlineStr">
+        <is>
+          <t>Design Lab (open with ?lab=1)</t>
+        </is>
+      </c>
+      <c r="C187" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D187" s="16" t="inlineStr">
+        <is>
+          <t>Card corner style picker</t>
+        </is>
+      </c>
+      <c r="E187" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F187" s="16" t="inlineStr">
+        <is>
+          <t>P2 medium</t>
+        </is>
+      </c>
+      <c r="G187" s="16" t="inlineStr"/>
+      <c r="H187" s="16" t="inlineStr"/>
+      <c r="I187" s="16" t="inlineStr"/>
+    </row>
+    <row r="188" ht="18" customHeight="1">
+      <c r="A188" s="16" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="B188" s="16" t="inlineStr">
+        <is>
+          <t>Design Lab (open with ?lab=1)</t>
+        </is>
+      </c>
+      <c r="C188" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D188" s="16" t="inlineStr">
+        <is>
+          <t>Modular palette: card surface, button background and text, borders, accents</t>
+        </is>
+      </c>
+      <c r="E188" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F188" s="16" t="inlineStr">
+        <is>
+          <t>P1 high</t>
+        </is>
+      </c>
+      <c r="G188" s="16" t="inlineStr"/>
+      <c r="H188" s="16" t="inlineStr"/>
+      <c r="I188" s="16" t="inlineStr"/>
+    </row>
+    <row r="189" ht="18" customHeight="1">
+      <c r="A189" s="16" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="B189" s="16" t="inlineStr">
+        <is>
+          <t>Design Lab (open with ?lab=1)</t>
+        </is>
+      </c>
+      <c r="C189" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D189" s="16" t="inlineStr">
+        <is>
+          <t>Each section can collapse or expand</t>
+        </is>
+      </c>
+      <c r="E189" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F189" s="16" t="inlineStr">
+        <is>
+          <t>P2 medium</t>
+        </is>
+      </c>
+      <c r="G189" s="16" t="inlineStr"/>
+      <c r="H189" s="16" t="inlineStr"/>
+      <c r="I189" s="16" t="inlineStr"/>
+    </row>
+    <row r="190" ht="18" customHeight="1">
+      <c r="A190" s="16" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="B190" s="16" t="inlineStr">
+        <is>
+          <t>Design Lab (open with ?lab=1)</t>
+        </is>
+      </c>
+      <c r="C190" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D190" s="16" t="inlineStr">
+        <is>
+          <t>Sitemap tab inside the panel (still there for quick navigation)</t>
+        </is>
+      </c>
+      <c r="E190" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F190" s="16" t="inlineStr">
+        <is>
+          <t>P3 low</t>
+        </is>
+      </c>
+      <c r="G190" s="16" t="inlineStr"/>
+      <c r="H190" s="16" t="inlineStr"/>
+      <c r="I190" s="16" t="inlineStr"/>
+    </row>
+    <row r="191" ht="20" customHeight="1">
+      <c r="A191" s="14" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="B191" s="14" t="inlineStr">
+        <is>
+          <t>Design tokens</t>
+        </is>
+      </c>
+      <c r="C191" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D191" s="15" t="inlineStr">
+        <is>
+          <t>The shared colour and font variables that the whole site reads from</t>
+        </is>
+      </c>
+      <c r="E191" s="15" t="inlineStr"/>
+      <c r="F191" s="15" t="inlineStr"/>
+      <c r="G191" s="15" t="inlineStr"/>
+      <c r="H191" s="15" t="inlineStr"/>
+      <c r="I191" s="15" t="inlineStr"/>
+    </row>
+    <row r="192" ht="18" customHeight="1">
+      <c r="A192" s="16" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="B192" s="16" t="inlineStr">
+        <is>
+          <t>Design tokens</t>
+        </is>
+      </c>
+      <c r="C192" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D192" s="16" t="inlineStr">
+        <is>
+          <t>Font tokens applied across the site</t>
+        </is>
+      </c>
+      <c r="E192" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F192" s="16" t="inlineStr">
+        <is>
+          <t>P1 high</t>
+        </is>
+      </c>
+      <c r="G192" s="16" t="inlineStr"/>
+      <c r="H192" s="16" t="inlineStr"/>
+      <c r="I192" s="16" t="inlineStr"/>
+    </row>
+    <row r="193" ht="18" customHeight="1">
+      <c r="A193" s="16" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="B193" s="16" t="inlineStr">
+        <is>
+          <t>Design tokens</t>
+        </is>
+      </c>
+      <c r="C193" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D193" s="16" t="inlineStr">
+        <is>
+          <t>Palette tokens (background, card, ink, button, line, accents)</t>
+        </is>
+      </c>
+      <c r="E193" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F193" s="16" t="inlineStr">
+        <is>
+          <t>P1 high</t>
+        </is>
+      </c>
+      <c r="G193" s="16" t="inlineStr"/>
+      <c r="H193" s="16" t="inlineStr"/>
+      <c r="I193" s="16" t="inlineStr"/>
+    </row>
+    <row r="194" ht="18" customHeight="1">
+      <c r="A194" s="16" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="B194" s="16" t="inlineStr">
+        <is>
+          <t>Design tokens</t>
+        </is>
+      </c>
+      <c r="C194" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D194" s="16" t="inlineStr">
+        <is>
+          <t>Card radius token</t>
+        </is>
+      </c>
+      <c r="E194" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F194" s="16" t="inlineStr">
+        <is>
+          <t>P2 medium</t>
+        </is>
+      </c>
+      <c r="G194" s="16" t="inlineStr"/>
+      <c r="H194" s="16" t="inlineStr"/>
+      <c r="I194" s="16" t="inlineStr"/>
+    </row>
+    <row r="195" ht="18" customHeight="1">
+      <c r="A195" s="16" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="B195" s="16" t="inlineStr">
+        <is>
+          <t>Design tokens</t>
+        </is>
+      </c>
+      <c r="C195" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D195" s="16" t="inlineStr">
+        <is>
+          <t>Refactor all old hardcoded fonts to use the tokens</t>
+        </is>
+      </c>
+      <c r="E195" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F195" s="16" t="inlineStr">
+        <is>
+          <t>P1 high</t>
+        </is>
+      </c>
+      <c r="G195" s="16" t="inlineStr"/>
+      <c r="H195" s="16" t="inlineStr"/>
+      <c r="I195" s="16" t="inlineStr"/>
+    </row>
+    <row r="196" ht="18" customHeight="1">
+      <c r="A196" s="16" t="inlineStr">
+        <is>
+          <t>Design system</t>
+        </is>
+      </c>
+      <c r="B196" s="16" t="inlineStr">
+        <is>
+          <t>Design tokens</t>
+        </is>
+      </c>
+      <c r="C196" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D196" s="16" t="inlineStr">
+        <is>
+          <t>Refactor inner pages (quiz, account) to use the same card token</t>
+        </is>
+      </c>
+      <c r="E196" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F196" s="16" t="inlineStr">
+        <is>
+          <t>P2 medium</t>
+        </is>
+      </c>
+      <c r="G196" s="16" t="inlineStr"/>
+      <c r="H196" s="16" t="inlineStr"/>
+      <c r="I196" s="16" t="inlineStr"/>
+    </row>
+    <row r="197" ht="22" customHeight="1">
+      <c r="A197" s="13" t="inlineStr">
+        <is>
+          <t>OTHER THINGS TO DO</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="20" customHeight="1">
+      <c r="A198" s="14" t="inlineStr">
+        <is>
+          <t>Other things to do</t>
+        </is>
+      </c>
+      <c r="B198" s="14" t="inlineStr">
+        <is>
+          <t>Brand identity</t>
+        </is>
+      </c>
+      <c r="C198" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D198" s="15" t="inlineStr">
+        <is>
+          <t>Logo, favicon, brand voice</t>
+        </is>
+      </c>
+      <c r="E198" s="15" t="inlineStr"/>
+      <c r="F198" s="15" t="inlineStr"/>
+      <c r="G198" s="15" t="inlineStr"/>
+      <c r="H198" s="15" t="inlineStr"/>
+      <c r="I198" s="15" t="inlineStr"/>
+    </row>
+    <row r="199" ht="18" customHeight="1">
+      <c r="A199" s="16" t="inlineStr">
+        <is>
+          <t>Other things to do</t>
+        </is>
+      </c>
+      <c r="B199" s="16" t="inlineStr">
+        <is>
+          <t>Brand identity</t>
+        </is>
+      </c>
+      <c r="C199" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D199" s="16" t="inlineStr">
+        <is>
+          <t>Final logo design (currently using the rusalka illustration)</t>
+        </is>
+      </c>
+      <c r="E199" s="20" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="F199" s="16" t="inlineStr">
+        <is>
+          <t>P0 critical</t>
+        </is>
+      </c>
+      <c r="G199" s="16" t="inlineStr"/>
+      <c r="H199" s="16" t="inlineStr"/>
+      <c r="I199" s="16" t="inlineStr"/>
+    </row>
+    <row r="200" ht="18" customHeight="1">
+      <c r="A200" s="16" t="inlineStr">
+        <is>
+          <t>Other things to do</t>
+        </is>
+      </c>
+      <c r="B200" s="16" t="inlineStr">
+        <is>
+          <t>Brand identity</t>
+        </is>
+      </c>
+      <c r="C200" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D200" s="16" t="inlineStr">
+        <is>
+          <t>Favicon that matches the brand</t>
+        </is>
+      </c>
+      <c r="E200" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F200" s="16" t="inlineStr">
+        <is>
+          <t>P2 medium</t>
+        </is>
+      </c>
+      <c r="G200" s="16" t="inlineStr"/>
+      <c r="H200" s="16" t="inlineStr"/>
+      <c r="I200" s="16" t="inlineStr"/>
+    </row>
+    <row r="201" ht="18" customHeight="1">
+      <c r="A201" s="16" t="inlineStr">
+        <is>
+          <t>Other things to do</t>
+        </is>
+      </c>
+      <c r="B201" s="16" t="inlineStr">
+        <is>
+          <t>Brand identity</t>
+        </is>
+      </c>
+      <c r="C201" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D201" s="16" t="inlineStr">
+        <is>
+          <t>Preview image used when sharing on social media</t>
+        </is>
+      </c>
+      <c r="E201" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F201" s="16" t="inlineStr">
+        <is>
+          <t>P2 medium</t>
+        </is>
+      </c>
+      <c r="G201" s="16" t="inlineStr"/>
+      <c r="H201" s="16" t="inlineStr"/>
+      <c r="I201" s="16" t="inlineStr"/>
+    </row>
+    <row r="202" ht="18" customHeight="1">
+      <c r="A202" s="16" t="inlineStr">
+        <is>
+          <t>Other things to do</t>
+        </is>
+      </c>
+      <c r="B202" s="16" t="inlineStr">
+        <is>
+          <t>Brand identity</t>
+        </is>
+      </c>
+      <c r="C202" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D202" s="16" t="inlineStr">
+        <is>
+          <t>Written guide for brand voice and tone</t>
+        </is>
+      </c>
+      <c r="E202" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F202" s="16" t="inlineStr">
+        <is>
+          <t>P2 medium</t>
+        </is>
+      </c>
+      <c r="G202" s="16" t="inlineStr"/>
+      <c r="H202" s="16" t="inlineStr"/>
+      <c r="I202" s="16" t="inlineStr"/>
+    </row>
+    <row r="203" ht="20" customHeight="1">
+      <c r="A203" s="14" t="inlineStr">
+        <is>
+          <t>Other things to do</t>
+        </is>
+      </c>
+      <c r="B203" s="14" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C203" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D203" s="15" t="inlineStr">
+        <is>
+          <t>Making the site usable by people with disabilities</t>
+        </is>
+      </c>
+      <c r="E203" s="15" t="inlineStr"/>
+      <c r="F203" s="15" t="inlineStr"/>
+      <c r="G203" s="15" t="inlineStr"/>
+      <c r="H203" s="15" t="inlineStr"/>
+      <c r="I203" s="15" t="inlineStr"/>
+    </row>
+    <row r="204" ht="18" customHeight="1">
+      <c r="A204" s="16" t="inlineStr">
+        <is>
+          <t>Other things to do</t>
+        </is>
+      </c>
+      <c r="B204" s="16" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C204" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D204" s="16" t="inlineStr">
+        <is>
+          <t>Check colour contrast on every palette</t>
+        </is>
+      </c>
+      <c r="E204" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F204" s="16" t="inlineStr">
+        <is>
+          <t>P1 high</t>
+        </is>
+      </c>
+      <c r="G204" s="16" t="inlineStr"/>
+      <c r="H204" s="16" t="inlineStr"/>
+      <c r="I204" s="16" t="inlineStr"/>
+    </row>
+    <row r="205" ht="18" customHeight="1">
+      <c r="A205" s="16" t="inlineStr">
+        <is>
+          <t>Other things to do</t>
+        </is>
+      </c>
+      <c r="B205" s="16" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C205" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D205" s="16" t="inlineStr">
+        <is>
+          <t>Make the quiz fully navigable with the keyboard</t>
+        </is>
+      </c>
+      <c r="E205" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F205" s="16" t="inlineStr">
+        <is>
+          <t>P1 high</t>
+        </is>
+      </c>
+      <c r="G205" s="16" t="inlineStr"/>
+      <c r="H205" s="16" t="inlineStr"/>
+      <c r="I205" s="16" t="inlineStr"/>
+    </row>
+    <row r="206" ht="18" customHeight="1">
+      <c r="A206" s="16" t="inlineStr">
+        <is>
+          <t>Other things to do</t>
+        </is>
+      </c>
+      <c r="B206" s="16" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C206" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D206" s="16" t="inlineStr">
+        <is>
+          <t>Make the results page work for screen readers</t>
+        </is>
+      </c>
+      <c r="E206" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F206" s="16" t="inlineStr">
+        <is>
+          <t>P1 high</t>
+        </is>
+      </c>
+      <c r="G206" s="16" t="inlineStr"/>
+      <c r="H206" s="16" t="inlineStr"/>
+      <c r="I206" s="16" t="inlineStr"/>
+    </row>
+    <row r="207" ht="18" customHeight="1">
+      <c r="A207" s="16" t="inlineStr">
+        <is>
+          <t>Other things to do</t>
+        </is>
+      </c>
+      <c r="B207" s="16" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C207" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D207" s="16" t="inlineStr">
+        <is>
+          <t>Make sure every clickable thing shows a focus ring</t>
+        </is>
+      </c>
+      <c r="E207" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F207" s="16" t="inlineStr">
+        <is>
+          <t>P1 high</t>
+        </is>
+      </c>
+      <c r="G207" s="16" t="inlineStr"/>
+      <c r="H207" s="16" t="inlineStr"/>
+      <c r="I207" s="16" t="inlineStr"/>
+    </row>
+    <row r="208" ht="20" customHeight="1">
+      <c r="A208" s="14" t="inlineStr">
+        <is>
+          <t>Other things to do</t>
+        </is>
+      </c>
+      <c r="B208" s="14" t="inlineStr">
+        <is>
+          <t>Speed and performance</t>
+        </is>
+      </c>
+      <c r="C208" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D208" s="15" t="inlineStr">
+        <is>
+          <t>Making the site fast to load</t>
+        </is>
+      </c>
+      <c r="E208" s="15" t="inlineStr"/>
+      <c r="F208" s="15" t="inlineStr"/>
+      <c r="G208" s="15" t="inlineStr"/>
+      <c r="H208" s="15" t="inlineStr"/>
+      <c r="I208" s="15" t="inlineStr"/>
+    </row>
+    <row r="209" ht="18" customHeight="1">
+      <c r="A209" s="16" t="inlineStr">
+        <is>
+          <t>Other things to do</t>
+        </is>
+      </c>
+      <c r="B209" s="16" t="inlineStr">
+        <is>
+          <t>Speed and performance</t>
+        </is>
+      </c>
+      <c r="C209" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D209" s="16" t="inlineStr">
+        <is>
+          <t>Hero video set up to load quickly</t>
+        </is>
+      </c>
+      <c r="E209" s="17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F209" s="16" t="inlineStr">
+        <is>
+          <t>P1 high</t>
+        </is>
+      </c>
+      <c r="G209" s="16" t="inlineStr"/>
+      <c r="H209" s="16" t="inlineStr"/>
+      <c r="I209" s="16" t="inlineStr"/>
+    </row>
+    <row r="210" ht="18" customHeight="1">
+      <c r="A210" s="16" t="inlineStr">
+        <is>
+          <t>Other things to do</t>
+        </is>
+      </c>
+      <c r="B210" s="16" t="inlineStr">
+        <is>
+          <t>Speed and performance</t>
+        </is>
+      </c>
+      <c r="C210" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D210" s="16" t="inlineStr">
+        <is>
+          <t>Re-encode hero video to a smaller modern format</t>
+        </is>
+      </c>
+      <c r="E210" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F210" s="16" t="inlineStr">
+        <is>
+          <t>P2 medium</t>
+        </is>
+      </c>
+      <c r="G210" s="16" t="inlineStr"/>
+      <c r="H210" s="16" t="inlineStr"/>
+      <c r="I210" s="16" t="inlineStr"/>
+    </row>
+    <row r="211" ht="18" customHeight="1">
+      <c r="A211" s="16" t="inlineStr">
+        <is>
+          <t>Other things to do</t>
+        </is>
+      </c>
+      <c r="B211" s="16" t="inlineStr">
+        <is>
+          <t>Speed and performance</t>
+        </is>
+      </c>
+      <c r="C211" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D211" s="16" t="inlineStr">
+        <is>
+          <t>Use Next.js optimised image component for product photos</t>
+        </is>
+      </c>
+      <c r="E211" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F211" s="16" t="inlineStr">
+        <is>
+          <t>P1 high</t>
+        </is>
+      </c>
+      <c r="G211" s="16" t="inlineStr"/>
+      <c r="H211" s="16" t="inlineStr"/>
+      <c r="I211" s="16" t="inlineStr"/>
+    </row>
+    <row r="212" ht="18" customHeight="1">
+      <c r="A212" s="16" t="inlineStr">
+        <is>
+          <t>Other things to do</t>
+        </is>
+      </c>
+      <c r="B212" s="16" t="inlineStr">
+        <is>
+          <t>Speed and performance</t>
+        </is>
+      </c>
+      <c r="C212" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D212" s="16" t="inlineStr">
+        <is>
+          <t>Load only the font weights we actually use</t>
+        </is>
+      </c>
+      <c r="E212" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F212" s="16" t="inlineStr">
+        <is>
+          <t>P2 medium</t>
+        </is>
+      </c>
+      <c r="G212" s="16" t="inlineStr"/>
+      <c r="H212" s="16" t="inlineStr"/>
+      <c r="I212" s="16" t="inlineStr"/>
+    </row>
+    <row r="213" ht="18" customHeight="1">
+      <c r="A213" s="16" t="inlineStr">
+        <is>
+          <t>Other things to do</t>
+        </is>
+      </c>
+      <c r="B213" s="16" t="inlineStr">
+        <is>
+          <t>Speed and performance</t>
+        </is>
+      </c>
+      <c r="C213" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D213" s="16" t="inlineStr">
+        <is>
+          <t>Run a Google speed test and fix the worst issues</t>
+        </is>
+      </c>
+      <c r="E213" s="19" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F213" s="16" t="inlineStr">
+        <is>
+          <t>P1 high</t>
+        </is>
+      </c>
+      <c r="G213" s="16" t="inlineStr"/>
+      <c r="H213" s="16" t="inlineStr"/>
+      <c r="I213" s="16" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="10">
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A134:I134"/>
+    <mergeCell ref="A128:I128"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A116:I116"/>
-    <mergeCell ref="A70:I70"/>
-    <mergeCell ref="A56:I56"/>
-    <mergeCell ref="A135:I135"/>
-    <mergeCell ref="A87:I87"/>
-    <mergeCell ref="A48:I48"/>
+    <mergeCell ref="A178:I178"/>
+    <mergeCell ref="A84:I84"/>
+    <mergeCell ref="A150:I150"/>
+    <mergeCell ref="A197:I197"/>
+    <mergeCell ref="A120:I120"/>
+    <mergeCell ref="A100:I100"/>
   </mergeCells>
-  <conditionalFormatting sqref="E2:E151">
+  <conditionalFormatting sqref="E2:E213">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>
@@ -5845,10 +7678,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="E4 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E16 E17 E18 E19 E20 E21 E23 E24 E25 E26 E27 E28 E30 E31 E32 E33 E34 E35 E36 E38 E39 E40 E41 E42 E44 E45 E46 E47 E50 E51 E52 E53 E54 E55 E58 E59 E60 E61 E63 E64 E65 E67 E68 E69 E72 E73 E74 E75 E76 E77 E78 E79 E80 E81 E83 E84 E85 E86 E89 E90 E91 E92 E93 E95 E96 E97 E98 E99 E100 E102 E103 E104 E105 E106 E108 E109 E110 E111 E112 E113 E114 E115 E118 E119 E120 E121 E122 E123 E124 E125 E126 E127 E128 E130 E131 E132 E133 E134 E137 E138 E139 E140 E142 E143 E144 E145 E147 E148 E149 E150 E151" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid status" error="Pick a status from the dropdown" type="list">
+    <dataValidation sqref="E4 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E17 E18 E19 E20 E21 E23 E25 E27 E29 E31 E33 E35 E37 E39 E41 E43 E45 E47 E49 E51 E53 E55 E57 E59 E61 E63 E65 E67 E69 E71 E73 E75 E77 E79 E81 E83 E86 E87 E88 E89 E90 E91 E93 E94 E95 E97 E98 E99 E102 E103 E104 E105 E106 E107 E108 E110 E111 E112 E113 E114 E116 E117 E118 E119 E122 E123 E124 E125 E126 E127 E130 E131 E132 E133 E136 E137 E138 E139 E140 E141 E142 E143 E144 E145 E147 E148 E149 E152 E153 E154 E155 E157 E158 E159 E160 E161 E162 E164 E165 E166 E167 E168 E170 E171 E172 E173 E174 E175 E176 E177 E180 E181 E182 E183 E184 E185 E186 E187 E188 E189 E190 E192 E193 E194 E195 E196 E199 E200 E201 E202 E204 E205 E206 E207 E209 E210 E211 E212 E213" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid status" error="Pick a status from the dropdown" type="list">
       <formula1>"Todo,In progress,Done,Blocked,Skipped,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F16 F17 F18 F19 F20 F21 F23 F24 F25 F26 F27 F28 F30 F31 F32 F33 F34 F35 F36 F38 F39 F40 F41 F42 F44 F45 F46 F47 F50 F51 F52 F53 F54 F55 F58 F59 F60 F61 F63 F64 F65 F67 F68 F69 F72 F73 F74 F75 F76 F77 F78 F79 F80 F81 F83 F84 F85 F86 F89 F90 F91 F92 F93 F95 F96 F97 F98 F99 F100 F102 F103 F104 F105 F106 F108 F109 F110 F111 F112 F113 F114 F115 F118 F119 F120 F121 F122 F123 F124 F125 F126 F127 F128 F130 F131 F132 F133 F134 F137 F138 F139 F140 F142 F143 F144 F145 F147 F148 F149 F150 F151" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F17 F18 F19 F20 F21 F23 F25 F27 F29 F31 F33 F35 F37 F39 F41 F43 F45 F47 F49 F51 F53 F55 F57 F59 F61 F63 F65 F67 F69 F71 F73 F75 F77 F79 F81 F83 F86 F87 F88 F89 F90 F91 F93 F94 F95 F97 F98 F99 F102 F103 F104 F105 F106 F107 F108 F110 F111 F112 F113 F114 F116 F117 F118 F119 F122 F123 F124 F125 F126 F127 F130 F131 F132 F133 F136 F137 F138 F139 F140 F141 F142 F143 F144 F145 F147 F148 F149 F152 F153 F154 F155 F157 F158 F159 F160 F161 F162 F164 F165 F166 F167 F168 F170 F171 F172 F173 F174 F175 F176 F177 F180 F181 F182 F183 F184 F185 F186 F187 F188 F189 F190 F192 F193 F194 F195 F196 F199 F200 F201 F202 F204 F205 F206 F207 F209 F210 F211 F212 F213" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P0 critical,P1 high,P2 medium,P3 low"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/Atelier-Rusalka-Sitemap.xlsx
+++ b/docs/Atelier-Rusalka-Sitemap.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +36,13 @@
       <b val="1"/>
       <color rgb="00F8F2E6"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Helvetica"/>
+      <b val="1"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="Helvetica"/>
@@ -138,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -146,25 +153,28 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -658,405 +668,405 @@
           <t>/</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>The landing page (hero video, featured section, subscription cards, footer)</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="4" t="inlineStr"/>
+      <c r="E3" s="5" t="inlineStr"/>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr"/>
+      <c r="H3" s="5" t="inlineStr"/>
+      <c r="I3" s="5" t="inlineStr"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Homepage</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Top promo bar with welcome offer</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Homepage</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Site nav with logo and wordmark</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Homepage</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>Hero with single looping video</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Homepage</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Hero CTA button placed bottom right</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Homepage</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>Featured section with halo badge and trust line</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr"/>
-      <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Homepage</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>Compose your formula button copy</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr"/>
-      <c r="H9" s="5" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Homepage</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>Subscription section with three cards</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr"/>
+      <c r="I10" s="6" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Homepage</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>Footer that scales with the page</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Homepage</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Mobile menu (hamburger)</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Homepage</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>Layout scales to large external monitors</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr"/>
-      <c r="H13" s="5" t="inlineStr"/>
-      <c r="I13" s="5" t="inlineStr"/>
+      <c r="G13" s="6" t="inlineStr"/>
+      <c r="H13" s="6" t="inlineStr"/>
+      <c r="I13" s="6" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Homepage</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>Real product photo for featured section</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr"/>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>Waiting on photography assets</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -1081,199 +1091,199 @@
           <t>/quiz</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>The quiz is a single page that walks the customer through 31 questions one at a time. Each question below shares the same URL but is tracked separately so we can polish each step.</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
-      <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="4" t="inlineStr"/>
-      <c r="I16" s="4" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>Quiz overview</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>/quiz</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>Quiz framework working end to end</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
+      <c r="I17" s="6" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>Quiz overview</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>/quiz</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>Each question reachable by a step number in the URL</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>In progress</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>Refactoring quiz from single-page screen state to per-route pages (/quiz/q/[id]). Designers can deep-link any question.</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr"/>
+      <c r="I18" s="6" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>Quiz overview</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>/quiz</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>Save partial answers if customer drops off</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr"/>
-      <c r="H19" s="5" t="inlineStr"/>
-      <c r="I19" s="5" t="inlineStr"/>
+      <c r="G19" s="6" t="inlineStr"/>
+      <c r="H19" s="6" t="inlineStr"/>
+      <c r="I19" s="6" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Quiz overview</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>/quiz</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>Polish quiz typography across all questions</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr"/>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>Headings and body text feel too small or mono on some steps</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr"/>
+      <c r="I20" s="6" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>Quiz overview</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>/quiz</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>Mobile usability check on every question</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr"/>
-      <c r="H21" s="5" t="inlineStr"/>
-      <c r="I21" s="5" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+      <c r="I21" s="6" t="inlineStr"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
@@ -1291,51 +1301,51 @@
           <t>/quiz/q/1</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>About You: How old are you?</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="4" t="inlineStr"/>
-      <c r="H22" s="4" t="inlineStr"/>
-      <c r="I22" s="4" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>Step 1 of 31</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>/quiz/q/1</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>Design and copy polish for this step</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
+      <c r="G23" s="6" t="inlineStr"/>
+      <c r="H23" s="6" t="inlineStr"/>
+      <c r="I23" s="6" t="inlineStr"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
@@ -1353,51 +1363,51 @@
           <t>/quiz/sex</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>About You: What is your biological sex?</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr"/>
-      <c r="G24" s="4" t="inlineStr"/>
-      <c r="H24" s="4" t="inlineStr"/>
-      <c r="I24" s="4" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>Step 2 of 31</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>/quiz/sex</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>Design and copy polish for this step</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr"/>
-      <c r="H25" s="5" t="inlineStr"/>
-      <c r="I25" s="5" t="inlineStr"/>
+      <c r="G25" s="6" t="inlineStr"/>
+      <c r="H25" s="6" t="inlineStr"/>
+      <c r="I25" s="6" t="inlineStr"/>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
@@ -1415,51 +1425,51 @@
           <t>/quiz/q/3</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>About You: Where do you live?</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr"/>
-      <c r="F26" s="4" t="inlineStr"/>
-      <c r="G26" s="4" t="inlineStr"/>
-      <c r="H26" s="4" t="inlineStr"/>
-      <c r="I26" s="4" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>Step 3 of 31</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>/quiz/q/3</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>Design and copy polish for this step</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr"/>
-      <c r="H27" s="5" t="inlineStr"/>
-      <c r="I27" s="5" t="inlineStr"/>
+      <c r="G27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="inlineStr"/>
+      <c r="I27" s="6" t="inlineStr"/>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
@@ -1477,51 +1487,51 @@
           <t>/quiz/q/4</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>About You: How would you describe your environment?</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr"/>
-      <c r="F28" s="4" t="inlineStr"/>
-      <c r="G28" s="4" t="inlineStr"/>
-      <c r="H28" s="4" t="inlineStr"/>
-      <c r="I28" s="4" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>Step 4 of 31</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>/quiz/q/4</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>Design and copy polish for this step</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
+      <c r="G29" s="6" t="inlineStr"/>
+      <c r="H29" s="6" t="inlineStr"/>
+      <c r="I29" s="6" t="inlineStr"/>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
@@ -1539,51 +1549,51 @@
           <t>/quiz/q/5</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>About You: How much water do you drink daily?</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr"/>
-      <c r="F30" s="4" t="inlineStr"/>
-      <c r="G30" s="4" t="inlineStr"/>
-      <c r="H30" s="4" t="inlineStr"/>
-      <c r="I30" s="4" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Step 5 of 31</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>/quiz/q/5</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>Design and copy polish for this step</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr"/>
-      <c r="H31" s="5" t="inlineStr"/>
-      <c r="I31" s="5" t="inlineStr"/>
+      <c r="G31" s="6" t="inlineStr"/>
+      <c r="H31" s="6" t="inlineStr"/>
+      <c r="I31" s="6" t="inlineStr"/>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
@@ -1601,51 +1611,51 @@
           <t>/quiz/q/6</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>About You: How many hours of sleep do you typically get?</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr"/>
-      <c r="F32" s="4" t="inlineStr"/>
-      <c r="G32" s="4" t="inlineStr"/>
-      <c r="H32" s="4" t="inlineStr"/>
-      <c r="I32" s="4" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="5" t="inlineStr"/>
+      <c r="I32" s="5" t="inlineStr"/>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>Step 6 of 31</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>/quiz/q/6</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>Design and copy polish for this step</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr"/>
-      <c r="H33" s="5" t="inlineStr"/>
-      <c r="I33" s="5" t="inlineStr"/>
+      <c r="G33" s="6" t="inlineStr"/>
+      <c r="H33" s="6" t="inlineStr"/>
+      <c r="I33" s="6" t="inlineStr"/>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
@@ -1663,51 +1673,51 @@
           <t>/quiz/q/7</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>About You: How would you rate your daily stress level?</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr"/>
-      <c r="F34" s="4" t="inlineStr"/>
-      <c r="G34" s="4" t="inlineStr"/>
-      <c r="H34" s="4" t="inlineStr"/>
-      <c r="I34" s="4" t="inlineStr"/>
+      <c r="E34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="5" t="inlineStr"/>
+      <c r="I34" s="5" t="inlineStr"/>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>Step 7 of 31</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>/quiz/q/7</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>Design and copy polish for this step</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr"/>
-      <c r="H35" s="5" t="inlineStr"/>
-      <c r="I35" s="5" t="inlineStr"/>
+      <c r="G35" s="6" t="inlineStr"/>
+      <c r="H35" s="6" t="inlineStr"/>
+      <c r="I35" s="6" t="inlineStr"/>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
@@ -1725,51 +1735,51 @@
           <t>/quiz/q/8</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>About You: How would you describe your diet?</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr"/>
-      <c r="F36" s="4" t="inlineStr"/>
-      <c r="G36" s="4" t="inlineStr"/>
-      <c r="H36" s="4" t="inlineStr"/>
-      <c r="I36" s="4" t="inlineStr"/>
+      <c r="E36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="5" t="inlineStr"/>
+      <c r="H36" s="5" t="inlineStr"/>
+      <c r="I36" s="5" t="inlineStr"/>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>Step 8 of 31</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>/quiz/q/8</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>Design and copy polish for this step</t>
         </is>
       </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr"/>
-      <c r="H37" s="5" t="inlineStr"/>
-      <c r="I37" s="5" t="inlineStr"/>
+      <c r="G37" s="6" t="inlineStr"/>
+      <c r="H37" s="6" t="inlineStr"/>
+      <c r="I37" s="6" t="inlineStr"/>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
@@ -1787,51 +1797,51 @@
           <t>/quiz/q/9</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>About You: How much daily sun exposure do you get?</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr"/>
-      <c r="F38" s="4" t="inlineStr"/>
-      <c r="G38" s="4" t="inlineStr"/>
-      <c r="H38" s="4" t="inlineStr"/>
-      <c r="I38" s="4" t="inlineStr"/>
+      <c r="E38" s="5" t="inlineStr"/>
+      <c r="F38" s="5" t="inlineStr"/>
+      <c r="G38" s="5" t="inlineStr"/>
+      <c r="H38" s="5" t="inlineStr"/>
+      <c r="I38" s="5" t="inlineStr"/>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>Step 9 of 31</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>/quiz/q/9</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>Design and copy polish for this step</t>
         </is>
       </c>
-      <c r="E39" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr"/>
-      <c r="H39" s="5" t="inlineStr"/>
-      <c r="I39" s="5" t="inlineStr"/>
+      <c r="G39" s="6" t="inlineStr"/>
+      <c r="H39" s="6" t="inlineStr"/>
+      <c r="I39" s="6" t="inlineStr"/>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
@@ -1849,51 +1859,51 @@
           <t>/quiz/q/10</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>About You: Are you currently pregnant or breastfeeding?</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr"/>
-      <c r="F40" s="4" t="inlineStr"/>
-      <c r="G40" s="4" t="inlineStr"/>
-      <c r="H40" s="4" t="inlineStr"/>
-      <c r="I40" s="4" t="inlineStr"/>
+      <c r="E40" s="5" t="inlineStr"/>
+      <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="5" t="inlineStr"/>
+      <c r="H40" s="5" t="inlineStr"/>
+      <c r="I40" s="5" t="inlineStr"/>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>Step 10 of 31</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>/quiz/q/10</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>Design and copy polish for this step</t>
         </is>
       </c>
-      <c r="E41" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr"/>
-      <c r="H41" s="5" t="inlineStr"/>
-      <c r="I41" s="5" t="inlineStr"/>
+      <c r="G41" s="6" t="inlineStr"/>
+      <c r="H41" s="6" t="inlineStr"/>
+      <c r="I41" s="6" t="inlineStr"/>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
@@ -1911,51 +1921,51 @@
           <t>/quiz/q/11</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>Your Skin: How would you describe your skin type?</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr"/>
-      <c r="F42" s="4" t="inlineStr"/>
-      <c r="G42" s="4" t="inlineStr"/>
-      <c r="H42" s="4" t="inlineStr"/>
-      <c r="I42" s="4" t="inlineStr"/>
+      <c r="E42" s="5" t="inlineStr"/>
+      <c r="F42" s="5" t="inlineStr"/>
+      <c r="G42" s="5" t="inlineStr"/>
+      <c r="H42" s="5" t="inlineStr"/>
+      <c r="I42" s="5" t="inlineStr"/>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>Step 11 of 31</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>/quiz/q/11</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>Design and copy polish for this step</t>
         </is>
       </c>
-      <c r="E43" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr"/>
-      <c r="H43" s="5" t="inlineStr"/>
-      <c r="I43" s="5" t="inlineStr"/>
+      <c r="G43" s="6" t="inlineStr"/>
+      <c r="H43" s="6" t="inlineStr"/>
+      <c r="I43" s="6" t="inlineStr"/>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
@@ -1973,51 +1983,51 @@
           <t>/quiz/q/12</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>Your Skin: What are your biggest skin concerns right now?</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr"/>
-      <c r="F44" s="4" t="inlineStr"/>
-      <c r="G44" s="4" t="inlineStr"/>
-      <c r="H44" s="4" t="inlineStr"/>
-      <c r="I44" s="4" t="inlineStr"/>
+      <c r="E44" s="5" t="inlineStr"/>
+      <c r="F44" s="5" t="inlineStr"/>
+      <c r="G44" s="5" t="inlineStr"/>
+      <c r="H44" s="5" t="inlineStr"/>
+      <c r="I44" s="5" t="inlineStr"/>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>Step 12 of 31</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>/quiz/q/12</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>Design and copy polish for this step</t>
         </is>
       </c>
-      <c r="E45" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr"/>
-      <c r="H45" s="5" t="inlineStr"/>
-      <c r="I45" s="5" t="inlineStr"/>
+      <c r="G45" s="6" t="inlineStr"/>
+      <c r="H45" s="6" t="inlineStr"/>
+      <c r="I45" s="6" t="inlineStr"/>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
@@ -2035,51 +2045,51 @@
           <t>/quiz/q/13</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>Your Skin: How sensitive is your skin to the sun?</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr"/>
-      <c r="F46" s="4" t="inlineStr"/>
-      <c r="G46" s="4" t="inlineStr"/>
-      <c r="H46" s="4" t="inlineStr"/>
-      <c r="I46" s="4" t="inlineStr"/>
+      <c r="E46" s="5" t="inlineStr"/>
+      <c r="F46" s="5" t="inlineStr"/>
+      <c r="G46" s="5" t="inlineStr"/>
+      <c r="H46" s="5" t="inlineStr"/>
+      <c r="I46" s="5" t="inlineStr"/>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>Step 13 of 31</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>/quiz/q/13</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>Design and copy polish for this step</t>
         </is>
       </c>
-      <c r="E47" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr"/>
-      <c r="H47" s="5" t="inlineStr"/>
-      <c r="I47" s="5" t="inlineStr"/>
+      <c r="G47" s="6" t="inlineStr"/>
+      <c r="H47" s="6" t="inlineStr"/>
+      <c r="I47" s="6" t="inlineStr"/>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
@@ -2097,51 +2107,51 @@
           <t>/quiz/q/14</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>Your Skin: How does your skin feel after cleansing with just water?</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr"/>
-      <c r="F48" s="4" t="inlineStr"/>
-      <c r="G48" s="4" t="inlineStr"/>
-      <c r="H48" s="4" t="inlineStr"/>
-      <c r="I48" s="4" t="inlineStr"/>
+      <c r="E48" s="5" t="inlineStr"/>
+      <c r="F48" s="5" t="inlineStr"/>
+      <c r="G48" s="5" t="inlineStr"/>
+      <c r="H48" s="5" t="inlineStr"/>
+      <c r="I48" s="5" t="inlineStr"/>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>Step 14 of 31</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>/quiz/q/14</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>Design and copy polish for this step</t>
         </is>
       </c>
-      <c r="E49" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="E49" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr"/>
-      <c r="H49" s="5" t="inlineStr"/>
-      <c r="I49" s="5" t="inlineStr"/>
+      <c r="G49" s="6" t="inlineStr"/>
+      <c r="H49" s="6" t="inlineStr"/>
+      <c r="I49" s="6" t="inlineStr"/>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
@@ -2159,51 +2169,51 @@
           <t>/quiz/q/15</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>Your Skin: How often do you experience breakouts?</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr"/>
-      <c r="F50" s="4" t="inlineStr"/>
-      <c r="G50" s="4" t="inlineStr"/>
-      <c r="H50" s="4" t="inlineStr"/>
-      <c r="I50" s="4" t="inlineStr"/>
+      <c r="E50" s="5" t="inlineStr"/>
+      <c r="F50" s="5" t="inlineStr"/>
+      <c r="G50" s="5" t="inlineStr"/>
+      <c r="H50" s="5" t="inlineStr"/>
+      <c r="I50" s="5" t="inlineStr"/>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>Step 15 of 31</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>/quiz/q/15</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>Design and copy polish for this step</t>
         </is>
       </c>
-      <c r="E51" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr"/>
-      <c r="H51" s="5" t="inlineStr"/>
-      <c r="I51" s="5" t="inlineStr"/>
+      <c r="G51" s="6" t="inlineStr"/>
+      <c r="H51" s="6" t="inlineStr"/>
+      <c r="I51" s="6" t="inlineStr"/>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
@@ -2221,51 +2231,51 @@
           <t>/quiz/q/16</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>Your Skin: Do you experience any of the following?</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr"/>
-      <c r="F52" s="4" t="inlineStr"/>
-      <c r="G52" s="4" t="inlineStr"/>
-      <c r="H52" s="4" t="inlineStr"/>
-      <c r="I52" s="4" t="inlineStr"/>
+      <c r="E52" s="5" t="inlineStr"/>
+      <c r="F52" s="5" t="inlineStr"/>
+      <c r="G52" s="5" t="inlineStr"/>
+      <c r="H52" s="5" t="inlineStr"/>
+      <c r="I52" s="5" t="inlineStr"/>
     </row>
     <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>Step 16 of 31</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>/quiz/q/16</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>Design and copy polish for this step</t>
         </is>
       </c>
-      <c r="E53" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="E53" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G53" s="5" t="inlineStr"/>
-      <c r="H53" s="5" t="inlineStr"/>
-      <c r="I53" s="5" t="inlineStr"/>
+      <c r="G53" s="6" t="inlineStr"/>
+      <c r="H53" s="6" t="inlineStr"/>
+      <c r="I53" s="6" t="inlineStr"/>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
@@ -2283,51 +2293,51 @@
           <t>/quiz/q/17</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>Your Skin: How visible are your pores?</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr"/>
-      <c r="F54" s="4" t="inlineStr"/>
-      <c r="G54" s="4" t="inlineStr"/>
-      <c r="H54" s="4" t="inlineStr"/>
-      <c r="I54" s="4" t="inlineStr"/>
+      <c r="E54" s="5" t="inlineStr"/>
+      <c r="F54" s="5" t="inlineStr"/>
+      <c r="G54" s="5" t="inlineStr"/>
+      <c r="H54" s="5" t="inlineStr"/>
+      <c r="I54" s="5" t="inlineStr"/>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>Step 17 of 31</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
         <is>
           <t>/quiz/q/17</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t>Design and copy polish for this step</t>
         </is>
       </c>
-      <c r="E55" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G55" s="5" t="inlineStr"/>
-      <c r="H55" s="5" t="inlineStr"/>
-      <c r="I55" s="5" t="inlineStr"/>
+      <c r="G55" s="6" t="inlineStr"/>
+      <c r="H55" s="6" t="inlineStr"/>
+      <c r="I55" s="6" t="inlineStr"/>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
@@ -2345,51 +2355,51 @@
           <t>/quiz/q/18</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>Your Skin: How would you describe your skin tone?</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr"/>
-      <c r="F56" s="4" t="inlineStr"/>
-      <c r="G56" s="4" t="inlineStr"/>
-      <c r="H56" s="4" t="inlineStr"/>
-      <c r="I56" s="4" t="inlineStr"/>
+      <c r="E56" s="5" t="inlineStr"/>
+      <c r="F56" s="5" t="inlineStr"/>
+      <c r="G56" s="5" t="inlineStr"/>
+      <c r="H56" s="5" t="inlineStr"/>
+      <c r="I56" s="5" t="inlineStr"/>
     </row>
     <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>Step 18 of 31</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>/quiz/q/18</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t>Design and copy polish for this step</t>
         </is>
       </c>
-      <c r="E57" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="E57" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G57" s="5" t="inlineStr"/>
-      <c r="H57" s="5" t="inlineStr"/>
-      <c r="I57" s="5" t="inlineStr"/>
+      <c r="G57" s="6" t="inlineStr"/>
+      <c r="H57" s="6" t="inlineStr"/>
+      <c r="I57" s="6" t="inlineStr"/>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
@@ -2407,51 +2417,51 @@
           <t>/quiz/q/19</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>Your Skin: Rate the following about your skin right now.</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr"/>
-      <c r="F58" s="4" t="inlineStr"/>
-      <c r="G58" s="4" t="inlineStr"/>
-      <c r="H58" s="4" t="inlineStr"/>
-      <c r="I58" s="4" t="inlineStr"/>
+      <c r="E58" s="5" t="inlineStr"/>
+      <c r="F58" s="5" t="inlineStr"/>
+      <c r="G58" s="5" t="inlineStr"/>
+      <c r="H58" s="5" t="inlineStr"/>
+      <c r="I58" s="5" t="inlineStr"/>
     </row>
     <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="5" t="inlineStr">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>Step 19 of 31</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>/quiz/q/19</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D59" s="6" t="inlineStr">
         <is>
           <t>Design and copy polish for this step</t>
         </is>
       </c>
-      <c r="E59" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="E59" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G59" s="5" t="inlineStr"/>
-      <c r="H59" s="5" t="inlineStr"/>
-      <c r="I59" s="5" t="inlineStr"/>
+      <c r="G59" s="6" t="inlineStr"/>
+      <c r="H59" s="6" t="inlineStr"/>
+      <c r="I59" s="6" t="inlineStr"/>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
@@ -2469,51 +2479,51 @@
           <t>/quiz/q/20</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>Your Skin: Have you ever had an allergic reaction to a skincare product?</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr"/>
-      <c r="F60" s="4" t="inlineStr"/>
-      <c r="G60" s="4" t="inlineStr"/>
-      <c r="H60" s="4" t="inlineStr"/>
-      <c r="I60" s="4" t="inlineStr"/>
+      <c r="E60" s="5" t="inlineStr"/>
+      <c r="F60" s="5" t="inlineStr"/>
+      <c r="G60" s="5" t="inlineStr"/>
+      <c r="H60" s="5" t="inlineStr"/>
+      <c r="I60" s="5" t="inlineStr"/>
     </row>
     <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="5" t="inlineStr">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>Step 20 of 31</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C61" s="6" t="inlineStr">
         <is>
           <t>/quiz/q/20</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D61" s="6" t="inlineStr">
         <is>
           <t>Design and copy polish for this step</t>
         </is>
       </c>
-      <c r="E61" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F61" s="5" t="inlineStr">
+      <c r="E61" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G61" s="5" t="inlineStr"/>
-      <c r="H61" s="5" t="inlineStr"/>
-      <c r="I61" s="5" t="inlineStr"/>
+      <c r="G61" s="6" t="inlineStr"/>
+      <c r="H61" s="6" t="inlineStr"/>
+      <c r="I61" s="6" t="inlineStr"/>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="3" t="inlineStr">
@@ -2531,51 +2541,51 @@
           <t>/quiz/q/21</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>Routine and Preferences: How many steps is your current skincare routine?</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr"/>
-      <c r="F62" s="4" t="inlineStr"/>
-      <c r="G62" s="4" t="inlineStr"/>
-      <c r="H62" s="4" t="inlineStr"/>
-      <c r="I62" s="4" t="inlineStr"/>
+      <c r="E62" s="5" t="inlineStr"/>
+      <c r="F62" s="5" t="inlineStr"/>
+      <c r="G62" s="5" t="inlineStr"/>
+      <c r="H62" s="5" t="inlineStr"/>
+      <c r="I62" s="5" t="inlineStr"/>
     </row>
     <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="5" t="inlineStr">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>Step 21 of 31</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr">
         <is>
           <t>/quiz/q/21</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D63" s="6" t="inlineStr">
         <is>
           <t>Design and copy polish for this step</t>
         </is>
       </c>
-      <c r="E63" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F63" s="5" t="inlineStr">
+      <c r="E63" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G63" s="5" t="inlineStr"/>
-      <c r="H63" s="5" t="inlineStr"/>
-      <c r="I63" s="5" t="inlineStr"/>
+      <c r="G63" s="6" t="inlineStr"/>
+      <c r="H63" s="6" t="inlineStr"/>
+      <c r="I63" s="6" t="inlineStr"/>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="3" t="inlineStr">
@@ -2593,51 +2603,51 @@
           <t>/quiz/q/22</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>Routine and Preferences: What texture do you prefer in a moisturiser?</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr"/>
-      <c r="F64" s="4" t="inlineStr"/>
-      <c r="G64" s="4" t="inlineStr"/>
-      <c r="H64" s="4" t="inlineStr"/>
-      <c r="I64" s="4" t="inlineStr"/>
+      <c r="E64" s="5" t="inlineStr"/>
+      <c r="F64" s="5" t="inlineStr"/>
+      <c r="G64" s="5" t="inlineStr"/>
+      <c r="H64" s="5" t="inlineStr"/>
+      <c r="I64" s="5" t="inlineStr"/>
     </row>
     <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="5" t="inlineStr">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B65" s="5" t="inlineStr">
+      <c r="B65" s="6" t="inlineStr">
         <is>
           <t>Step 22 of 31</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C65" s="6" t="inlineStr">
         <is>
           <t>/quiz/q/22</t>
         </is>
       </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="D65" s="6" t="inlineStr">
         <is>
           <t>Design and copy polish for this step</t>
         </is>
       </c>
-      <c r="E65" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F65" s="5" t="inlineStr">
+      <c r="E65" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G65" s="5" t="inlineStr"/>
-      <c r="H65" s="5" t="inlineStr"/>
-      <c r="I65" s="5" t="inlineStr"/>
+      <c r="G65" s="6" t="inlineStr"/>
+      <c r="H65" s="6" t="inlineStr"/>
+      <c r="I65" s="6" t="inlineStr"/>
     </row>
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="3" t="inlineStr">
@@ -2655,51 +2665,51 @@
           <t>/quiz/q/23</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="D66" s="5" t="inlineStr">
         <is>
           <t>Routine and Preferences: What type of cleanser do you prefer?</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr"/>
-      <c r="F66" s="4" t="inlineStr"/>
-      <c r="G66" s="4" t="inlineStr"/>
-      <c r="H66" s="4" t="inlineStr"/>
-      <c r="I66" s="4" t="inlineStr"/>
+      <c r="E66" s="5" t="inlineStr"/>
+      <c r="F66" s="5" t="inlineStr"/>
+      <c r="G66" s="5" t="inlineStr"/>
+      <c r="H66" s="5" t="inlineStr"/>
+      <c r="I66" s="5" t="inlineStr"/>
     </row>
     <row r="67" ht="18" customHeight="1">
-      <c r="A67" s="5" t="inlineStr">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B67" s="5" t="inlineStr">
+      <c r="B67" s="6" t="inlineStr">
         <is>
           <t>Step 23 of 31</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C67" s="6" t="inlineStr">
         <is>
           <t>/quiz/q/23</t>
         </is>
       </c>
-      <c r="D67" s="5" t="inlineStr">
+      <c r="D67" s="6" t="inlineStr">
         <is>
           <t>Design and copy polish for this step</t>
         </is>
       </c>
-      <c r="E67" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F67" s="5" t="inlineStr">
+      <c r="E67" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G67" s="5" t="inlineStr"/>
-      <c r="H67" s="5" t="inlineStr"/>
-      <c r="I67" s="5" t="inlineStr"/>
+      <c r="G67" s="6" t="inlineStr"/>
+      <c r="H67" s="6" t="inlineStr"/>
+      <c r="I67" s="6" t="inlineStr"/>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="3" t="inlineStr">
@@ -2717,51 +2727,51 @@
           <t>/quiz/q/24</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="D68" s="5" t="inlineStr">
         <is>
           <t>Routine and Preferences: Rank these skincare priorities from most to least important.</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr"/>
-      <c r="F68" s="4" t="inlineStr"/>
-      <c r="G68" s="4" t="inlineStr"/>
-      <c r="H68" s="4" t="inlineStr"/>
-      <c r="I68" s="4" t="inlineStr"/>
+      <c r="E68" s="5" t="inlineStr"/>
+      <c r="F68" s="5" t="inlineStr"/>
+      <c r="G68" s="5" t="inlineStr"/>
+      <c r="H68" s="5" t="inlineStr"/>
+      <c r="I68" s="5" t="inlineStr"/>
     </row>
     <row r="69" ht="18" customHeight="1">
-      <c r="A69" s="5" t="inlineStr">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B69" s="5" t="inlineStr">
+      <c r="B69" s="6" t="inlineStr">
         <is>
           <t>Step 24 of 31</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C69" s="6" t="inlineStr">
         <is>
           <t>/quiz/q/24</t>
         </is>
       </c>
-      <c r="D69" s="5" t="inlineStr">
+      <c r="D69" s="6" t="inlineStr">
         <is>
           <t>Design and copy polish for this step</t>
         </is>
       </c>
-      <c r="E69" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F69" s="5" t="inlineStr">
+      <c r="E69" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G69" s="5" t="inlineStr"/>
-      <c r="H69" s="5" t="inlineStr"/>
-      <c r="I69" s="5" t="inlineStr"/>
+      <c r="G69" s="6" t="inlineStr"/>
+      <c r="H69" s="6" t="inlineStr"/>
+      <c r="I69" s="6" t="inlineStr"/>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="3" t="inlineStr">
@@ -2779,51 +2789,51 @@
           <t>/quiz/q/25</t>
         </is>
       </c>
-      <c r="D70" s="4" t="inlineStr">
+      <c r="D70" s="5" t="inlineStr">
         <is>
           <t>Routine and Preferences: Which ingredient philosophies matter to you?</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr"/>
-      <c r="F70" s="4" t="inlineStr"/>
-      <c r="G70" s="4" t="inlineStr"/>
-      <c r="H70" s="4" t="inlineStr"/>
-      <c r="I70" s="4" t="inlineStr"/>
+      <c r="E70" s="5" t="inlineStr"/>
+      <c r="F70" s="5" t="inlineStr"/>
+      <c r="G70" s="5" t="inlineStr"/>
+      <c r="H70" s="5" t="inlineStr"/>
+      <c r="I70" s="5" t="inlineStr"/>
     </row>
     <row r="71" ht="18" customHeight="1">
-      <c r="A71" s="5" t="inlineStr">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="B71" s="6" t="inlineStr">
         <is>
           <t>Step 25 of 31</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C71" s="6" t="inlineStr">
         <is>
           <t>/quiz/q/25</t>
         </is>
       </c>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="D71" s="6" t="inlineStr">
         <is>
           <t>Design and copy polish for this step</t>
         </is>
       </c>
-      <c r="E71" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F71" s="5" t="inlineStr">
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G71" s="5" t="inlineStr"/>
-      <c r="H71" s="5" t="inlineStr"/>
-      <c r="I71" s="5" t="inlineStr"/>
+      <c r="G71" s="6" t="inlineStr"/>
+      <c r="H71" s="6" t="inlineStr"/>
+      <c r="I71" s="6" t="inlineStr"/>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="3" t="inlineStr">
@@ -2841,51 +2851,51 @@
           <t>/quiz/q/26</t>
         </is>
       </c>
-      <c r="D72" s="4" t="inlineStr">
+      <c r="D72" s="5" t="inlineStr">
         <is>
           <t>Routine and Preferences: How adventurous are you with skincare ingredients?</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr"/>
-      <c r="F72" s="4" t="inlineStr"/>
-      <c r="G72" s="4" t="inlineStr"/>
-      <c r="H72" s="4" t="inlineStr"/>
-      <c r="I72" s="4" t="inlineStr"/>
+      <c r="E72" s="5" t="inlineStr"/>
+      <c r="F72" s="5" t="inlineStr"/>
+      <c r="G72" s="5" t="inlineStr"/>
+      <c r="H72" s="5" t="inlineStr"/>
+      <c r="I72" s="5" t="inlineStr"/>
     </row>
     <row r="73" ht="18" customHeight="1">
-      <c r="A73" s="5" t="inlineStr">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B73" s="5" t="inlineStr">
+      <c r="B73" s="6" t="inlineStr">
         <is>
           <t>Step 26 of 31</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C73" s="6" t="inlineStr">
         <is>
           <t>/quiz/q/26</t>
         </is>
       </c>
-      <c r="D73" s="5" t="inlineStr">
+      <c r="D73" s="6" t="inlineStr">
         <is>
           <t>Design and copy polish for this step</t>
         </is>
       </c>
-      <c r="E73" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F73" s="5" t="inlineStr">
+      <c r="E73" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G73" s="5" t="inlineStr"/>
-      <c r="H73" s="5" t="inlineStr"/>
-      <c r="I73" s="5" t="inlineStr"/>
+      <c r="G73" s="6" t="inlineStr"/>
+      <c r="H73" s="6" t="inlineStr"/>
+      <c r="I73" s="6" t="inlineStr"/>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="3" t="inlineStr">
@@ -2903,51 +2913,51 @@
           <t>/quiz/q/27</t>
         </is>
       </c>
-      <c r="D74" s="4" t="inlineStr">
+      <c r="D74" s="5" t="inlineStr">
         <is>
           <t>Routine and Preferences: Have you used retinol or retinoids before?</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr"/>
-      <c r="F74" s="4" t="inlineStr"/>
-      <c r="G74" s="4" t="inlineStr"/>
-      <c r="H74" s="4" t="inlineStr"/>
-      <c r="I74" s="4" t="inlineStr"/>
+      <c r="E74" s="5" t="inlineStr"/>
+      <c r="F74" s="5" t="inlineStr"/>
+      <c r="G74" s="5" t="inlineStr"/>
+      <c r="H74" s="5" t="inlineStr"/>
+      <c r="I74" s="5" t="inlineStr"/>
     </row>
     <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="5" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B75" s="5" t="inlineStr">
+      <c r="B75" s="6" t="inlineStr">
         <is>
           <t>Step 27 of 31</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C75" s="6" t="inlineStr">
         <is>
           <t>/quiz/q/27</t>
         </is>
       </c>
-      <c r="D75" s="5" t="inlineStr">
+      <c r="D75" s="6" t="inlineStr">
         <is>
           <t>Design and copy polish for this step</t>
         </is>
       </c>
-      <c r="E75" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F75" s="5" t="inlineStr">
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G75" s="5" t="inlineStr"/>
-      <c r="H75" s="5" t="inlineStr"/>
-      <c r="I75" s="5" t="inlineStr"/>
+      <c r="G75" s="6" t="inlineStr"/>
+      <c r="H75" s="6" t="inlineStr"/>
+      <c r="I75" s="6" t="inlineStr"/>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="3" t="inlineStr">
@@ -2965,51 +2975,51 @@
           <t>/quiz/q/28</t>
         </is>
       </c>
-      <c r="D76" s="4" t="inlineStr">
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>Routine and Preferences: How much time do you spend on your skincare routine?</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr"/>
-      <c r="F76" s="4" t="inlineStr"/>
-      <c r="G76" s="4" t="inlineStr"/>
-      <c r="H76" s="4" t="inlineStr"/>
-      <c r="I76" s="4" t="inlineStr"/>
+      <c r="E76" s="5" t="inlineStr"/>
+      <c r="F76" s="5" t="inlineStr"/>
+      <c r="G76" s="5" t="inlineStr"/>
+      <c r="H76" s="5" t="inlineStr"/>
+      <c r="I76" s="5" t="inlineStr"/>
     </row>
     <row r="77" ht="18" customHeight="1">
-      <c r="A77" s="5" t="inlineStr">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B77" s="5" t="inlineStr">
+      <c r="B77" s="6" t="inlineStr">
         <is>
           <t>Step 28 of 31</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C77" s="6" t="inlineStr">
         <is>
           <t>/quiz/q/28</t>
         </is>
       </c>
-      <c r="D77" s="5" t="inlineStr">
+      <c r="D77" s="6" t="inlineStr">
         <is>
           <t>Design and copy polish for this step</t>
         </is>
       </c>
-      <c r="E77" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F77" s="5" t="inlineStr">
+      <c r="E77" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G77" s="5" t="inlineStr"/>
-      <c r="H77" s="5" t="inlineStr"/>
-      <c r="I77" s="5" t="inlineStr"/>
+      <c r="G77" s="6" t="inlineStr"/>
+      <c r="H77" s="6" t="inlineStr"/>
+      <c r="I77" s="6" t="inlineStr"/>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="3" t="inlineStr">
@@ -3027,51 +3037,51 @@
           <t>/quiz/q/29</t>
         </is>
       </c>
-      <c r="D78" s="4" t="inlineStr">
+      <c r="D78" s="5" t="inlineStr">
         <is>
           <t>Routine and Preferences: Is there anything you would like to avoid in your products?</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr"/>
-      <c r="F78" s="4" t="inlineStr"/>
-      <c r="G78" s="4" t="inlineStr"/>
-      <c r="H78" s="4" t="inlineStr"/>
-      <c r="I78" s="4" t="inlineStr"/>
+      <c r="E78" s="5" t="inlineStr"/>
+      <c r="F78" s="5" t="inlineStr"/>
+      <c r="G78" s="5" t="inlineStr"/>
+      <c r="H78" s="5" t="inlineStr"/>
+      <c r="I78" s="5" t="inlineStr"/>
     </row>
     <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="5" t="inlineStr">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B79" s="5" t="inlineStr">
+      <c r="B79" s="6" t="inlineStr">
         <is>
           <t>Step 29 of 31</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
+      <c r="C79" s="6" t="inlineStr">
         <is>
           <t>/quiz/q/29</t>
         </is>
       </c>
-      <c r="D79" s="5" t="inlineStr">
+      <c r="D79" s="6" t="inlineStr">
         <is>
           <t>Design and copy polish for this step</t>
         </is>
       </c>
-      <c r="E79" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F79" s="5" t="inlineStr">
+      <c r="E79" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G79" s="5" t="inlineStr"/>
-      <c r="H79" s="5" t="inlineStr"/>
-      <c r="I79" s="5" t="inlineStr"/>
+      <c r="G79" s="6" t="inlineStr"/>
+      <c r="H79" s="6" t="inlineStr"/>
+      <c r="I79" s="6" t="inlineStr"/>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="3" t="inlineStr">
@@ -3089,51 +3099,51 @@
           <t>/quiz/q/30</t>
         </is>
       </c>
-      <c r="D80" s="4" t="inlineStr">
+      <c r="D80" s="5" t="inlineStr">
         <is>
           <t>Routine and Preferences: Do you have any known skin allergies?</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr"/>
-      <c r="F80" s="4" t="inlineStr"/>
-      <c r="G80" s="4" t="inlineStr"/>
-      <c r="H80" s="4" t="inlineStr"/>
-      <c r="I80" s="4" t="inlineStr"/>
+      <c r="E80" s="5" t="inlineStr"/>
+      <c r="F80" s="5" t="inlineStr"/>
+      <c r="G80" s="5" t="inlineStr"/>
+      <c r="H80" s="5" t="inlineStr"/>
+      <c r="I80" s="5" t="inlineStr"/>
     </row>
     <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="5" t="inlineStr">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B81" s="5" t="inlineStr">
+      <c r="B81" s="6" t="inlineStr">
         <is>
           <t>Step 30 of 31</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="C81" s="6" t="inlineStr">
         <is>
           <t>/quiz/q/30</t>
         </is>
       </c>
-      <c r="D81" s="5" t="inlineStr">
+      <c r="D81" s="6" t="inlineStr">
         <is>
           <t>Design and copy polish for this step</t>
         </is>
       </c>
-      <c r="E81" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F81" s="5" t="inlineStr">
+      <c r="E81" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G81" s="5" t="inlineStr"/>
-      <c r="H81" s="5" t="inlineStr"/>
-      <c r="I81" s="5" t="inlineStr"/>
+      <c r="G81" s="6" t="inlineStr"/>
+      <c r="H81" s="6" t="inlineStr"/>
+      <c r="I81" s="6" t="inlineStr"/>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="3" t="inlineStr">
@@ -3151,51 +3161,51 @@
           <t>/quiz/q/31</t>
         </is>
       </c>
-      <c r="D82" s="4" t="inlineStr">
+      <c r="D82" s="5" t="inlineStr">
         <is>
           <t>Routine and Preferences: Would you like fragrance in your products?</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr"/>
-      <c r="F82" s="4" t="inlineStr"/>
-      <c r="G82" s="4" t="inlineStr"/>
-      <c r="H82" s="4" t="inlineStr"/>
-      <c r="I82" s="4" t="inlineStr"/>
+      <c r="E82" s="5" t="inlineStr"/>
+      <c r="F82" s="5" t="inlineStr"/>
+      <c r="G82" s="5" t="inlineStr"/>
+      <c r="H82" s="5" t="inlineStr"/>
+      <c r="I82" s="5" t="inlineStr"/>
     </row>
     <row r="83" ht="18" customHeight="1">
-      <c r="A83" s="5" t="inlineStr">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>Consultation quiz</t>
         </is>
       </c>
-      <c r="B83" s="5" t="inlineStr">
+      <c r="B83" s="6" t="inlineStr">
         <is>
           <t>Step 31 of 31</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
+      <c r="C83" s="6" t="inlineStr">
         <is>
           <t>/quiz/q/31</t>
         </is>
       </c>
-      <c r="D83" s="5" t="inlineStr">
+      <c r="D83" s="6" t="inlineStr">
         <is>
           <t>Design and copy polish for this step</t>
         </is>
       </c>
-      <c r="E83" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F83" s="5" t="inlineStr">
+      <c r="E83" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G83" s="5" t="inlineStr"/>
-      <c r="H83" s="5" t="inlineStr"/>
-      <c r="I83" s="5" t="inlineStr"/>
+      <c r="G83" s="6" t="inlineStr"/>
+      <c r="H83" s="6" t="inlineStr"/>
+      <c r="I83" s="6" t="inlineStr"/>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
@@ -3220,226 +3230,226 @@
           <t>/results</t>
         </is>
       </c>
-      <c r="D85" s="4" t="inlineStr">
+      <c r="D85" s="5" t="inlineStr">
         <is>
           <t>The page that shows the customer their personalised products and the regimen we recommend</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr"/>
-      <c r="F85" s="4" t="inlineStr"/>
-      <c r="G85" s="4" t="inlineStr"/>
-      <c r="H85" s="4" t="inlineStr"/>
-      <c r="I85" s="4" t="inlineStr"/>
+      <c r="E85" s="5" t="inlineStr"/>
+      <c r="F85" s="5" t="inlineStr"/>
+      <c r="G85" s="5" t="inlineStr"/>
+      <c r="H85" s="5" t="inlineStr"/>
+      <c r="I85" s="5" t="inlineStr"/>
     </row>
     <row r="86" ht="18" customHeight="1">
-      <c r="A86" s="5" t="inlineStr">
+      <c r="A86" s="6" t="inlineStr">
         <is>
           <t>After the quiz</t>
         </is>
       </c>
-      <c r="B86" s="5" t="inlineStr">
+      <c r="B86" s="6" t="inlineStr">
         <is>
           <t>Results</t>
         </is>
       </c>
-      <c r="C86" s="5" t="inlineStr">
+      <c r="C86" s="6" t="inlineStr">
         <is>
           <t>/results</t>
         </is>
       </c>
-      <c r="D86" s="5" t="inlineStr">
+      <c r="D86" s="6" t="inlineStr">
         <is>
           <t>Trust line near the top</t>
         </is>
       </c>
-      <c r="E86" s="6" t="inlineStr">
+      <c r="E86" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F86" s="5" t="inlineStr">
+      <c r="F86" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G86" s="5" t="inlineStr"/>
-      <c r="H86" s="5" t="inlineStr"/>
-      <c r="I86" s="5" t="inlineStr"/>
+      <c r="G86" s="6" t="inlineStr"/>
+      <c r="H86" s="6" t="inlineStr"/>
+      <c r="I86" s="6" t="inlineStr"/>
     </row>
     <row r="87" ht="18" customHeight="1">
-      <c r="A87" s="5" t="inlineStr">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>After the quiz</t>
         </is>
       </c>
-      <c r="B87" s="5" t="inlineStr">
+      <c r="B87" s="6" t="inlineStr">
         <is>
           <t>Results</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr">
+      <c r="C87" s="6" t="inlineStr">
         <is>
           <t>/results</t>
         </is>
       </c>
-      <c r="D87" s="5" t="inlineStr">
+      <c r="D87" s="6" t="inlineStr">
         <is>
           <t>Ingredient cards expand when clicked to show details</t>
         </is>
       </c>
-      <c r="E87" s="6" t="inlineStr">
+      <c r="E87" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F87" s="5" t="inlineStr">
+      <c r="F87" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G87" s="5" t="inlineStr"/>
-      <c r="H87" s="5" t="inlineStr"/>
-      <c r="I87" s="5" t="inlineStr"/>
+      <c r="G87" s="6" t="inlineStr"/>
+      <c r="H87" s="6" t="inlineStr"/>
+      <c r="I87" s="6" t="inlineStr"/>
     </row>
     <row r="88" ht="18" customHeight="1">
-      <c r="A88" s="5" t="inlineStr">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>After the quiz</t>
         </is>
       </c>
-      <c r="B88" s="5" t="inlineStr">
+      <c r="B88" s="6" t="inlineStr">
         <is>
           <t>Results</t>
         </is>
       </c>
-      <c r="C88" s="5" t="inlineStr">
+      <c r="C88" s="6" t="inlineStr">
         <is>
           <t>/results</t>
         </is>
       </c>
-      <c r="D88" s="5" t="inlineStr">
+      <c r="D88" s="6" t="inlineStr">
         <is>
           <t>3D botanical scene shows alongside the recommendation</t>
         </is>
       </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="E88" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F88" s="5" t="inlineStr">
+      <c r="F88" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G88" s="5" t="inlineStr"/>
-      <c r="H88" s="5" t="inlineStr"/>
-      <c r="I88" s="5" t="inlineStr"/>
+      <c r="G88" s="6" t="inlineStr"/>
+      <c r="H88" s="6" t="inlineStr"/>
+      <c r="I88" s="6" t="inlineStr"/>
     </row>
     <row r="89" ht="18" customHeight="1">
-      <c r="A89" s="5" t="inlineStr">
+      <c r="A89" s="6" t="inlineStr">
         <is>
           <t>After the quiz</t>
         </is>
       </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="B89" s="6" t="inlineStr">
         <is>
           <t>Results</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
+      <c r="C89" s="6" t="inlineStr">
         <is>
           <t>/results</t>
         </is>
       </c>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="D89" s="6" t="inlineStr">
         <is>
           <t>Subscription plan picker is side by side</t>
         </is>
       </c>
-      <c r="E89" s="6" t="inlineStr">
+      <c r="E89" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F89" s="5" t="inlineStr">
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G89" s="5" t="inlineStr"/>
-      <c r="H89" s="5" t="inlineStr"/>
-      <c r="I89" s="5" t="inlineStr"/>
+      <c r="G89" s="6" t="inlineStr"/>
+      <c r="H89" s="6" t="inlineStr"/>
+      <c r="I89" s="6" t="inlineStr"/>
     </row>
     <row r="90" ht="18" customHeight="1">
-      <c r="A90" s="5" t="inlineStr">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>After the quiz</t>
         </is>
       </c>
-      <c r="B90" s="5" t="inlineStr">
+      <c r="B90" s="6" t="inlineStr">
         <is>
           <t>Results</t>
         </is>
       </c>
-      <c r="C90" s="5" t="inlineStr">
+      <c r="C90" s="6" t="inlineStr">
         <is>
           <t>/results</t>
         </is>
       </c>
-      <c r="D90" s="5" t="inlineStr">
+      <c r="D90" s="6" t="inlineStr">
         <is>
           <t>Mobile usability check</t>
         </is>
       </c>
-      <c r="E90" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F90" s="5" t="inlineStr">
+      <c r="E90" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G90" s="5" t="inlineStr"/>
-      <c r="H90" s="5" t="inlineStr"/>
-      <c r="I90" s="5" t="inlineStr"/>
+      <c r="G90" s="6" t="inlineStr"/>
+      <c r="H90" s="6" t="inlineStr"/>
+      <c r="I90" s="6" t="inlineStr"/>
     </row>
     <row r="91" ht="18" customHeight="1">
-      <c r="A91" s="5" t="inlineStr">
+      <c r="A91" s="6" t="inlineStr">
         <is>
           <t>After the quiz</t>
         </is>
       </c>
-      <c r="B91" s="5" t="inlineStr">
+      <c r="B91" s="6" t="inlineStr">
         <is>
           <t>Results</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
+      <c r="C91" s="6" t="inlineStr">
         <is>
           <t>/results</t>
         </is>
       </c>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="D91" s="6" t="inlineStr">
         <is>
           <t>Empty state and error state designs</t>
         </is>
       </c>
-      <c r="E91" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F91" s="5" t="inlineStr">
+      <c r="E91" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G91" s="5" t="inlineStr"/>
-      <c r="H91" s="5" t="inlineStr"/>
-      <c r="I91" s="5" t="inlineStr"/>
+      <c r="G91" s="6" t="inlineStr"/>
+      <c r="H91" s="6" t="inlineStr"/>
+      <c r="I91" s="6" t="inlineStr"/>
     </row>
     <row r="92" ht="20" customHeight="1">
       <c r="A92" s="3" t="inlineStr">
@@ -3457,121 +3467,121 @@
           <t>/analysis</t>
         </is>
       </c>
-      <c r="D92" s="4" t="inlineStr">
+      <c r="D92" s="5" t="inlineStr">
         <is>
           <t>A breakdown of the customer's skin profile from their quiz answers</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr"/>
-      <c r="F92" s="4" t="inlineStr"/>
-      <c r="G92" s="4" t="inlineStr"/>
-      <c r="H92" s="4" t="inlineStr"/>
-      <c r="I92" s="4" t="inlineStr"/>
+      <c r="E92" s="5" t="inlineStr"/>
+      <c r="F92" s="5" t="inlineStr"/>
+      <c r="G92" s="5" t="inlineStr"/>
+      <c r="H92" s="5" t="inlineStr"/>
+      <c r="I92" s="5" t="inlineStr"/>
     </row>
     <row r="93" ht="18" customHeight="1">
-      <c r="A93" s="5" t="inlineStr">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>After the quiz</t>
         </is>
       </c>
-      <c r="B93" s="5" t="inlineStr">
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>Skin Analysis</t>
         </is>
       </c>
-      <c r="C93" s="5" t="inlineStr">
+      <c r="C93" s="6" t="inlineStr">
         <is>
           <t>/analysis</t>
         </is>
       </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="D93" s="6" t="inlineStr">
         <is>
           <t>Show the profile information clearly</t>
         </is>
       </c>
-      <c r="E93" s="6" t="inlineStr">
+      <c r="E93" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F93" s="5" t="inlineStr">
+      <c r="F93" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G93" s="5" t="inlineStr"/>
-      <c r="H93" s="5" t="inlineStr"/>
-      <c r="I93" s="5" t="inlineStr"/>
+      <c r="G93" s="6" t="inlineStr"/>
+      <c r="H93" s="6" t="inlineStr"/>
+      <c r="I93" s="6" t="inlineStr"/>
     </row>
     <row r="94" ht="18" customHeight="1">
-      <c r="A94" s="5" t="inlineStr">
+      <c r="A94" s="6" t="inlineStr">
         <is>
           <t>After the quiz</t>
         </is>
       </c>
-      <c r="B94" s="5" t="inlineStr">
+      <c r="B94" s="6" t="inlineStr">
         <is>
           <t>Skin Analysis</t>
         </is>
       </c>
-      <c r="C94" s="5" t="inlineStr">
+      <c r="C94" s="6" t="inlineStr">
         <is>
           <t>/analysis</t>
         </is>
       </c>
-      <c r="D94" s="5" t="inlineStr">
+      <c r="D94" s="6" t="inlineStr">
         <is>
           <t>Visual breakdown of concerns and priorities</t>
         </is>
       </c>
-      <c r="E94" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F94" s="5" t="inlineStr">
+      <c r="E94" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G94" s="5" t="inlineStr"/>
-      <c r="H94" s="5" t="inlineStr"/>
-      <c r="I94" s="5" t="inlineStr"/>
+      <c r="G94" s="6" t="inlineStr"/>
+      <c r="H94" s="6" t="inlineStr"/>
+      <c r="I94" s="6" t="inlineStr"/>
     </row>
     <row r="95" ht="18" customHeight="1">
-      <c r="A95" s="5" t="inlineStr">
+      <c r="A95" s="6" t="inlineStr">
         <is>
           <t>After the quiz</t>
         </is>
       </c>
-      <c r="B95" s="5" t="inlineStr">
+      <c r="B95" s="6" t="inlineStr">
         <is>
           <t>Skin Analysis</t>
         </is>
       </c>
-      <c r="C95" s="5" t="inlineStr">
+      <c r="C95" s="6" t="inlineStr">
         <is>
           <t>/analysis</t>
         </is>
       </c>
-      <c r="D95" s="5" t="inlineStr">
+      <c r="D95" s="6" t="inlineStr">
         <is>
           <t>Compare with their previous quiz if they retake it</t>
         </is>
       </c>
-      <c r="E95" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F95" s="5" t="inlineStr">
+      <c r="E95" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
         <is>
           <t>P3 low</t>
         </is>
       </c>
-      <c r="G95" s="5" t="inlineStr"/>
-      <c r="H95" s="5" t="inlineStr"/>
-      <c r="I95" s="5" t="inlineStr"/>
+      <c r="G95" s="6" t="inlineStr"/>
+      <c r="H95" s="6" t="inlineStr"/>
+      <c r="I95" s="6" t="inlineStr"/>
     </row>
     <row r="96" ht="20" customHeight="1">
       <c r="A96" s="3" t="inlineStr">
@@ -3589,121 +3599,121 @@
           <t>/report</t>
         </is>
       </c>
-      <c r="D96" s="4" t="inlineStr">
+      <c r="D96" s="5" t="inlineStr">
         <is>
           <t>A longer page that explains the customer's regimen in depth</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr"/>
-      <c r="F96" s="4" t="inlineStr"/>
-      <c r="G96" s="4" t="inlineStr"/>
-      <c r="H96" s="4" t="inlineStr"/>
-      <c r="I96" s="4" t="inlineStr"/>
+      <c r="E96" s="5" t="inlineStr"/>
+      <c r="F96" s="5" t="inlineStr"/>
+      <c r="G96" s="5" t="inlineStr"/>
+      <c r="H96" s="5" t="inlineStr"/>
+      <c r="I96" s="5" t="inlineStr"/>
     </row>
     <row r="97" ht="18" customHeight="1">
-      <c r="A97" s="5" t="inlineStr">
+      <c r="A97" s="6" t="inlineStr">
         <is>
           <t>After the quiz</t>
         </is>
       </c>
-      <c r="B97" s="5" t="inlineStr">
+      <c r="B97" s="6" t="inlineStr">
         <is>
           <t>Detailed Report</t>
         </is>
       </c>
-      <c r="C97" s="5" t="inlineStr">
+      <c r="C97" s="6" t="inlineStr">
         <is>
           <t>/report</t>
         </is>
       </c>
-      <c r="D97" s="5" t="inlineStr">
+      <c r="D97" s="6" t="inlineStr">
         <is>
           <t>Explain the rationale behind each product</t>
         </is>
       </c>
-      <c r="E97" s="6" t="inlineStr">
+      <c r="E97" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F97" s="5" t="inlineStr">
+      <c r="F97" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G97" s="5" t="inlineStr"/>
-      <c r="H97" s="5" t="inlineStr"/>
-      <c r="I97" s="5" t="inlineStr"/>
+      <c r="G97" s="6" t="inlineStr"/>
+      <c r="H97" s="6" t="inlineStr"/>
+      <c r="I97" s="6" t="inlineStr"/>
     </row>
     <row r="98" ht="18" customHeight="1">
-      <c r="A98" s="5" t="inlineStr">
+      <c r="A98" s="6" t="inlineStr">
         <is>
           <t>After the quiz</t>
         </is>
       </c>
-      <c r="B98" s="5" t="inlineStr">
+      <c r="B98" s="6" t="inlineStr">
         <is>
           <t>Detailed Report</t>
         </is>
       </c>
-      <c r="C98" s="5" t="inlineStr">
+      <c r="C98" s="6" t="inlineStr">
         <is>
           <t>/report</t>
         </is>
       </c>
-      <c r="D98" s="5" t="inlineStr">
+      <c r="D98" s="6" t="inlineStr">
         <is>
           <t>Make it look right when printed</t>
         </is>
       </c>
-      <c r="E98" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F98" s="5" t="inlineStr">
+      <c r="E98" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G98" s="5" t="inlineStr"/>
-      <c r="H98" s="5" t="inlineStr"/>
-      <c r="I98" s="5" t="inlineStr"/>
+      <c r="G98" s="6" t="inlineStr"/>
+      <c r="H98" s="6" t="inlineStr"/>
+      <c r="I98" s="6" t="inlineStr"/>
     </row>
     <row r="99" ht="18" customHeight="1">
-      <c r="A99" s="5" t="inlineStr">
+      <c r="A99" s="6" t="inlineStr">
         <is>
           <t>After the quiz</t>
         </is>
       </c>
-      <c r="B99" s="5" t="inlineStr">
+      <c r="B99" s="6" t="inlineStr">
         <is>
           <t>Detailed Report</t>
         </is>
       </c>
-      <c r="C99" s="5" t="inlineStr">
+      <c r="C99" s="6" t="inlineStr">
         <is>
           <t>/report</t>
         </is>
       </c>
-      <c r="D99" s="5" t="inlineStr">
+      <c r="D99" s="6" t="inlineStr">
         <is>
           <t>Add a download as PDF option</t>
         </is>
       </c>
-      <c r="E99" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F99" s="5" t="inlineStr">
+      <c r="E99" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
         <is>
           <t>P3 low</t>
         </is>
       </c>
-      <c r="G99" s="5" t="inlineStr"/>
-      <c r="H99" s="5" t="inlineStr"/>
-      <c r="I99" s="5" t="inlineStr"/>
+      <c r="G99" s="6" t="inlineStr"/>
+      <c r="H99" s="6" t="inlineStr"/>
+      <c r="I99" s="6" t="inlineStr"/>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
@@ -3728,541 +3738,541 @@
           <t>/cart</t>
         </is>
       </c>
-      <c r="D101" s="4" t="inlineStr">
+      <c r="D101" s="5" t="inlineStr">
         <is>
           <t>The customer's bag and where they pick their subscription plan</t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr"/>
-      <c r="F101" s="4" t="inlineStr"/>
-      <c r="G101" s="4" t="inlineStr"/>
-      <c r="H101" s="4" t="inlineStr"/>
-      <c r="I101" s="4" t="inlineStr"/>
+      <c r="E101" s="5" t="inlineStr"/>
+      <c r="F101" s="5" t="inlineStr"/>
+      <c r="G101" s="5" t="inlineStr"/>
+      <c r="H101" s="5" t="inlineStr"/>
+      <c r="I101" s="5" t="inlineStr"/>
     </row>
     <row r="102" ht="18" customHeight="1">
-      <c r="A102" s="5" t="inlineStr">
+      <c r="A102" s="6" t="inlineStr">
         <is>
           <t>Cart and checkout</t>
         </is>
       </c>
-      <c r="B102" s="5" t="inlineStr">
+      <c r="B102" s="6" t="inlineStr">
         <is>
           <t>Cart</t>
         </is>
       </c>
-      <c r="C102" s="5" t="inlineStr">
+      <c r="C102" s="6" t="inlineStr">
         <is>
           <t>/cart</t>
         </is>
       </c>
-      <c r="D102" s="5" t="inlineStr">
+      <c r="D102" s="6" t="inlineStr">
         <is>
           <t>Three subscription plan cards side by side</t>
         </is>
       </c>
-      <c r="E102" s="6" t="inlineStr">
+      <c r="E102" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F102" s="5" t="inlineStr">
+      <c r="F102" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G102" s="5" t="inlineStr"/>
-      <c r="H102" s="5" t="inlineStr"/>
-      <c r="I102" s="5" t="inlineStr"/>
+      <c r="G102" s="6" t="inlineStr"/>
+      <c r="H102" s="6" t="inlineStr"/>
+      <c r="I102" s="6" t="inlineStr"/>
     </row>
     <row r="103" ht="18" customHeight="1">
-      <c r="A103" s="5" t="inlineStr">
+      <c r="A103" s="6" t="inlineStr">
         <is>
           <t>Cart and checkout</t>
         </is>
       </c>
-      <c r="B103" s="5" t="inlineStr">
+      <c r="B103" s="6" t="inlineStr">
         <is>
           <t>Cart</t>
         </is>
       </c>
-      <c r="C103" s="5" t="inlineStr">
+      <c r="C103" s="6" t="inlineStr">
         <is>
           <t>/cart</t>
         </is>
       </c>
-      <c r="D103" s="5" t="inlineStr">
+      <c r="D103" s="6" t="inlineStr">
         <is>
           <t>Bi-monthly plan selected by default with 'Most Popular' tag</t>
         </is>
       </c>
-      <c r="E103" s="6" t="inlineStr">
+      <c r="E103" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F103" s="5" t="inlineStr">
+      <c r="F103" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G103" s="5" t="inlineStr"/>
-      <c r="H103" s="5" t="inlineStr"/>
-      <c r="I103" s="5" t="inlineStr"/>
+      <c r="G103" s="6" t="inlineStr"/>
+      <c r="H103" s="6" t="inlineStr"/>
+      <c r="I103" s="6" t="inlineStr"/>
     </row>
     <row r="104" ht="18" customHeight="1">
-      <c r="A104" s="5" t="inlineStr">
+      <c r="A104" s="6" t="inlineStr">
         <is>
           <t>Cart and checkout</t>
         </is>
       </c>
-      <c r="B104" s="5" t="inlineStr">
+      <c r="B104" s="6" t="inlineStr">
         <is>
           <t>Cart</t>
         </is>
       </c>
-      <c r="C104" s="5" t="inlineStr">
+      <c r="C104" s="6" t="inlineStr">
         <is>
           <t>/cart</t>
         </is>
       </c>
-      <c r="D104" s="5" t="inlineStr">
+      <c r="D104" s="6" t="inlineStr">
         <is>
           <t>Reassurance copy inside each plan card</t>
         </is>
       </c>
-      <c r="E104" s="6" t="inlineStr">
+      <c r="E104" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F104" s="5" t="inlineStr">
+      <c r="F104" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G104" s="5" t="inlineStr"/>
-      <c r="H104" s="5" t="inlineStr"/>
-      <c r="I104" s="5" t="inlineStr"/>
+      <c r="G104" s="6" t="inlineStr"/>
+      <c r="H104" s="6" t="inlineStr"/>
+      <c r="I104" s="6" t="inlineStr"/>
     </row>
     <row r="105" ht="18" customHeight="1">
-      <c r="A105" s="5" t="inlineStr">
+      <c r="A105" s="6" t="inlineStr">
         <is>
           <t>Cart and checkout</t>
         </is>
       </c>
-      <c r="B105" s="5" t="inlineStr">
+      <c r="B105" s="6" t="inlineStr">
         <is>
           <t>Cart</t>
         </is>
       </c>
-      <c r="C105" s="5" t="inlineStr">
+      <c r="C105" s="6" t="inlineStr">
         <is>
           <t>/cart</t>
         </is>
       </c>
-      <c r="D105" s="5" t="inlineStr">
+      <c r="D105" s="6" t="inlineStr">
         <is>
           <t>Trust strip under the checkout button</t>
         </is>
       </c>
-      <c r="E105" s="6" t="inlineStr">
+      <c r="E105" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F105" s="5" t="inlineStr">
+      <c r="F105" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G105" s="5" t="inlineStr"/>
-      <c r="H105" s="5" t="inlineStr"/>
-      <c r="I105" s="5" t="inlineStr"/>
+      <c r="G105" s="6" t="inlineStr"/>
+      <c r="H105" s="6" t="inlineStr"/>
+      <c r="I105" s="6" t="inlineStr"/>
     </row>
     <row r="106" ht="18" customHeight="1">
-      <c r="A106" s="5" t="inlineStr">
+      <c r="A106" s="6" t="inlineStr">
         <is>
           <t>Cart and checkout</t>
         </is>
       </c>
-      <c r="B106" s="5" t="inlineStr">
+      <c r="B106" s="6" t="inlineStr">
         <is>
           <t>Cart</t>
         </is>
       </c>
-      <c r="C106" s="5" t="inlineStr">
+      <c r="C106" s="6" t="inlineStr">
         <is>
           <t>/cart</t>
         </is>
       </c>
-      <c r="D106" s="5" t="inlineStr">
+      <c r="D106" s="6" t="inlineStr">
         <is>
           <t>Card colours follow the palette</t>
         </is>
       </c>
-      <c r="E106" s="6" t="inlineStr">
+      <c r="E106" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F106" s="5" t="inlineStr">
+      <c r="F106" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G106" s="5" t="inlineStr"/>
-      <c r="H106" s="5" t="inlineStr"/>
-      <c r="I106" s="5" t="inlineStr"/>
+      <c r="G106" s="6" t="inlineStr"/>
+      <c r="H106" s="6" t="inlineStr"/>
+      <c r="I106" s="6" t="inlineStr"/>
     </row>
     <row r="107" ht="18" customHeight="1">
-      <c r="A107" s="5" t="inlineStr">
+      <c r="A107" s="6" t="inlineStr">
         <is>
           <t>Cart and checkout</t>
         </is>
       </c>
-      <c r="B107" s="5" t="inlineStr">
+      <c r="B107" s="6" t="inlineStr">
         <is>
           <t>Cart</t>
         </is>
       </c>
-      <c r="C107" s="5" t="inlineStr">
+      <c r="C107" s="6" t="inlineStr">
         <is>
           <t>/cart</t>
         </is>
       </c>
-      <c r="D107" s="5" t="inlineStr">
+      <c r="D107" s="6" t="inlineStr">
         <is>
           <t>Empty cart screen invites them to start the quiz</t>
         </is>
       </c>
-      <c r="E107" s="6" t="inlineStr">
+      <c r="E107" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F107" s="5" t="inlineStr">
+      <c r="F107" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G107" s="5" t="inlineStr"/>
-      <c r="H107" s="5" t="inlineStr"/>
-      <c r="I107" s="5" t="inlineStr"/>
+      <c r="G107" s="6" t="inlineStr"/>
+      <c r="H107" s="6" t="inlineStr"/>
+      <c r="I107" s="6" t="inlineStr"/>
     </row>
     <row r="108" ht="18" customHeight="1">
-      <c r="A108" s="5" t="inlineStr">
+      <c r="A108" s="6" t="inlineStr">
         <is>
           <t>Cart and checkout</t>
         </is>
       </c>
-      <c r="B108" s="5" t="inlineStr">
+      <c r="B108" s="6" t="inlineStr">
         <is>
           <t>Cart</t>
         </is>
       </c>
-      <c r="C108" s="5" t="inlineStr">
+      <c r="C108" s="6" t="inlineStr">
         <is>
           <t>/cart</t>
         </is>
       </c>
-      <c r="D108" s="5" t="inlineStr">
+      <c r="D108" s="6" t="inlineStr">
         <is>
           <t>Stacks to one column on mobile</t>
         </is>
       </c>
-      <c r="E108" s="6" t="inlineStr">
+      <c r="E108" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F108" s="5" t="inlineStr">
+      <c r="F108" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G108" s="5" t="inlineStr"/>
-      <c r="H108" s="5" t="inlineStr"/>
-      <c r="I108" s="5" t="inlineStr"/>
+      <c r="G108" s="6" t="inlineStr"/>
+      <c r="H108" s="6" t="inlineStr"/>
+      <c r="I108" s="6" t="inlineStr"/>
     </row>
     <row r="109" ht="18" customHeight="1">
-      <c r="A109" s="5" t="inlineStr">
+      <c r="A109" s="6" t="inlineStr">
         <is>
           <t>Cart and checkout</t>
         </is>
       </c>
-      <c r="B109" s="5" t="inlineStr">
+      <c r="B109" s="6" t="inlineStr">
         <is>
           <t>Cart</t>
         </is>
       </c>
-      <c r="C109" s="5" t="inlineStr">
+      <c r="C109" s="6" t="inlineStr">
         <is>
           <t>/cart</t>
         </is>
       </c>
-      <c r="D109" s="5" t="inlineStr">
+      <c r="D109" s="6" t="inlineStr">
         <is>
           <t>Routine summary panel with name, skin type, concerns, fragrance</t>
         </is>
       </c>
-      <c r="E109" s="6" t="inlineStr">
+      <c r="E109" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F109" s="5" t="inlineStr">
+      <c r="F109" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G109" s="5" t="inlineStr"/>
-      <c r="H109" s="5" t="inlineStr"/>
-      <c r="I109" s="5" t="inlineStr"/>
+      <c r="G109" s="6" t="inlineStr"/>
+      <c r="H109" s="6" t="inlineStr"/>
+      <c r="I109" s="6" t="inlineStr"/>
     </row>
     <row r="110" ht="18" customHeight="1">
-      <c r="A110" s="5" t="inlineStr">
+      <c r="A110" s="6" t="inlineStr">
         <is>
           <t>Cart and checkout</t>
         </is>
       </c>
-      <c r="B110" s="5" t="inlineStr">
+      <c r="B110" s="6" t="inlineStr">
         <is>
           <t>Cart</t>
         </is>
       </c>
-      <c r="C110" s="5" t="inlineStr">
+      <c r="C110" s="6" t="inlineStr">
         <is>
           <t>/cart</t>
         </is>
       </c>
-      <c r="D110" s="5" t="inlineStr">
+      <c r="D110" s="6" t="inlineStr">
         <is>
           <t>Numbered routine steps (Cleanser → Serum → Moisturizer)</t>
         </is>
       </c>
-      <c r="E110" s="6" t="inlineStr">
+      <c r="E110" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F110" s="5" t="inlineStr">
+      <c r="F110" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G110" s="5" t="inlineStr"/>
-      <c r="H110" s="5" t="inlineStr"/>
-      <c r="I110" s="5" t="inlineStr"/>
+      <c r="G110" s="6" t="inlineStr"/>
+      <c r="H110" s="6" t="inlineStr"/>
+      <c r="I110" s="6" t="inlineStr"/>
     </row>
     <row r="111" ht="18" customHeight="1">
-      <c r="A111" s="5" t="inlineStr">
+      <c r="A111" s="6" t="inlineStr">
         <is>
           <t>Cart and checkout</t>
         </is>
       </c>
-      <c r="B111" s="5" t="inlineStr">
+      <c r="B111" s="6" t="inlineStr">
         <is>
           <t>Cart</t>
         </is>
       </c>
-      <c r="C111" s="5" t="inlineStr">
+      <c r="C111" s="6" t="inlineStr">
         <is>
           <t>/cart</t>
         </is>
       </c>
-      <c r="D111" s="5" t="inlineStr">
+      <c r="D111" s="6" t="inlineStr">
         <is>
           <t>Per-item 'Selected for {concerns}' microcopy from the matching engine</t>
         </is>
       </c>
-      <c r="E111" s="6" t="inlineStr">
+      <c r="E111" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F111" s="5" t="inlineStr">
+      <c r="F111" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G111" s="5" t="inlineStr"/>
-      <c r="H111" s="5" t="inlineStr"/>
-      <c r="I111" s="5" t="inlineStr"/>
+      <c r="G111" s="6" t="inlineStr"/>
+      <c r="H111" s="6" t="inlineStr"/>
+      <c r="I111" s="6" t="inlineStr"/>
     </row>
     <row r="112" ht="18" customHeight="1">
-      <c r="A112" s="5" t="inlineStr">
+      <c r="A112" s="6" t="inlineStr">
         <is>
           <t>Cart and checkout</t>
         </is>
       </c>
-      <c r="B112" s="5" t="inlineStr">
+      <c r="B112" s="6" t="inlineStr">
         <is>
           <t>Cart</t>
         </is>
       </c>
-      <c r="C112" s="5" t="inlineStr">
+      <c r="C112" s="6" t="inlineStr">
         <is>
           <t>/cart</t>
         </is>
       </c>
-      <c r="D112" s="5" t="inlineStr">
+      <c r="D112" s="6" t="inlineStr">
         <is>
           <t>Subscription nudge banner with one-tap switch to bi-monthly</t>
         </is>
       </c>
-      <c r="E112" s="6" t="inlineStr">
+      <c r="E112" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F112" s="5" t="inlineStr">
+      <c r="F112" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G112" s="5" t="inlineStr"/>
-      <c r="H112" s="5" t="inlineStr"/>
-      <c r="I112" s="5" t="inlineStr"/>
+      <c r="G112" s="6" t="inlineStr"/>
+      <c r="H112" s="6" t="inlineStr"/>
+      <c r="I112" s="6" t="inlineStr"/>
     </row>
     <row r="113" ht="18" customHeight="1">
-      <c r="A113" s="5" t="inlineStr">
+      <c r="A113" s="6" t="inlineStr">
         <is>
           <t>Cart and checkout</t>
         </is>
       </c>
-      <c r="B113" s="5" t="inlineStr">
+      <c r="B113" s="6" t="inlineStr">
         <is>
           <t>Cart</t>
         </is>
       </c>
-      <c r="C113" s="5" t="inlineStr">
+      <c r="C113" s="6" t="inlineStr">
         <is>
           <t>/cart</t>
         </is>
       </c>
-      <c r="D113" s="5" t="inlineStr">
+      <c r="D113" s="6" t="inlineStr">
         <is>
           <t>Per-plan inline price with savings chip and strikethrough anchor</t>
         </is>
       </c>
-      <c r="E113" s="6" t="inlineStr">
+      <c r="E113" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F113" s="5" t="inlineStr">
+      <c r="F113" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G113" s="5" t="inlineStr"/>
-      <c r="H113" s="5" t="inlineStr"/>
-      <c r="I113" s="5" t="inlineStr"/>
+      <c r="G113" s="6" t="inlineStr"/>
+      <c r="H113" s="6" t="inlineStr"/>
+      <c r="I113" s="6" t="inlineStr"/>
     </row>
     <row r="114" ht="18" customHeight="1">
-      <c r="A114" s="5" t="inlineStr">
+      <c r="A114" s="6" t="inlineStr">
         <is>
           <t>Cart and checkout</t>
         </is>
       </c>
-      <c r="B114" s="5" t="inlineStr">
+      <c r="B114" s="6" t="inlineStr">
         <is>
           <t>Cart</t>
         </is>
       </c>
-      <c r="C114" s="5" t="inlineStr">
+      <c r="C114" s="6" t="inlineStr">
         <is>
           <t>/cart</t>
         </is>
       </c>
-      <c r="D114" s="5" t="inlineStr">
+      <c r="D114" s="6" t="inlineStr">
         <is>
           <t>Ship-to country selector with grouped region dropdown</t>
         </is>
       </c>
-      <c r="E114" s="6" t="inlineStr">
+      <c r="E114" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F114" s="5" t="inlineStr">
+      <c r="F114" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G114" s="5" t="inlineStr"/>
-      <c r="H114" s="5" t="inlineStr"/>
-      <c r="I114" s="5" t="inlineStr"/>
+      <c r="G114" s="6" t="inlineStr"/>
+      <c r="H114" s="6" t="inlineStr"/>
+      <c r="I114" s="6" t="inlineStr"/>
     </row>
     <row r="115" ht="18" customHeight="1">
-      <c r="A115" s="5" t="inlineStr">
+      <c r="A115" s="6" t="inlineStr">
         <is>
           <t>Cart and checkout</t>
         </is>
       </c>
-      <c r="B115" s="5" t="inlineStr">
+      <c r="B115" s="6" t="inlineStr">
         <is>
           <t>Cart</t>
         </is>
       </c>
-      <c r="C115" s="5" t="inlineStr">
+      <c r="C115" s="6" t="inlineStr">
         <is>
           <t>/cart</t>
         </is>
       </c>
-      <c r="D115" s="5" t="inlineStr">
+      <c r="D115" s="6" t="inlineStr">
         <is>
           <t>Multi-currency pricing (EUR / GBP / USD) repriced live on country change</t>
         </is>
       </c>
-      <c r="E115" s="6" t="inlineStr">
+      <c r="E115" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F115" s="5" t="inlineStr">
+      <c r="F115" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G115" s="5" t="inlineStr"/>
-      <c r="H115" s="5" t="inlineStr"/>
-      <c r="I115" s="5" t="inlineStr"/>
+      <c r="G115" s="6" t="inlineStr"/>
+      <c r="H115" s="6" t="inlineStr"/>
+      <c r="I115" s="6" t="inlineStr"/>
     </row>
     <row r="116" ht="18" customHeight="1">
-      <c r="A116" s="5" t="inlineStr">
+      <c r="A116" s="6" t="inlineStr">
         <is>
           <t>Cart and checkout</t>
         </is>
       </c>
-      <c r="B116" s="5" t="inlineStr">
+      <c r="B116" s="6" t="inlineStr">
         <is>
           <t>Cart</t>
         </is>
       </c>
-      <c r="C116" s="5" t="inlineStr">
+      <c r="C116" s="6" t="inlineStr">
         <is>
           <t>/cart</t>
         </is>
       </c>
-      <c r="D116" s="5" t="inlineStr">
+      <c r="D116" s="6" t="inlineStr">
         <is>
           <t>'Edit responses' link returns to results to adjust the formula</t>
         </is>
       </c>
-      <c r="E116" s="6" t="inlineStr">
+      <c r="E116" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F116" s="5" t="inlineStr">
+      <c r="F116" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G116" s="5" t="inlineStr"/>
-      <c r="H116" s="5" t="inlineStr"/>
-      <c r="I116" s="5" t="inlineStr"/>
+      <c r="G116" s="6" t="inlineStr"/>
+      <c r="H116" s="6" t="inlineStr"/>
+      <c r="I116" s="6" t="inlineStr"/>
     </row>
     <row r="117" ht="20" customHeight="1">
       <c r="A117" s="3" t="inlineStr">
@@ -4280,226 +4290,226 @@
           <t>/checkout</t>
         </is>
       </c>
-      <c r="D117" s="4" t="inlineStr">
+      <c r="D117" s="5" t="inlineStr">
         <is>
           <t>The handoff to Stripe where the customer enters card details</t>
         </is>
       </c>
-      <c r="E117" s="4" t="inlineStr"/>
-      <c r="F117" s="4" t="inlineStr"/>
-      <c r="G117" s="4" t="inlineStr"/>
-      <c r="H117" s="4" t="inlineStr"/>
-      <c r="I117" s="4" t="inlineStr"/>
+      <c r="E117" s="5" t="inlineStr"/>
+      <c r="F117" s="5" t="inlineStr"/>
+      <c r="G117" s="5" t="inlineStr"/>
+      <c r="H117" s="5" t="inlineStr"/>
+      <c r="I117" s="5" t="inlineStr"/>
     </row>
     <row r="118" ht="18" customHeight="1">
-      <c r="A118" s="5" t="inlineStr">
+      <c r="A118" s="6" t="inlineStr">
         <is>
           <t>Cart and checkout</t>
         </is>
       </c>
-      <c r="B118" s="5" t="inlineStr">
+      <c r="B118" s="6" t="inlineStr">
         <is>
           <t>Checkout</t>
         </is>
       </c>
-      <c r="C118" s="5" t="inlineStr">
+      <c r="C118" s="6" t="inlineStr">
         <is>
           <t>/checkout</t>
         </is>
       </c>
-      <c r="D118" s="5" t="inlineStr">
+      <c r="D118" s="6" t="inlineStr">
         <is>
           <t>Hand off to Stripe for payment</t>
         </is>
       </c>
-      <c r="E118" s="6" t="inlineStr">
+      <c r="E118" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F118" s="5" t="inlineStr">
+      <c r="F118" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G118" s="5" t="inlineStr"/>
-      <c r="H118" s="5" t="inlineStr"/>
-      <c r="I118" s="5" t="inlineStr"/>
+      <c r="G118" s="6" t="inlineStr"/>
+      <c r="H118" s="6" t="inlineStr"/>
+      <c r="I118" s="6" t="inlineStr"/>
     </row>
     <row r="119" ht="18" customHeight="1">
-      <c r="A119" s="5" t="inlineStr">
+      <c r="A119" s="6" t="inlineStr">
         <is>
           <t>Cart and checkout</t>
         </is>
       </c>
-      <c r="B119" s="5" t="inlineStr">
+      <c r="B119" s="6" t="inlineStr">
         <is>
           <t>Checkout</t>
         </is>
       </c>
-      <c r="C119" s="5" t="inlineStr">
+      <c r="C119" s="6" t="inlineStr">
         <is>
           <t>/checkout</t>
         </is>
       </c>
-      <c r="D119" s="5" t="inlineStr">
+      <c r="D119" s="6" t="inlineStr">
         <is>
           <t>Trust strip under the pay button</t>
         </is>
       </c>
-      <c r="E119" s="6" t="inlineStr">
+      <c r="E119" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F119" s="5" t="inlineStr">
+      <c r="F119" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G119" s="5" t="inlineStr"/>
-      <c r="H119" s="5" t="inlineStr"/>
-      <c r="I119" s="5" t="inlineStr"/>
+      <c r="G119" s="6" t="inlineStr"/>
+      <c r="H119" s="6" t="inlineStr"/>
+      <c r="I119" s="6" t="inlineStr"/>
     </row>
     <row r="120" ht="18" customHeight="1">
-      <c r="A120" s="5" t="inlineStr">
+      <c r="A120" s="6" t="inlineStr">
         <is>
           <t>Cart and checkout</t>
         </is>
       </c>
-      <c r="B120" s="5" t="inlineStr">
+      <c r="B120" s="6" t="inlineStr">
         <is>
           <t>Checkout</t>
         </is>
       </c>
-      <c r="C120" s="5" t="inlineStr">
+      <c r="C120" s="6" t="inlineStr">
         <is>
           <t>/checkout</t>
         </is>
       </c>
-      <c r="D120" s="5" t="inlineStr">
+      <c r="D120" s="6" t="inlineStr">
         <is>
           <t>Buttons follow the palette</t>
         </is>
       </c>
-      <c r="E120" s="6" t="inlineStr">
+      <c r="E120" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F120" s="5" t="inlineStr">
+      <c r="F120" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G120" s="5" t="inlineStr"/>
-      <c r="H120" s="5" t="inlineStr"/>
-      <c r="I120" s="5" t="inlineStr"/>
+      <c r="G120" s="6" t="inlineStr"/>
+      <c r="H120" s="6" t="inlineStr"/>
+      <c r="I120" s="6" t="inlineStr"/>
     </row>
     <row r="121" ht="18" customHeight="1">
-      <c r="A121" s="5" t="inlineStr">
+      <c r="A121" s="6" t="inlineStr">
         <is>
           <t>Cart and checkout</t>
         </is>
       </c>
-      <c r="B121" s="5" t="inlineStr">
+      <c r="B121" s="6" t="inlineStr">
         <is>
           <t>Checkout</t>
         </is>
       </c>
-      <c r="C121" s="5" t="inlineStr">
+      <c r="C121" s="6" t="inlineStr">
         <is>
           <t>/checkout</t>
         </is>
       </c>
-      <c r="D121" s="5" t="inlineStr">
+      <c r="D121" s="6" t="inlineStr">
         <is>
           <t>Recurring charge note for subscription plans</t>
         </is>
       </c>
-      <c r="E121" s="6" t="inlineStr">
+      <c r="E121" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F121" s="5" t="inlineStr">
+      <c r="F121" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G121" s="5" t="inlineStr"/>
-      <c r="H121" s="5" t="inlineStr"/>
-      <c r="I121" s="5" t="inlineStr"/>
+      <c r="G121" s="6" t="inlineStr"/>
+      <c r="H121" s="6" t="inlineStr"/>
+      <c r="I121" s="6" t="inlineStr"/>
     </row>
     <row r="122" ht="18" customHeight="1">
-      <c r="A122" s="5" t="inlineStr">
+      <c r="A122" s="6" t="inlineStr">
         <is>
           <t>Cart and checkout</t>
         </is>
       </c>
-      <c r="B122" s="5" t="inlineStr">
+      <c r="B122" s="6" t="inlineStr">
         <is>
           <t>Checkout</t>
         </is>
       </c>
-      <c r="C122" s="5" t="inlineStr">
+      <c r="C122" s="6" t="inlineStr">
         <is>
           <t>/checkout</t>
         </is>
       </c>
-      <c r="D122" s="5" t="inlineStr">
+      <c r="D122" s="6" t="inlineStr">
         <is>
           <t>Error message styling when payment fails</t>
         </is>
       </c>
-      <c r="E122" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F122" s="5" t="inlineStr">
+      <c r="E122" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F122" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G122" s="5" t="inlineStr"/>
-      <c r="H122" s="5" t="inlineStr"/>
-      <c r="I122" s="5" t="inlineStr"/>
+      <c r="G122" s="6" t="inlineStr"/>
+      <c r="H122" s="6" t="inlineStr"/>
+      <c r="I122" s="6" t="inlineStr"/>
     </row>
     <row r="123" ht="18" customHeight="1">
-      <c r="A123" s="5" t="inlineStr">
+      <c r="A123" s="6" t="inlineStr">
         <is>
           <t>Cart and checkout</t>
         </is>
       </c>
-      <c r="B123" s="5" t="inlineStr">
+      <c r="B123" s="6" t="inlineStr">
         <is>
           <t>Checkout</t>
         </is>
       </c>
-      <c r="C123" s="5" t="inlineStr">
+      <c r="C123" s="6" t="inlineStr">
         <is>
           <t>/checkout</t>
         </is>
       </c>
-      <c r="D123" s="5" t="inlineStr">
+      <c r="D123" s="6" t="inlineStr">
         <is>
           <t>Currency-aware totals match the chosen ship-to country</t>
         </is>
       </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="E123" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F123" s="5" t="inlineStr">
+      <c r="F123" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G123" s="5" t="inlineStr"/>
-      <c r="H123" s="5" t="inlineStr"/>
-      <c r="I123" s="5" t="inlineStr"/>
+      <c r="G123" s="6" t="inlineStr"/>
+      <c r="H123" s="6" t="inlineStr"/>
+      <c r="I123" s="6" t="inlineStr"/>
     </row>
     <row r="124" ht="20" customHeight="1">
       <c r="A124" s="3" t="inlineStr">
@@ -4517,191 +4527,191 @@
           <t>/confirmation</t>
         </is>
       </c>
-      <c r="D124" s="4" t="inlineStr">
+      <c r="D124" s="5" t="inlineStr">
         <is>
           <t>The thank you page after a successful payment</t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr"/>
-      <c r="F124" s="4" t="inlineStr"/>
-      <c r="G124" s="4" t="inlineStr"/>
-      <c r="H124" s="4" t="inlineStr"/>
-      <c r="I124" s="4" t="inlineStr"/>
+      <c r="E124" s="5" t="inlineStr"/>
+      <c r="F124" s="5" t="inlineStr"/>
+      <c r="G124" s="5" t="inlineStr"/>
+      <c r="H124" s="5" t="inlineStr"/>
+      <c r="I124" s="5" t="inlineStr"/>
     </row>
     <row r="125" ht="18" customHeight="1">
-      <c r="A125" s="5" t="inlineStr">
+      <c r="A125" s="6" t="inlineStr">
         <is>
           <t>Cart and checkout</t>
         </is>
       </c>
-      <c r="B125" s="5" t="inlineStr">
+      <c r="B125" s="6" t="inlineStr">
         <is>
           <t>Confirmation</t>
         </is>
       </c>
-      <c r="C125" s="5" t="inlineStr">
+      <c r="C125" s="6" t="inlineStr">
         <is>
           <t>/confirmation</t>
         </is>
       </c>
-      <c r="D125" s="5" t="inlineStr">
+      <c r="D125" s="6" t="inlineStr">
         <is>
           <t>Verify the Stripe session and confirm the order</t>
         </is>
       </c>
-      <c r="E125" s="6" t="inlineStr">
+      <c r="E125" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F125" s="5" t="inlineStr">
+      <c r="F125" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G125" s="5" t="inlineStr"/>
-      <c r="H125" s="5" t="inlineStr"/>
-      <c r="I125" s="5" t="inlineStr"/>
+      <c r="G125" s="6" t="inlineStr"/>
+      <c r="H125" s="6" t="inlineStr"/>
+      <c r="I125" s="6" t="inlineStr"/>
     </row>
     <row r="126" ht="18" customHeight="1">
-      <c r="A126" s="5" t="inlineStr">
+      <c r="A126" s="6" t="inlineStr">
         <is>
           <t>Cart and checkout</t>
         </is>
       </c>
-      <c r="B126" s="5" t="inlineStr">
+      <c r="B126" s="6" t="inlineStr">
         <is>
           <t>Confirmation</t>
         </is>
       </c>
-      <c r="C126" s="5" t="inlineStr">
+      <c r="C126" s="6" t="inlineStr">
         <is>
           <t>/confirmation</t>
         </is>
       </c>
-      <c r="D126" s="5" t="inlineStr">
+      <c r="D126" s="6" t="inlineStr">
         <is>
           <t>Auto-create the order in our system after payment</t>
         </is>
       </c>
-      <c r="E126" s="6" t="inlineStr">
+      <c r="E126" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F126" s="5" t="inlineStr">
+      <c r="F126" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G126" s="5" t="inlineStr"/>
-      <c r="H126" s="5" t="inlineStr"/>
-      <c r="I126" s="5" t="inlineStr"/>
+      <c r="G126" s="6" t="inlineStr"/>
+      <c r="H126" s="6" t="inlineStr"/>
+      <c r="I126" s="6" t="inlineStr"/>
     </row>
     <row r="127" ht="18" customHeight="1">
-      <c r="A127" s="5" t="inlineStr">
+      <c r="A127" s="6" t="inlineStr">
         <is>
           <t>Cart and checkout</t>
         </is>
       </c>
-      <c r="B127" s="5" t="inlineStr">
+      <c r="B127" s="6" t="inlineStr">
         <is>
           <t>Confirmation</t>
         </is>
       </c>
-      <c r="C127" s="5" t="inlineStr">
+      <c r="C127" s="6" t="inlineStr">
         <is>
           <t>/confirmation</t>
         </is>
       </c>
-      <c r="D127" s="5" t="inlineStr">
+      <c r="D127" s="6" t="inlineStr">
         <is>
           <t>Show order details and next steps</t>
         </is>
       </c>
-      <c r="E127" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F127" s="5" t="inlineStr">
+      <c r="E127" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F127" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G127" s="5" t="inlineStr"/>
-      <c r="H127" s="5" t="inlineStr"/>
-      <c r="I127" s="5" t="inlineStr"/>
+      <c r="G127" s="6" t="inlineStr"/>
+      <c r="H127" s="6" t="inlineStr"/>
+      <c r="I127" s="6" t="inlineStr"/>
     </row>
     <row r="128" ht="18" customHeight="1">
-      <c r="A128" s="5" t="inlineStr">
+      <c r="A128" s="6" t="inlineStr">
         <is>
           <t>Cart and checkout</t>
         </is>
       </c>
-      <c r="B128" s="5" t="inlineStr">
+      <c r="B128" s="6" t="inlineStr">
         <is>
           <t>Confirmation</t>
         </is>
       </c>
-      <c r="C128" s="5" t="inlineStr">
+      <c r="C128" s="6" t="inlineStr">
         <is>
           <t>/confirmation</t>
         </is>
       </c>
-      <c r="D128" s="5" t="inlineStr">
+      <c r="D128" s="6" t="inlineStr">
         <is>
           <t>Show tracking link once the courier integration is live</t>
         </is>
       </c>
-      <c r="E128" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F128" s="5" t="inlineStr">
+      <c r="E128" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F128" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G128" s="5" t="inlineStr"/>
-      <c r="H128" s="5" t="inlineStr"/>
-      <c r="I128" s="5" t="inlineStr"/>
+      <c r="G128" s="6" t="inlineStr"/>
+      <c r="H128" s="6" t="inlineStr"/>
+      <c r="I128" s="6" t="inlineStr"/>
     </row>
     <row r="129" ht="18" customHeight="1">
-      <c r="A129" s="5" t="inlineStr">
+      <c r="A129" s="6" t="inlineStr">
         <is>
           <t>Cart and checkout</t>
         </is>
       </c>
-      <c r="B129" s="5" t="inlineStr">
+      <c r="B129" s="6" t="inlineStr">
         <is>
           <t>Confirmation</t>
         </is>
       </c>
-      <c r="C129" s="5" t="inlineStr">
+      <c r="C129" s="6" t="inlineStr">
         <is>
           <t>/confirmation</t>
         </is>
       </c>
-      <c r="D129" s="5" t="inlineStr">
+      <c r="D129" s="6" t="inlineStr">
         <is>
           <t>Currency symbol comes from Stripe session, not hardcoded</t>
         </is>
       </c>
-      <c r="E129" s="6" t="inlineStr">
+      <c r="E129" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F129" s="5" t="inlineStr">
+      <c r="F129" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G129" s="5" t="inlineStr"/>
-      <c r="H129" s="5" t="inlineStr"/>
-      <c r="I129" s="5" t="inlineStr"/>
+      <c r="G129" s="6" t="inlineStr"/>
+      <c r="H129" s="6" t="inlineStr"/>
+      <c r="I129" s="6" t="inlineStr"/>
     </row>
     <row r="130" ht="22" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
@@ -4726,265 +4736,265 @@
           <t>/account</t>
         </is>
       </c>
-      <c r="D131" s="4" t="inlineStr">
+      <c r="D131" s="5" t="inlineStr">
         <is>
           <t>Where the customer manages their orders, subscription, and profile</t>
         </is>
       </c>
-      <c r="E131" s="4" t="inlineStr"/>
-      <c r="F131" s="4" t="inlineStr"/>
-      <c r="G131" s="4" t="inlineStr"/>
-      <c r="H131" s="4" t="inlineStr"/>
-      <c r="I131" s="4" t="inlineStr"/>
+      <c r="E131" s="5" t="inlineStr"/>
+      <c r="F131" s="5" t="inlineStr"/>
+      <c r="G131" s="5" t="inlineStr"/>
+      <c r="H131" s="5" t="inlineStr"/>
+      <c r="I131" s="5" t="inlineStr"/>
     </row>
     <row r="132" ht="18" customHeight="1">
-      <c r="A132" s="5" t="inlineStr">
+      <c r="A132" s="6" t="inlineStr">
         <is>
           <t>Customer account</t>
         </is>
       </c>
-      <c r="B132" s="5" t="inlineStr">
+      <c r="B132" s="6" t="inlineStr">
         <is>
           <t>Account dashboard</t>
         </is>
       </c>
-      <c r="C132" s="5" t="inlineStr">
+      <c r="C132" s="6" t="inlineStr">
         <is>
           <t>/account</t>
         </is>
       </c>
-      <c r="D132" s="5" t="inlineStr">
+      <c r="D132" s="6" t="inlineStr">
         <is>
           <t>Sign in works end to end</t>
         </is>
       </c>
-      <c r="E132" s="6" t="inlineStr">
+      <c r="E132" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F132" s="5" t="inlineStr">
+      <c r="F132" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G132" s="5" t="inlineStr"/>
-      <c r="H132" s="5" t="inlineStr"/>
-      <c r="I132" s="5" t="inlineStr"/>
+      <c r="G132" s="6" t="inlineStr"/>
+      <c r="H132" s="6" t="inlineStr"/>
+      <c r="I132" s="6" t="inlineStr"/>
     </row>
     <row r="133" ht="18" customHeight="1">
-      <c r="A133" s="5" t="inlineStr">
+      <c r="A133" s="6" t="inlineStr">
         <is>
           <t>Customer account</t>
         </is>
       </c>
-      <c r="B133" s="5" t="inlineStr">
+      <c r="B133" s="6" t="inlineStr">
         <is>
           <t>Account dashboard</t>
         </is>
       </c>
-      <c r="C133" s="5" t="inlineStr">
+      <c r="C133" s="6" t="inlineStr">
         <is>
           <t>/account</t>
         </is>
       </c>
-      <c r="D133" s="5" t="inlineStr">
+      <c r="D133" s="6" t="inlineStr">
         <is>
           <t>Dashboard layout looks right</t>
         </is>
       </c>
-      <c r="E133" s="6" t="inlineStr">
+      <c r="E133" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F133" s="5" t="inlineStr">
+      <c r="F133" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G133" s="5" t="inlineStr"/>
-      <c r="H133" s="5" t="inlineStr"/>
-      <c r="I133" s="5" t="inlineStr"/>
+      <c r="G133" s="6" t="inlineStr"/>
+      <c r="H133" s="6" t="inlineStr"/>
+      <c r="I133" s="6" t="inlineStr"/>
     </row>
     <row r="134" ht="18" customHeight="1">
-      <c r="A134" s="5" t="inlineStr">
+      <c r="A134" s="6" t="inlineStr">
         <is>
           <t>Customer account</t>
         </is>
       </c>
-      <c r="B134" s="5" t="inlineStr">
+      <c r="B134" s="6" t="inlineStr">
         <is>
           <t>Account dashboard</t>
         </is>
       </c>
-      <c r="C134" s="5" t="inlineStr">
+      <c r="C134" s="6" t="inlineStr">
         <is>
           <t>/account</t>
         </is>
       </c>
-      <c r="D134" s="5" t="inlineStr">
+      <c r="D134" s="6" t="inlineStr">
         <is>
           <t>Past orders view</t>
         </is>
       </c>
-      <c r="E134" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F134" s="5" t="inlineStr">
+      <c r="E134" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F134" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G134" s="5" t="inlineStr"/>
-      <c r="H134" s="5" t="inlineStr"/>
-      <c r="I134" s="5" t="inlineStr"/>
+      <c r="G134" s="6" t="inlineStr"/>
+      <c r="H134" s="6" t="inlineStr"/>
+      <c r="I134" s="6" t="inlineStr"/>
     </row>
     <row r="135" ht="18" customHeight="1">
-      <c r="A135" s="5" t="inlineStr">
+      <c r="A135" s="6" t="inlineStr">
         <is>
           <t>Customer account</t>
         </is>
       </c>
-      <c r="B135" s="5" t="inlineStr">
+      <c r="B135" s="6" t="inlineStr">
         <is>
           <t>Account dashboard</t>
         </is>
       </c>
-      <c r="C135" s="5" t="inlineStr">
+      <c r="C135" s="6" t="inlineStr">
         <is>
           <t>/account</t>
         </is>
       </c>
-      <c r="D135" s="5" t="inlineStr">
+      <c r="D135" s="6" t="inlineStr">
         <is>
           <t>Subscription management (pause, cancel, change plan)</t>
         </is>
       </c>
-      <c r="E135" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F135" s="5" t="inlineStr">
+      <c r="E135" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G135" s="5" t="inlineStr"/>
-      <c r="H135" s="5" t="inlineStr"/>
-      <c r="I135" s="5" t="inlineStr"/>
+      <c r="G135" s="6" t="inlineStr"/>
+      <c r="H135" s="6" t="inlineStr"/>
+      <c r="I135" s="6" t="inlineStr"/>
     </row>
     <row r="136" ht="18" customHeight="1">
-      <c r="A136" s="5" t="inlineStr">
+      <c r="A136" s="6" t="inlineStr">
         <is>
           <t>Customer account</t>
         </is>
       </c>
-      <c r="B136" s="5" t="inlineStr">
+      <c r="B136" s="6" t="inlineStr">
         <is>
           <t>Account dashboard</t>
         </is>
       </c>
-      <c r="C136" s="5" t="inlineStr">
+      <c r="C136" s="6" t="inlineStr">
         <is>
           <t>/account</t>
         </is>
       </c>
-      <c r="D136" s="5" t="inlineStr">
+      <c r="D136" s="6" t="inlineStr">
         <is>
           <t>Retake the quiz from inside the account</t>
         </is>
       </c>
-      <c r="E136" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F136" s="5" t="inlineStr">
+      <c r="E136" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F136" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G136" s="5" t="inlineStr"/>
-      <c r="H136" s="5" t="inlineStr"/>
-      <c r="I136" s="5" t="inlineStr"/>
+      <c r="G136" s="6" t="inlineStr"/>
+      <c r="H136" s="6" t="inlineStr"/>
+      <c r="I136" s="6" t="inlineStr"/>
     </row>
     <row r="137" ht="18" customHeight="1">
-      <c r="A137" s="5" t="inlineStr">
+      <c r="A137" s="6" t="inlineStr">
         <is>
           <t>Customer account</t>
         </is>
       </c>
-      <c r="B137" s="5" t="inlineStr">
+      <c r="B137" s="6" t="inlineStr">
         <is>
           <t>Account dashboard</t>
         </is>
       </c>
-      <c r="C137" s="5" t="inlineStr">
+      <c r="C137" s="6" t="inlineStr">
         <is>
           <t>/account</t>
         </is>
       </c>
-      <c r="D137" s="5" t="inlineStr">
+      <c r="D137" s="6" t="inlineStr">
         <is>
           <t>Edit profile and shipping address</t>
         </is>
       </c>
-      <c r="E137" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F137" s="5" t="inlineStr">
+      <c r="E137" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F137" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G137" s="5" t="inlineStr"/>
-      <c r="H137" s="5" t="inlineStr"/>
-      <c r="I137" s="5" t="inlineStr"/>
+      <c r="G137" s="6" t="inlineStr"/>
+      <c r="H137" s="6" t="inlineStr"/>
+      <c r="I137" s="6" t="inlineStr"/>
     </row>
     <row r="138" ht="18" customHeight="1">
-      <c r="A138" s="5" t="inlineStr">
+      <c r="A138" s="6" t="inlineStr">
         <is>
           <t>Customer account</t>
         </is>
       </c>
-      <c r="B138" s="5" t="inlineStr">
+      <c r="B138" s="6" t="inlineStr">
         <is>
           <t>Account dashboard</t>
         </is>
       </c>
-      <c r="C138" s="5" t="inlineStr">
+      <c r="C138" s="6" t="inlineStr">
         <is>
           <t>/account</t>
         </is>
       </c>
-      <c r="D138" s="5" t="inlineStr">
+      <c r="D138" s="6" t="inlineStr">
         <is>
           <t>'Manage payment &amp; billing' button → opens Stripe Customer Portal</t>
         </is>
       </c>
-      <c r="E138" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F138" s="5" t="inlineStr">
+      <c r="E138" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F138" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G138" s="5" t="inlineStr"/>
-      <c r="H138" s="5" t="inlineStr">
+      <c r="G138" s="6" t="inlineStr"/>
+      <c r="H138" s="6" t="inlineStr">
         <is>
           <t>Customer Portal handles add/remove/update cards, invoices, subscription pause/cancel, failed-payment recovery.</t>
         </is>
       </c>
-      <c r="I138" s="5" t="inlineStr"/>
+      <c r="I138" s="6" t="inlineStr"/>
     </row>
     <row r="139" ht="22" customHeight="1">
       <c r="A139" s="2" t="inlineStr">
@@ -5009,156 +5019,156 @@
           <t>/ingredients</t>
         </is>
       </c>
-      <c r="D140" s="4" t="inlineStr">
+      <c r="D140" s="5" t="inlineStr">
         <is>
           <t>A glossary of all the botanicals we use</t>
         </is>
       </c>
-      <c r="E140" s="4" t="inlineStr"/>
-      <c r="F140" s="4" t="inlineStr"/>
-      <c r="G140" s="4" t="inlineStr"/>
-      <c r="H140" s="4" t="inlineStr"/>
-      <c r="I140" s="4" t="inlineStr"/>
+      <c r="E140" s="5" t="inlineStr"/>
+      <c r="F140" s="5" t="inlineStr"/>
+      <c r="G140" s="5" t="inlineStr"/>
+      <c r="H140" s="5" t="inlineStr"/>
+      <c r="I140" s="5" t="inlineStr"/>
     </row>
     <row r="141" ht="18" customHeight="1">
-      <c r="A141" s="5" t="inlineStr">
+      <c r="A141" s="6" t="inlineStr">
         <is>
           <t>Reference pages</t>
         </is>
       </c>
-      <c r="B141" s="5" t="inlineStr">
+      <c r="B141" s="6" t="inlineStr">
         <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="C141" s="5" t="inlineStr">
+      <c r="C141" s="6" t="inlineStr">
         <is>
           <t>/ingredients</t>
         </is>
       </c>
-      <c r="D141" s="5" t="inlineStr">
+      <c r="D141" s="6" t="inlineStr">
         <is>
           <t>Show every ingredient from the database</t>
         </is>
       </c>
-      <c r="E141" s="6" t="inlineStr">
+      <c r="E141" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F141" s="5" t="inlineStr">
+      <c r="F141" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G141" s="5" t="inlineStr"/>
-      <c r="H141" s="5" t="inlineStr"/>
-      <c r="I141" s="5" t="inlineStr"/>
+      <c r="G141" s="6" t="inlineStr"/>
+      <c r="H141" s="6" t="inlineStr"/>
+      <c r="I141" s="6" t="inlineStr"/>
     </row>
     <row r="142" ht="18" customHeight="1">
-      <c r="A142" s="5" t="inlineStr">
+      <c r="A142" s="6" t="inlineStr">
         <is>
           <t>Reference pages</t>
         </is>
       </c>
-      <c r="B142" s="5" t="inlineStr">
+      <c r="B142" s="6" t="inlineStr">
         <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="C142" s="5" t="inlineStr">
+      <c r="C142" s="6" t="inlineStr">
         <is>
           <t>/ingredients</t>
         </is>
       </c>
-      <c r="D142" s="5" t="inlineStr">
+      <c r="D142" s="6" t="inlineStr">
         <is>
           <t>Filter by function or type</t>
         </is>
       </c>
-      <c r="E142" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F142" s="5" t="inlineStr">
+      <c r="E142" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F142" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G142" s="5" t="inlineStr"/>
-      <c r="H142" s="5" t="inlineStr"/>
-      <c r="I142" s="5" t="inlineStr"/>
+      <c r="G142" s="6" t="inlineStr"/>
+      <c r="H142" s="6" t="inlineStr"/>
+      <c r="I142" s="6" t="inlineStr"/>
     </row>
     <row r="143" ht="18" customHeight="1">
-      <c r="A143" s="5" t="inlineStr">
+      <c r="A143" s="6" t="inlineStr">
         <is>
           <t>Reference pages</t>
         </is>
       </c>
-      <c r="B143" s="5" t="inlineStr">
+      <c r="B143" s="6" t="inlineStr">
         <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="C143" s="5" t="inlineStr">
+      <c r="C143" s="6" t="inlineStr">
         <is>
           <t>/ingredients</t>
         </is>
       </c>
-      <c r="D143" s="5" t="inlineStr">
+      <c r="D143" s="6" t="inlineStr">
         <is>
           <t>Detail page per ingredient (origin, function, scientific name)</t>
         </is>
       </c>
-      <c r="E143" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F143" s="5" t="inlineStr">
+      <c r="E143" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F143" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G143" s="5" t="inlineStr"/>
-      <c r="H143" s="5" t="inlineStr"/>
-      <c r="I143" s="5" t="inlineStr"/>
+      <c r="G143" s="6" t="inlineStr"/>
+      <c r="H143" s="6" t="inlineStr"/>
+      <c r="I143" s="6" t="inlineStr"/>
     </row>
     <row r="144" ht="18" customHeight="1">
-      <c r="A144" s="5" t="inlineStr">
+      <c r="A144" s="6" t="inlineStr">
         <is>
           <t>Reference pages</t>
         </is>
       </c>
-      <c r="B144" s="5" t="inlineStr">
+      <c r="B144" s="6" t="inlineStr">
         <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="C144" s="5" t="inlineStr">
+      <c r="C144" s="6" t="inlineStr">
         <is>
           <t>/ingredients</t>
         </is>
       </c>
-      <c r="D144" s="5" t="inlineStr">
+      <c r="D144" s="6" t="inlineStr">
         <is>
           <t>Type and layout polish</t>
         </is>
       </c>
-      <c r="E144" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F144" s="5" t="inlineStr">
+      <c r="E144" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F144" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G144" s="5" t="inlineStr"/>
-      <c r="H144" s="5" t="inlineStr"/>
-      <c r="I144" s="5" t="inlineStr"/>
+      <c r="G144" s="6" t="inlineStr"/>
+      <c r="H144" s="6" t="inlineStr"/>
+      <c r="I144" s="6" t="inlineStr"/>
     </row>
     <row r="145" ht="22" customHeight="1">
       <c r="A145" s="2" t="inlineStr">
@@ -5178,371 +5188,371 @@
           <t>Fulfillment Studio</t>
         </is>
       </c>
-      <c r="C146" s="4" t="inlineStr">
+      <c r="C146" s="5" t="inlineStr">
         <is>
           <t>fulfillment-studio (separate dashboard)</t>
         </is>
       </c>
-      <c r="D146" s="4" t="inlineStr">
+      <c r="D146" s="5" t="inlineStr">
         <is>
           <t>The operations dashboard for picking, packing, printing labels, and exporting product data</t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr"/>
-      <c r="F146" s="4" t="inlineStr"/>
-      <c r="G146" s="4" t="inlineStr"/>
-      <c r="H146" s="4" t="inlineStr"/>
-      <c r="I146" s="4" t="inlineStr"/>
+      <c r="E146" s="5" t="inlineStr"/>
+      <c r="F146" s="5" t="inlineStr"/>
+      <c r="G146" s="5" t="inlineStr"/>
+      <c r="H146" s="5" t="inlineStr"/>
+      <c r="I146" s="5" t="inlineStr"/>
     </row>
     <row r="147" ht="18" customHeight="1">
-      <c r="A147" s="5" t="inlineStr">
+      <c r="A147" s="6" t="inlineStr">
         <is>
           <t>Admin tools</t>
         </is>
       </c>
-      <c r="B147" s="5" t="inlineStr">
+      <c r="B147" s="6" t="inlineStr">
         <is>
           <t>Fulfillment Studio</t>
         </is>
       </c>
-      <c r="C147" s="5" t="inlineStr">
+      <c r="C147" s="6" t="inlineStr">
         <is>
           <t>fulfillment-studio (separate dashboard)</t>
         </is>
       </c>
-      <c r="D147" s="5" t="inlineStr">
+      <c r="D147" s="6" t="inlineStr">
         <is>
           <t>Only admins can sign in</t>
         </is>
       </c>
-      <c r="E147" s="6" t="inlineStr">
+      <c r="E147" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F147" s="5" t="inlineStr">
+      <c r="F147" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G147" s="5" t="inlineStr"/>
-      <c r="H147" s="5" t="inlineStr"/>
-      <c r="I147" s="5" t="inlineStr"/>
+      <c r="G147" s="6" t="inlineStr"/>
+      <c r="H147" s="6" t="inlineStr"/>
+      <c r="I147" s="6" t="inlineStr"/>
     </row>
     <row r="148" ht="18" customHeight="1">
-      <c r="A148" s="5" t="inlineStr">
+      <c r="A148" s="6" t="inlineStr">
         <is>
           <t>Admin tools</t>
         </is>
       </c>
-      <c r="B148" s="5" t="inlineStr">
+      <c r="B148" s="6" t="inlineStr">
         <is>
           <t>Fulfillment Studio</t>
         </is>
       </c>
-      <c r="C148" s="5" t="inlineStr">
+      <c r="C148" s="6" t="inlineStr">
         <is>
           <t>fulfillment-studio (separate dashboard)</t>
         </is>
       </c>
-      <c r="D148" s="5" t="inlineStr">
+      <c r="D148" s="6" t="inlineStr">
         <is>
           <t>List of pending and fulfilled orders with filters</t>
         </is>
       </c>
-      <c r="E148" s="6" t="inlineStr">
+      <c r="E148" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F148" s="5" t="inlineStr">
+      <c r="F148" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G148" s="5" t="inlineStr"/>
-      <c r="H148" s="5" t="inlineStr"/>
-      <c r="I148" s="5" t="inlineStr"/>
+      <c r="G148" s="6" t="inlineStr"/>
+      <c r="H148" s="6" t="inlineStr"/>
+      <c r="I148" s="6" t="inlineStr"/>
     </row>
     <row r="149" ht="18" customHeight="1">
-      <c r="A149" s="5" t="inlineStr">
+      <c r="A149" s="6" t="inlineStr">
         <is>
           <t>Admin tools</t>
         </is>
       </c>
-      <c r="B149" s="5" t="inlineStr">
+      <c r="B149" s="6" t="inlineStr">
         <is>
           <t>Fulfillment Studio</t>
         </is>
       </c>
-      <c r="C149" s="5" t="inlineStr">
+      <c r="C149" s="6" t="inlineStr">
         <is>
           <t>fulfillment-studio (separate dashboard)</t>
         </is>
       </c>
-      <c r="D149" s="5" t="inlineStr">
+      <c r="D149" s="6" t="inlineStr">
         <is>
           <t>Assign barcodes when an order is fulfilled</t>
         </is>
       </c>
-      <c r="E149" s="6" t="inlineStr">
+      <c r="E149" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F149" s="5" t="inlineStr">
+      <c r="F149" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G149" s="5" t="inlineStr"/>
-      <c r="H149" s="5" t="inlineStr"/>
-      <c r="I149" s="5" t="inlineStr"/>
+      <c r="G149" s="6" t="inlineStr"/>
+      <c r="H149" s="6" t="inlineStr"/>
+      <c r="I149" s="6" t="inlineStr"/>
     </row>
     <row r="150" ht="18" customHeight="1">
-      <c r="A150" s="5" t="inlineStr">
+      <c r="A150" s="6" t="inlineStr">
         <is>
           <t>Admin tools</t>
         </is>
       </c>
-      <c r="B150" s="5" t="inlineStr">
+      <c r="B150" s="6" t="inlineStr">
         <is>
           <t>Fulfillment Studio</t>
         </is>
       </c>
-      <c r="C150" s="5" t="inlineStr">
+      <c r="C150" s="6" t="inlineStr">
         <is>
           <t>fulfillment-studio (separate dashboard)</t>
         </is>
       </c>
-      <c r="D150" s="5" t="inlineStr">
+      <c r="D150" s="6" t="inlineStr">
         <is>
           <t>Print one or all labels at once</t>
         </is>
       </c>
-      <c r="E150" s="6" t="inlineStr">
+      <c r="E150" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F150" s="5" t="inlineStr">
+      <c r="F150" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G150" s="5" t="inlineStr"/>
-      <c r="H150" s="5" t="inlineStr"/>
-      <c r="I150" s="5" t="inlineStr"/>
+      <c r="G150" s="6" t="inlineStr"/>
+      <c r="H150" s="6" t="inlineStr"/>
+      <c r="I150" s="6" t="inlineStr"/>
     </row>
     <row r="151" ht="18" customHeight="1">
-      <c r="A151" s="5" t="inlineStr">
+      <c r="A151" s="6" t="inlineStr">
         <is>
           <t>Admin tools</t>
         </is>
       </c>
-      <c r="B151" s="5" t="inlineStr">
+      <c r="B151" s="6" t="inlineStr">
         <is>
           <t>Fulfillment Studio</t>
         </is>
       </c>
-      <c r="C151" s="5" t="inlineStr">
+      <c r="C151" s="6" t="inlineStr">
         <is>
           <t>fulfillment-studio (separate dashboard)</t>
         </is>
       </c>
-      <c r="D151" s="5" t="inlineStr">
+      <c r="D151" s="6" t="inlineStr">
         <is>
           <t>Barcodes printed at GS1 standard size</t>
         </is>
       </c>
-      <c r="E151" s="6" t="inlineStr">
+      <c r="E151" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F151" s="5" t="inlineStr">
+      <c r="F151" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G151" s="5" t="inlineStr"/>
-      <c r="H151" s="5" t="inlineStr"/>
-      <c r="I151" s="5" t="inlineStr"/>
+      <c r="G151" s="6" t="inlineStr"/>
+      <c r="H151" s="6" t="inlineStr"/>
+      <c r="I151" s="6" t="inlineStr"/>
     </row>
     <row r="152" ht="18" customHeight="1">
-      <c r="A152" s="5" t="inlineStr">
+      <c r="A152" s="6" t="inlineStr">
         <is>
           <t>Admin tools</t>
         </is>
       </c>
-      <c r="B152" s="5" t="inlineStr">
+      <c r="B152" s="6" t="inlineStr">
         <is>
           <t>Fulfillment Studio</t>
         </is>
       </c>
-      <c r="C152" s="5" t="inlineStr">
+      <c r="C152" s="6" t="inlineStr">
         <is>
           <t>fulfillment-studio (separate dashboard)</t>
         </is>
       </c>
-      <c r="D152" s="5" t="inlineStr">
+      <c r="D152" s="6" t="inlineStr">
         <is>
           <t>Download an XML file per product for INCI Beauty</t>
         </is>
       </c>
-      <c r="E152" s="6" t="inlineStr">
+      <c r="E152" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F152" s="5" t="inlineStr">
+      <c r="F152" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G152" s="5" t="inlineStr"/>
-      <c r="H152" s="5" t="inlineStr"/>
-      <c r="I152" s="5" t="inlineStr"/>
+      <c r="G152" s="6" t="inlineStr"/>
+      <c r="H152" s="6" t="inlineStr"/>
+      <c r="I152" s="6" t="inlineStr"/>
     </row>
     <row r="153" ht="18" customHeight="1">
-      <c r="A153" s="5" t="inlineStr">
+      <c r="A153" s="6" t="inlineStr">
         <is>
           <t>Admin tools</t>
         </is>
       </c>
-      <c r="B153" s="5" t="inlineStr">
+      <c r="B153" s="6" t="inlineStr">
         <is>
           <t>Fulfillment Studio</t>
         </is>
       </c>
-      <c r="C153" s="5" t="inlineStr">
+      <c r="C153" s="6" t="inlineStr">
         <is>
           <t>fulfillment-studio (separate dashboard)</t>
         </is>
       </c>
-      <c r="D153" s="5" t="inlineStr">
+      <c r="D153" s="6" t="inlineStr">
         <is>
           <t>Cancel an order or delete a test order</t>
         </is>
       </c>
-      <c r="E153" s="6" t="inlineStr">
+      <c r="E153" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F153" s="5" t="inlineStr">
+      <c r="F153" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G153" s="5" t="inlineStr"/>
-      <c r="H153" s="5" t="inlineStr"/>
-      <c r="I153" s="5" t="inlineStr"/>
+      <c r="G153" s="6" t="inlineStr"/>
+      <c r="H153" s="6" t="inlineStr"/>
+      <c r="I153" s="6" t="inlineStr"/>
     </row>
     <row r="154" ht="18" customHeight="1">
-      <c r="A154" s="5" t="inlineStr">
+      <c r="A154" s="6" t="inlineStr">
         <is>
           <t>Admin tools</t>
         </is>
       </c>
-      <c r="B154" s="5" t="inlineStr">
+      <c r="B154" s="6" t="inlineStr">
         <is>
           <t>Fulfillment Studio</t>
         </is>
       </c>
-      <c r="C154" s="5" t="inlineStr">
+      <c r="C154" s="6" t="inlineStr">
         <is>
           <t>fulfillment-studio (separate dashboard)</t>
         </is>
       </c>
-      <c r="D154" s="5" t="inlineStr">
+      <c r="D154" s="6" t="inlineStr">
         <is>
           <t>Create a shipment with the Direx courier</t>
         </is>
       </c>
-      <c r="E154" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F154" s="5" t="inlineStr">
+      <c r="E154" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F154" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G154" s="5" t="inlineStr"/>
-      <c r="H154" s="5" t="inlineStr"/>
-      <c r="I154" s="5" t="inlineStr"/>
+      <c r="G154" s="6" t="inlineStr"/>
+      <c r="H154" s="6" t="inlineStr"/>
+      <c r="I154" s="6" t="inlineStr"/>
     </row>
     <row r="155" ht="18" customHeight="1">
-      <c r="A155" s="5" t="inlineStr">
+      <c r="A155" s="6" t="inlineStr">
         <is>
           <t>Admin tools</t>
         </is>
       </c>
-      <c r="B155" s="5" t="inlineStr">
+      <c r="B155" s="6" t="inlineStr">
         <is>
           <t>Fulfillment Studio</t>
         </is>
       </c>
-      <c r="C155" s="5" t="inlineStr">
+      <c r="C155" s="6" t="inlineStr">
         <is>
           <t>fulfillment-studio (separate dashboard)</t>
         </is>
       </c>
-      <c r="D155" s="5" t="inlineStr">
+      <c r="D155" s="6" t="inlineStr">
         <is>
           <t>Close the daily manifest and schedule a pickup</t>
         </is>
       </c>
-      <c r="E155" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F155" s="5" t="inlineStr">
+      <c r="E155" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F155" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G155" s="5" t="inlineStr"/>
-      <c r="H155" s="5" t="inlineStr"/>
-      <c r="I155" s="5" t="inlineStr"/>
+      <c r="G155" s="6" t="inlineStr"/>
+      <c r="H155" s="6" t="inlineStr"/>
+      <c r="I155" s="6" t="inlineStr"/>
     </row>
     <row r="156" ht="18" customHeight="1">
-      <c r="A156" s="5" t="inlineStr">
+      <c r="A156" s="6" t="inlineStr">
         <is>
           <t>Admin tools</t>
         </is>
       </c>
-      <c r="B156" s="5" t="inlineStr">
+      <c r="B156" s="6" t="inlineStr">
         <is>
           <t>Fulfillment Studio</t>
         </is>
       </c>
-      <c r="C156" s="5" t="inlineStr">
+      <c r="C156" s="6" t="inlineStr">
         <is>
           <t>fulfillment-studio (separate dashboard)</t>
         </is>
       </c>
-      <c r="D156" s="5" t="inlineStr">
+      <c r="D156" s="6" t="inlineStr">
         <is>
           <t>Auto deploy this dashboard when we push (currently manual)</t>
         </is>
       </c>
-      <c r="E156" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F156" s="5" t="inlineStr">
+      <c r="E156" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F156" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G156" s="5" t="inlineStr"/>
-      <c r="H156" s="5" t="inlineStr"/>
-      <c r="I156" s="5" t="inlineStr"/>
+      <c r="G156" s="6" t="inlineStr"/>
+      <c r="H156" s="6" t="inlineStr"/>
+      <c r="I156" s="6" t="inlineStr"/>
     </row>
     <row r="157" ht="20" customHeight="1">
       <c r="A157" s="3" t="inlineStr">
@@ -5555,126 +5565,126 @@
           <t>Barcode Studio</t>
         </is>
       </c>
-      <c r="C157" s="4" t="inlineStr">
+      <c r="C157" s="5" t="inlineStr">
         <is>
           <t>barcode-studio (separate dashboard)</t>
         </is>
       </c>
-      <c r="D157" s="4" t="inlineStr">
+      <c r="D157" s="5" t="inlineStr">
         <is>
           <t>Where we manage our pool of product barcodes</t>
         </is>
       </c>
-      <c r="E157" s="4" t="inlineStr"/>
-      <c r="F157" s="4" t="inlineStr"/>
-      <c r="G157" s="4" t="inlineStr"/>
-      <c r="H157" s="4" t="inlineStr"/>
-      <c r="I157" s="4" t="inlineStr"/>
+      <c r="E157" s="5" t="inlineStr"/>
+      <c r="F157" s="5" t="inlineStr"/>
+      <c r="G157" s="5" t="inlineStr"/>
+      <c r="H157" s="5" t="inlineStr"/>
+      <c r="I157" s="5" t="inlineStr"/>
     </row>
     <row r="158" ht="18" customHeight="1">
-      <c r="A158" s="5" t="inlineStr">
+      <c r="A158" s="6" t="inlineStr">
         <is>
           <t>Admin tools</t>
         </is>
       </c>
-      <c r="B158" s="5" t="inlineStr">
+      <c r="B158" s="6" t="inlineStr">
         <is>
           <t>Barcode Studio</t>
         </is>
       </c>
-      <c r="C158" s="5" t="inlineStr">
+      <c r="C158" s="6" t="inlineStr">
         <is>
           <t>barcode-studio (separate dashboard)</t>
         </is>
       </c>
-      <c r="D158" s="5" t="inlineStr">
+      <c r="D158" s="6" t="inlineStr">
         <is>
           <t>Manage which company prefix we issue from</t>
         </is>
       </c>
-      <c r="E158" s="6" t="inlineStr">
+      <c r="E158" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F158" s="5" t="inlineStr">
+      <c r="F158" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G158" s="5" t="inlineStr"/>
-      <c r="H158" s="5" t="inlineStr"/>
-      <c r="I158" s="5" t="inlineStr"/>
+      <c r="G158" s="6" t="inlineStr"/>
+      <c r="H158" s="6" t="inlineStr"/>
+      <c r="I158" s="6" t="inlineStr"/>
     </row>
     <row r="159" ht="18" customHeight="1">
-      <c r="A159" s="5" t="inlineStr">
+      <c r="A159" s="6" t="inlineStr">
         <is>
           <t>Admin tools</t>
         </is>
       </c>
-      <c r="B159" s="5" t="inlineStr">
+      <c r="B159" s="6" t="inlineStr">
         <is>
           <t>Barcode Studio</t>
         </is>
       </c>
-      <c r="C159" s="5" t="inlineStr">
+      <c r="C159" s="6" t="inlineStr">
         <is>
           <t>barcode-studio (separate dashboard)</t>
         </is>
       </c>
-      <c r="D159" s="5" t="inlineStr">
+      <c r="D159" s="6" t="inlineStr">
         <is>
           <t>Bulk import barcodes from an Excel file</t>
         </is>
       </c>
-      <c r="E159" s="6" t="inlineStr">
+      <c r="E159" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F159" s="5" t="inlineStr">
+      <c r="F159" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G159" s="5" t="inlineStr"/>
-      <c r="H159" s="5" t="inlineStr"/>
-      <c r="I159" s="5" t="inlineStr"/>
+      <c r="G159" s="6" t="inlineStr"/>
+      <c r="H159" s="6" t="inlineStr"/>
+      <c r="I159" s="6" t="inlineStr"/>
     </row>
     <row r="160" ht="18" customHeight="1">
-      <c r="A160" s="5" t="inlineStr">
+      <c r="A160" s="6" t="inlineStr">
         <is>
           <t>Admin tools</t>
         </is>
       </c>
-      <c r="B160" s="5" t="inlineStr">
+      <c r="B160" s="6" t="inlineStr">
         <is>
           <t>Barcode Studio</t>
         </is>
       </c>
-      <c r="C160" s="5" t="inlineStr">
+      <c r="C160" s="6" t="inlineStr">
         <is>
           <t>barcode-studio (separate dashboard)</t>
         </is>
       </c>
-      <c r="D160" s="5" t="inlineStr">
+      <c r="D160" s="6" t="inlineStr">
         <is>
           <t>Live preview at the actual print size</t>
         </is>
       </c>
-      <c r="E160" s="6" t="inlineStr">
+      <c r="E160" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F160" s="5" t="inlineStr">
+      <c r="F160" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G160" s="5" t="inlineStr"/>
-      <c r="H160" s="5" t="inlineStr"/>
-      <c r="I160" s="5" t="inlineStr"/>
+      <c r="G160" s="6" t="inlineStr"/>
+      <c r="H160" s="6" t="inlineStr"/>
+      <c r="I160" s="6" t="inlineStr"/>
     </row>
     <row r="161" ht="22" customHeight="1">
       <c r="A161" s="2" t="inlineStr">
@@ -5694,344 +5704,344 @@
           <t>Stripe (payments)</t>
         </is>
       </c>
-      <c r="C162" s="4" t="inlineStr">
+      <c r="C162" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D162" s="4" t="inlineStr">
+      <c r="D162" s="5" t="inlineStr">
         <is>
           <t>How we charge customers and run subscriptions</t>
         </is>
       </c>
-      <c r="E162" s="4" t="inlineStr"/>
-      <c r="F162" s="4" t="inlineStr"/>
-      <c r="G162" s="4" t="inlineStr"/>
-      <c r="H162" s="4" t="inlineStr"/>
-      <c r="I162" s="4" t="inlineStr"/>
+      <c r="E162" s="5" t="inlineStr"/>
+      <c r="F162" s="5" t="inlineStr"/>
+      <c r="G162" s="5" t="inlineStr"/>
+      <c r="H162" s="5" t="inlineStr"/>
+      <c r="I162" s="5" t="inlineStr"/>
     </row>
     <row r="163" ht="18" customHeight="1">
-      <c r="A163" s="5" t="inlineStr">
+      <c r="A163" s="6" t="inlineStr">
         <is>
           <t>Outside services we connect to</t>
         </is>
       </c>
-      <c r="B163" s="5" t="inlineStr">
+      <c r="B163" s="6" t="inlineStr">
         <is>
           <t>Stripe (payments)</t>
         </is>
       </c>
-      <c r="C163" s="5" t="inlineStr">
+      <c r="C163" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D163" s="5" t="inlineStr">
+      <c r="D163" s="6" t="inlineStr">
         <is>
           <t>Send the customer to Stripe to pay</t>
         </is>
       </c>
-      <c r="E163" s="6" t="inlineStr">
+      <c r="E163" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F163" s="5" t="inlineStr">
+      <c r="F163" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G163" s="5" t="inlineStr"/>
-      <c r="H163" s="5" t="inlineStr"/>
-      <c r="I163" s="5" t="inlineStr"/>
+      <c r="G163" s="6" t="inlineStr"/>
+      <c r="H163" s="6" t="inlineStr"/>
+      <c r="I163" s="6" t="inlineStr"/>
     </row>
     <row r="164" ht="18" customHeight="1">
-      <c r="A164" s="5" t="inlineStr">
+      <c r="A164" s="6" t="inlineStr">
         <is>
           <t>Outside services we connect to</t>
         </is>
       </c>
-      <c r="B164" s="5" t="inlineStr">
+      <c r="B164" s="6" t="inlineStr">
         <is>
           <t>Stripe (payments)</t>
         </is>
       </c>
-      <c r="C164" s="5" t="inlineStr">
+      <c r="C164" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D164" s="5" t="inlineStr">
+      <c r="D164" s="6" t="inlineStr">
         <is>
           <t>Automatically create the order when Stripe confirms payment</t>
         </is>
       </c>
-      <c r="E164" s="6" t="inlineStr">
+      <c r="E164" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F164" s="5" t="inlineStr">
+      <c r="F164" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G164" s="5" t="inlineStr"/>
-      <c r="H164" s="5" t="inlineStr"/>
-      <c r="I164" s="5" t="inlineStr"/>
+      <c r="G164" s="6" t="inlineStr"/>
+      <c r="H164" s="6" t="inlineStr"/>
+      <c r="I164" s="6" t="inlineStr"/>
     </row>
     <row r="165" ht="18" customHeight="1">
-      <c r="A165" s="5" t="inlineStr">
+      <c r="A165" s="6" t="inlineStr">
         <is>
           <t>Outside services we connect to</t>
         </is>
       </c>
-      <c r="B165" s="5" t="inlineStr">
+      <c r="B165" s="6" t="inlineStr">
         <is>
           <t>Stripe (payments)</t>
         </is>
       </c>
-      <c r="C165" s="5" t="inlineStr">
+      <c r="C165" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D165" s="5" t="inlineStr">
+      <c r="D165" s="6" t="inlineStr">
         <is>
           <t>Subscription billing (bi-monthly and annual)</t>
         </is>
       </c>
-      <c r="E165" s="6" t="inlineStr">
+      <c r="E165" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F165" s="5" t="inlineStr">
+      <c r="F165" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G165" s="5" t="inlineStr"/>
-      <c r="H165" s="5" t="inlineStr"/>
-      <c r="I165" s="5" t="inlineStr"/>
+      <c r="G165" s="6" t="inlineStr"/>
+      <c r="H165" s="6" t="inlineStr"/>
+      <c r="I165" s="6" t="inlineStr"/>
     </row>
     <row r="166" ht="18" customHeight="1">
-      <c r="A166" s="5" t="inlineStr">
+      <c r="A166" s="6" t="inlineStr">
         <is>
           <t>Outside services we connect to</t>
         </is>
       </c>
-      <c r="B166" s="5" t="inlineStr">
+      <c r="B166" s="6" t="inlineStr">
         <is>
           <t>Stripe (payments)</t>
         </is>
       </c>
-      <c r="C166" s="5" t="inlineStr">
+      <c r="C166" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D166" s="5" t="inlineStr">
+      <c r="D166" s="6" t="inlineStr">
         <is>
           <t>Plan for what happens when a recurring charge fails</t>
         </is>
       </c>
-      <c r="E166" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F166" s="5" t="inlineStr">
+      <c r="E166" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F166" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G166" s="5" t="inlineStr"/>
-      <c r="H166" s="5" t="inlineStr"/>
-      <c r="I166" s="5" t="inlineStr"/>
+      <c r="G166" s="6" t="inlineStr"/>
+      <c r="H166" s="6" t="inlineStr"/>
+      <c r="I166" s="6" t="inlineStr"/>
     </row>
     <row r="167" ht="18" customHeight="1">
-      <c r="A167" s="5" t="inlineStr">
+      <c r="A167" s="6" t="inlineStr">
         <is>
           <t>Outside services we connect to</t>
         </is>
       </c>
-      <c r="B167" s="5" t="inlineStr">
+      <c r="B167" s="6" t="inlineStr">
         <is>
           <t>Stripe (payments)</t>
         </is>
       </c>
-      <c r="C167" s="5" t="inlineStr">
+      <c r="C167" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D167" s="5" t="inlineStr">
+      <c r="D167" s="6" t="inlineStr">
         <is>
           <t>Multi-currency Checkout Session (EUR / GBP / USD)</t>
         </is>
       </c>
-      <c r="E167" s="6" t="inlineStr">
+      <c r="E167" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F167" s="5" t="inlineStr">
+      <c r="F167" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G167" s="5" t="inlineStr"/>
-      <c r="H167" s="5" t="inlineStr"/>
-      <c r="I167" s="5" t="inlineStr"/>
+      <c r="G167" s="6" t="inlineStr"/>
+      <c r="H167" s="6" t="inlineStr"/>
+      <c r="I167" s="6" t="inlineStr"/>
     </row>
     <row r="168" ht="18" customHeight="1">
-      <c r="A168" s="5" t="inlineStr">
+      <c r="A168" s="6" t="inlineStr">
         <is>
           <t>Outside services we connect to</t>
         </is>
       </c>
-      <c r="B168" s="5" t="inlineStr">
+      <c r="B168" s="6" t="inlineStr">
         <is>
           <t>Stripe (payments)</t>
         </is>
       </c>
-      <c r="C168" s="5" t="inlineStr">
+      <c r="C168" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D168" s="5" t="inlineStr">
+      <c r="D168" s="6" t="inlineStr">
         <is>
           <t>Expanded allowed_countries to all Phase-1 shipping regions</t>
         </is>
       </c>
-      <c r="E168" s="6" t="inlineStr">
+      <c r="E168" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F168" s="5" t="inlineStr">
+      <c r="F168" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G168" s="5" t="inlineStr"/>
-      <c r="H168" s="5" t="inlineStr"/>
-      <c r="I168" s="5" t="inlineStr"/>
+      <c r="G168" s="6" t="inlineStr"/>
+      <c r="H168" s="6" t="inlineStr"/>
+      <c r="I168" s="6" t="inlineStr"/>
     </row>
     <row r="169" ht="18" customHeight="1">
-      <c r="A169" s="5" t="inlineStr">
+      <c r="A169" s="6" t="inlineStr">
         <is>
           <t>Outside services we connect to</t>
         </is>
       </c>
-      <c r="B169" s="5" t="inlineStr">
+      <c r="B169" s="6" t="inlineStr">
         <is>
           <t>Stripe (payments)</t>
         </is>
       </c>
-      <c r="C169" s="5" t="inlineStr">
+      <c r="C169" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D169" s="5" t="inlineStr">
+      <c r="D169" s="6" t="inlineStr">
         <is>
           <t>Enable country-specific payment methods in Stripe Dashboard (iDEAL, Bancontact, SEPA, BACS, ACH, Apple/Google Pay, Klarna, Link)</t>
         </is>
       </c>
-      <c r="E169" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F169" s="5" t="inlineStr">
+      <c r="E169" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F169" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G169" s="5" t="inlineStr"/>
-      <c r="H169" s="5" t="inlineStr">
+      <c r="G169" s="6" t="inlineStr"/>
+      <c r="H169" s="6" t="inlineStr">
         <is>
           <t>Code path is ready — Stripe auto-displays methods when payment_method_types is omitted. Just needs dashboard enablement.</t>
         </is>
       </c>
-      <c r="I169" s="5" t="inlineStr"/>
+      <c r="I169" s="6" t="inlineStr"/>
     </row>
     <row r="170" ht="18" customHeight="1">
-      <c r="A170" s="5" t="inlineStr">
+      <c r="A170" s="6" t="inlineStr">
         <is>
           <t>Outside services we connect to</t>
         </is>
       </c>
-      <c r="B170" s="5" t="inlineStr">
+      <c r="B170" s="6" t="inlineStr">
         <is>
           <t>Stripe (payments)</t>
         </is>
       </c>
-      <c r="C170" s="5" t="inlineStr">
+      <c r="C170" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D170" s="5" t="inlineStr">
+      <c r="D170" s="6" t="inlineStr">
         <is>
           <t>Stripe Customer Portal for saved payment methods + invoices + subscription pause</t>
         </is>
       </c>
-      <c r="E170" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F170" s="5" t="inlineStr">
+      <c r="E170" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F170" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G170" s="5" t="inlineStr"/>
-      <c r="H170" s="5" t="inlineStr">
+      <c r="G170" s="6" t="inlineStr"/>
+      <c r="H170" s="6" t="inlineStr">
         <is>
           <t>Requires stripe_customer_id column on customers and a /api/billing-portal-session route.</t>
         </is>
       </c>
-      <c r="I170" s="5" t="inlineStr"/>
+      <c r="I170" s="6" t="inlineStr"/>
     </row>
     <row r="171" ht="18" customHeight="1">
-      <c r="A171" s="5" t="inlineStr">
+      <c r="A171" s="6" t="inlineStr">
         <is>
           <t>Outside services we connect to</t>
         </is>
       </c>
-      <c r="B171" s="5" t="inlineStr">
+      <c r="B171" s="6" t="inlineStr">
         <is>
           <t>Stripe (payments)</t>
         </is>
       </c>
-      <c r="C171" s="5" t="inlineStr">
+      <c r="C171" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D171" s="5" t="inlineStr">
+      <c r="D171" s="6" t="inlineStr">
         <is>
           <t>Save stripe_customer_id from checkout.session.completed webhook</t>
         </is>
       </c>
-      <c r="E171" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F171" s="5" t="inlineStr">
+      <c r="E171" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F171" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G171" s="5" t="inlineStr"/>
-      <c r="H171" s="5" t="inlineStr"/>
-      <c r="I171" s="5" t="inlineStr"/>
+      <c r="G171" s="6" t="inlineStr"/>
+      <c r="H171" s="6" t="inlineStr"/>
+      <c r="I171" s="6" t="inlineStr"/>
     </row>
     <row r="172" ht="20" customHeight="1">
       <c r="A172" s="3" t="inlineStr">
@@ -6044,231 +6054,231 @@
           <t>Supabase (database and storage)</t>
         </is>
       </c>
-      <c r="C172" s="4" t="inlineStr">
+      <c r="C172" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D172" s="4" t="inlineStr">
+      <c r="D172" s="5" t="inlineStr">
         <is>
           <t>Where customer data, products, and images live</t>
         </is>
       </c>
-      <c r="E172" s="4" t="inlineStr"/>
-      <c r="F172" s="4" t="inlineStr"/>
-      <c r="G172" s="4" t="inlineStr"/>
-      <c r="H172" s="4" t="inlineStr"/>
-      <c r="I172" s="4" t="inlineStr"/>
+      <c r="E172" s="5" t="inlineStr"/>
+      <c r="F172" s="5" t="inlineStr"/>
+      <c r="G172" s="5" t="inlineStr"/>
+      <c r="H172" s="5" t="inlineStr"/>
+      <c r="I172" s="5" t="inlineStr"/>
     </row>
     <row r="173" ht="18" customHeight="1">
-      <c r="A173" s="5" t="inlineStr">
+      <c r="A173" s="6" t="inlineStr">
         <is>
           <t>Outside services we connect to</t>
         </is>
       </c>
-      <c r="B173" s="5" t="inlineStr">
+      <c r="B173" s="6" t="inlineStr">
         <is>
           <t>Supabase (database and storage)</t>
         </is>
       </c>
-      <c r="C173" s="5" t="inlineStr">
+      <c r="C173" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D173" s="5" t="inlineStr">
+      <c r="D173" s="6" t="inlineStr">
         <is>
           <t>Products and ingredients data set up</t>
         </is>
       </c>
-      <c r="E173" s="6" t="inlineStr">
+      <c r="E173" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F173" s="5" t="inlineStr">
+      <c r="F173" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G173" s="5" t="inlineStr"/>
-      <c r="H173" s="5" t="inlineStr"/>
-      <c r="I173" s="5" t="inlineStr"/>
+      <c r="G173" s="6" t="inlineStr"/>
+      <c r="H173" s="6" t="inlineStr"/>
+      <c r="I173" s="6" t="inlineStr"/>
     </row>
     <row r="174" ht="18" customHeight="1">
-      <c r="A174" s="5" t="inlineStr">
+      <c r="A174" s="6" t="inlineStr">
         <is>
           <t>Outside services we connect to</t>
         </is>
       </c>
-      <c r="B174" s="5" t="inlineStr">
+      <c r="B174" s="6" t="inlineStr">
         <is>
           <t>Supabase (database and storage)</t>
         </is>
       </c>
-      <c r="C174" s="5" t="inlineStr">
+      <c r="C174" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D174" s="5" t="inlineStr">
+      <c r="D174" s="6" t="inlineStr">
         <is>
           <t>Customer orders and quiz results data set up</t>
         </is>
       </c>
-      <c r="E174" s="6" t="inlineStr">
+      <c r="E174" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F174" s="5" t="inlineStr">
+      <c r="F174" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G174" s="5" t="inlineStr"/>
-      <c r="H174" s="5" t="inlineStr"/>
-      <c r="I174" s="5" t="inlineStr"/>
+      <c r="G174" s="6" t="inlineStr"/>
+      <c r="H174" s="6" t="inlineStr"/>
+      <c r="I174" s="6" t="inlineStr"/>
     </row>
     <row r="175" ht="18" customHeight="1">
-      <c r="A175" s="5" t="inlineStr">
+      <c r="A175" s="6" t="inlineStr">
         <is>
           <t>Outside services we connect to</t>
         </is>
       </c>
-      <c r="B175" s="5" t="inlineStr">
+      <c r="B175" s="6" t="inlineStr">
         <is>
           <t>Supabase (database and storage)</t>
         </is>
       </c>
-      <c r="C175" s="5" t="inlineStr">
+      <c r="C175" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D175" s="5" t="inlineStr">
+      <c r="D175" s="6" t="inlineStr">
         <is>
           <t>Barcode pool and product records data set up</t>
         </is>
       </c>
-      <c r="E175" s="6" t="inlineStr">
+      <c r="E175" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F175" s="5" t="inlineStr">
+      <c r="F175" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G175" s="5" t="inlineStr"/>
-      <c r="H175" s="5" t="inlineStr"/>
-      <c r="I175" s="5" t="inlineStr"/>
+      <c r="G175" s="6" t="inlineStr"/>
+      <c r="H175" s="6" t="inlineStr"/>
+      <c r="I175" s="6" t="inlineStr"/>
     </row>
     <row r="176" ht="18" customHeight="1">
-      <c r="A176" s="5" t="inlineStr">
+      <c r="A176" s="6" t="inlineStr">
         <is>
           <t>Outside services we connect to</t>
         </is>
       </c>
-      <c r="B176" s="5" t="inlineStr">
+      <c r="B176" s="6" t="inlineStr">
         <is>
           <t>Supabase (database and storage)</t>
         </is>
       </c>
-      <c r="C176" s="5" t="inlineStr">
+      <c r="C176" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D176" s="5" t="inlineStr">
+      <c r="D176" s="6" t="inlineStr">
         <is>
           <t>Admin role check so only the right people can use the dashboard</t>
         </is>
       </c>
-      <c r="E176" s="6" t="inlineStr">
+      <c r="E176" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F176" s="5" t="inlineStr">
+      <c r="F176" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G176" s="5" t="inlineStr"/>
-      <c r="H176" s="5" t="inlineStr"/>
-      <c r="I176" s="5" t="inlineStr"/>
+      <c r="G176" s="6" t="inlineStr"/>
+      <c r="H176" s="6" t="inlineStr"/>
+      <c r="I176" s="6" t="inlineStr"/>
     </row>
     <row r="177" ht="18" customHeight="1">
-      <c r="A177" s="5" t="inlineStr">
+      <c r="A177" s="6" t="inlineStr">
         <is>
           <t>Outside services we connect to</t>
         </is>
       </c>
-      <c r="B177" s="5" t="inlineStr">
+      <c r="B177" s="6" t="inlineStr">
         <is>
           <t>Supabase (database and storage)</t>
         </is>
       </c>
-      <c r="C177" s="5" t="inlineStr">
+      <c r="C177" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D177" s="5" t="inlineStr">
+      <c r="D177" s="6" t="inlineStr">
         <is>
           <t>Public product image storage (the bucket called products)</t>
         </is>
       </c>
-      <c r="E177" s="6" t="inlineStr">
+      <c r="E177" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F177" s="5" t="inlineStr">
+      <c r="F177" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G177" s="5" t="inlineStr"/>
-      <c r="H177" s="5" t="inlineStr"/>
-      <c r="I177" s="5" t="inlineStr"/>
+      <c r="G177" s="6" t="inlineStr"/>
+      <c r="H177" s="6" t="inlineStr"/>
+      <c r="I177" s="6" t="inlineStr"/>
     </row>
     <row r="178" ht="18" customHeight="1">
-      <c r="A178" s="5" t="inlineStr">
+      <c r="A178" s="6" t="inlineStr">
         <is>
           <t>Outside services we connect to</t>
         </is>
       </c>
-      <c r="B178" s="5" t="inlineStr">
+      <c r="B178" s="6" t="inlineStr">
         <is>
           <t>Supabase (database and storage)</t>
         </is>
       </c>
-      <c r="C178" s="5" t="inlineStr">
+      <c r="C178" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D178" s="5" t="inlineStr">
+      <c r="D178" s="6" t="inlineStr">
         <is>
           <t>Upload one real product photo per barcode</t>
         </is>
       </c>
-      <c r="E178" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F178" s="5" t="inlineStr">
+      <c r="E178" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F178" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G178" s="5" t="inlineStr"/>
-      <c r="H178" s="5" t="inlineStr"/>
-      <c r="I178" s="5" t="inlineStr"/>
+      <c r="G178" s="6" t="inlineStr"/>
+      <c r="H178" s="6" t="inlineStr"/>
+      <c r="I178" s="6" t="inlineStr"/>
     </row>
     <row r="179" ht="20" customHeight="1">
       <c r="A179" s="3" t="inlineStr">
@@ -6281,348 +6291,348 @@
           <t>INCI Beauty (product import)</t>
         </is>
       </c>
-      <c r="C179" s="4" t="inlineStr">
+      <c r="C179" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D179" s="4" t="inlineStr">
+      <c r="D179" s="5" t="inlineStr">
         <is>
           <t>External cosmetic ingredient database where our products get listed</t>
         </is>
       </c>
-      <c r="E179" s="4" t="inlineStr"/>
-      <c r="F179" s="4" t="inlineStr"/>
-      <c r="G179" s="4" t="inlineStr"/>
-      <c r="H179" s="4" t="inlineStr"/>
-      <c r="I179" s="4" t="inlineStr"/>
+      <c r="E179" s="5" t="inlineStr"/>
+      <c r="F179" s="5" t="inlineStr"/>
+      <c r="G179" s="5" t="inlineStr"/>
+      <c r="H179" s="5" t="inlineStr"/>
+      <c r="I179" s="5" t="inlineStr"/>
     </row>
     <row r="180" ht="18" customHeight="1">
-      <c r="A180" s="5" t="inlineStr">
+      <c r="A180" s="6" t="inlineStr">
         <is>
           <t>Outside services we connect to</t>
         </is>
       </c>
-      <c r="B180" s="5" t="inlineStr">
+      <c r="B180" s="6" t="inlineStr">
         <is>
           <t>INCI Beauty (product import)</t>
         </is>
       </c>
-      <c r="C180" s="5" t="inlineStr">
+      <c r="C180" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D180" s="5" t="inlineStr">
+      <c r="D180" s="6" t="inlineStr">
         <is>
           <t>Generate the XML file from each product</t>
         </is>
       </c>
-      <c r="E180" s="6" t="inlineStr">
+      <c r="E180" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F180" s="5" t="inlineStr">
+      <c r="F180" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G180" s="5" t="inlineStr"/>
-      <c r="H180" s="5" t="inlineStr"/>
-      <c r="I180" s="5" t="inlineStr"/>
+      <c r="G180" s="6" t="inlineStr"/>
+      <c r="H180" s="6" t="inlineStr"/>
+      <c r="I180" s="6" t="inlineStr"/>
     </row>
     <row r="181" ht="18" customHeight="1">
-      <c r="A181" s="5" t="inlineStr">
+      <c r="A181" s="6" t="inlineStr">
         <is>
           <t>Outside services we connect to</t>
         </is>
       </c>
-      <c r="B181" s="5" t="inlineStr">
+      <c r="B181" s="6" t="inlineStr">
         <is>
           <t>INCI Beauty (product import)</t>
         </is>
       </c>
-      <c r="C181" s="5" t="inlineStr">
+      <c r="C181" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D181" s="5" t="inlineStr">
+      <c r="D181" s="6" t="inlineStr">
         <is>
           <t>Download button inside the fulfillment dashboard</t>
         </is>
       </c>
-      <c r="E181" s="6" t="inlineStr">
+      <c r="E181" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F181" s="5" t="inlineStr">
+      <c r="F181" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G181" s="5" t="inlineStr"/>
-      <c r="H181" s="5" t="inlineStr"/>
-      <c r="I181" s="5" t="inlineStr"/>
+      <c r="G181" s="6" t="inlineStr"/>
+      <c r="H181" s="6" t="inlineStr"/>
+      <c r="I181" s="6" t="inlineStr"/>
     </row>
     <row r="182" ht="18" customHeight="1">
-      <c r="A182" s="5" t="inlineStr">
+      <c r="A182" s="6" t="inlineStr">
         <is>
           <t>Outside services we connect to</t>
         </is>
       </c>
-      <c r="B182" s="5" t="inlineStr">
+      <c r="B182" s="6" t="inlineStr">
         <is>
           <t>INCI Beauty (product import)</t>
         </is>
       </c>
-      <c r="C182" s="5" t="inlineStr">
+      <c r="C182" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D182" s="5" t="inlineStr">
+      <c r="D182" s="6" t="inlineStr">
         <is>
           <t>Placeholder image hosted publicly</t>
         </is>
       </c>
-      <c r="E182" s="6" t="inlineStr">
+      <c r="E182" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F182" s="5" t="inlineStr">
+      <c r="F182" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G182" s="5" t="inlineStr"/>
-      <c r="H182" s="5" t="inlineStr"/>
-      <c r="I182" s="5" t="inlineStr"/>
+      <c r="G182" s="6" t="inlineStr"/>
+      <c r="H182" s="6" t="inlineStr"/>
+      <c r="I182" s="6" t="inlineStr"/>
     </row>
     <row r="183" ht="18" customHeight="1">
-      <c r="A183" s="5" t="inlineStr">
+      <c r="A183" s="6" t="inlineStr">
         <is>
           <t>Outside services we connect to</t>
         </is>
       </c>
-      <c r="B183" s="5" t="inlineStr">
+      <c r="B183" s="6" t="inlineStr">
         <is>
           <t>INCI Beauty (product import)</t>
         </is>
       </c>
-      <c r="C183" s="5" t="inlineStr">
+      <c r="C183" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D183" s="5" t="inlineStr">
+      <c r="D183" s="6" t="inlineStr">
         <is>
           <t>Use a different image per product</t>
         </is>
       </c>
-      <c r="E183" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F183" s="5" t="inlineStr">
+      <c r="E183" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F183" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G183" s="5" t="inlineStr"/>
-      <c r="H183" s="5" t="inlineStr"/>
-      <c r="I183" s="5" t="inlineStr"/>
+      <c r="G183" s="6" t="inlineStr"/>
+      <c r="H183" s="6" t="inlineStr"/>
+      <c r="I183" s="6" t="inlineStr"/>
     </row>
     <row r="184" ht="18" customHeight="1">
-      <c r="A184" s="5" t="inlineStr">
+      <c r="A184" s="6" t="inlineStr">
         <is>
           <t>Outside services we connect to</t>
         </is>
       </c>
-      <c r="B184" s="5" t="inlineStr">
+      <c r="B184" s="6" t="inlineStr">
         <is>
           <t>INCI Beauty (product import)</t>
         </is>
       </c>
-      <c r="C184" s="5" t="inlineStr">
+      <c r="C184" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D184" s="5" t="inlineStr">
+      <c r="D184" s="6" t="inlineStr">
         <is>
           <t>Try a real import on INCI Beauty and confirm it works</t>
         </is>
       </c>
-      <c r="E184" s="8" t="inlineStr">
+      <c r="E184" s="9" t="inlineStr">
         <is>
           <t>In progress</t>
         </is>
       </c>
-      <c r="F184" s="5" t="inlineStr">
+      <c r="F184" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G184" s="5" t="inlineStr"/>
-      <c r="H184" s="5" t="inlineStr">
+      <c r="G184" s="6" t="inlineStr"/>
+      <c r="H184" s="6" t="inlineStr">
         <is>
           <t>First two imports rejected — invalid INCI ingredient names, wrong &lt;info&gt; usage, image mismatch. INCI Beauty deployed a fix for the image-ignored bug on their side. Test XML drafted for BOV to re-test the upload pipeline.</t>
         </is>
       </c>
-      <c r="I184" s="5" t="inlineStr"/>
+      <c r="I184" s="6" t="inlineStr"/>
     </row>
     <row r="185" ht="18" customHeight="1">
-      <c r="A185" s="5" t="inlineStr">
+      <c r="A185" s="6" t="inlineStr">
         <is>
           <t>Outside services we connect to</t>
         </is>
       </c>
-      <c r="B185" s="5" t="inlineStr">
+      <c r="B185" s="6" t="inlineStr">
         <is>
           <t>INCI Beauty (product import)</t>
         </is>
       </c>
-      <c r="C185" s="5" t="inlineStr">
+      <c r="C185" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D185" s="5" t="inlineStr">
+      <c r="D185" s="6" t="inlineStr">
         <is>
           <t>Fix &lt;info&gt; field — emit self-closing instead of stuffing net_content</t>
         </is>
       </c>
-      <c r="E185" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F185" s="5" t="inlineStr">
+      <c r="E185" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F185" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G185" s="5" t="inlineStr"/>
-      <c r="H185" s="5" t="inlineStr"/>
-      <c r="I185" s="5" t="inlineStr"/>
+      <c r="G185" s="6" t="inlineStr"/>
+      <c r="H185" s="6" t="inlineStr"/>
+      <c r="I185" s="6" t="inlineStr"/>
     </row>
     <row r="186" ht="18" customHeight="1">
-      <c r="A186" s="5" t="inlineStr">
+      <c r="A186" s="6" t="inlineStr">
         <is>
           <t>Outside services we connect to</t>
         </is>
       </c>
-      <c r="B186" s="5" t="inlineStr">
+      <c r="B186" s="6" t="inlineStr">
         <is>
           <t>INCI Beauty (product import)</t>
         </is>
       </c>
-      <c r="C186" s="5" t="inlineStr">
+      <c r="C186" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D186" s="5" t="inlineStr">
+      <c r="D186" s="6" t="inlineStr">
         <is>
           <t>Per-product images served from /products/{gtin}.jpg with placeholder fallback</t>
         </is>
       </c>
-      <c r="E186" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F186" s="5" t="inlineStr">
+      <c r="E186" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F186" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G186" s="5" t="inlineStr"/>
-      <c r="H186" s="5" t="inlineStr"/>
-      <c r="I186" s="5" t="inlineStr"/>
+      <c r="G186" s="6" t="inlineStr"/>
+      <c r="H186" s="6" t="inlineStr"/>
+      <c r="I186" s="6" t="inlineStr"/>
     </row>
     <row r="187" ht="18" customHeight="1">
-      <c r="A187" s="5" t="inlineStr">
+      <c r="A187" s="6" t="inlineStr">
         <is>
           <t>Outside services we connect to</t>
         </is>
       </c>
-      <c r="B187" s="5" t="inlineStr">
+      <c r="B187" s="6" t="inlineStr">
         <is>
           <t>INCI Beauty (product import)</t>
         </is>
       </c>
-      <c r="C187" s="5" t="inlineStr">
+      <c r="C187" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D187" s="5" t="inlineStr">
+      <c r="D187" s="6" t="inlineStr">
         <is>
           <t>ingredients.inci_name column + COSING-validated names for every ingredient</t>
         </is>
       </c>
-      <c r="E187" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F187" s="5" t="inlineStr">
+      <c r="E187" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F187" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G187" s="5" t="inlineStr"/>
-      <c r="H187" s="5" t="inlineStr">
+      <c r="G187" s="6" t="inlineStr"/>
+      <c r="H187" s="6" t="inlineStr">
         <is>
           <t>Blocker for INCI Beauty acceptance — current ingredient names ('pH adjuster', 'Emulgade 1000 NI') are functional descriptors, not INCI.</t>
         </is>
       </c>
-      <c r="I187" s="5" t="inlineStr"/>
+      <c r="I187" s="6" t="inlineStr"/>
     </row>
     <row r="188" ht="18" customHeight="1">
-      <c r="A188" s="5" t="inlineStr">
+      <c r="A188" s="6" t="inlineStr">
         <is>
           <t>Outside services we connect to</t>
         </is>
       </c>
-      <c r="B188" s="5" t="inlineStr">
+      <c r="B188" s="6" t="inlineStr">
         <is>
           <t>INCI Beauty (product import)</t>
         </is>
       </c>
-      <c r="C188" s="5" t="inlineStr">
+      <c r="C188" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D188" s="5" t="inlineStr">
+      <c r="D188" s="6" t="inlineStr">
         <is>
           <t>Update GS1 Verified portal entry for each GTIN we submit</t>
         </is>
       </c>
-      <c r="E188" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F188" s="5" t="inlineStr">
+      <c r="E188" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F188" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G188" s="5" t="inlineStr"/>
-      <c r="H188" s="5" t="inlineStr">
+      <c r="G188" s="6" t="inlineStr"/>
+      <c r="H188" s="6" t="inlineStr">
         <is>
           <t>Operational — not technical. Ensures GS1 registry matches what we ship to INCI.</t>
         </is>
       </c>
-      <c r="I188" s="5" t="inlineStr"/>
+      <c r="I188" s="6" t="inlineStr"/>
     </row>
     <row r="189" ht="20" customHeight="1">
       <c r="A189" s="3" t="inlineStr">
@@ -6635,305 +6645,305 @@
           <t>Direx Courier (Bulgarian shipping)</t>
         </is>
       </c>
-      <c r="C189" s="4" t="inlineStr">
+      <c r="C189" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D189" s="4" t="inlineStr">
+      <c r="D189" s="5" t="inlineStr">
         <is>
           <t>The courier that picks up parcels from our warehouse and delivers them</t>
         </is>
       </c>
-      <c r="E189" s="4" t="inlineStr"/>
-      <c r="F189" s="4" t="inlineStr"/>
-      <c r="G189" s="4" t="inlineStr"/>
-      <c r="H189" s="4" t="inlineStr"/>
-      <c r="I189" s="4" t="inlineStr"/>
+      <c r="E189" s="5" t="inlineStr"/>
+      <c r="F189" s="5" t="inlineStr"/>
+      <c r="G189" s="5" t="inlineStr"/>
+      <c r="H189" s="5" t="inlineStr"/>
+      <c r="I189" s="5" t="inlineStr"/>
     </row>
     <row r="190" ht="18" customHeight="1">
-      <c r="A190" s="5" t="inlineStr">
+      <c r="A190" s="6" t="inlineStr">
         <is>
           <t>Outside services we connect to</t>
         </is>
       </c>
-      <c r="B190" s="5" t="inlineStr">
+      <c r="B190" s="6" t="inlineStr">
         <is>
           <t>Direx Courier (Bulgarian shipping)</t>
         </is>
       </c>
-      <c r="C190" s="5" t="inlineStr">
+      <c r="C190" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D190" s="5" t="inlineStr">
+      <c r="D190" s="6" t="inlineStr">
         <is>
           <t>Get our login working with their system</t>
         </is>
       </c>
-      <c r="E190" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F190" s="5" t="inlineStr">
+      <c r="E190" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F190" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G190" s="5" t="inlineStr"/>
-      <c r="H190" s="5" t="inlineStr"/>
-      <c r="I190" s="5" t="inlineStr"/>
+      <c r="G190" s="6" t="inlineStr"/>
+      <c r="H190" s="6" t="inlineStr"/>
+      <c r="I190" s="6" t="inlineStr"/>
     </row>
     <row r="191" ht="18" customHeight="1">
-      <c r="A191" s="5" t="inlineStr">
+      <c r="A191" s="6" t="inlineStr">
         <is>
           <t>Outside services we connect to</t>
         </is>
       </c>
-      <c r="B191" s="5" t="inlineStr">
+      <c r="B191" s="6" t="inlineStr">
         <is>
           <t>Direx Courier (Bulgarian shipping)</t>
         </is>
       </c>
-      <c r="C191" s="5" t="inlineStr">
+      <c r="C191" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D191" s="5" t="inlineStr">
+      <c r="D191" s="6" t="inlineStr">
         <is>
           <t>Register the warehouse as a sender on their portal</t>
         </is>
       </c>
-      <c r="E191" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F191" s="5" t="inlineStr">
+      <c r="E191" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F191" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G191" s="5" t="inlineStr"/>
-      <c r="H191" s="5" t="inlineStr">
+      <c r="G191" s="6" t="inlineStr"/>
+      <c r="H191" s="6" t="inlineStr">
         <is>
           <t>Operational, not technical</t>
         </is>
       </c>
-      <c r="I191" s="5" t="inlineStr"/>
+      <c r="I191" s="6" t="inlineStr"/>
     </row>
     <row r="192" ht="18" customHeight="1">
-      <c r="A192" s="5" t="inlineStr">
+      <c r="A192" s="6" t="inlineStr">
         <is>
           <t>Outside services we connect to</t>
         </is>
       </c>
-      <c r="B192" s="5" t="inlineStr">
+      <c r="B192" s="6" t="inlineStr">
         <is>
           <t>Direx Courier (Bulgarian shipping)</t>
         </is>
       </c>
-      <c r="C192" s="5" t="inlineStr">
+      <c r="C192" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D192" s="5" t="inlineStr">
+      <c r="D192" s="6" t="inlineStr">
         <is>
           <t>Confirm whether we ship Bulgaria only, or international too</t>
         </is>
       </c>
-      <c r="E192" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F192" s="5" t="inlineStr">
+      <c r="E192" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F192" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G192" s="5" t="inlineStr"/>
-      <c r="H192" s="5" t="inlineStr"/>
-      <c r="I192" s="5" t="inlineStr"/>
+      <c r="G192" s="6" t="inlineStr"/>
+      <c r="H192" s="6" t="inlineStr"/>
+      <c r="I192" s="6" t="inlineStr"/>
     </row>
     <row r="193" ht="18" customHeight="1">
-      <c r="A193" s="5" t="inlineStr">
+      <c r="A193" s="6" t="inlineStr">
         <is>
           <t>Outside services we connect to</t>
         </is>
       </c>
-      <c r="B193" s="5" t="inlineStr">
+      <c r="B193" s="6" t="inlineStr">
         <is>
           <t>Direx Courier (Bulgarian shipping)</t>
         </is>
       </c>
-      <c r="C193" s="5" t="inlineStr">
+      <c r="C193" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D193" s="5" t="inlineStr">
+      <c r="D193" s="6" t="inlineStr">
         <is>
           <t>Add a Create Shipment button per order with label download</t>
         </is>
       </c>
-      <c r="E193" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F193" s="5" t="inlineStr">
+      <c r="E193" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F193" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G193" s="5" t="inlineStr"/>
-      <c r="H193" s="5" t="inlineStr"/>
-      <c r="I193" s="5" t="inlineStr"/>
+      <c r="G193" s="6" t="inlineStr"/>
+      <c r="H193" s="6" t="inlineStr"/>
+      <c r="I193" s="6" t="inlineStr"/>
     </row>
     <row r="194" ht="18" customHeight="1">
-      <c r="A194" s="5" t="inlineStr">
+      <c r="A194" s="6" t="inlineStr">
         <is>
           <t>Outside services we connect to</t>
         </is>
       </c>
-      <c r="B194" s="5" t="inlineStr">
+      <c r="B194" s="6" t="inlineStr">
         <is>
           <t>Direx Courier (Bulgarian shipping)</t>
         </is>
       </c>
-      <c r="C194" s="5" t="inlineStr">
+      <c r="C194" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D194" s="5" t="inlineStr">
+      <c r="D194" s="6" t="inlineStr">
         <is>
           <t>Close manifest and schedule pickup actions</t>
         </is>
       </c>
-      <c r="E194" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F194" s="5" t="inlineStr">
+      <c r="E194" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F194" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G194" s="5" t="inlineStr"/>
-      <c r="H194" s="5" t="inlineStr"/>
-      <c r="I194" s="5" t="inlineStr"/>
+      <c r="G194" s="6" t="inlineStr"/>
+      <c r="H194" s="6" t="inlineStr"/>
+      <c r="I194" s="6" t="inlineStr"/>
     </row>
     <row r="195" ht="18" customHeight="1">
-      <c r="A195" s="5" t="inlineStr">
+      <c r="A195" s="6" t="inlineStr">
         <is>
           <t>Outside services we connect to</t>
         </is>
       </c>
-      <c r="B195" s="5" t="inlineStr">
+      <c r="B195" s="6" t="inlineStr">
         <is>
           <t>Direx Courier (Bulgarian shipping)</t>
         </is>
       </c>
-      <c r="C195" s="5" t="inlineStr">
+      <c r="C195" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D195" s="5" t="inlineStr">
+      <c r="D195" s="6" t="inlineStr">
         <is>
           <t>Automatic tracking updates every 6 hours</t>
         </is>
       </c>
-      <c r="E195" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F195" s="5" t="inlineStr">
+      <c r="E195" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F195" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G195" s="5" t="inlineStr"/>
-      <c r="H195" s="5" t="inlineStr"/>
-      <c r="I195" s="5" t="inlineStr"/>
+      <c r="G195" s="6" t="inlineStr"/>
+      <c r="H195" s="6" t="inlineStr"/>
+      <c r="I195" s="6" t="inlineStr"/>
     </row>
     <row r="196" ht="18" customHeight="1">
-      <c r="A196" s="5" t="inlineStr">
+      <c r="A196" s="6" t="inlineStr">
         <is>
           <t>Outside services we connect to</t>
         </is>
       </c>
-      <c r="B196" s="5" t="inlineStr">
+      <c r="B196" s="6" t="inlineStr">
         <is>
           <t>Direx Courier (Bulgarian shipping)</t>
         </is>
       </c>
-      <c r="C196" s="5" t="inlineStr">
+      <c r="C196" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D196" s="5" t="inlineStr">
+      <c r="D196" s="6" t="inlineStr">
         <is>
           <t>Customer can see tracking from their account</t>
         </is>
       </c>
-      <c r="E196" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F196" s="5" t="inlineStr">
+      <c r="E196" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F196" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G196" s="5" t="inlineStr"/>
-      <c r="H196" s="5" t="inlineStr"/>
-      <c r="I196" s="5" t="inlineStr"/>
+      <c r="G196" s="6" t="inlineStr"/>
+      <c r="H196" s="6" t="inlineStr"/>
+      <c r="I196" s="6" t="inlineStr"/>
     </row>
     <row r="197" ht="18" customHeight="1">
-      <c r="A197" s="5" t="inlineStr">
+      <c r="A197" s="6" t="inlineStr">
         <is>
           <t>Outside services we connect to</t>
         </is>
       </c>
-      <c r="B197" s="5" t="inlineStr">
+      <c r="B197" s="6" t="inlineStr">
         <is>
           <t>Direx Courier (Bulgarian shipping)</t>
         </is>
       </c>
-      <c r="C197" s="5" t="inlineStr">
+      <c r="C197" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D197" s="5" t="inlineStr">
+      <c r="D197" s="6" t="inlineStr">
         <is>
           <t>Shipped email with tracking link</t>
         </is>
       </c>
-      <c r="E197" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F197" s="5" t="inlineStr">
+      <c r="E197" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F197" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G197" s="5" t="inlineStr"/>
-      <c r="H197" s="5" t="inlineStr"/>
-      <c r="I197" s="5" t="inlineStr"/>
+      <c r="G197" s="6" t="inlineStr"/>
+      <c r="H197" s="6" t="inlineStr"/>
+      <c r="I197" s="6" t="inlineStr"/>
     </row>
     <row r="198" ht="22" customHeight="1">
       <c r="A198" s="2" t="inlineStr">
@@ -6953,406 +6963,406 @@
           <t>Design Lab (open with ?lab=1)</t>
         </is>
       </c>
-      <c r="C199" s="4" t="inlineStr">
+      <c r="C199" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D199" s="4" t="inlineStr">
+      <c r="D199" s="5" t="inlineStr">
         <is>
           <t>The floating dev panel for trying different fonts, palettes, and card styles live on the page</t>
         </is>
       </c>
-      <c r="E199" s="4" t="inlineStr"/>
-      <c r="F199" s="4" t="inlineStr"/>
-      <c r="G199" s="4" t="inlineStr"/>
-      <c r="H199" s="4" t="inlineStr"/>
-      <c r="I199" s="4" t="inlineStr"/>
+      <c r="E199" s="5" t="inlineStr"/>
+      <c r="F199" s="5" t="inlineStr"/>
+      <c r="G199" s="5" t="inlineStr"/>
+      <c r="H199" s="5" t="inlineStr"/>
+      <c r="I199" s="5" t="inlineStr"/>
     </row>
     <row r="200" ht="18" customHeight="1">
-      <c r="A200" s="5" t="inlineStr">
+      <c r="A200" s="6" t="inlineStr">
         <is>
           <t>Design system</t>
         </is>
       </c>
-      <c r="B200" s="5" t="inlineStr">
+      <c r="B200" s="6" t="inlineStr">
         <is>
           <t>Design Lab (open with ?lab=1)</t>
         </is>
       </c>
-      <c r="C200" s="5" t="inlineStr">
+      <c r="C200" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D200" s="5" t="inlineStr">
+      <c r="D200" s="6" t="inlineStr">
         <is>
           <t>Five font slots (headlines, inner pages, body, inner body, captions and buttons)</t>
         </is>
       </c>
-      <c r="E200" s="6" t="inlineStr">
+      <c r="E200" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F200" s="5" t="inlineStr">
+      <c r="F200" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G200" s="5" t="inlineStr"/>
-      <c r="H200" s="5" t="inlineStr"/>
-      <c r="I200" s="5" t="inlineStr"/>
+      <c r="G200" s="6" t="inlineStr"/>
+      <c r="H200" s="6" t="inlineStr"/>
+      <c r="I200" s="6" t="inlineStr"/>
     </row>
     <row r="201" ht="18" customHeight="1">
-      <c r="A201" s="5" t="inlineStr">
+      <c r="A201" s="6" t="inlineStr">
         <is>
           <t>Design system</t>
         </is>
       </c>
-      <c r="B201" s="5" t="inlineStr">
+      <c r="B201" s="6" t="inlineStr">
         <is>
           <t>Design Lab (open with ?lab=1)</t>
         </is>
       </c>
-      <c r="C201" s="5" t="inlineStr">
+      <c r="C201" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D201" s="5" t="inlineStr">
+      <c r="D201" s="6" t="inlineStr">
         <is>
           <t>Roughly 70 fonts to choose from</t>
         </is>
       </c>
-      <c r="E201" s="6" t="inlineStr">
+      <c r="E201" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F201" s="5" t="inlineStr">
+      <c r="F201" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G201" s="5" t="inlineStr"/>
-      <c r="H201" s="5" t="inlineStr"/>
-      <c r="I201" s="5" t="inlineStr"/>
+      <c r="G201" s="6" t="inlineStr"/>
+      <c r="H201" s="6" t="inlineStr"/>
+      <c r="I201" s="6" t="inlineStr"/>
     </row>
     <row r="202" ht="18" customHeight="1">
-      <c r="A202" s="5" t="inlineStr">
+      <c r="A202" s="6" t="inlineStr">
         <is>
           <t>Design system</t>
         </is>
       </c>
-      <c r="B202" s="5" t="inlineStr">
+      <c r="B202" s="6" t="inlineStr">
         <is>
           <t>Design Lab (open with ?lab=1)</t>
         </is>
       </c>
-      <c r="C202" s="5" t="inlineStr">
+      <c r="C202" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D202" s="5" t="inlineStr">
+      <c r="D202" s="6" t="inlineStr">
         <is>
           <t>Picker mode: click any text to see what controls it</t>
         </is>
       </c>
-      <c r="E202" s="6" t="inlineStr">
+      <c r="E202" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F202" s="5" t="inlineStr">
+      <c r="F202" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G202" s="5" t="inlineStr"/>
-      <c r="H202" s="5" t="inlineStr"/>
-      <c r="I202" s="5" t="inlineStr"/>
+      <c r="G202" s="6" t="inlineStr"/>
+      <c r="H202" s="6" t="inlineStr"/>
+      <c r="I202" s="6" t="inlineStr"/>
     </row>
     <row r="203" ht="18" customHeight="1">
-      <c r="A203" s="5" t="inlineStr">
+      <c r="A203" s="6" t="inlineStr">
         <is>
           <t>Design system</t>
         </is>
       </c>
-      <c r="B203" s="5" t="inlineStr">
+      <c r="B203" s="6" t="inlineStr">
         <is>
           <t>Design Lab (open with ?lab=1)</t>
         </is>
       </c>
-      <c r="C203" s="5" t="inlineStr">
+      <c r="C203" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D203" s="5" t="inlineStr">
+      <c r="D203" s="6" t="inlineStr">
         <is>
           <t>Per element override panel with bold, italic, underline, colour</t>
         </is>
       </c>
-      <c r="E203" s="6" t="inlineStr">
+      <c r="E203" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F203" s="5" t="inlineStr">
+      <c r="F203" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G203" s="5" t="inlineStr"/>
-      <c r="H203" s="5" t="inlineStr"/>
-      <c r="I203" s="5" t="inlineStr"/>
+      <c r="G203" s="6" t="inlineStr"/>
+      <c r="H203" s="6" t="inlineStr"/>
+      <c r="I203" s="6" t="inlineStr"/>
     </row>
     <row r="204" ht="18" customHeight="1">
-      <c r="A204" s="5" t="inlineStr">
+      <c r="A204" s="6" t="inlineStr">
         <is>
           <t>Design system</t>
         </is>
       </c>
-      <c r="B204" s="5" t="inlineStr">
+      <c r="B204" s="6" t="inlineStr">
         <is>
           <t>Design Lab (open with ?lab=1)</t>
         </is>
       </c>
-      <c r="C204" s="5" t="inlineStr">
+      <c r="C204" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D204" s="5" t="inlineStr">
+      <c r="D204" s="6" t="inlineStr">
         <is>
           <t>Six built-in design directions plus your own saved ones</t>
         </is>
       </c>
-      <c r="E204" s="6" t="inlineStr">
+      <c r="E204" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F204" s="5" t="inlineStr">
+      <c r="F204" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G204" s="5" t="inlineStr"/>
-      <c r="H204" s="5" t="inlineStr"/>
-      <c r="I204" s="5" t="inlineStr"/>
+      <c r="G204" s="6" t="inlineStr"/>
+      <c r="H204" s="6" t="inlineStr"/>
+      <c r="I204" s="6" t="inlineStr"/>
     </row>
     <row r="205" ht="18" customHeight="1">
-      <c r="A205" s="5" t="inlineStr">
+      <c r="A205" s="6" t="inlineStr">
         <is>
           <t>Design system</t>
         </is>
       </c>
-      <c r="B205" s="5" t="inlineStr">
+      <c r="B205" s="6" t="inlineStr">
         <is>
           <t>Design Lab (open with ?lab=1)</t>
         </is>
       </c>
-      <c r="C205" s="5" t="inlineStr">
+      <c r="C205" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D205" s="5" t="inlineStr">
+      <c r="D205" s="6" t="inlineStr">
         <is>
           <t>Six brand inspired directions (Aesop, Le Labo, Glossier, etc.)</t>
         </is>
       </c>
-      <c r="E205" s="6" t="inlineStr">
+      <c r="E205" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F205" s="5" t="inlineStr">
+      <c r="F205" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G205" s="5" t="inlineStr"/>
-      <c r="H205" s="5" t="inlineStr"/>
-      <c r="I205" s="5" t="inlineStr"/>
+      <c r="G205" s="6" t="inlineStr"/>
+      <c r="H205" s="6" t="inlineStr"/>
+      <c r="I205" s="6" t="inlineStr"/>
     </row>
     <row r="206" ht="18" customHeight="1">
-      <c r="A206" s="5" t="inlineStr">
+      <c r="A206" s="6" t="inlineStr">
         <is>
           <t>Design system</t>
         </is>
       </c>
-      <c r="B206" s="5" t="inlineStr">
+      <c r="B206" s="6" t="inlineStr">
         <is>
           <t>Design Lab (open with ?lab=1)</t>
         </is>
       </c>
-      <c r="C206" s="5" t="inlineStr">
+      <c r="C206" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D206" s="5" t="inlineStr">
+      <c r="D206" s="6" t="inlineStr">
         <is>
           <t>Seven built-in palettes plus your own hex picker</t>
         </is>
       </c>
-      <c r="E206" s="6" t="inlineStr">
+      <c r="E206" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F206" s="5" t="inlineStr">
+      <c r="F206" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G206" s="5" t="inlineStr"/>
-      <c r="H206" s="5" t="inlineStr"/>
-      <c r="I206" s="5" t="inlineStr"/>
+      <c r="G206" s="6" t="inlineStr"/>
+      <c r="H206" s="6" t="inlineStr"/>
+      <c r="I206" s="6" t="inlineStr"/>
     </row>
     <row r="207" ht="18" customHeight="1">
-      <c r="A207" s="5" t="inlineStr">
+      <c r="A207" s="6" t="inlineStr">
         <is>
           <t>Design system</t>
         </is>
       </c>
-      <c r="B207" s="5" t="inlineStr">
+      <c r="B207" s="6" t="inlineStr">
         <is>
           <t>Design Lab (open with ?lab=1)</t>
         </is>
       </c>
-      <c r="C207" s="5" t="inlineStr">
+      <c r="C207" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D207" s="5" t="inlineStr">
+      <c r="D207" s="6" t="inlineStr">
         <is>
           <t>Card corner style picker</t>
         </is>
       </c>
-      <c r="E207" s="6" t="inlineStr">
+      <c r="E207" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F207" s="5" t="inlineStr">
+      <c r="F207" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G207" s="5" t="inlineStr"/>
-      <c r="H207" s="5" t="inlineStr"/>
-      <c r="I207" s="5" t="inlineStr"/>
+      <c r="G207" s="6" t="inlineStr"/>
+      <c r="H207" s="6" t="inlineStr"/>
+      <c r="I207" s="6" t="inlineStr"/>
     </row>
     <row r="208" ht="18" customHeight="1">
-      <c r="A208" s="5" t="inlineStr">
+      <c r="A208" s="6" t="inlineStr">
         <is>
           <t>Design system</t>
         </is>
       </c>
-      <c r="B208" s="5" t="inlineStr">
+      <c r="B208" s="6" t="inlineStr">
         <is>
           <t>Design Lab (open with ?lab=1)</t>
         </is>
       </c>
-      <c r="C208" s="5" t="inlineStr">
+      <c r="C208" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D208" s="5" t="inlineStr">
+      <c r="D208" s="6" t="inlineStr">
         <is>
           <t>Modular palette: card surface, button background and text, borders, accents</t>
         </is>
       </c>
-      <c r="E208" s="6" t="inlineStr">
+      <c r="E208" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F208" s="5" t="inlineStr">
+      <c r="F208" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G208" s="5" t="inlineStr"/>
-      <c r="H208" s="5" t="inlineStr"/>
-      <c r="I208" s="5" t="inlineStr"/>
+      <c r="G208" s="6" t="inlineStr"/>
+      <c r="H208" s="6" t="inlineStr"/>
+      <c r="I208" s="6" t="inlineStr"/>
     </row>
     <row r="209" ht="18" customHeight="1">
-      <c r="A209" s="5" t="inlineStr">
+      <c r="A209" s="6" t="inlineStr">
         <is>
           <t>Design system</t>
         </is>
       </c>
-      <c r="B209" s="5" t="inlineStr">
+      <c r="B209" s="6" t="inlineStr">
         <is>
           <t>Design Lab (open with ?lab=1)</t>
         </is>
       </c>
-      <c r="C209" s="5" t="inlineStr">
+      <c r="C209" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D209" s="5" t="inlineStr">
+      <c r="D209" s="6" t="inlineStr">
         <is>
           <t>Each section can collapse or expand</t>
         </is>
       </c>
-      <c r="E209" s="6" t="inlineStr">
+      <c r="E209" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F209" s="5" t="inlineStr">
+      <c r="F209" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G209" s="5" t="inlineStr"/>
-      <c r="H209" s="5" t="inlineStr"/>
-      <c r="I209" s="5" t="inlineStr"/>
+      <c r="G209" s="6" t="inlineStr"/>
+      <c r="H209" s="6" t="inlineStr"/>
+      <c r="I209" s="6" t="inlineStr"/>
     </row>
     <row r="210" ht="18" customHeight="1">
-      <c r="A210" s="5" t="inlineStr">
+      <c r="A210" s="6" t="inlineStr">
         <is>
           <t>Design system</t>
         </is>
       </c>
-      <c r="B210" s="5" t="inlineStr">
+      <c r="B210" s="6" t="inlineStr">
         <is>
           <t>Design Lab (open with ?lab=1)</t>
         </is>
       </c>
-      <c r="C210" s="5" t="inlineStr">
+      <c r="C210" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D210" s="5" t="inlineStr">
+      <c r="D210" s="6" t="inlineStr">
         <is>
           <t>Sitemap tab inside the panel (still there for quick navigation)</t>
         </is>
       </c>
-      <c r="E210" s="6" t="inlineStr">
+      <c r="E210" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F210" s="5" t="inlineStr">
+      <c r="F210" s="6" t="inlineStr">
         <is>
           <t>P3 low</t>
         </is>
       </c>
-      <c r="G210" s="5" t="inlineStr"/>
-      <c r="H210" s="5" t="inlineStr"/>
-      <c r="I210" s="5" t="inlineStr"/>
+      <c r="G210" s="6" t="inlineStr"/>
+      <c r="H210" s="6" t="inlineStr"/>
+      <c r="I210" s="6" t="inlineStr"/>
     </row>
     <row r="211" ht="20" customHeight="1">
       <c r="A211" s="3" t="inlineStr">
@@ -7365,196 +7375,196 @@
           <t>Design tokens</t>
         </is>
       </c>
-      <c r="C211" s="4" t="inlineStr">
+      <c r="C211" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D211" s="4" t="inlineStr">
+      <c r="D211" s="5" t="inlineStr">
         <is>
           <t>The shared colour and font variables that the whole site reads from</t>
         </is>
       </c>
-      <c r="E211" s="4" t="inlineStr"/>
-      <c r="F211" s="4" t="inlineStr"/>
-      <c r="G211" s="4" t="inlineStr"/>
-      <c r="H211" s="4" t="inlineStr"/>
-      <c r="I211" s="4" t="inlineStr"/>
+      <c r="E211" s="5" t="inlineStr"/>
+      <c r="F211" s="5" t="inlineStr"/>
+      <c r="G211" s="5" t="inlineStr"/>
+      <c r="H211" s="5" t="inlineStr"/>
+      <c r="I211" s="5" t="inlineStr"/>
     </row>
     <row r="212" ht="18" customHeight="1">
-      <c r="A212" s="5" t="inlineStr">
+      <c r="A212" s="6" t="inlineStr">
         <is>
           <t>Design system</t>
         </is>
       </c>
-      <c r="B212" s="5" t="inlineStr">
+      <c r="B212" s="6" t="inlineStr">
         <is>
           <t>Design tokens</t>
         </is>
       </c>
-      <c r="C212" s="5" t="inlineStr">
+      <c r="C212" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D212" s="5" t="inlineStr">
+      <c r="D212" s="6" t="inlineStr">
         <is>
           <t>Font tokens applied across the site</t>
         </is>
       </c>
-      <c r="E212" s="6" t="inlineStr">
+      <c r="E212" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F212" s="5" t="inlineStr">
+      <c r="F212" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G212" s="5" t="inlineStr"/>
-      <c r="H212" s="5" t="inlineStr"/>
-      <c r="I212" s="5" t="inlineStr"/>
+      <c r="G212" s="6" t="inlineStr"/>
+      <c r="H212" s="6" t="inlineStr"/>
+      <c r="I212" s="6" t="inlineStr"/>
     </row>
     <row r="213" ht="18" customHeight="1">
-      <c r="A213" s="5" t="inlineStr">
+      <c r="A213" s="6" t="inlineStr">
         <is>
           <t>Design system</t>
         </is>
       </c>
-      <c r="B213" s="5" t="inlineStr">
+      <c r="B213" s="6" t="inlineStr">
         <is>
           <t>Design tokens</t>
         </is>
       </c>
-      <c r="C213" s="5" t="inlineStr">
+      <c r="C213" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D213" s="5" t="inlineStr">
+      <c r="D213" s="6" t="inlineStr">
         <is>
           <t>Palette tokens (background, card, ink, button, line, accents)</t>
         </is>
       </c>
-      <c r="E213" s="6" t="inlineStr">
+      <c r="E213" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F213" s="5" t="inlineStr">
+      <c r="F213" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G213" s="5" t="inlineStr"/>
-      <c r="H213" s="5" t="inlineStr"/>
-      <c r="I213" s="5" t="inlineStr"/>
+      <c r="G213" s="6" t="inlineStr"/>
+      <c r="H213" s="6" t="inlineStr"/>
+      <c r="I213" s="6" t="inlineStr"/>
     </row>
     <row r="214" ht="18" customHeight="1">
-      <c r="A214" s="5" t="inlineStr">
+      <c r="A214" s="6" t="inlineStr">
         <is>
           <t>Design system</t>
         </is>
       </c>
-      <c r="B214" s="5" t="inlineStr">
+      <c r="B214" s="6" t="inlineStr">
         <is>
           <t>Design tokens</t>
         </is>
       </c>
-      <c r="C214" s="5" t="inlineStr">
+      <c r="C214" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D214" s="5" t="inlineStr">
+      <c r="D214" s="6" t="inlineStr">
         <is>
           <t>Card radius token</t>
         </is>
       </c>
-      <c r="E214" s="6" t="inlineStr">
+      <c r="E214" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F214" s="5" t="inlineStr">
+      <c r="F214" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G214" s="5" t="inlineStr"/>
-      <c r="H214" s="5" t="inlineStr"/>
-      <c r="I214" s="5" t="inlineStr"/>
+      <c r="G214" s="6" t="inlineStr"/>
+      <c r="H214" s="6" t="inlineStr"/>
+      <c r="I214" s="6" t="inlineStr"/>
     </row>
     <row r="215" ht="18" customHeight="1">
-      <c r="A215" s="5" t="inlineStr">
+      <c r="A215" s="6" t="inlineStr">
         <is>
           <t>Design system</t>
         </is>
       </c>
-      <c r="B215" s="5" t="inlineStr">
+      <c r="B215" s="6" t="inlineStr">
         <is>
           <t>Design tokens</t>
         </is>
       </c>
-      <c r="C215" s="5" t="inlineStr">
+      <c r="C215" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D215" s="5" t="inlineStr">
+      <c r="D215" s="6" t="inlineStr">
         <is>
           <t>Refactor all old hardcoded fonts to use the tokens</t>
         </is>
       </c>
-      <c r="E215" s="6" t="inlineStr">
+      <c r="E215" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F215" s="5" t="inlineStr">
+      <c r="F215" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G215" s="5" t="inlineStr"/>
-      <c r="H215" s="5" t="inlineStr"/>
-      <c r="I215" s="5" t="inlineStr"/>
+      <c r="G215" s="6" t="inlineStr"/>
+      <c r="H215" s="6" t="inlineStr"/>
+      <c r="I215" s="6" t="inlineStr"/>
     </row>
     <row r="216" ht="18" customHeight="1">
-      <c r="A216" s="5" t="inlineStr">
+      <c r="A216" s="6" t="inlineStr">
         <is>
           <t>Design system</t>
         </is>
       </c>
-      <c r="B216" s="5" t="inlineStr">
+      <c r="B216" s="6" t="inlineStr">
         <is>
           <t>Design tokens</t>
         </is>
       </c>
-      <c r="C216" s="5" t="inlineStr">
+      <c r="C216" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D216" s="5" t="inlineStr">
+      <c r="D216" s="6" t="inlineStr">
         <is>
           <t>Refactor inner pages (quiz, account) to use the same card token</t>
         </is>
       </c>
-      <c r="E216" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F216" s="5" t="inlineStr">
+      <c r="E216" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F216" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G216" s="5" t="inlineStr"/>
-      <c r="H216" s="5" t="inlineStr"/>
-      <c r="I216" s="5" t="inlineStr"/>
+      <c r="G216" s="6" t="inlineStr"/>
+      <c r="H216" s="6" t="inlineStr"/>
+      <c r="I216" s="6" t="inlineStr"/>
     </row>
     <row r="217" ht="22" customHeight="1">
       <c r="A217" s="2" t="inlineStr">
@@ -7574,161 +7584,161 @@
           <t>Brand identity</t>
         </is>
       </c>
-      <c r="C218" s="4" t="inlineStr">
+      <c r="C218" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D218" s="4" t="inlineStr">
+      <c r="D218" s="5" t="inlineStr">
         <is>
           <t>Logo, favicon, brand voice</t>
         </is>
       </c>
-      <c r="E218" s="4" t="inlineStr"/>
-      <c r="F218" s="4" t="inlineStr"/>
-      <c r="G218" s="4" t="inlineStr"/>
-      <c r="H218" s="4" t="inlineStr"/>
-      <c r="I218" s="4" t="inlineStr"/>
+      <c r="E218" s="5" t="inlineStr"/>
+      <c r="F218" s="5" t="inlineStr"/>
+      <c r="G218" s="5" t="inlineStr"/>
+      <c r="H218" s="5" t="inlineStr"/>
+      <c r="I218" s="5" t="inlineStr"/>
     </row>
     <row r="219" ht="18" customHeight="1">
-      <c r="A219" s="5" t="inlineStr">
+      <c r="A219" s="6" t="inlineStr">
         <is>
           <t>Other things to do</t>
         </is>
       </c>
-      <c r="B219" s="5" t="inlineStr">
+      <c r="B219" s="6" t="inlineStr">
         <is>
           <t>Brand identity</t>
         </is>
       </c>
-      <c r="C219" s="5" t="inlineStr">
+      <c r="C219" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D219" s="5" t="inlineStr">
+      <c r="D219" s="6" t="inlineStr">
         <is>
           <t>Final logo design (currently using the rusalka illustration)</t>
         </is>
       </c>
-      <c r="E219" s="8" t="inlineStr">
+      <c r="E219" s="9" t="inlineStr">
         <is>
           <t>In progress</t>
         </is>
       </c>
-      <c r="F219" s="5" t="inlineStr">
+      <c r="F219" s="6" t="inlineStr">
         <is>
           <t>P0 critical</t>
         </is>
       </c>
-      <c r="G219" s="5" t="inlineStr"/>
-      <c r="H219" s="5" t="inlineStr"/>
-      <c r="I219" s="5" t="inlineStr"/>
+      <c r="G219" s="6" t="inlineStr"/>
+      <c r="H219" s="6" t="inlineStr"/>
+      <c r="I219" s="6" t="inlineStr"/>
     </row>
     <row r="220" ht="18" customHeight="1">
-      <c r="A220" s="5" t="inlineStr">
+      <c r="A220" s="6" t="inlineStr">
         <is>
           <t>Other things to do</t>
         </is>
       </c>
-      <c r="B220" s="5" t="inlineStr">
+      <c r="B220" s="6" t="inlineStr">
         <is>
           <t>Brand identity</t>
         </is>
       </c>
-      <c r="C220" s="5" t="inlineStr">
+      <c r="C220" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D220" s="5" t="inlineStr">
+      <c r="D220" s="6" t="inlineStr">
         <is>
           <t>Favicon that matches the brand</t>
         </is>
       </c>
-      <c r="E220" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F220" s="5" t="inlineStr">
+      <c r="E220" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F220" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G220" s="5" t="inlineStr"/>
-      <c r="H220" s="5" t="inlineStr"/>
-      <c r="I220" s="5" t="inlineStr"/>
+      <c r="G220" s="6" t="inlineStr"/>
+      <c r="H220" s="6" t="inlineStr"/>
+      <c r="I220" s="6" t="inlineStr"/>
     </row>
     <row r="221" ht="18" customHeight="1">
-      <c r="A221" s="5" t="inlineStr">
+      <c r="A221" s="6" t="inlineStr">
         <is>
           <t>Other things to do</t>
         </is>
       </c>
-      <c r="B221" s="5" t="inlineStr">
+      <c r="B221" s="6" t="inlineStr">
         <is>
           <t>Brand identity</t>
         </is>
       </c>
-      <c r="C221" s="5" t="inlineStr">
+      <c r="C221" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D221" s="5" t="inlineStr">
+      <c r="D221" s="6" t="inlineStr">
         <is>
           <t>Preview image used when sharing on social media</t>
         </is>
       </c>
-      <c r="E221" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F221" s="5" t="inlineStr">
+      <c r="E221" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F221" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G221" s="5" t="inlineStr"/>
-      <c r="H221" s="5" t="inlineStr"/>
-      <c r="I221" s="5" t="inlineStr"/>
+      <c r="G221" s="6" t="inlineStr"/>
+      <c r="H221" s="6" t="inlineStr"/>
+      <c r="I221" s="6" t="inlineStr"/>
     </row>
     <row r="222" ht="18" customHeight="1">
-      <c r="A222" s="5" t="inlineStr">
+      <c r="A222" s="6" t="inlineStr">
         <is>
           <t>Other things to do</t>
         </is>
       </c>
-      <c r="B222" s="5" t="inlineStr">
+      <c r="B222" s="6" t="inlineStr">
         <is>
           <t>Brand identity</t>
         </is>
       </c>
-      <c r="C222" s="5" t="inlineStr">
+      <c r="C222" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D222" s="5" t="inlineStr">
+      <c r="D222" s="6" t="inlineStr">
         <is>
           <t>Written guide for brand voice and tone</t>
         </is>
       </c>
-      <c r="E222" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F222" s="5" t="inlineStr">
+      <c r="E222" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F222" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G222" s="5" t="inlineStr"/>
-      <c r="H222" s="5" t="inlineStr"/>
-      <c r="I222" s="5" t="inlineStr"/>
+      <c r="G222" s="6" t="inlineStr"/>
+      <c r="H222" s="6" t="inlineStr"/>
+      <c r="I222" s="6" t="inlineStr"/>
     </row>
     <row r="223" ht="20" customHeight="1">
       <c r="A223" s="3" t="inlineStr">
@@ -7741,161 +7751,161 @@
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="C223" s="4" t="inlineStr">
+      <c r="C223" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D223" s="4" t="inlineStr">
+      <c r="D223" s="5" t="inlineStr">
         <is>
           <t>Making the site usable by people with disabilities</t>
         </is>
       </c>
-      <c r="E223" s="4" t="inlineStr"/>
-      <c r="F223" s="4" t="inlineStr"/>
-      <c r="G223" s="4" t="inlineStr"/>
-      <c r="H223" s="4" t="inlineStr"/>
-      <c r="I223" s="4" t="inlineStr"/>
+      <c r="E223" s="5" t="inlineStr"/>
+      <c r="F223" s="5" t="inlineStr"/>
+      <c r="G223" s="5" t="inlineStr"/>
+      <c r="H223" s="5" t="inlineStr"/>
+      <c r="I223" s="5" t="inlineStr"/>
     </row>
     <row r="224" ht="18" customHeight="1">
-      <c r="A224" s="5" t="inlineStr">
+      <c r="A224" s="6" t="inlineStr">
         <is>
           <t>Other things to do</t>
         </is>
       </c>
-      <c r="B224" s="5" t="inlineStr">
+      <c r="B224" s="6" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="C224" s="5" t="inlineStr">
+      <c r="C224" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D224" s="5" t="inlineStr">
+      <c r="D224" s="6" t="inlineStr">
         <is>
           <t>Check colour contrast on every palette</t>
         </is>
       </c>
-      <c r="E224" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F224" s="5" t="inlineStr">
+      <c r="E224" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F224" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G224" s="5" t="inlineStr"/>
-      <c r="H224" s="5" t="inlineStr"/>
-      <c r="I224" s="5" t="inlineStr"/>
+      <c r="G224" s="6" t="inlineStr"/>
+      <c r="H224" s="6" t="inlineStr"/>
+      <c r="I224" s="6" t="inlineStr"/>
     </row>
     <row r="225" ht="18" customHeight="1">
-      <c r="A225" s="5" t="inlineStr">
+      <c r="A225" s="6" t="inlineStr">
         <is>
           <t>Other things to do</t>
         </is>
       </c>
-      <c r="B225" s="5" t="inlineStr">
+      <c r="B225" s="6" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="C225" s="5" t="inlineStr">
+      <c r="C225" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D225" s="5" t="inlineStr">
+      <c r="D225" s="6" t="inlineStr">
         <is>
           <t>Make the quiz fully navigable with the keyboard</t>
         </is>
       </c>
-      <c r="E225" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F225" s="5" t="inlineStr">
+      <c r="E225" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F225" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G225" s="5" t="inlineStr"/>
-      <c r="H225" s="5" t="inlineStr"/>
-      <c r="I225" s="5" t="inlineStr"/>
+      <c r="G225" s="6" t="inlineStr"/>
+      <c r="H225" s="6" t="inlineStr"/>
+      <c r="I225" s="6" t="inlineStr"/>
     </row>
     <row r="226" ht="18" customHeight="1">
-      <c r="A226" s="5" t="inlineStr">
+      <c r="A226" s="6" t="inlineStr">
         <is>
           <t>Other things to do</t>
         </is>
       </c>
-      <c r="B226" s="5" t="inlineStr">
+      <c r="B226" s="6" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="C226" s="5" t="inlineStr">
+      <c r="C226" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D226" s="5" t="inlineStr">
+      <c r="D226" s="6" t="inlineStr">
         <is>
           <t>Make the results page work for screen readers</t>
         </is>
       </c>
-      <c r="E226" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F226" s="5" t="inlineStr">
+      <c r="E226" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F226" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G226" s="5" t="inlineStr"/>
-      <c r="H226" s="5" t="inlineStr"/>
-      <c r="I226" s="5" t="inlineStr"/>
+      <c r="G226" s="6" t="inlineStr"/>
+      <c r="H226" s="6" t="inlineStr"/>
+      <c r="I226" s="6" t="inlineStr"/>
     </row>
     <row r="227" ht="18" customHeight="1">
-      <c r="A227" s="5" t="inlineStr">
+      <c r="A227" s="6" t="inlineStr">
         <is>
           <t>Other things to do</t>
         </is>
       </c>
-      <c r="B227" s="5" t="inlineStr">
+      <c r="B227" s="6" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="C227" s="5" t="inlineStr">
+      <c r="C227" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D227" s="5" t="inlineStr">
+      <c r="D227" s="6" t="inlineStr">
         <is>
           <t>Make sure every clickable thing shows a focus ring</t>
         </is>
       </c>
-      <c r="E227" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F227" s="5" t="inlineStr">
+      <c r="E227" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F227" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G227" s="5" t="inlineStr"/>
-      <c r="H227" s="5" t="inlineStr"/>
-      <c r="I227" s="5" t="inlineStr"/>
+      <c r="G227" s="6" t="inlineStr"/>
+      <c r="H227" s="6" t="inlineStr"/>
+      <c r="I227" s="6" t="inlineStr"/>
     </row>
     <row r="228" ht="20" customHeight="1">
       <c r="A228" s="3" t="inlineStr">
@@ -7908,196 +7918,196 @@
           <t>Speed and performance</t>
         </is>
       </c>
-      <c r="C228" s="4" t="inlineStr">
+      <c r="C228" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D228" s="4" t="inlineStr">
+      <c r="D228" s="5" t="inlineStr">
         <is>
           <t>Making the site fast to load</t>
         </is>
       </c>
-      <c r="E228" s="4" t="inlineStr"/>
-      <c r="F228" s="4" t="inlineStr"/>
-      <c r="G228" s="4" t="inlineStr"/>
-      <c r="H228" s="4" t="inlineStr"/>
-      <c r="I228" s="4" t="inlineStr"/>
+      <c r="E228" s="5" t="inlineStr"/>
+      <c r="F228" s="5" t="inlineStr"/>
+      <c r="G228" s="5" t="inlineStr"/>
+      <c r="H228" s="5" t="inlineStr"/>
+      <c r="I228" s="5" t="inlineStr"/>
     </row>
     <row r="229" ht="18" customHeight="1">
-      <c r="A229" s="5" t="inlineStr">
+      <c r="A229" s="6" t="inlineStr">
         <is>
           <t>Other things to do</t>
         </is>
       </c>
-      <c r="B229" s="5" t="inlineStr">
+      <c r="B229" s="6" t="inlineStr">
         <is>
           <t>Speed and performance</t>
         </is>
       </c>
-      <c r="C229" s="5" t="inlineStr">
+      <c r="C229" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D229" s="5" t="inlineStr">
+      <c r="D229" s="6" t="inlineStr">
         <is>
           <t>Hero video set up to load quickly</t>
         </is>
       </c>
-      <c r="E229" s="6" t="inlineStr">
+      <c r="E229" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F229" s="5" t="inlineStr">
+      <c r="F229" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G229" s="5" t="inlineStr"/>
-      <c r="H229" s="5" t="inlineStr"/>
-      <c r="I229" s="5" t="inlineStr"/>
+      <c r="G229" s="6" t="inlineStr"/>
+      <c r="H229" s="6" t="inlineStr"/>
+      <c r="I229" s="6" t="inlineStr"/>
     </row>
     <row r="230" ht="18" customHeight="1">
-      <c r="A230" s="5" t="inlineStr">
+      <c r="A230" s="6" t="inlineStr">
         <is>
           <t>Other things to do</t>
         </is>
       </c>
-      <c r="B230" s="5" t="inlineStr">
+      <c r="B230" s="6" t="inlineStr">
         <is>
           <t>Speed and performance</t>
         </is>
       </c>
-      <c r="C230" s="5" t="inlineStr">
+      <c r="C230" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D230" s="5" t="inlineStr">
+      <c r="D230" s="6" t="inlineStr">
         <is>
           <t>Re-encode hero video to a smaller modern format</t>
         </is>
       </c>
-      <c r="E230" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F230" s="5" t="inlineStr">
+      <c r="E230" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F230" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G230" s="5" t="inlineStr"/>
-      <c r="H230" s="5" t="inlineStr"/>
-      <c r="I230" s="5" t="inlineStr"/>
+      <c r="G230" s="6" t="inlineStr"/>
+      <c r="H230" s="6" t="inlineStr"/>
+      <c r="I230" s="6" t="inlineStr"/>
     </row>
     <row r="231" ht="18" customHeight="1">
-      <c r="A231" s="5" t="inlineStr">
+      <c r="A231" s="6" t="inlineStr">
         <is>
           <t>Other things to do</t>
         </is>
       </c>
-      <c r="B231" s="5" t="inlineStr">
+      <c r="B231" s="6" t="inlineStr">
         <is>
           <t>Speed and performance</t>
         </is>
       </c>
-      <c r="C231" s="5" t="inlineStr">
+      <c r="C231" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D231" s="5" t="inlineStr">
+      <c r="D231" s="6" t="inlineStr">
         <is>
           <t>Use Next.js optimised image component for product photos</t>
         </is>
       </c>
-      <c r="E231" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F231" s="5" t="inlineStr">
+      <c r="E231" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F231" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G231" s="5" t="inlineStr"/>
-      <c r="H231" s="5" t="inlineStr"/>
-      <c r="I231" s="5" t="inlineStr"/>
+      <c r="G231" s="6" t="inlineStr"/>
+      <c r="H231" s="6" t="inlineStr"/>
+      <c r="I231" s="6" t="inlineStr"/>
     </row>
     <row r="232" ht="18" customHeight="1">
-      <c r="A232" s="5" t="inlineStr">
+      <c r="A232" s="6" t="inlineStr">
         <is>
           <t>Other things to do</t>
         </is>
       </c>
-      <c r="B232" s="5" t="inlineStr">
+      <c r="B232" s="6" t="inlineStr">
         <is>
           <t>Speed and performance</t>
         </is>
       </c>
-      <c r="C232" s="5" t="inlineStr">
+      <c r="C232" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D232" s="5" t="inlineStr">
+      <c r="D232" s="6" t="inlineStr">
         <is>
           <t>Load only the font weights we actually use</t>
         </is>
       </c>
-      <c r="E232" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F232" s="5" t="inlineStr">
+      <c r="E232" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F232" s="6" t="inlineStr">
         <is>
           <t>P2 medium</t>
         </is>
       </c>
-      <c r="G232" s="5" t="inlineStr"/>
-      <c r="H232" s="5" t="inlineStr"/>
-      <c r="I232" s="5" t="inlineStr"/>
+      <c r="G232" s="6" t="inlineStr"/>
+      <c r="H232" s="6" t="inlineStr"/>
+      <c r="I232" s="6" t="inlineStr"/>
     </row>
     <row r="233" ht="18" customHeight="1">
-      <c r="A233" s="5" t="inlineStr">
+      <c r="A233" s="6" t="inlineStr">
         <is>
           <t>Other things to do</t>
         </is>
       </c>
-      <c r="B233" s="5" t="inlineStr">
+      <c r="B233" s="6" t="inlineStr">
         <is>
           <t>Speed and performance</t>
         </is>
       </c>
-      <c r="C233" s="5" t="inlineStr">
+      <c r="C233" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D233" s="5" t="inlineStr">
+      <c r="D233" s="6" t="inlineStr">
         <is>
           <t>Run a Google speed test and fix the worst issues</t>
         </is>
       </c>
-      <c r="E233" s="9" t="inlineStr">
-        <is>
-          <t>Todo</t>
-        </is>
-      </c>
-      <c r="F233" s="5" t="inlineStr">
+      <c r="E233" s="10" t="inlineStr">
+        <is>
+          <t>Todo</t>
+        </is>
+      </c>
+      <c r="F233" s="6" t="inlineStr">
         <is>
           <t>P1 high</t>
         </is>
       </c>
-      <c r="G233" s="5" t="inlineStr"/>
-      <c r="H233" s="5" t="inlineStr"/>
-      <c r="I233" s="5" t="inlineStr"/>
+      <c r="G233" s="6" t="inlineStr"/>
+      <c r="H233" s="6" t="inlineStr"/>
+      <c r="I233" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -8137,6 +8147,49 @@
       <formula1>"P0 critical,P1 high,P2 medium,P3 low"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C82" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C85" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C117" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C124" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C131" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C140" r:id="rId41"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>